--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,12 +45,6 @@
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -471,7 +465,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Kalkulation7" displayName="Kalkulation7" ref="A1:Q778" headerRowCount="1" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q778"/>
+  <autoFilter ref="A1:Q778">
+    <filterColumn colId="0" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="MAP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:N738">
     <sortCondition ref="A1:A3"/>
   </sortState>
@@ -881,7 +881,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" hidden="1" ht="30" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -956,7 +956,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" hidden="1" ht="45" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="135" customHeight="1">
+    <row r="4" hidden="1" ht="135" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" hidden="1" ht="45" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1">
+    <row r="6" hidden="1" ht="120" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" hidden="1" ht="90" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" hidden="1" ht="30" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" hidden="1" ht="30" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" hidden="1" ht="75" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" hidden="1" ht="60" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
+    <row r="12" hidden="1" ht="120" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" hidden="1" ht="60" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" hidden="1" ht="45" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" hidden="1" ht="30" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="105" customHeight="1">
+    <row r="16" hidden="1" ht="105" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" hidden="1" ht="60" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="75" customHeight="1">
+    <row r="18" hidden="1" ht="75" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" hidden="1" ht="60" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20" hidden="1" ht="90" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="105" customHeight="1">
+    <row r="21" hidden="1" ht="105" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" hidden="1" ht="60" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="75" customHeight="1">
+    <row r="23" hidden="1" ht="75" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" hidden="1" ht="60" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="90" customHeight="1">
+    <row r="25" hidden="1" ht="90" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="75" customHeight="1">
+    <row r="26" hidden="1" ht="75" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="90" customHeight="1">
+    <row r="27" hidden="1" ht="90" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="90" customHeight="1">
+    <row r="28" hidden="1" ht="90" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="120" customHeight="1">
+    <row r="29" hidden="1" ht="120" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="120" customHeight="1">
+    <row r="30" hidden="1" ht="120" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="90" customHeight="1">
+    <row r="31" hidden="1" ht="90" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="105" customHeight="1">
+    <row r="32" hidden="1" ht="105" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="90" customHeight="1">
+    <row r="33" hidden="1" ht="90" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="90" customHeight="1">
+    <row r="34" hidden="1" ht="90" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" hidden="1" ht="60" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="90" customHeight="1">
+    <row r="36" hidden="1" ht="90" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="105" customHeight="1">
+    <row r="37" hidden="1" ht="105" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="75" customHeight="1">
+    <row r="38" hidden="1" ht="75" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="75" customHeight="1">
+    <row r="39" hidden="1" ht="75" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" hidden="1" ht="60" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" hidden="1" ht="60" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" hidden="1" ht="45" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" hidden="1" ht="60" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" hidden="1" ht="60" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
+    <row r="45" hidden="1" ht="45" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="75" customHeight="1">
+    <row r="46" hidden="1" ht="75" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="75" customHeight="1">
+    <row r="47" hidden="1" ht="75" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="90" customHeight="1">
+    <row r="48" hidden="1" ht="90" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="45" customHeight="1">
+    <row r="49" hidden="1" ht="45" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="75" customHeight="1">
+    <row r="50" hidden="1" ht="75" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="75" customHeight="1">
+    <row r="51" hidden="1" ht="75" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52" hidden="1" ht="60" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53" hidden="1" ht="60" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54" hidden="1" ht="60" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="90" customHeight="1">
+    <row r="55" hidden="1" ht="90" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="90" customHeight="1">
+    <row r="56" hidden="1" ht="90" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="90" customHeight="1">
+    <row r="57" hidden="1" ht="90" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="75" customHeight="1">
+    <row r="58" hidden="1" ht="75" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="75" customHeight="1">
+    <row r="59" hidden="1" ht="75" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="90" customHeight="1">
+    <row r="60" hidden="1" ht="90" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
+    <row r="61" hidden="1" ht="60" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="90" customHeight="1">
+    <row r="62" hidden="1" ht="90" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="75" customHeight="1">
+    <row r="63" hidden="1" ht="75" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" hidden="1" ht="60" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" hidden="1" ht="60" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="75" customHeight="1">
+    <row r="66" hidden="1" ht="75" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="105" customHeight="1">
+    <row r="67" hidden="1" ht="105" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="75" customHeight="1">
+    <row r="68" hidden="1" ht="75" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="90" customHeight="1">
+    <row r="69" hidden="1" ht="90" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="90" customHeight="1">
+    <row r="70" hidden="1" ht="90" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71" hidden="1" ht="60" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="75" customHeight="1">
+    <row r="72" hidden="1" ht="75" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
+    <row r="73" hidden="1" ht="60" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="120" customHeight="1">
+    <row r="74" hidden="1" ht="120" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
+    <row r="75" hidden="1" ht="60" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="45" customHeight="1">
+    <row r="76" hidden="1" ht="45" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="45" customHeight="1">
+    <row r="77" hidden="1" ht="45" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="75" customHeight="1">
+    <row r="78" hidden="1" ht="75" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" hidden="1" ht="30" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="105" customHeight="1">
+    <row r="80" hidden="1" ht="105" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="150" customHeight="1">
+    <row r="81" hidden="1" ht="150" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="135" customHeight="1">
+    <row r="82" hidden="1" ht="135" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="120" customHeight="1">
+    <row r="83" hidden="1" ht="120" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="120" customHeight="1">
+    <row r="84" hidden="1" ht="120" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="180" customHeight="1">
+    <row r="85" hidden="1" ht="180" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="75" customHeight="1">
+    <row r="86" hidden="1" ht="75" customHeight="1">
       <c r="A86" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="87" hidden="1" ht="30" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7467,7 +7467,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" hidden="1" ht="30" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" hidden="1" ht="30" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" hidden="1" ht="30" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="165" customHeight="1">
+    <row r="91" hidden="1" ht="165" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1">
+    <row r="92" hidden="1" ht="30" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="165" customHeight="1">
+    <row r="93" hidden="1" ht="165" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
+    <row r="94" hidden="1" ht="60" customHeight="1">
       <c r="A94" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="30" customHeight="1">
+    <row r="95" hidden="1" ht="30" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="210" customHeight="1">
+    <row r="96" hidden="1" ht="210" customHeight="1">
       <c r="A96" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1">
+    <row r="97" hidden="1" ht="30" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8233,7 +8233,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1">
+    <row r="98" hidden="1" ht="30" customHeight="1">
       <c r="A98" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="120" customHeight="1">
+    <row r="99" hidden="1" ht="120" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="120" customHeight="1">
+    <row r="100" hidden="1" ht="120" customHeight="1">
       <c r="A100" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="120" customHeight="1">
+    <row r="101" hidden="1" ht="120" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="120" customHeight="1">
+    <row r="102" hidden="1" ht="120" customHeight="1">
       <c r="A102" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="90" customHeight="1">
+    <row r="103" hidden="1" ht="90" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="45" customHeight="1">
+    <row r="104" hidden="1" ht="45" customHeight="1">
       <c r="A104" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8771,7 +8771,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
+    <row r="105" hidden="1" ht="60" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
+    <row r="106" hidden="1" ht="60" customHeight="1">
       <c r="A106" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
+    <row r="107" hidden="1" ht="60" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
           <t>TTW</t>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="105" customHeight="1">
+    <row r="108" hidden="1" ht="105" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="120" customHeight="1">
+    <row r="109" hidden="1" ht="120" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="105" customHeight="1">
+    <row r="110" hidden="1" ht="105" customHeight="1">
       <c r="A110" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="135" customHeight="1">
+    <row r="111" hidden="1" ht="135" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="165" customHeight="1">
+    <row r="112" hidden="1" ht="165" customHeight="1">
       <c r="A112" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="105" customHeight="1">
+    <row r="113" hidden="1" ht="105" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="120" customHeight="1">
+    <row r="114" hidden="1" ht="120" customHeight="1">
       <c r="A114" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="45" customHeight="1">
+    <row r="115" hidden="1" ht="45" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="45" customHeight="1">
+    <row r="116" hidden="1" ht="45" customHeight="1">
       <c r="A116" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="90" customHeight="1">
+    <row r="117" hidden="1" ht="90" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="30" customHeight="1">
+    <row r="118" hidden="1" ht="30" customHeight="1">
       <c r="A118" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="135" customHeight="1">
+    <row r="119" hidden="1" ht="135" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="75" customHeight="1">
+    <row r="120" hidden="1" ht="75" customHeight="1">
       <c r="A120" s="29" t="inlineStr">
         <is>
           <t>TTS</t>
@@ -9974,7 +9974,7 @@
       <c r="S120" s="4" t="n"/>
       <c r="T120" s="4" t="n"/>
     </row>
-    <row r="121" ht="195" customHeight="1">
+    <row r="121" hidden="1" ht="195" customHeight="1">
       <c r="A121" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="300" customHeight="1">
+    <row r="122" hidden="1" ht="300" customHeight="1">
       <c r="A122" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="90" customHeight="1">
+    <row r="123" hidden="1" ht="90" customHeight="1">
       <c r="A123" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="165" customHeight="1">
+    <row r="124" hidden="1" ht="165" customHeight="1">
       <c r="A124" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="409.5" customHeight="1">
+    <row r="125" hidden="1" ht="409.5" customHeight="1">
       <c r="A125" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10474,7 +10474,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="90" customHeight="1">
+    <row r="126" hidden="1" ht="90" customHeight="1">
       <c r="A126" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="90" customHeight="1">
+    <row r="127" hidden="1" ht="90" customHeight="1">
       <c r="A127" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="90" customHeight="1">
+    <row r="128" hidden="1" ht="90" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -10714,7 +10714,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="180" customHeight="1">
+    <row r="129" hidden="1" ht="180" customHeight="1">
       <c r="A129" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="90" customHeight="1">
+    <row r="130" hidden="1" ht="90" customHeight="1">
       <c r="A130" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="105" customHeight="1">
+    <row r="131" hidden="1" ht="105" customHeight="1">
       <c r="A131" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="90" customHeight="1">
+    <row r="132" hidden="1" ht="90" customHeight="1">
       <c r="A132" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11044,7 +11044,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="120" customHeight="1">
+    <row r="133" hidden="1" ht="120" customHeight="1">
       <c r="A133" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="285" customHeight="1">
+    <row r="134" hidden="1" ht="285" customHeight="1">
       <c r="A134" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11235,7 +11235,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="255" customHeight="1">
+    <row r="135" hidden="1" ht="255" customHeight="1">
       <c r="A135" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="30" customHeight="1">
+    <row r="136" hidden="1" ht="30" customHeight="1">
       <c r="A136" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11400,7 +11400,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="75" customHeight="1">
+    <row r="137" hidden="1" ht="75" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="75" customHeight="1">
+    <row r="138" hidden="1" ht="75" customHeight="1">
       <c r="A138" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="409.5" customHeight="1">
+    <row r="139" hidden="1" ht="409.5" customHeight="1">
       <c r="A139" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11701,7 +11701,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="195" customHeight="1">
+    <row r="140" hidden="1" ht="195" customHeight="1">
       <c r="A140" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="105" customHeight="1">
+    <row r="141" hidden="1" ht="105" customHeight="1">
       <c r="A141" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="330" customHeight="1">
+    <row r="142" hidden="1" ht="330" customHeight="1">
       <c r="A142" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="135" customHeight="1">
+    <row r="143" hidden="1" ht="135" customHeight="1">
       <c r="A143" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="105" customHeight="1">
+    <row r="144" hidden="1" ht="105" customHeight="1">
       <c r="A144" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12134,7 +12134,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="105" customHeight="1">
+    <row r="145" hidden="1" ht="105" customHeight="1">
       <c r="A145" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="135" customHeight="1">
+    <row r="146" hidden="1" ht="135" customHeight="1">
       <c r="A146" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12297,7 +12297,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="120" customHeight="1">
+    <row r="147" hidden="1" ht="120" customHeight="1">
       <c r="A147" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12380,7 +12380,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="120" customHeight="1">
+    <row r="148" hidden="1" ht="120" customHeight="1">
       <c r="A148" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="180" customHeight="1">
+    <row r="149" hidden="1" ht="180" customHeight="1">
       <c r="A149" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="105" customHeight="1">
+    <row r="150" hidden="1" ht="105" customHeight="1">
       <c r="A150" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="225" customHeight="1">
+    <row r="151" hidden="1" ht="225" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12726,7 +12726,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="195" customHeight="1">
+    <row r="152" hidden="1" ht="195" customHeight="1">
       <c r="A152" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="30" customHeight="1">
+    <row r="153" hidden="1" ht="30" customHeight="1">
       <c r="A153" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="30" customHeight="1">
+    <row r="154" hidden="1" ht="30" customHeight="1">
       <c r="A154" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="225" customHeight="1">
+    <row r="155" hidden="1" ht="225" customHeight="1">
       <c r="A155" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13064,7 +13064,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="225" customHeight="1">
+    <row r="156" hidden="1" ht="225" customHeight="1">
       <c r="A156" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="105" customHeight="1">
+    <row r="157" hidden="1" ht="105" customHeight="1">
       <c r="A157" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="1" ht="90" customHeight="1">
       <c r="A158" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="120" customHeight="1">
+    <row r="159" hidden="1" ht="120" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="120" customHeight="1">
+    <row r="160" hidden="1" ht="120" customHeight="1">
       <c r="A160" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="195" customHeight="1">
+    <row r="161" hidden="1" ht="195" customHeight="1">
       <c r="A161" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13551,7 +13551,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="105" customHeight="1">
+    <row r="162" hidden="1" ht="105" customHeight="1">
       <c r="A162" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="240" customHeight="1">
+    <row r="163" hidden="1" ht="240" customHeight="1">
       <c r="A163" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13730,7 +13730,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="120" customHeight="1">
+    <row r="164" hidden="1" ht="120" customHeight="1">
       <c r="A164" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="120" customHeight="1">
+    <row r="165" hidden="1" ht="120" customHeight="1">
       <c r="A165" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -13896,7 +13896,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="30" customHeight="1">
+    <row r="166" hidden="1" ht="30" customHeight="1">
       <c r="A166" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="30" customHeight="1">
+    <row r="167" hidden="1" ht="30" customHeight="1">
       <c r="A167" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="75" customHeight="1">
+    <row r="168" hidden="1" ht="75" customHeight="1">
       <c r="A168" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="75" customHeight="1">
+    <row r="169" hidden="1" ht="75" customHeight="1">
       <c r="A169" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="75" customHeight="1">
+    <row r="170" hidden="1" ht="75" customHeight="1">
       <c r="A170" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="75" customHeight="1">
+    <row r="171" hidden="1" ht="75" customHeight="1">
       <c r="A171" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14361,7 +14361,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="105" customHeight="1">
+    <row r="172" hidden="1" ht="105" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14445,7 +14445,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="90" customHeight="1">
+    <row r="173" hidden="1" ht="90" customHeight="1">
       <c r="A173" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="105" customHeight="1">
+    <row r="174" hidden="1" ht="105" customHeight="1">
       <c r="A174" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -14608,7 +14608,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
+    <row r="175" hidden="1" ht="60" customHeight="1">
       <c r="A175" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="105" customHeight="1">
+    <row r="176" hidden="1" ht="105" customHeight="1">
       <c r="A176" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="120" customHeight="1">
+    <row r="177" hidden="1" ht="120" customHeight="1">
       <c r="A177" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="30" customHeight="1">
+    <row r="178" hidden="1" ht="30" customHeight="1">
       <c r="A178" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="135" customHeight="1">
+    <row r="179" hidden="1" ht="135" customHeight="1">
       <c r="A179" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="135" customHeight="1">
+    <row r="180" hidden="1" ht="135" customHeight="1">
       <c r="A180" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="90" customHeight="1">
+    <row r="181" hidden="1" ht="90" customHeight="1">
       <c r="A181" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15151,7 +15151,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="135" customHeight="1">
+    <row r="182" hidden="1" ht="135" customHeight="1">
       <c r="A182" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15230,7 +15230,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="135" customHeight="1">
+    <row r="183" hidden="1" ht="135" customHeight="1">
       <c r="A183" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15309,7 +15309,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="135" customHeight="1">
+    <row r="184" hidden="1" ht="135" customHeight="1">
       <c r="A184" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="135" customHeight="1">
+    <row r="185" hidden="1" ht="135" customHeight="1">
       <c r="A185" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15471,7 +15471,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="135" customHeight="1">
+    <row r="186" hidden="1" ht="135" customHeight="1">
       <c r="A186" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15551,7 +15551,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="135" customHeight="1">
+    <row r="187" hidden="1" ht="135" customHeight="1">
       <c r="A187" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="135" customHeight="1">
+    <row r="188" hidden="1" ht="135" customHeight="1">
       <c r="A188" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15711,7 +15711,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="135" customHeight="1">
+    <row r="189" hidden="1" ht="135" customHeight="1">
       <c r="A189" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15791,7 +15791,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="135" customHeight="1">
+    <row r="190" hidden="1" ht="135" customHeight="1">
       <c r="A190" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="135" customHeight="1">
+    <row r="191" hidden="1" ht="135" customHeight="1">
       <c r="A191" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="135" customHeight="1">
+    <row r="192" hidden="1" ht="135" customHeight="1">
       <c r="A192" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16024,7 +16024,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="135" customHeight="1">
+    <row r="193" hidden="1" ht="135" customHeight="1">
       <c r="A193" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="135" customHeight="1">
+    <row r="194" hidden="1" ht="135" customHeight="1">
       <c r="A194" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16176,7 +16176,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="45" customHeight="1">
+    <row r="195" hidden="1" ht="45" customHeight="1">
       <c r="A195" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="45" customHeight="1">
+    <row r="196" hidden="1" ht="45" customHeight="1">
       <c r="A196" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16297,7 +16297,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="30" customHeight="1">
+    <row r="197" hidden="1" ht="30" customHeight="1">
       <c r="A197" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="30" customHeight="1">
+    <row r="198" hidden="1" ht="30" customHeight="1">
       <c r="A198" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16417,7 +16417,7 @@
         </is>
       </c>
     </row>
-    <row r="199">
+    <row r="199" hidden="1" ht="90" customHeight="1">
       <c r="A199" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
     </row>
-    <row r="200">
+    <row r="200" hidden="1" ht="90" customHeight="1">
       <c r="A200" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16535,7 +16535,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
+    <row r="201" hidden="1" ht="90" customHeight="1">
       <c r="A201" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16594,7 +16594,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="1" ht="90" customHeight="1">
       <c r="A202" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="1" ht="90" customHeight="1">
       <c r="A203" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="1" ht="90" customHeight="1">
       <c r="A204" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16771,7 +16771,7 @@
         </is>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="1" ht="90" customHeight="1">
       <c r="A205" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16830,7 +16830,7 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="135" customHeight="1">
+    <row r="206" hidden="1" ht="135" customHeight="1">
       <c r="A206" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16908,7 +16908,7 @@
         </is>
       </c>
     </row>
-    <row r="207" ht="135" customHeight="1">
+    <row r="207" hidden="1" ht="135" customHeight="1">
       <c r="A207" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -16986,7 +16986,7 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="135" customHeight="1">
+    <row r="208" hidden="1" ht="135" customHeight="1">
       <c r="A208" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17064,7 +17064,7 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="135" customHeight="1">
+    <row r="209" hidden="1" ht="135" customHeight="1">
       <c r="A209" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="135" customHeight="1">
+    <row r="210" hidden="1" ht="135" customHeight="1">
       <c r="A210" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17220,7 +17220,7 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="135" customHeight="1">
+    <row r="211" hidden="1" ht="135" customHeight="1">
       <c r="A211" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17303,7 +17303,7 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="135" customHeight="1">
+    <row r="212" hidden="1" ht="135" customHeight="1">
       <c r="A212" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17383,7 +17383,7 @@
         </is>
       </c>
     </row>
-    <row r="213">
+    <row r="213" hidden="1" ht="75" customHeight="1">
       <c r="A213" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="30" customHeight="1">
+    <row r="214" hidden="1" ht="30" customHeight="1">
       <c r="A214" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17502,7 +17502,7 @@
         </is>
       </c>
     </row>
-    <row r="215">
+    <row r="215" hidden="1" ht="90" customHeight="1">
       <c r="A215" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="240" customHeight="1">
+    <row r="216" hidden="1" ht="240" customHeight="1">
       <c r="A216" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="240" customHeight="1">
+    <row r="217" hidden="1" ht="240" customHeight="1">
       <c r="A217" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17755,7 +17755,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="240" customHeight="1">
+    <row r="218" hidden="1" ht="240" customHeight="1">
       <c r="A218" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17852,7 +17852,7 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="30" customHeight="1">
+    <row r="219" hidden="1" ht="30" customHeight="1">
       <c r="A219" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="30" customHeight="1">
+    <row r="220" hidden="1" ht="30" customHeight="1">
       <c r="A220" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
     </row>
-    <row r="221" ht="30" customHeight="1">
+    <row r="221" hidden="1" ht="30" customHeight="1">
       <c r="A221" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18045,7 +18045,7 @@
         </is>
       </c>
     </row>
-    <row r="222">
+    <row r="222" hidden="1" ht="90" customHeight="1">
       <c r="A222" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18104,7 +18104,7 @@
         </is>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="1" ht="90" customHeight="1">
       <c r="A223" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18163,7 +18163,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="1" ht="90" customHeight="1">
       <c r="A224" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18222,7 +18222,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="1" ht="90" customHeight="1">
       <c r="A225" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" hidden="1" ht="90" customHeight="1">
       <c r="A226" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18340,7 +18340,7 @@
         </is>
       </c>
     </row>
-    <row r="227">
+    <row r="227" hidden="1" ht="90" customHeight="1">
       <c r="A227" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18399,7 +18399,7 @@
         </is>
       </c>
     </row>
-    <row r="228">
+    <row r="228" hidden="1" ht="90" customHeight="1">
       <c r="A228" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18458,7 +18458,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" hidden="1" ht="90" customHeight="1">
       <c r="A229" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18517,7 +18517,7 @@
         </is>
       </c>
     </row>
-    <row r="230" ht="30" customHeight="1">
+    <row r="230" hidden="1" ht="30" customHeight="1">
       <c r="A230" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18577,7 +18577,7 @@
         </is>
       </c>
     </row>
-    <row r="231">
+    <row r="231" hidden="1" ht="90" customHeight="1">
       <c r="A231" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18636,7 +18636,7 @@
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" hidden="1" ht="90" customHeight="1">
       <c r="A232" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18695,7 +18695,7 @@
         </is>
       </c>
     </row>
-    <row r="233" ht="30" customHeight="1">
+    <row r="233" hidden="1" ht="30" customHeight="1">
       <c r="A233" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18755,7 +18755,7 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="45" customHeight="1">
+    <row r="234" hidden="1" ht="45" customHeight="1">
       <c r="A234" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" hidden="1" ht="90" customHeight="1">
       <c r="A235" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18874,7 +18874,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" hidden="1" ht="90" customHeight="1">
       <c r="A236" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18933,7 +18933,7 @@
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="1" ht="90" customHeight="1">
       <c r="A237" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -18992,7 +18992,7 @@
         </is>
       </c>
     </row>
-    <row r="238" ht="30" customHeight="1">
+    <row r="238" hidden="1" ht="30" customHeight="1">
       <c r="A238" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19052,7 +19052,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="30" customHeight="1">
+    <row r="239" hidden="1" ht="30" customHeight="1">
       <c r="A239" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19112,7 +19112,7 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="60" customHeight="1">
+    <row r="240" hidden="1" ht="60" customHeight="1">
       <c r="A240" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19173,7 +19173,7 @@
         </is>
       </c>
     </row>
-    <row r="241" ht="135" customHeight="1">
+    <row r="241" hidden="1" ht="135" customHeight="1">
       <c r="A241" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19257,7 +19257,7 @@
         </is>
       </c>
     </row>
-    <row r="242" ht="135" customHeight="1">
+    <row r="242" hidden="1" ht="135" customHeight="1">
       <c r="A242" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19341,7 +19341,7 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="135" customHeight="1">
+    <row r="243" hidden="1" ht="135" customHeight="1">
       <c r="A243" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="135" customHeight="1">
+    <row r="244" hidden="1" ht="135" customHeight="1">
       <c r="A244" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
     </row>
-    <row r="245" ht="30" customHeight="1">
+    <row r="245" hidden="1" ht="30" customHeight="1">
       <c r="A245" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19569,7 +19569,7 @@
         </is>
       </c>
     </row>
-    <row r="246" ht="135" customHeight="1">
+    <row r="246" hidden="1" ht="135" customHeight="1">
       <c r="A246" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19647,7 +19647,7 @@
         </is>
       </c>
     </row>
-    <row r="247" ht="135" customHeight="1">
+    <row r="247" hidden="1" ht="135" customHeight="1">
       <c r="A247" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19725,7 +19725,7 @@
         </is>
       </c>
     </row>
-    <row r="248" ht="135" customHeight="1">
+    <row r="248" hidden="1" ht="135" customHeight="1">
       <c r="A248" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19803,7 +19803,7 @@
         </is>
       </c>
     </row>
-    <row r="249" ht="135" customHeight="1">
+    <row r="249" hidden="1" ht="135" customHeight="1">
       <c r="A249" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
     </row>
-    <row r="250" ht="135" customHeight="1">
+    <row r="250" hidden="1" ht="135" customHeight="1">
       <c r="A250" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -19959,7 +19959,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="135" customHeight="1">
+    <row r="251" hidden="1" ht="135" customHeight="1">
       <c r="A251" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20037,7 +20037,7 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="135" customHeight="1">
+    <row r="252" hidden="1" ht="135" customHeight="1">
       <c r="A252" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="75" customHeight="1">
+    <row r="253" hidden="1" ht="75" customHeight="1">
       <c r="A253" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20189,7 +20189,7 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="135" customHeight="1">
+    <row r="254" hidden="1" ht="135" customHeight="1">
       <c r="A254" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20267,7 +20267,7 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="135" customHeight="1">
+    <row r="255" hidden="1" ht="135" customHeight="1">
       <c r="A255" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20345,7 +20345,7 @@
         </is>
       </c>
     </row>
-    <row r="256" ht="135" customHeight="1">
+    <row r="256" hidden="1" ht="135" customHeight="1">
       <c r="A256" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20423,7 +20423,7 @@
         </is>
       </c>
     </row>
-    <row r="257" ht="135" customHeight="1">
+    <row r="257" hidden="1" ht="135" customHeight="1">
       <c r="A257" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20502,7 +20502,7 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="135" customHeight="1">
+    <row r="258" hidden="1" ht="135" customHeight="1">
       <c r="A258" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="135" customHeight="1">
+    <row r="259" hidden="1" ht="135" customHeight="1">
       <c r="A259" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="135" customHeight="1">
+    <row r="260" hidden="1" ht="135" customHeight="1">
       <c r="A260" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="105" customHeight="1">
+    <row r="261" hidden="1" ht="105" customHeight="1">
       <c r="A261" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20812,7 +20812,7 @@
         </is>
       </c>
     </row>
-    <row r="262" ht="135" customHeight="1">
+    <row r="262" hidden="1" ht="135" customHeight="1">
       <c r="A262" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20890,7 +20890,7 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="135" customHeight="1">
+    <row r="263" hidden="1" ht="135" customHeight="1">
       <c r="A263" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
     </row>
-    <row r="264" ht="135" customHeight="1">
+    <row r="264" hidden="1" ht="135" customHeight="1">
       <c r="A264" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21046,7 +21046,7 @@
         </is>
       </c>
     </row>
-    <row r="265" ht="135" customHeight="1">
+    <row r="265" hidden="1" ht="135" customHeight="1">
       <c r="A265" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
     </row>
-    <row r="266" ht="135" customHeight="1">
+    <row r="266" hidden="1" ht="135" customHeight="1">
       <c r="A266" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
     </row>
-    <row r="267" ht="135" customHeight="1">
+    <row r="267" hidden="1" ht="135" customHeight="1">
       <c r="A267" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21280,7 +21280,7 @@
         </is>
       </c>
     </row>
-    <row r="268" ht="135" customHeight="1">
+    <row r="268" hidden="1" ht="135" customHeight="1">
       <c r="A268" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21358,7 +21358,7 @@
         </is>
       </c>
     </row>
-    <row r="269" ht="135" customHeight="1">
+    <row r="269" hidden="1" ht="135" customHeight="1">
       <c r="A269" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
     </row>
-    <row r="270" ht="135" customHeight="1">
+    <row r="270" hidden="1" ht="135" customHeight="1">
       <c r="A270" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21514,7 +21514,7 @@
         </is>
       </c>
     </row>
-    <row r="271" ht="135" customHeight="1">
+    <row r="271" hidden="1" ht="135" customHeight="1">
       <c r="A271" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21592,7 +21592,7 @@
         </is>
       </c>
     </row>
-    <row r="272" ht="135" customHeight="1">
+    <row r="272" hidden="1" ht="135" customHeight="1">
       <c r="A272" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21670,7 +21670,7 @@
         </is>
       </c>
     </row>
-    <row r="273" ht="135" customHeight="1">
+    <row r="273" hidden="1" ht="135" customHeight="1">
       <c r="A273" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21748,7 +21748,7 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="135" customHeight="1">
+    <row r="274" hidden="1" ht="135" customHeight="1">
       <c r="A274" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
     </row>
-    <row r="275" ht="135" customHeight="1">
+    <row r="275" hidden="1" ht="135" customHeight="1">
       <c r="A275" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21906,7 +21906,7 @@
         </is>
       </c>
     </row>
-    <row r="276" ht="135" customHeight="1">
+    <row r="276" hidden="1" ht="135" customHeight="1">
       <c r="A276" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
     </row>
-    <row r="277" ht="135" customHeight="1">
+    <row r="277" hidden="1" ht="135" customHeight="1">
       <c r="A277" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22062,7 +22062,7 @@
         </is>
       </c>
     </row>
-    <row r="278" ht="30" customHeight="1">
+    <row r="278" hidden="1" ht="30" customHeight="1">
       <c r="A278" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22131,7 +22131,7 @@
         </is>
       </c>
     </row>
-    <row r="279" ht="135" customHeight="1">
+    <row r="279" hidden="1" ht="135" customHeight="1">
       <c r="A279" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22209,7 +22209,7 @@
         </is>
       </c>
     </row>
-    <row r="280" ht="135" customHeight="1">
+    <row r="280" hidden="1" ht="135" customHeight="1">
       <c r="A280" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22287,7 +22287,7 @@
         </is>
       </c>
     </row>
-    <row r="281" ht="135" customHeight="1">
+    <row r="281" hidden="1" ht="135" customHeight="1">
       <c r="A281" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
     </row>
-    <row r="282" ht="135" customHeight="1">
+    <row r="282" hidden="1" ht="135" customHeight="1">
       <c r="A282" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22443,7 +22443,7 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="135" customHeight="1">
+    <row r="283" hidden="1" ht="135" customHeight="1">
       <c r="A283" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22521,7 +22521,7 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="135" customHeight="1">
+    <row r="284" hidden="1" ht="135" customHeight="1">
       <c r="A284" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22599,7 +22599,7 @@
         </is>
       </c>
     </row>
-    <row r="285" ht="135" customHeight="1">
+    <row r="285" hidden="1" ht="135" customHeight="1">
       <c r="A285" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22677,7 +22677,7 @@
         </is>
       </c>
     </row>
-    <row r="286" ht="75" customHeight="1">
+    <row r="286" hidden="1" ht="75" customHeight="1">
       <c r="A286" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22753,7 +22753,7 @@
         </is>
       </c>
     </row>
-    <row r="287" ht="135" customHeight="1">
+    <row r="287" hidden="1" ht="135" customHeight="1">
       <c r="A287" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22831,7 +22831,7 @@
         </is>
       </c>
     </row>
-    <row r="288" ht="135" customHeight="1">
+    <row r="288" hidden="1" ht="135" customHeight="1">
       <c r="A288" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22909,7 +22909,7 @@
         </is>
       </c>
     </row>
-    <row r="289" ht="135" customHeight="1">
+    <row r="289" hidden="1" ht="135" customHeight="1">
       <c r="A289" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -22987,7 +22987,7 @@
         </is>
       </c>
     </row>
-    <row r="290" ht="135" customHeight="1">
+    <row r="290" hidden="1" ht="135" customHeight="1">
       <c r="A290" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23065,7 +23065,7 @@
         </is>
       </c>
     </row>
-    <row r="291" ht="135" customHeight="1">
+    <row r="291" hidden="1" ht="135" customHeight="1">
       <c r="A291" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23143,7 +23143,7 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="135" customHeight="1">
+    <row r="292" hidden="1" ht="135" customHeight="1">
       <c r="A292" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23221,7 +23221,7 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="135" customHeight="1">
+    <row r="293" hidden="1" ht="135" customHeight="1">
       <c r="A293" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23299,7 +23299,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="105" customHeight="1">
+    <row r="294" hidden="1" ht="105" customHeight="1">
       <c r="A294" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
     </row>
-    <row r="295" ht="135" customHeight="1">
+    <row r="295" hidden="1" ht="135" customHeight="1">
       <c r="A295" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23454,7 +23454,7 @@
         </is>
       </c>
     </row>
-    <row r="296" ht="135" customHeight="1">
+    <row r="296" hidden="1" ht="135" customHeight="1">
       <c r="A296" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="135" customHeight="1">
+    <row r="297" hidden="1" ht="135" customHeight="1">
       <c r="A297" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23610,7 +23610,7 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="135" customHeight="1">
+    <row r="298" hidden="1" ht="135" customHeight="1">
       <c r="A298" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="135" customHeight="1">
+    <row r="299" hidden="1" ht="135" customHeight="1">
       <c r="A299" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23767,7 +23767,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="135" customHeight="1">
+    <row r="300" hidden="1" ht="135" customHeight="1">
       <c r="A300" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23846,7 +23846,7 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="135" customHeight="1">
+    <row r="301" hidden="1" ht="135" customHeight="1">
       <c r="A301" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -23924,7 +23924,7 @@
         </is>
       </c>
     </row>
-    <row r="302" ht="135" customHeight="1">
+    <row r="302" hidden="1" ht="135" customHeight="1">
       <c r="A302" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24002,7 +24002,7 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="135" customHeight="1">
+    <row r="303" hidden="1" ht="135" customHeight="1">
       <c r="A303" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24080,7 +24080,7 @@
         </is>
       </c>
     </row>
-    <row r="304" ht="135" customHeight="1">
+    <row r="304" hidden="1" ht="135" customHeight="1">
       <c r="A304" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="135" customHeight="1">
+    <row r="305" hidden="1" ht="135" customHeight="1">
       <c r="A305" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
     </row>
-    <row r="306" ht="135" customHeight="1">
+    <row r="306" hidden="1" ht="135" customHeight="1">
       <c r="A306" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24314,7 +24314,7 @@
         </is>
       </c>
     </row>
-    <row r="307" ht="135" customHeight="1">
+    <row r="307" hidden="1" ht="135" customHeight="1">
       <c r="A307" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
     </row>
-    <row r="308">
+    <row r="308" hidden="1" ht="90" customHeight="1">
       <c r="A308" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24451,7 +24451,7 @@
         </is>
       </c>
     </row>
-    <row r="309" ht="135" customHeight="1">
+    <row r="309" hidden="1" ht="135" customHeight="1">
       <c r="A309" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
     </row>
-    <row r="310" ht="105" customHeight="1">
+    <row r="310" hidden="1" ht="105" customHeight="1">
       <c r="A310" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24619,7 +24619,7 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="60" customHeight="1">
+    <row r="311" hidden="1" ht="60" customHeight="1">
       <c r="A311" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24697,7 +24697,7 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="60" customHeight="1">
+    <row r="312" hidden="1" ht="60" customHeight="1">
       <c r="A312" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24775,7 +24775,7 @@
         </is>
       </c>
     </row>
-    <row r="313" ht="30" customHeight="1">
+    <row r="313" hidden="1" ht="30" customHeight="1">
       <c r="A313" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24849,7 +24849,7 @@
         </is>
       </c>
     </row>
-    <row r="314" ht="45" customHeight="1">
+    <row r="314" hidden="1" ht="45" customHeight="1">
       <c r="A314" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -24926,7 +24926,7 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="75" customHeight="1">
+    <row r="315" hidden="1" ht="75" customHeight="1">
       <c r="A315" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25006,7 +25006,7 @@
         </is>
       </c>
     </row>
-    <row r="316" ht="75" customHeight="1">
+    <row r="316" hidden="1" ht="75" customHeight="1">
       <c r="A316" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25086,7 +25086,7 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="120" customHeight="1">
+    <row r="317" hidden="1" ht="120" customHeight="1">
       <c r="A317" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -25171,7 +25171,7 @@
         </is>
       </c>
     </row>
-    <row r="318" ht="60" customHeight="1">
+    <row r="318" hidden="1" ht="60" customHeight="1">
       <c r="A318" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25249,7 +25249,7 @@
         </is>
       </c>
     </row>
-    <row r="319" ht="90" customHeight="1">
+    <row r="319" hidden="1" ht="90" customHeight="1">
       <c r="A319" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25330,7 +25330,7 @@
         </is>
       </c>
     </row>
-    <row r="320" ht="45" customHeight="1">
+    <row r="320" hidden="1" ht="45" customHeight="1">
       <c r="A320" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25407,7 +25407,7 @@
         </is>
       </c>
     </row>
-    <row r="321" ht="75" customHeight="1">
+    <row r="321" hidden="1" ht="75" customHeight="1">
       <c r="A321" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25486,7 +25486,7 @@
         </is>
       </c>
     </row>
-    <row r="322" ht="75" customHeight="1">
+    <row r="322" hidden="1" ht="75" customHeight="1">
       <c r="A322" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25566,7 +25566,7 @@
         </is>
       </c>
     </row>
-    <row r="323" ht="165" customHeight="1">
+    <row r="323" hidden="1" ht="165" customHeight="1">
       <c r="A323" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25659,7 +25659,7 @@
         </is>
       </c>
     </row>
-    <row r="324" ht="165" customHeight="1">
+    <row r="324" hidden="1" ht="165" customHeight="1">
       <c r="A324" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
     </row>
-    <row r="325" ht="90" customHeight="1">
+    <row r="325" hidden="1" ht="90" customHeight="1">
       <c r="A325" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -25833,7 +25833,7 @@
         </is>
       </c>
     </row>
-    <row r="326" ht="30" customHeight="1">
+    <row r="326" hidden="1" ht="30" customHeight="1">
       <c r="A326" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -25892,7 +25892,7 @@
         </is>
       </c>
     </row>
-    <row r="327" ht="90" customHeight="1">
+    <row r="327" hidden="1" ht="90" customHeight="1">
       <c r="A327" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
     </row>
-    <row r="328" ht="165" customHeight="1">
+    <row r="328" hidden="1" ht="165" customHeight="1">
       <c r="A328" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
     </row>
-    <row r="329" ht="90" customHeight="1">
+    <row r="329" hidden="1" ht="90" customHeight="1">
       <c r="A329" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26145,7 +26145,7 @@
         </is>
       </c>
     </row>
-    <row r="330" ht="90" customHeight="1">
+    <row r="330" hidden="1" ht="90" customHeight="1">
       <c r="A330" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26227,7 +26227,7 @@
         </is>
       </c>
     </row>
-    <row r="331" ht="90" customHeight="1">
+    <row r="331" hidden="1" ht="90" customHeight="1">
       <c r="A331" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
     </row>
-    <row r="332" ht="120" customHeight="1">
+    <row r="332" hidden="1" ht="120" customHeight="1">
       <c r="A332" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26392,7 +26392,7 @@
         </is>
       </c>
     </row>
-    <row r="333" ht="90" customHeight="1">
+    <row r="333" hidden="1" ht="90" customHeight="1">
       <c r="A333" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26472,7 +26472,7 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="90" customHeight="1">
+    <row r="334" hidden="1" ht="90" customHeight="1">
       <c r="A334" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26552,7 +26552,7 @@
         </is>
       </c>
     </row>
-    <row r="335" ht="90" customHeight="1">
+    <row r="335" hidden="1" ht="90" customHeight="1">
       <c r="A335" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26635,7 +26635,7 @@
         </is>
       </c>
     </row>
-    <row r="336" ht="135" customHeight="1">
+    <row r="336" hidden="1" ht="135" customHeight="1">
       <c r="A336" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26719,7 +26719,7 @@
         </is>
       </c>
     </row>
-    <row r="337" ht="60" customHeight="1">
+    <row r="337" hidden="1" ht="60" customHeight="1">
       <c r="A337" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26796,7 +26796,7 @@
         </is>
       </c>
     </row>
-    <row r="338" ht="105" customHeight="1">
+    <row r="338" hidden="1" ht="105" customHeight="1">
       <c r="A338" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26874,7 +26874,7 @@
         </is>
       </c>
     </row>
-    <row r="339" ht="75" customHeight="1">
+    <row r="339" hidden="1" ht="75" customHeight="1">
       <c r="A339" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -26950,7 +26950,7 @@
         </is>
       </c>
     </row>
-    <row r="340" ht="105" customHeight="1">
+    <row r="340" hidden="1" ht="105" customHeight="1">
       <c r="A340" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27027,7 +27027,7 @@
         </is>
       </c>
     </row>
-    <row r="341" ht="120" customHeight="1">
+    <row r="341" hidden="1" ht="120" customHeight="1">
       <c r="A341" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27105,7 +27105,7 @@
         </is>
       </c>
     </row>
-    <row r="342" ht="75" customHeight="1">
+    <row r="342" hidden="1" ht="75" customHeight="1">
       <c r="A342" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27180,7 +27180,7 @@
         </is>
       </c>
     </row>
-    <row r="343" ht="240" customHeight="1">
+    <row r="343" hidden="1" ht="240" customHeight="1">
       <c r="A343" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27269,7 +27269,7 @@
         </is>
       </c>
     </row>
-    <row r="344" ht="60" customHeight="1">
+    <row r="344" hidden="1" ht="60" customHeight="1">
       <c r="A344" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
     </row>
-    <row r="345" ht="135" customHeight="1">
+    <row r="345" hidden="1" ht="135" customHeight="1">
       <c r="A345" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27426,7 +27426,7 @@
         </is>
       </c>
     </row>
-    <row r="346" ht="135" customHeight="1">
+    <row r="346" hidden="1" ht="135" customHeight="1">
       <c r="A346" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27510,7 +27510,7 @@
         </is>
       </c>
     </row>
-    <row r="347" ht="105" customHeight="1">
+    <row r="347" hidden="1" ht="105" customHeight="1">
       <c r="A347" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27590,7 +27590,7 @@
         </is>
       </c>
     </row>
-    <row r="348" ht="75" customHeight="1">
+    <row r="348" hidden="1" ht="75" customHeight="1">
       <c r="A348" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
     </row>
-    <row r="349" ht="45" customHeight="1">
+    <row r="349" hidden="1" ht="45" customHeight="1">
       <c r="A349" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27736,7 +27736,7 @@
         </is>
       </c>
     </row>
-    <row r="350" ht="90" customHeight="1">
+    <row r="350" hidden="1" ht="90" customHeight="1">
       <c r="A350" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27814,7 +27814,7 @@
         </is>
       </c>
     </row>
-    <row r="351" ht="60" customHeight="1">
+    <row r="351" hidden="1" ht="60" customHeight="1">
       <c r="A351" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27887,7 +27887,7 @@
         </is>
       </c>
     </row>
-    <row r="352" ht="75" customHeight="1">
+    <row r="352" hidden="1" ht="75" customHeight="1">
       <c r="A352" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
     </row>
-    <row r="353" ht="90" customHeight="1">
+    <row r="353" hidden="1" ht="90" customHeight="1">
       <c r="A353" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28033,7 +28033,7 @@
         </is>
       </c>
     </row>
-    <row r="354" ht="45" customHeight="1">
+    <row r="354" hidden="1" ht="45" customHeight="1">
       <c r="A354" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28105,7 +28105,7 @@
         </is>
       </c>
     </row>
-    <row r="355" ht="105" customHeight="1">
+    <row r="355" hidden="1" ht="105" customHeight="1">
       <c r="A355" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28181,7 +28181,7 @@
         </is>
       </c>
     </row>
-    <row r="356" ht="30" customHeight="1">
+    <row r="356" hidden="1" ht="30" customHeight="1">
       <c r="A356" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28251,7 +28251,7 @@
         </is>
       </c>
     </row>
-    <row r="357" ht="75" customHeight="1">
+    <row r="357" hidden="1" ht="75" customHeight="1">
       <c r="A357" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28326,7 +28326,7 @@
         </is>
       </c>
     </row>
-    <row r="358" ht="105" customHeight="1">
+    <row r="358" hidden="1" ht="105" customHeight="1">
       <c r="A358" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28403,7 +28403,7 @@
         </is>
       </c>
     </row>
-    <row r="359" ht="75" customHeight="1">
+    <row r="359" hidden="1" ht="75" customHeight="1">
       <c r="A359" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28479,7 +28479,7 @@
         </is>
       </c>
     </row>
-    <row r="360" ht="30" customHeight="1">
+    <row r="360" hidden="1" ht="30" customHeight="1">
       <c r="A360" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28551,7 +28551,7 @@
         </is>
       </c>
     </row>
-    <row r="361" ht="165" customHeight="1">
+    <row r="361" hidden="1" ht="165" customHeight="1">
       <c r="A361" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28637,7 +28637,7 @@
         </is>
       </c>
     </row>
-    <row r="362" ht="105" customHeight="1">
+    <row r="362" hidden="1" ht="105" customHeight="1">
       <c r="A362" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28723,7 +28723,7 @@
         </is>
       </c>
     </row>
-    <row r="363" ht="225" customHeight="1">
+    <row r="363" hidden="1" ht="225" customHeight="1">
       <c r="A363" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28809,7 +28809,7 @@
         </is>
       </c>
     </row>
-    <row r="364" ht="225" customHeight="1">
+    <row r="364" hidden="1" ht="225" customHeight="1">
       <c r="A364" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
     </row>
-    <row r="365" ht="90" customHeight="1">
+    <row r="365" hidden="1" ht="90" customHeight="1">
       <c r="A365" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -28976,7 +28976,7 @@
         </is>
       </c>
     </row>
-    <row r="366" ht="120" customHeight="1">
+    <row r="366" hidden="1" ht="120" customHeight="1">
       <c r="A366" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29058,7 +29058,7 @@
         </is>
       </c>
     </row>
-    <row r="367" ht="75" customHeight="1">
+    <row r="367" hidden="1" ht="75" customHeight="1">
       <c r="A367" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
     </row>
-    <row r="368" ht="90" customHeight="1">
+    <row r="368" hidden="1" ht="90" customHeight="1">
       <c r="A368" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29215,7 +29215,7 @@
         </is>
       </c>
     </row>
-    <row r="369" ht="45" customHeight="1">
+    <row r="369" hidden="1" ht="45" customHeight="1">
       <c r="A369" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29287,7 +29287,7 @@
         </is>
       </c>
     </row>
-    <row r="370" ht="60" customHeight="1">
+    <row r="370" hidden="1" ht="60" customHeight="1">
       <c r="A370" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29361,7 +29361,7 @@
         </is>
       </c>
     </row>
-    <row r="371" ht="90" customHeight="1">
+    <row r="371" hidden="1" ht="90" customHeight="1">
       <c r="A371" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29439,7 +29439,7 @@
         </is>
       </c>
     </row>
-    <row r="372" ht="105" customHeight="1">
+    <row r="372" hidden="1" ht="105" customHeight="1">
       <c r="A372" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29516,7 +29516,7 @@
         </is>
       </c>
     </row>
-    <row r="373" ht="75" customHeight="1">
+    <row r="373" hidden="1" ht="75" customHeight="1">
       <c r="A373" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29592,7 +29592,7 @@
         </is>
       </c>
     </row>
-    <row r="374" ht="75" customHeight="1">
+    <row r="374" hidden="1" ht="75" customHeight="1">
       <c r="A374" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29671,7 +29671,7 @@
         </is>
       </c>
     </row>
-    <row r="375" ht="60" customHeight="1">
+    <row r="375" hidden="1" ht="60" customHeight="1">
       <c r="A375" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -29747,7 +29747,7 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="90" customHeight="1">
+    <row r="376" hidden="1" ht="90" customHeight="1">
       <c r="A376" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
     </row>
-    <row r="377" ht="105" customHeight="1">
+    <row r="377" hidden="1" ht="105" customHeight="1">
       <c r="A377" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29910,7 +29910,7 @@
         </is>
       </c>
     </row>
-    <row r="378" ht="60" customHeight="1">
+    <row r="378" hidden="1" ht="60" customHeight="1">
       <c r="A378" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -29985,7 +29985,7 @@
         </is>
       </c>
     </row>
-    <row r="379" ht="165" customHeight="1">
+    <row r="379" hidden="1" ht="165" customHeight="1">
       <c r="A379" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -30070,7 +30070,7 @@
         </is>
       </c>
     </row>
-    <row r="380" ht="150" customHeight="1">
+    <row r="380" hidden="1" ht="150" customHeight="1">
       <c r="A380" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -30164,7 +30164,7 @@
         </is>
       </c>
     </row>
-    <row r="381" ht="105" customHeight="1">
+    <row r="381" hidden="1" ht="105" customHeight="1">
       <c r="A381" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30248,7 +30248,7 @@
         </is>
       </c>
     </row>
-    <row r="382" ht="135" customHeight="1">
+    <row r="382" hidden="1" ht="135" customHeight="1">
       <c r="A382" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -30333,7 +30333,7 @@
         </is>
       </c>
     </row>
-    <row r="383" ht="135" customHeight="1">
+    <row r="383" hidden="1" ht="135" customHeight="1">
       <c r="A383" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30407,7 +30407,7 @@
         </is>
       </c>
     </row>
-    <row r="384" ht="30" customHeight="1">
+    <row r="384" hidden="1" ht="30" customHeight="1">
       <c r="A384" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
     </row>
-    <row r="385" ht="30" customHeight="1">
+    <row r="385" hidden="1" ht="30" customHeight="1">
       <c r="A385" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -30551,7 +30551,7 @@
         </is>
       </c>
     </row>
-    <row r="386" ht="90" customHeight="1">
+    <row r="386" hidden="1" ht="90" customHeight="1">
       <c r="A386" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30622,7 +30622,7 @@
         </is>
       </c>
     </row>
-    <row r="387" ht="90" customHeight="1">
+    <row r="387" hidden="1" ht="90" customHeight="1">
       <c r="A387" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30699,7 +30699,7 @@
         </is>
       </c>
     </row>
-    <row r="388" ht="120" customHeight="1">
+    <row r="388" hidden="1" ht="120" customHeight="1">
       <c r="A388" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30781,7 +30781,7 @@
         </is>
       </c>
     </row>
-    <row r="389" ht="135" customHeight="1">
+    <row r="389" hidden="1" ht="135" customHeight="1">
       <c r="A389" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30862,7 +30862,7 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="75" customHeight="1">
+    <row r="390" hidden="1" ht="75" customHeight="1">
       <c r="A390" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -30939,7 +30939,7 @@
         </is>
       </c>
     </row>
-    <row r="391" ht="105" customHeight="1">
+    <row r="391" hidden="1" ht="105" customHeight="1">
       <c r="A391" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31016,7 +31016,7 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="105" customHeight="1">
+    <row r="392" hidden="1" ht="105" customHeight="1">
       <c r="A392" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31093,7 +31093,7 @@
         </is>
       </c>
     </row>
-    <row r="393" ht="105" customHeight="1">
+    <row r="393" hidden="1" ht="105" customHeight="1">
       <c r="A393" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31170,7 +31170,7 @@
         </is>
       </c>
     </row>
-    <row r="394" ht="90" customHeight="1">
+    <row r="394" hidden="1" ht="90" customHeight="1">
       <c r="A394" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31251,7 +31251,7 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="90" customHeight="1">
+    <row r="395" hidden="1" ht="90" customHeight="1">
       <c r="A395" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31333,7 +31333,7 @@
         </is>
       </c>
     </row>
-    <row r="396" ht="90" customHeight="1">
+    <row r="396" hidden="1" ht="90" customHeight="1">
       <c r="A396" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31415,7 +31415,7 @@
         </is>
       </c>
     </row>
-    <row r="397" ht="75" customHeight="1">
+    <row r="397" hidden="1" ht="75" customHeight="1">
       <c r="A397" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31492,7 +31492,7 @@
         </is>
       </c>
     </row>
-    <row r="398" ht="60" customHeight="1">
+    <row r="398" hidden="1" ht="60" customHeight="1">
       <c r="A398" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31567,7 +31567,7 @@
         </is>
       </c>
     </row>
-    <row r="399" ht="105" customHeight="1">
+    <row r="399" hidden="1" ht="105" customHeight="1">
       <c r="A399" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
     </row>
-    <row r="400" ht="90" customHeight="1">
+    <row r="400" hidden="1" ht="90" customHeight="1">
       <c r="A400" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31731,7 +31731,7 @@
         </is>
       </c>
     </row>
-    <row r="401" ht="135" customHeight="1">
+    <row r="401" hidden="1" ht="135" customHeight="1">
       <c r="A401" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31816,7 +31816,7 @@
         </is>
       </c>
     </row>
-    <row r="402" ht="135" customHeight="1">
+    <row r="402" hidden="1" ht="135" customHeight="1">
       <c r="A402" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -31899,7 +31899,7 @@
         </is>
       </c>
     </row>
-    <row r="403" ht="105" customHeight="1">
+    <row r="403" hidden="1" ht="105" customHeight="1">
       <c r="A403" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -31981,7 +31981,7 @@
         </is>
       </c>
     </row>
-    <row r="404" ht="90" customHeight="1">
+    <row r="404" hidden="1" ht="90" customHeight="1">
       <c r="A404" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32061,7 +32061,7 @@
         </is>
       </c>
     </row>
-    <row r="405" ht="90" customHeight="1">
+    <row r="405" hidden="1" ht="90" customHeight="1">
       <c r="A405" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
     </row>
-    <row r="406" ht="90" customHeight="1">
+    <row r="406" hidden="1" ht="90" customHeight="1">
       <c r="A406" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -32214,7 +32214,7 @@
         </is>
       </c>
     </row>
-    <row r="407" ht="60" customHeight="1">
+    <row r="407" hidden="1" ht="60" customHeight="1">
       <c r="A407" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32291,7 +32291,7 @@
         </is>
       </c>
     </row>
-    <row r="408" ht="45" customHeight="1">
+    <row r="408" hidden="1" ht="45" customHeight="1">
       <c r="A408" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32365,7 +32365,7 @@
         </is>
       </c>
     </row>
-    <row r="409" ht="60" customHeight="1">
+    <row r="409" hidden="1" ht="60" customHeight="1">
       <c r="A409" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -32440,7 +32440,7 @@
         </is>
       </c>
     </row>
-    <row r="410" ht="60" customHeight="1">
+    <row r="410" hidden="1" ht="60" customHeight="1">
       <c r="A410" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32514,7 +32514,7 @@
         </is>
       </c>
     </row>
-    <row r="411" ht="75" customHeight="1">
+    <row r="411" hidden="1" ht="75" customHeight="1">
       <c r="A411" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32591,7 +32591,7 @@
         </is>
       </c>
     </row>
-    <row r="412" ht="120" customHeight="1">
+    <row r="412" hidden="1" ht="120" customHeight="1">
       <c r="A412" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32671,7 +32671,7 @@
         </is>
       </c>
     </row>
-    <row r="413" ht="45" customHeight="1">
+    <row r="413" hidden="1" ht="45" customHeight="1">
       <c r="A413" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32746,7 +32746,7 @@
         </is>
       </c>
     </row>
-    <row r="414" ht="60" customHeight="1">
+    <row r="414" hidden="1" ht="60" customHeight="1">
       <c r="A414" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32819,7 +32819,7 @@
         </is>
       </c>
     </row>
-    <row r="415" ht="60" customHeight="1">
+    <row r="415" hidden="1" ht="60" customHeight="1">
       <c r="A415" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" hidden="1" ht="60" customHeight="1">
       <c r="A416" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -32966,7 +32966,7 @@
         </is>
       </c>
     </row>
-    <row r="417" ht="120" customHeight="1">
+    <row r="417" hidden="1" ht="120" customHeight="1">
       <c r="A417" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33042,7 +33042,7 @@
         </is>
       </c>
     </row>
-    <row r="418" ht="120" customHeight="1">
+    <row r="418" hidden="1" ht="120" customHeight="1">
       <c r="A418" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33121,7 +33121,7 @@
         </is>
       </c>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" hidden="1" ht="60" customHeight="1">
       <c r="A419" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33198,7 +33198,7 @@
         </is>
       </c>
     </row>
-    <row r="420" ht="45" customHeight="1">
+    <row r="420" hidden="1" ht="45" customHeight="1">
       <c r="A420" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33257,7 +33257,7 @@
         </is>
       </c>
     </row>
-    <row r="421" ht="180" customHeight="1">
+    <row r="421" hidden="1" ht="180" customHeight="1">
       <c r="A421" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33347,7 +33347,7 @@
         </is>
       </c>
     </row>
-    <row r="422" ht="60" customHeight="1">
+    <row r="422" hidden="1" ht="60" customHeight="1">
       <c r="A422" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33424,7 +33424,7 @@
         </is>
       </c>
     </row>
-    <row r="423" ht="45" customHeight="1">
+    <row r="423" hidden="1" ht="45" customHeight="1">
       <c r="A423" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33497,7 +33497,7 @@
         </is>
       </c>
     </row>
-    <row r="424" ht="45" customHeight="1">
+    <row r="424" hidden="1" ht="45" customHeight="1">
       <c r="A424" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33569,7 +33569,7 @@
         </is>
       </c>
     </row>
-    <row r="425" ht="45" customHeight="1">
+    <row r="425" hidden="1" ht="45" customHeight="1">
       <c r="A425" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33641,7 +33641,7 @@
         </is>
       </c>
     </row>
-    <row r="426" ht="105" customHeight="1">
+    <row r="426" hidden="1" ht="105" customHeight="1">
       <c r="A426" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -33725,7 +33725,7 @@
         </is>
       </c>
     </row>
-    <row r="427" ht="90" customHeight="1">
+    <row r="427" hidden="1" ht="90" customHeight="1">
       <c r="A427" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33809,7 +33809,7 @@
         </is>
       </c>
     </row>
-    <row r="428" ht="120" customHeight="1">
+    <row r="428" hidden="1" ht="120" customHeight="1">
       <c r="A428" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33894,7 +33894,7 @@
         </is>
       </c>
     </row>
-    <row r="429" ht="135" customHeight="1">
+    <row r="429" hidden="1" ht="135" customHeight="1">
       <c r="A429" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -33981,7 +33981,7 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="75" customHeight="1">
+    <row r="430" hidden="1" ht="75" customHeight="1">
       <c r="A430" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -34064,7 +34064,7 @@
         </is>
       </c>
     </row>
-    <row r="431" ht="75" customHeight="1">
+    <row r="431" hidden="1" ht="75" customHeight="1">
       <c r="A431" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34145,7 +34145,7 @@
         </is>
       </c>
     </row>
-    <row r="432" ht="105" customHeight="1">
+    <row r="432" hidden="1" ht="105" customHeight="1">
       <c r="A432" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34228,7 +34228,7 @@
         </is>
       </c>
     </row>
-    <row r="433" ht="105" customHeight="1">
+    <row r="433" hidden="1" ht="105" customHeight="1">
       <c r="A433" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34309,7 +34309,7 @@
         </is>
       </c>
     </row>
-    <row r="434" ht="60" customHeight="1">
+    <row r="434" hidden="1" ht="60" customHeight="1">
       <c r="A434" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34384,7 +34384,7 @@
         </is>
       </c>
     </row>
-    <row r="435" ht="105" customHeight="1">
+    <row r="435" hidden="1" ht="105" customHeight="1">
       <c r="A435" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
     </row>
-    <row r="436" ht="75" customHeight="1">
+    <row r="436" hidden="1" ht="75" customHeight="1">
       <c r="A436" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34536,7 +34536,7 @@
         </is>
       </c>
     </row>
-    <row r="437" ht="45" customHeight="1">
+    <row r="437" hidden="1" ht="45" customHeight="1">
       <c r="A437" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34609,7 +34609,7 @@
         </is>
       </c>
     </row>
-    <row r="438" ht="90" customHeight="1">
+    <row r="438" hidden="1" ht="90" customHeight="1">
       <c r="A438" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -34685,7 +34685,7 @@
         </is>
       </c>
     </row>
-    <row r="439" ht="75" customHeight="1">
+    <row r="439" hidden="1" ht="75" customHeight="1">
       <c r="A439" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34759,7 +34759,7 @@
         </is>
       </c>
     </row>
-    <row r="440" ht="60" customHeight="1">
+    <row r="440" hidden="1" ht="60" customHeight="1">
       <c r="A440" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34837,7 +34837,7 @@
         </is>
       </c>
     </row>
-    <row r="441" ht="75" customHeight="1">
+    <row r="441" hidden="1" ht="75" customHeight="1">
       <c r="A441" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34913,7 +34913,7 @@
         </is>
       </c>
     </row>
-    <row r="442" ht="60" customHeight="1">
+    <row r="442" hidden="1" ht="60" customHeight="1">
       <c r="A442" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -34989,7 +34989,7 @@
         </is>
       </c>
     </row>
-    <row r="443" ht="60" customHeight="1">
+    <row r="443" hidden="1" ht="60" customHeight="1">
       <c r="A443" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -35063,7 +35063,7 @@
         </is>
       </c>
     </row>
-    <row r="444" ht="45" customHeight="1">
+    <row r="444" hidden="1" ht="45" customHeight="1">
       <c r="A444" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -35135,7 +35135,7 @@
         </is>
       </c>
     </row>
-    <row r="445" ht="75" customHeight="1">
+    <row r="445" hidden="1" ht="75" customHeight="1">
       <c r="A445" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35211,7 +35211,7 @@
         </is>
       </c>
     </row>
-    <row r="446" ht="60" customHeight="1">
+    <row r="446" hidden="1" ht="60" customHeight="1">
       <c r="A446" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35284,7 +35284,7 @@
         </is>
       </c>
     </row>
-    <row r="447" ht="60" customHeight="1">
+    <row r="447" hidden="1" ht="60" customHeight="1">
       <c r="A447" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35362,7 +35362,7 @@
         </is>
       </c>
     </row>
-    <row r="448" ht="75" customHeight="1">
+    <row r="448" hidden="1" ht="75" customHeight="1">
       <c r="A448" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35438,7 +35438,7 @@
         </is>
       </c>
     </row>
-    <row r="449" ht="75" customHeight="1">
+    <row r="449" hidden="1" ht="75" customHeight="1">
       <c r="A449" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -35512,7 +35512,7 @@
         </is>
       </c>
     </row>
-    <row r="450" ht="45" customHeight="1">
+    <row r="450" hidden="1" ht="45" customHeight="1">
       <c r="A450" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35579,7 +35579,7 @@
         </is>
       </c>
     </row>
-    <row r="451" ht="45" customHeight="1">
+    <row r="451" hidden="1" ht="45" customHeight="1">
       <c r="A451" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -35646,7 +35646,7 @@
         </is>
       </c>
     </row>
-    <row r="452" ht="45" customHeight="1">
+    <row r="452" hidden="1" ht="45" customHeight="1">
       <c r="A452" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -35705,7 +35705,7 @@
         </is>
       </c>
     </row>
-    <row r="453" ht="90" customHeight="1">
+    <row r="453" hidden="1" ht="90" customHeight="1">
       <c r="A453" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35767,7 +35767,7 @@
         </is>
       </c>
     </row>
-    <row r="454" ht="90" customHeight="1">
+    <row r="454" hidden="1" ht="90" customHeight="1">
       <c r="A454" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35829,7 +35829,7 @@
         </is>
       </c>
     </row>
-    <row r="455" ht="105" customHeight="1">
+    <row r="455" hidden="1" ht="105" customHeight="1">
       <c r="A455" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35892,7 +35892,7 @@
         </is>
       </c>
     </row>
-    <row r="456" ht="75" customHeight="1">
+    <row r="456" hidden="1" ht="75" customHeight="1">
       <c r="A456" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -35953,7 +35953,7 @@
         </is>
       </c>
     </row>
-    <row r="457" ht="75" customHeight="1">
+    <row r="457" hidden="1" ht="75" customHeight="1">
       <c r="A457" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36014,7 +36014,7 @@
         </is>
       </c>
     </row>
-    <row r="458" ht="75" customHeight="1">
+    <row r="458" hidden="1" ht="75" customHeight="1">
       <c r="A458" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36075,7 +36075,7 @@
         </is>
       </c>
     </row>
-    <row r="459" ht="90" customHeight="1">
+    <row r="459" hidden="1" ht="90" customHeight="1">
       <c r="A459" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36137,7 +36137,7 @@
         </is>
       </c>
     </row>
-    <row r="460" ht="90" customHeight="1">
+    <row r="460" hidden="1" ht="90" customHeight="1">
       <c r="A460" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36199,7 +36199,7 @@
         </is>
       </c>
     </row>
-    <row r="461" ht="60" customHeight="1">
+    <row r="461" hidden="1" ht="60" customHeight="1">
       <c r="A461" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36259,7 +36259,7 @@
         </is>
       </c>
     </row>
-    <row r="462" ht="60" customHeight="1">
+    <row r="462" hidden="1" ht="60" customHeight="1">
       <c r="A462" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36319,7 +36319,7 @@
         </is>
       </c>
     </row>
-    <row r="463" ht="60" customHeight="1">
+    <row r="463" hidden="1" ht="60" customHeight="1">
       <c r="A463" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36379,7 +36379,7 @@
         </is>
       </c>
     </row>
-    <row r="464" ht="45" customHeight="1">
+    <row r="464" hidden="1" ht="45" customHeight="1">
       <c r="A464" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36438,7 +36438,7 @@
         </is>
       </c>
     </row>
-    <row r="465" ht="60" customHeight="1">
+    <row r="465" hidden="1" ht="60" customHeight="1">
       <c r="A465" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
     </row>
-    <row r="466" ht="45" customHeight="1">
+    <row r="466" hidden="1" ht="45" customHeight="1">
       <c r="A466" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36557,7 +36557,7 @@
         </is>
       </c>
     </row>
-    <row r="467" ht="30" customHeight="1">
+    <row r="467" hidden="1" ht="30" customHeight="1">
       <c r="A467" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36615,7 +36615,7 @@
         </is>
       </c>
     </row>
-    <row r="468" ht="45" customHeight="1">
+    <row r="468" hidden="1" ht="45" customHeight="1">
       <c r="A468" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
     </row>
-    <row r="469" ht="45" customHeight="1">
+    <row r="469" hidden="1" ht="45" customHeight="1">
       <c r="A469" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36733,7 +36733,7 @@
         </is>
       </c>
     </row>
-    <row r="470" ht="60" customHeight="1">
+    <row r="470" hidden="1" ht="60" customHeight="1">
       <c r="A470" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36793,7 +36793,7 @@
         </is>
       </c>
     </row>
-    <row r="471" ht="60" customHeight="1">
+    <row r="471" hidden="1" ht="60" customHeight="1">
       <c r="A471" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36853,7 +36853,7 @@
         </is>
       </c>
     </row>
-    <row r="472" ht="75" customHeight="1">
+    <row r="472" hidden="1" ht="75" customHeight="1">
       <c r="A472" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36914,7 +36914,7 @@
         </is>
       </c>
     </row>
-    <row r="473" ht="45" customHeight="1">
+    <row r="473" hidden="1" ht="45" customHeight="1">
       <c r="A473" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -36987,7 +36987,7 @@
         </is>
       </c>
     </row>
-    <row r="474" ht="60" customHeight="1">
+    <row r="474" hidden="1" ht="60" customHeight="1">
       <c r="A474" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37061,7 +37061,7 @@
         </is>
       </c>
     </row>
-    <row r="475" ht="45" customHeight="1">
+    <row r="475" hidden="1" ht="45" customHeight="1">
       <c r="A475" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37136,7 +37136,7 @@
         </is>
       </c>
     </row>
-    <row r="476" ht="60" customHeight="1">
+    <row r="476" hidden="1" ht="60" customHeight="1">
       <c r="A476" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
     </row>
-    <row r="477" ht="60" customHeight="1">
+    <row r="477" hidden="1" ht="60" customHeight="1">
       <c r="A477" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37290,7 +37290,7 @@
         </is>
       </c>
     </row>
-    <row r="478" ht="60" customHeight="1">
+    <row r="478" hidden="1" ht="60" customHeight="1">
       <c r="A478" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37366,7 +37366,7 @@
         </is>
       </c>
     </row>
-    <row r="479" ht="60" customHeight="1">
+    <row r="479" hidden="1" ht="60" customHeight="1">
       <c r="A479" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37443,7 +37443,7 @@
         </is>
       </c>
     </row>
-    <row r="480" ht="60" customHeight="1">
+    <row r="480" hidden="1" ht="60" customHeight="1">
       <c r="A480" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37520,7 +37520,7 @@
         </is>
       </c>
     </row>
-    <row r="481" ht="60" customHeight="1">
+    <row r="481" hidden="1" ht="60" customHeight="1">
       <c r="A481" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37599,7 +37599,7 @@
         </is>
       </c>
     </row>
-    <row r="482" ht="75" customHeight="1">
+    <row r="482" hidden="1" ht="75" customHeight="1">
       <c r="A482" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37679,7 +37679,7 @@
         </is>
       </c>
     </row>
-    <row r="483" ht="90" customHeight="1">
+    <row r="483" hidden="1" ht="90" customHeight="1">
       <c r="A483" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37758,7 +37758,7 @@
         </is>
       </c>
     </row>
-    <row r="484" ht="45" customHeight="1">
+    <row r="484" hidden="1" ht="45" customHeight="1">
       <c r="A484" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37832,7 +37832,7 @@
         </is>
       </c>
     </row>
-    <row r="485" ht="75" customHeight="1">
+    <row r="485" hidden="1" ht="75" customHeight="1">
       <c r="A485" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -37908,7 +37908,7 @@
         </is>
       </c>
     </row>
-    <row r="486" ht="75" customHeight="1">
+    <row r="486" hidden="1" ht="75" customHeight="1">
       <c r="A486" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -37989,7 +37989,7 @@
         </is>
       </c>
     </row>
-    <row r="487" ht="60" customHeight="1">
+    <row r="487" hidden="1" ht="60" customHeight="1">
       <c r="A487" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38065,7 +38065,7 @@
         </is>
       </c>
     </row>
-    <row r="488" ht="75" customHeight="1">
+    <row r="488" hidden="1" ht="75" customHeight="1">
       <c r="A488" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38140,7 +38140,7 @@
         </is>
       </c>
     </row>
-    <row r="489" ht="60" customHeight="1">
+    <row r="489" hidden="1" ht="60" customHeight="1">
       <c r="A489" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -38218,7 +38218,7 @@
         </is>
       </c>
     </row>
-    <row r="490" ht="45" customHeight="1">
+    <row r="490" hidden="1" ht="45" customHeight="1">
       <c r="A490" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38277,7 +38277,7 @@
         </is>
       </c>
     </row>
-    <row r="491" ht="75" customHeight="1">
+    <row r="491" hidden="1" ht="75" customHeight="1">
       <c r="A491" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -38353,7 +38353,7 @@
         </is>
       </c>
     </row>
-    <row r="492" ht="105" customHeight="1">
+    <row r="492" hidden="1" ht="105" customHeight="1">
       <c r="A492" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38433,7 +38433,7 @@
         </is>
       </c>
     </row>
-    <row r="493" ht="90" customHeight="1">
+    <row r="493" hidden="1" ht="90" customHeight="1">
       <c r="A493" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -38509,7 +38509,7 @@
         </is>
       </c>
     </row>
-    <row r="494" ht="30" customHeight="1">
+    <row r="494" hidden="1" ht="30" customHeight="1">
       <c r="A494" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38582,7 +38582,7 @@
         </is>
       </c>
     </row>
-    <row r="495" ht="30" customHeight="1">
+    <row r="495" hidden="1" ht="30" customHeight="1">
       <c r="A495" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38653,7 +38653,7 @@
         </is>
       </c>
     </row>
-    <row r="496" ht="75" customHeight="1">
+    <row r="496" hidden="1" ht="75" customHeight="1">
       <c r="A496" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38729,7 +38729,7 @@
         </is>
       </c>
     </row>
-    <row r="497" ht="60" customHeight="1">
+    <row r="497" hidden="1" ht="60" customHeight="1">
       <c r="A497" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -38803,7 +38803,7 @@
         </is>
       </c>
     </row>
-    <row r="498" ht="135" customHeight="1">
+    <row r="498" hidden="1" ht="135" customHeight="1">
       <c r="A498" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -38884,7 +38884,7 @@
         </is>
       </c>
     </row>
-    <row r="499" ht="90" customHeight="1">
+    <row r="499" hidden="1" ht="90" customHeight="1">
       <c r="A499" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -38962,7 +38962,7 @@
         </is>
       </c>
     </row>
-    <row r="500" ht="75" customHeight="1">
+    <row r="500" hidden="1" ht="75" customHeight="1">
       <c r="A500" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39039,7 +39039,7 @@
         </is>
       </c>
     </row>
-    <row r="501" ht="30" customHeight="1">
+    <row r="501" hidden="1" ht="30" customHeight="1">
       <c r="A501" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39097,7 +39097,7 @@
         </is>
       </c>
     </row>
-    <row r="502" ht="180" customHeight="1">
+    <row r="502" hidden="1" ht="180" customHeight="1">
       <c r="A502" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39184,7 +39184,7 @@
         </is>
       </c>
     </row>
-    <row r="503" ht="150" customHeight="1">
+    <row r="503" hidden="1" ht="150" customHeight="1">
       <c r="A503" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39264,7 +39264,7 @@
         </is>
       </c>
     </row>
-    <row r="504" ht="30" customHeight="1">
+    <row r="504" hidden="1" ht="30" customHeight="1">
       <c r="A504" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39322,7 +39322,7 @@
         </is>
       </c>
     </row>
-    <row r="505" ht="60" customHeight="1">
+    <row r="505" hidden="1" ht="60" customHeight="1">
       <c r="A505" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39391,7 +39391,7 @@
         </is>
       </c>
     </row>
-    <row r="506" ht="45" customHeight="1">
+    <row r="506" hidden="1" ht="45" customHeight="1">
       <c r="A506" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39454,7 +39454,7 @@
         </is>
       </c>
     </row>
-    <row r="507" ht="30" customHeight="1">
+    <row r="507" hidden="1" ht="30" customHeight="1">
       <c r="A507" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39516,7 +39516,7 @@
         </is>
       </c>
     </row>
-    <row r="508" ht="75" customHeight="1">
+    <row r="508" hidden="1" ht="75" customHeight="1">
       <c r="A508" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39589,7 +39589,7 @@
         </is>
       </c>
     </row>
-    <row r="509" ht="120" customHeight="1">
+    <row r="509" hidden="1" ht="120" customHeight="1">
       <c r="A509" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39668,7 +39668,7 @@
         </is>
       </c>
     </row>
-    <row r="510" ht="90" customHeight="1">
+    <row r="510" hidden="1" ht="90" customHeight="1">
       <c r="A510" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39737,7 +39737,7 @@
         </is>
       </c>
     </row>
-    <row r="511" ht="60" customHeight="1">
+    <row r="511" hidden="1" ht="60" customHeight="1">
       <c r="A511" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -39810,7 +39810,7 @@
         </is>
       </c>
     </row>
-    <row r="512" ht="30" customHeight="1">
+    <row r="512" hidden="1" ht="30" customHeight="1">
       <c r="A512" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39882,7 +39882,7 @@
         </is>
       </c>
     </row>
-    <row r="513" ht="30" customHeight="1">
+    <row r="513" hidden="1" ht="30" customHeight="1">
       <c r="A513" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -39954,7 +39954,7 @@
         </is>
       </c>
     </row>
-    <row r="514" ht="45" customHeight="1">
+    <row r="514" hidden="1" ht="45" customHeight="1">
       <c r="A514" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -40028,7 +40028,7 @@
         </is>
       </c>
     </row>
-    <row r="515" ht="45" customHeight="1">
+    <row r="515" hidden="1" ht="45" customHeight="1">
       <c r="A515" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40102,7 +40102,7 @@
         </is>
       </c>
     </row>
-    <row r="516" ht="75" customHeight="1">
+    <row r="516" hidden="1" ht="75" customHeight="1">
       <c r="A516" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -40178,7 +40178,7 @@
         </is>
       </c>
     </row>
-    <row r="517" ht="105" customHeight="1">
+    <row r="517" hidden="1" ht="105" customHeight="1">
       <c r="A517" s="15" t="inlineStr">
         <is>
           <t>LSE</t>
@@ -40257,7 +40257,7 @@
         </is>
       </c>
     </row>
-    <row r="518" ht="30" customHeight="1">
+    <row r="518" hidden="1" ht="30" customHeight="1">
       <c r="A518" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
     </row>
-    <row r="519" ht="210" customHeight="1">
+    <row r="519" hidden="1" ht="210" customHeight="1">
       <c r="A519" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40407,7 +40407,7 @@
         </is>
       </c>
     </row>
-    <row r="520" ht="60" customHeight="1">
+    <row r="520" hidden="1" ht="60" customHeight="1">
       <c r="A520" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40473,7 +40473,7 @@
         </is>
       </c>
     </row>
-    <row r="521" ht="60" customHeight="1">
+    <row r="521" hidden="1" ht="60" customHeight="1">
       <c r="A521" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40539,7 +40539,7 @@
         </is>
       </c>
     </row>
-    <row r="522" ht="45" customHeight="1">
+    <row r="522" hidden="1" ht="45" customHeight="1">
       <c r="A522" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40598,7 +40598,7 @@
         </is>
       </c>
     </row>
-    <row r="523" ht="45" customHeight="1">
+    <row r="523" hidden="1" ht="45" customHeight="1">
       <c r="A523" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40657,7 +40657,7 @@
         </is>
       </c>
     </row>
-    <row r="524" ht="45" customHeight="1">
+    <row r="524" hidden="1" ht="45" customHeight="1">
       <c r="A524" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40716,7 +40716,7 @@
         </is>
       </c>
     </row>
-    <row r="525" ht="75" customHeight="1">
+    <row r="525" hidden="1" ht="75" customHeight="1">
       <c r="A525" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40777,7 +40777,7 @@
         </is>
       </c>
     </row>
-    <row r="526" ht="75" customHeight="1">
+    <row r="526" hidden="1" ht="75" customHeight="1">
       <c r="A526" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40838,7 +40838,7 @@
         </is>
       </c>
     </row>
-    <row r="527" ht="60" customHeight="1">
+    <row r="527" hidden="1" ht="60" customHeight="1">
       <c r="A527" s="15" t="inlineStr">
         <is>
           <t>LSW</t>
@@ -40898,7 +40898,7 @@
         </is>
       </c>
     </row>
-    <row r="528" ht="60" customHeight="1">
+    <row r="528" hidden="1" ht="60" customHeight="1">
       <c r="A528" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -40967,7 +40967,7 @@
         </is>
       </c>
     </row>
-    <row r="529" ht="60" customHeight="1">
+    <row r="529" hidden="1" ht="60" customHeight="1">
       <c r="A529" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41038,7 +41038,7 @@
         </is>
       </c>
     </row>
-    <row r="530" ht="60" customHeight="1">
+    <row r="530" hidden="1" ht="60" customHeight="1">
       <c r="A530" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41109,7 +41109,7 @@
         </is>
       </c>
     </row>
-    <row r="531" ht="75" customHeight="1">
+    <row r="531" hidden="1" ht="75" customHeight="1">
       <c r="A531" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41182,7 +41182,7 @@
         </is>
       </c>
     </row>
-    <row r="532" ht="60" customHeight="1">
+    <row r="532" hidden="1" ht="60" customHeight="1">
       <c r="A532" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41253,7 +41253,7 @@
         </is>
       </c>
     </row>
-    <row r="533" ht="45" customHeight="1">
+    <row r="533" hidden="1" ht="45" customHeight="1">
       <c r="A533" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41322,7 +41322,7 @@
         </is>
       </c>
     </row>
-    <row r="534" ht="60" customHeight="1">
+    <row r="534" hidden="1" ht="60" customHeight="1">
       <c r="A534" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41391,7 +41391,7 @@
         </is>
       </c>
     </row>
-    <row r="535" ht="60" customHeight="1">
+    <row r="535" hidden="1" ht="60" customHeight="1">
       <c r="A535" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41460,7 +41460,7 @@
         </is>
       </c>
     </row>
-    <row r="536" ht="60" customHeight="1">
+    <row r="536" hidden="1" ht="60" customHeight="1">
       <c r="A536" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41529,7 +41529,7 @@
         </is>
       </c>
     </row>
-    <row r="537" ht="75" customHeight="1">
+    <row r="537" hidden="1" ht="75" customHeight="1">
       <c r="A537" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41596,7 +41596,7 @@
         </is>
       </c>
     </row>
-    <row r="538" ht="60" customHeight="1">
+    <row r="538" hidden="1" ht="60" customHeight="1">
       <c r="A538" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41665,7 +41665,7 @@
         </is>
       </c>
     </row>
-    <row r="539" ht="60" customHeight="1">
+    <row r="539" hidden="1" ht="60" customHeight="1">
       <c r="A539" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41736,7 +41736,7 @@
         </is>
       </c>
     </row>
-    <row r="540" ht="60" customHeight="1">
+    <row r="540" hidden="1" ht="60" customHeight="1">
       <c r="A540" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41805,7 +41805,7 @@
         </is>
       </c>
     </row>
-    <row r="541" ht="60" customHeight="1">
+    <row r="541" hidden="1" ht="60" customHeight="1">
       <c r="A541" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41876,7 +41876,7 @@
         </is>
       </c>
     </row>
-    <row r="542" ht="60" customHeight="1">
+    <row r="542" hidden="1" ht="60" customHeight="1">
       <c r="A542" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41947,7 +41947,7 @@
         </is>
       </c>
     </row>
-    <row r="543" ht="75" customHeight="1">
+    <row r="543" hidden="1" ht="75" customHeight="1">
       <c r="A543" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42018,7 +42018,7 @@
         </is>
       </c>
     </row>
-    <row r="544" ht="60" customHeight="1">
+    <row r="544" hidden="1" ht="60" customHeight="1">
       <c r="A544" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42089,7 +42089,7 @@
         </is>
       </c>
     </row>
-    <row r="545" ht="60" customHeight="1">
+    <row r="545" hidden="1" ht="60" customHeight="1">
       <c r="A545" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42160,7 +42160,7 @@
         </is>
       </c>
     </row>
-    <row r="546" ht="60" customHeight="1">
+    <row r="546" hidden="1" ht="60" customHeight="1">
       <c r="A546" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42231,7 +42231,7 @@
         </is>
       </c>
     </row>
-    <row r="547" ht="60" customHeight="1">
+    <row r="547" hidden="1" ht="60" customHeight="1">
       <c r="A547" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42302,7 +42302,7 @@
         </is>
       </c>
     </row>
-    <row r="548" ht="60" customHeight="1">
+    <row r="548" hidden="1" ht="60" customHeight="1">
       <c r="A548" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42373,7 +42373,7 @@
         </is>
       </c>
     </row>
-    <row r="549" ht="60" customHeight="1">
+    <row r="549" hidden="1" ht="60" customHeight="1">
       <c r="A549" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42442,7 +42442,7 @@
         </is>
       </c>
     </row>
-    <row r="550" ht="60" customHeight="1">
+    <row r="550" hidden="1" ht="60" customHeight="1">
       <c r="A550" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42514,7 +42514,7 @@
         </is>
       </c>
     </row>
-    <row r="551" ht="60" customHeight="1">
+    <row r="551" hidden="1" ht="60" customHeight="1">
       <c r="A551" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42581,7 +42581,7 @@
         </is>
       </c>
     </row>
-    <row r="552" ht="60" customHeight="1">
+    <row r="552" hidden="1" ht="60" customHeight="1">
       <c r="A552" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42652,7 +42652,7 @@
         </is>
       </c>
     </row>
-    <row r="553" ht="75" customHeight="1">
+    <row r="553" hidden="1" ht="75" customHeight="1">
       <c r="A553" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42721,7 +42721,7 @@
         </is>
       </c>
     </row>
-    <row r="554" ht="60" customHeight="1">
+    <row r="554" hidden="1" ht="60" customHeight="1">
       <c r="A554" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42792,7 +42792,7 @@
         </is>
       </c>
     </row>
-    <row r="555" ht="60" customHeight="1">
+    <row r="555" hidden="1" ht="60" customHeight="1">
       <c r="A555" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42863,7 +42863,7 @@
         </is>
       </c>
     </row>
-    <row r="556" ht="60" customHeight="1">
+    <row r="556" hidden="1" ht="60" customHeight="1">
       <c r="A556" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42932,7 +42932,7 @@
         </is>
       </c>
     </row>
-    <row r="557" ht="60" customHeight="1">
+    <row r="557" hidden="1" ht="60" customHeight="1">
       <c r="A557" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43003,7 +43003,7 @@
         </is>
       </c>
     </row>
-    <row r="558" ht="60" customHeight="1">
+    <row r="558" hidden="1" ht="60" customHeight="1">
       <c r="A558" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43074,7 +43074,7 @@
         </is>
       </c>
     </row>
-    <row r="559" ht="60" customHeight="1">
+    <row r="559" hidden="1" ht="60" customHeight="1">
       <c r="A559" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43145,7 +43145,7 @@
         </is>
       </c>
     </row>
-    <row r="560" ht="60" customHeight="1">
+    <row r="560" hidden="1" ht="60" customHeight="1">
       <c r="A560" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43217,7 +43217,7 @@
         </is>
       </c>
     </row>
-    <row r="561" ht="45" customHeight="1">
+    <row r="561" hidden="1" ht="45" customHeight="1">
       <c r="A561" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43288,7 +43288,7 @@
         </is>
       </c>
     </row>
-    <row r="562" ht="60" customHeight="1">
+    <row r="562" hidden="1" ht="60" customHeight="1">
       <c r="A562" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43355,7 +43355,7 @@
         </is>
       </c>
     </row>
-    <row r="563" ht="45" customHeight="1">
+    <row r="563" hidden="1" ht="45" customHeight="1">
       <c r="A563" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43424,7 +43424,7 @@
         </is>
       </c>
     </row>
-    <row r="564" ht="45" customHeight="1">
+    <row r="564" hidden="1" ht="45" customHeight="1">
       <c r="A564" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43493,7 +43493,7 @@
         </is>
       </c>
     </row>
-    <row r="565" ht="45" customHeight="1">
+    <row r="565" hidden="1" ht="45" customHeight="1">
       <c r="A565" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43562,7 +43562,7 @@
         </is>
       </c>
     </row>
-    <row r="566" ht="60" customHeight="1">
+    <row r="566" hidden="1" ht="60" customHeight="1">
       <c r="A566" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43631,7 +43631,7 @@
         </is>
       </c>
     </row>
-    <row r="567" ht="60" customHeight="1">
+    <row r="567" hidden="1" ht="60" customHeight="1">
       <c r="A567" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43700,7 +43700,7 @@
         </is>
       </c>
     </row>
-    <row r="568" ht="60" customHeight="1">
+    <row r="568" hidden="1" ht="60" customHeight="1">
       <c r="A568" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43771,7 +43771,7 @@
         </is>
       </c>
     </row>
-    <row r="569" ht="45" customHeight="1">
+    <row r="569" hidden="1" ht="45" customHeight="1">
       <c r="A569" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43842,7 +43842,7 @@
         </is>
       </c>
     </row>
-    <row r="570" ht="45" customHeight="1">
+    <row r="570" hidden="1" ht="45" customHeight="1">
       <c r="A570" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43911,7 +43911,7 @@
         </is>
       </c>
     </row>
-    <row r="571" ht="45" customHeight="1">
+    <row r="571" hidden="1" ht="45" customHeight="1">
       <c r="A571" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43980,7 +43980,7 @@
         </is>
       </c>
     </row>
-    <row r="572" ht="45" customHeight="1">
+    <row r="572" hidden="1" ht="45" customHeight="1">
       <c r="A572" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44051,7 +44051,7 @@
         </is>
       </c>
     </row>
-    <row r="573" ht="60" customHeight="1">
+    <row r="573" hidden="1" ht="60" customHeight="1">
       <c r="A573" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44122,7 +44122,7 @@
         </is>
       </c>
     </row>
-    <row r="574" ht="45" customHeight="1">
+    <row r="574" hidden="1" ht="45" customHeight="1">
       <c r="A574" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44191,7 +44191,7 @@
         </is>
       </c>
     </row>
-    <row r="575" ht="60" customHeight="1">
+    <row r="575" hidden="1" ht="60" customHeight="1">
       <c r="A575" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44262,7 +44262,7 @@
         </is>
       </c>
     </row>
-    <row r="576" ht="45" customHeight="1">
+    <row r="576" hidden="1" ht="45" customHeight="1">
       <c r="A576" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44333,7 +44333,7 @@
         </is>
       </c>
     </row>
-    <row r="577" ht="75" customHeight="1">
+    <row r="577" hidden="1" ht="75" customHeight="1">
       <c r="A577" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44404,7 +44404,7 @@
         </is>
       </c>
     </row>
-    <row r="578" ht="60" customHeight="1">
+    <row r="578" hidden="1" ht="60" customHeight="1">
       <c r="A578" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44473,7 +44473,7 @@
         </is>
       </c>
     </row>
-    <row r="579" ht="75" customHeight="1">
+    <row r="579" hidden="1" ht="75" customHeight="1">
       <c r="A579" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44542,7 +44542,7 @@
         </is>
       </c>
     </row>
-    <row r="580" ht="60" customHeight="1">
+    <row r="580" hidden="1" ht="60" customHeight="1">
       <c r="A580" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44613,7 +44613,7 @@
         </is>
       </c>
     </row>
-    <row r="581" ht="60" customHeight="1">
+    <row r="581" hidden="1" ht="60" customHeight="1">
       <c r="A581" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44684,7 +44684,7 @@
         </is>
       </c>
     </row>
-    <row r="582" ht="60" customHeight="1">
+    <row r="582" hidden="1" ht="60" customHeight="1">
       <c r="A582" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44751,7 +44751,7 @@
         </is>
       </c>
     </row>
-    <row r="583" ht="60" customHeight="1">
+    <row r="583" hidden="1" ht="60" customHeight="1">
       <c r="A583" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44820,7 +44820,7 @@
         </is>
       </c>
     </row>
-    <row r="584" ht="60" customHeight="1">
+    <row r="584" hidden="1" ht="60" customHeight="1">
       <c r="A584" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44889,7 +44889,7 @@
         </is>
       </c>
     </row>
-    <row r="585" ht="60" customHeight="1">
+    <row r="585" hidden="1" ht="60" customHeight="1">
       <c r="A585" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44958,7 +44958,7 @@
         </is>
       </c>
     </row>
-    <row r="586" ht="60" customHeight="1">
+    <row r="586" hidden="1" ht="60" customHeight="1">
       <c r="A586" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45027,7 +45027,7 @@
         </is>
       </c>
     </row>
-    <row r="587" ht="45" customHeight="1">
+    <row r="587" hidden="1" ht="45" customHeight="1">
       <c r="A587" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45096,7 +45096,7 @@
         </is>
       </c>
     </row>
-    <row r="588" ht="60" customHeight="1">
+    <row r="588" hidden="1" ht="60" customHeight="1">
       <c r="A588" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45165,7 +45165,7 @@
         </is>
       </c>
     </row>
-    <row r="589" ht="45" customHeight="1">
+    <row r="589" hidden="1" ht="45" customHeight="1">
       <c r="A589" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45234,7 +45234,7 @@
         </is>
       </c>
     </row>
-    <row r="590" ht="60" customHeight="1">
+    <row r="590" hidden="1" ht="60" customHeight="1">
       <c r="A590" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45303,7 +45303,7 @@
         </is>
       </c>
     </row>
-    <row r="591">
+    <row r="591" hidden="1">
       <c r="A591" s="8" t="n"/>
       <c r="B591" s="8" t="n"/>
       <c r="C591" s="3" t="n"/>
@@ -45330,7 +45330,7 @@
       <c r="P591" s="22" t="n"/>
       <c r="Q591" s="22" t="n"/>
     </row>
-    <row r="592">
+    <row r="592" hidden="1">
       <c r="A592" s="8" t="n"/>
       <c r="B592" s="8" t="n"/>
       <c r="C592" s="3" t="n"/>
@@ -45357,7 +45357,7 @@
       <c r="P592" s="22" t="n"/>
       <c r="Q592" s="22" t="n"/>
     </row>
-    <row r="593" ht="60" customHeight="1">
+    <row r="593" hidden="1" ht="60" customHeight="1">
       <c r="A593" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45427,7 +45427,7 @@
       <c r="S593" s="4" t="n"/>
       <c r="T593" s="4" t="n"/>
     </row>
-    <row r="594" ht="45" customHeight="1">
+    <row r="594" hidden="1" ht="45" customHeight="1">
       <c r="A594" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45497,7 +45497,7 @@
       <c r="S594" s="4" t="n"/>
       <c r="T594" s="4" t="n"/>
     </row>
-    <row r="595">
+    <row r="595" hidden="1" ht="105" customHeight="1">
       <c r="A595" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45563,7 +45563,7 @@
       <c r="S595" s="4" t="n"/>
       <c r="T595" s="4" t="n"/>
     </row>
-    <row r="596">
+    <row r="596" hidden="1" ht="90" customHeight="1">
       <c r="A596" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45633,7 +45633,7 @@
       <c r="S596" s="4" t="n"/>
       <c r="T596" s="4" t="n"/>
     </row>
-    <row r="597" ht="60" customHeight="1">
+    <row r="597" hidden="1" ht="60" customHeight="1">
       <c r="A597" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45703,7 +45703,7 @@
       <c r="S597" s="4" t="n"/>
       <c r="T597" s="4" t="n"/>
     </row>
-    <row r="598" ht="75" customHeight="1">
+    <row r="598" hidden="1" ht="75" customHeight="1">
       <c r="A598" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45777,7 +45777,7 @@
       <c r="S598" s="4" t="n"/>
       <c r="T598" s="4" t="n"/>
     </row>
-    <row r="599" ht="60" customHeight="1">
+    <row r="599" hidden="1" ht="60" customHeight="1">
       <c r="A599" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45851,7 +45851,7 @@
       <c r="S599" s="4" t="n"/>
       <c r="T599" s="4" t="n"/>
     </row>
-    <row r="600" ht="45" customHeight="1">
+    <row r="600" hidden="1" ht="45" customHeight="1">
       <c r="A600" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45925,7 +45925,7 @@
       <c r="S600" s="4" t="n"/>
       <c r="T600" s="4" t="n"/>
     </row>
-    <row r="601" ht="45" customHeight="1">
+    <row r="601" hidden="1" ht="45" customHeight="1">
       <c r="A601" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45995,7 +45995,7 @@
       <c r="S601" s="4" t="n"/>
       <c r="T601" s="4" t="n"/>
     </row>
-    <row r="602" ht="30" customHeight="1">
+    <row r="602" hidden="1" ht="30" customHeight="1">
       <c r="A602" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46061,7 +46061,7 @@
       <c r="S602" s="4" t="n"/>
       <c r="T602" s="4" t="n"/>
     </row>
-    <row r="603" ht="30" customHeight="1">
+    <row r="603" hidden="1" ht="30" customHeight="1">
       <c r="A603" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46127,7 +46127,7 @@
       <c r="S603" s="4" t="n"/>
       <c r="T603" s="4" t="n"/>
     </row>
-    <row r="604" ht="30" customHeight="1">
+    <row r="604" hidden="1" ht="30" customHeight="1">
       <c r="A604" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46193,7 +46193,7 @@
       <c r="S604" s="4" t="n"/>
       <c r="T604" s="4" t="n"/>
     </row>
-    <row r="605" ht="30" customHeight="1">
+    <row r="605" hidden="1" ht="30" customHeight="1">
       <c r="A605" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46259,7 +46259,7 @@
       <c r="S605" s="4" t="n"/>
       <c r="T605" s="4" t="n"/>
     </row>
-    <row r="606" ht="45" customHeight="1">
+    <row r="606" hidden="1" ht="45" customHeight="1">
       <c r="A606" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46325,7 +46325,7 @@
       <c r="S606" s="4" t="n"/>
       <c r="T606" s="4" t="n"/>
     </row>
-    <row r="607">
+    <row r="607" hidden="1" ht="105" customHeight="1">
       <c r="A607" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46391,7 +46391,7 @@
       <c r="S607" s="4" t="n"/>
       <c r="T607" s="4" t="n"/>
     </row>
-    <row r="608" ht="30" customHeight="1">
+    <row r="608" hidden="1" ht="30" customHeight="1">
       <c r="A608" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46457,7 +46457,7 @@
       <c r="S608" s="4" t="n"/>
       <c r="T608" s="4" t="n"/>
     </row>
-    <row r="609">
+    <row r="609" ht="180" customHeight="1">
       <c r="A609" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46495,7 +46495,7 @@
       </c>
       <c r="H609" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I609" s="15" t="inlineStr">
@@ -46524,11 +46524,11 @@
       <c r="P609" s="24" t="n"/>
       <c r="Q609" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0001 als MAP0001 Label Width. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
+          <t>KI: Ich verstehe diesen Parameter als Etiketten- bzw. Traegerbandbreite in 1/10 mm. Der Wert definiert zugleich die Sollposition der beiden Etikettenanschlaege: der rechte Nullpunkt liegt von oben gesehen an der rechten Bandkante, daher entspricht 20.0 mm dem Sollwert 200 und 55.0 mm dem Sollwert 550 fuer Einlauf- und Auslaufanschlag. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Der Wert definiert auch wo die beiden Etiekttenanschläge positioniert werden. Stelle Dir vor dass die Etikette von oben gesehen im Produktionsbetrieb von unten nach oben läuft und dass der 0-Punkt der Bahn auf der das Etikettenträgerband läuft ganz rechts ist. Wenn eine 20mm breite Etikette hier im format angegeben wird, müssen die beiden anschläge auf 200 (20mm) fahren, bei einer 55mm Etikette auf 550 usw.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="150" customHeight="1">
       <c r="A610" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46566,7 +46566,7 @@
       </c>
       <c r="H610" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I610" s="31" t="inlineStr">
@@ -46595,11 +46595,11 @@
       <c r="P610" s="38" t="n"/>
       <c r="Q610" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0002 als MAP0002 Label Length. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
+          <t>KI: Ich verstehe diesen Parameter als Soll-Etikettenlaenge ohne Gap in 1/10 mm. Der ESP muss die real gemessene Etikettenlaenge mit MAP0040 vergleichen; bei zu kurzer Laenge wird MAE0025 gesetzt, bei zu langer Laenge MAE0026. Der Raspi behandelt diese beiden Fehler als Produktionspause statt als Purge/Not-Stop. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Etikettenlänge wird für die Erfassungs/Sensorüberwachung der Etiekttenlänge verwendet. Der Parameter hängt zusammen mit MAP0040. Weicht die gemessene Länge im System mehr als MAP0040 nach oben/unten ab, wird ein entsprechender Fehler ausgelöst und die Produktion pausiert.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="210" customHeight="1">
       <c r="A611" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46637,7 +46637,7 @@
       </c>
       <c r="H611" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I611" s="15" t="inlineStr">
@@ -46666,11 +46666,11 @@
       <c r="P611" s="24" t="n"/>
       <c r="Q611" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0003 als MAP0003 Druckposition X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
+          <t>KI: Ich verstehe diesen Parameter als Druckposition in X-/Querrichtung auf dem Etikett. Fuer die Portalachse X gilt eine Umkehrlogik: ein positiver Druckpositionswert verschiebt den Tisch in negative X-Richtung, ein negativer Wert in positive X-Richtung. Die zusaetzliche Korrektur MAP0005 wird vorher auf den Druckpositionswert addiert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dies ist die Druckposition auf der Etikette in Querrichtung (wieder von oben gesehen rechts)ist der 0-Punkt. Das hat in der Steuerung folgende Funktion: Je nachdem welcher drucker (Laser/TTO) aktiv ist (bestimmt durch MAP0016) wird der tisch in X-Richtung weiter nach vorne bewegt. 0 heisst dabei dass die X-Achse im Produktionsbetrieb auf 0 geht und ein wert vom parameter hier von 20 bedeutet dass die X-Achse auf -20 (-2mmgeht ) und bei einem Wert von -20 muss die X-achse um 20 (2mm) nach vorne hier herrscht also ein Umkehrwert.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="240" customHeight="1">
       <c r="A612" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46708,7 +46708,7 @@
       </c>
       <c r="H612" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I612" s="31" t="inlineStr">
@@ -46737,11 +46737,11 @@
       <c r="P612" s="38" t="n"/>
       <c r="Q612" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0004 als MAP0004 Druckposition Y. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="613" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Druckposition in Y-/Laufrichtung auf dem Etikett. Der konkrete Stopppunkt ergibt sich aus MAP0018 fuer Laser oder MAP0019 fuer TTO plus MAP0004 und plus Korrektur MAP0006. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dies ist die Druckposition auf der Etikette in Längsrichtung (wieder von oben gesehen oben)ist der 0-Punkt. Das hat in der Steuerung folgende Funktion: Die Distanz MAP0018 bzw. MAP0019 (je nach aktivem Drucker) beschreibt die Position der Etikette in laufrichtung ganz am anfang (von oben gesehen). Der Wert 0 bedeutet somit, dass das Etiekttenband zum drucken bei genau Erfassungsanfang+MAP0018 oder MAP0019 + 0 stoppen muss. Steht hier z.b.50, soll der druck von oben gesehen in laufrichtung 5mm nach unten versetzt werden, was bedeutet, dass der stop-punkt zum drucken nun bei Erfassungsanfang des jewiligen Etiketts+MAP0018 oder MAP0019 + 50 stoppen muss.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="120" customHeight="1">
       <c r="A613" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46808,11 +46808,11 @@
       <c r="P613" s="24" t="n"/>
       <c r="Q613" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0005 als MAP0005 Korrektur Druckposition X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="614" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die X-Druckposition. Er wird auf MAP0003 addiert, bevor daraus die invertierte X-Achskorrektur fuer den Tisch gebildet wird. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Hier kann eine zusätliche Korrektur auf den X-Wert vorgenommen werden (dieser wird auf den X-Wert aufaddiert).. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="120" customHeight="1">
       <c r="A614" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46879,11 +46879,11 @@
       <c r="P614" s="38" t="n"/>
       <c r="Q614" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0006 als MAP0006 Korrektur Druckposition Y. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
+          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die Y-Druckposition. Er wird auf MAP0004 addiert und beeinflusst damit den exakten Druck-Stoppweg in Laufrichtung. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Hier kann eine zusätliche Korrektur auf den Y-Wert vorgenommen werden (dieser wird auf den Y-Wert aufaddiert).. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="150" customHeight="1">
       <c r="A615" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46921,7 +46921,7 @@
       </c>
       <c r="H615" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I615" s="15" t="inlineStr">
@@ -46950,11 +46950,11 @@
       <c r="P615" s="24" t="n"/>
       <c r="Q615" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0007 als MAP0007 Druckmaterialstärke. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
+          <t>KI: Ich verstehe diesen Parameter als Materialdicke bzw. Produktions-Z-Position des Tisches in 1/10 mm. Zusammen mit der Nullpunktkorrektur MAP0028 ergibt er den Z-Sollwert fuer den Produktionsbetrieb. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dieser wert Steuert die Z-Achse vom Tisch im Produktionsbetrieb und beschreibt die Etiekttendicke. Ein Wert von 1 bedeutet die Z-Achse muss im Produktionsbetrieb auf 1 fahren, ein wert von 50 bedeutet die Z-Achse muss im Produktionsbetrieb auf 50 fahren,. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="120" customHeight="1">
       <c r="A616" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H616" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I616" s="31" t="inlineStr">
@@ -47021,11 +47021,11 @@
       <c r="P616" s="38" t="n"/>
       <c r="Q616" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0008 als MAP0008 Position Etikettenerfassung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
+          <t>KI: Ich verstehe diesen Parameter als Querposition des Etikettenerfassungs-Sensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0029 kombiniert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den Etiekttenerfassungssensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="120" customHeight="1">
       <c r="A617" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47063,7 +47063,7 @@
       </c>
       <c r="H617" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I617" s="15" t="inlineStr">
@@ -47092,11 +47092,11 @@
       <c r="P617" s="24" t="n"/>
       <c r="Q617" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0009 als MAP0009 Position Entnahme-Kontrollsensor. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="618" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Querposition des Entnahme-/Kontrollsensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0030 kombiniert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den ENtnahme/Kontrollensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="120" customHeight="1">
       <c r="A618" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47134,7 +47134,7 @@
       </c>
       <c r="H618" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I618" s="31" t="inlineStr">
@@ -47163,11 +47163,11 @@
       <c r="P618" s="38" t="n"/>
       <c r="Q618" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0010 als MAP0010 Leseposition Material-Kontrollkamera X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="619" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als X-/Quer-Leseposition der Material-Kontrollkamera. Er beschreibt die formatabhaengige Kameraposition; die mechanische Achskorrektur fuer diese Kamera wird separat ueber MAP0033 bzw. die Motor-Sollposition MAP0060 beruecksichtigt. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den Etiekttenerfassungssensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="120" customHeight="1">
       <c r="A619" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47205,7 +47205,7 @@
       </c>
       <c r="H619" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I619" s="15" t="inlineStr">
@@ -47234,11 +47234,11 @@
       <c r="P619" s="24" t="n"/>
       <c r="Q619" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0011 als MAP0011 Leseposition Material-Kontrollkamera Y. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="620" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der Material-Kontrollkamera. Der Wert ist ein Prozessbezug fuer Trigger-/Auswertefenster und nicht die Motor-ID-5-Querachse selbst. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für die Materialkontrollkamera im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="120" customHeight="1">
       <c r="A620" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47276,7 +47276,7 @@
       </c>
       <c r="H620" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I620" s="31" t="inlineStr">
@@ -47305,11 +47305,11 @@
       <c r="P620" s="38" t="n"/>
       <c r="Q620" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0012 als MAP0012 Leseposition Verifizierungs-Kamera Y. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="621" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der OCR-/Verifizierungs-Kamera. Die Kamera ist aktuell nicht als eigene Verstellachse modelliert; der Wert bleibt aber fuer Prozessfenster und spaetere Verifikation relevant. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für OCE Verifikationskamera im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="210" customHeight="1">
       <c r="A621" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47347,7 +47347,7 @@
       </c>
       <c r="H621" s="29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I621" s="15" t="inlineStr">
@@ -47376,11 +47376,11 @@
       <c r="P621" s="24" t="n"/>
       <c r="Q621" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0013 als MAP0013 Rollenkern-Typ (Etikettenrollenkern). Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="622" ht="45" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Rollenkern-Typ fuer Auf- und Abwicklung (0=76 mm, 1=100 mm). Die vorhandene Hardware kann den Kern nicht sicher direkt erkennen; eine Plausibilisierung ueber Wicklerbewegung und Rollenfuellstand ist theoretisch denkbar, aber noch nicht freigegeben. Deshalb wird der Wert vorerst nur als lesbarer Format-/Materialhinweis an den ESP gespiegelt und nicht aktiv fuer Regelentscheidungen verwendet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist der Parameter für den Typ des aufgespannten Etiekttenrollenkerns auf der Auf-und ABwicklung. Momentan wird das noch nicht verwendet und es ist auch nicht sicher ob der Parameter drin bleibt., da nicht sicher ist, ob anhand der Bewegungen des auf-und abwicklers kontrolliert werden kann, welcher Kern (76 oder 100mm) aktuell aufgespannt ist. Aufgabe: Finde heraus ob das technisch machbar ist mit der vorhandenen Hardware und schreibe hier das Ergebnis rein, verändere noch nichts am Code diesbezüglich.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="225" customHeight="1">
       <c r="A622" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47418,7 +47418,7 @@
       </c>
       <c r="H622" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I622" s="31" t="inlineStr">
@@ -47447,11 +47447,11 @@
       <c r="P622" s="38" t="n"/>
       <c r="Q622" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Soll-Vorzugsgeschwindigkeit des Etikettenbandes im normalen Prozessbetrieb. Der ESP muss diesen Wert fuer die Taktbewegungen und fuer die dynamische Nachregelung des Etikettenantriebs verwenden; auf dem Raspi ist er vor allem fuer Transparenz, Logging und Bedienung relevant. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
+          <t>KI: Ich verstehe diesen Parameter als Soll-Transportgeschwindigkeit des Etikettenbands. Im kontinuierlichen Lasermodus ist er die Druck-/Bandgeschwindigkeit; in allen getakteten Modi ist er die Vorzugsgeschwindigkeit zwischen den Druckpositionen. Der ESP nutzt ihn fuer Taktbewegungen und dynamische Nachregelung, der Raspi fuer Transparenz, Logging und Bedienung. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Der Parameter ist hier noch nicht vollständig korrekt beschrieben. IM Kontinuierlichen Lasermodus (nicht getakteter Betrieb) ist dies die Vorzugsgeschwindigkeit der Eteikette über den Etiekttenantrieb. In jedem anderen Modus ist dieser Parameter die Vorzugsgeschwindigkeit zwischen den Druckpositionen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="135" customHeight="1">
       <c r="A623" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47489,7 +47489,7 @@
       </c>
       <c r="H623" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I623" s="15" t="inlineStr">
@@ -47518,11 +47518,11 @@
       <c r="P623" s="24" t="n"/>
       <c r="Q623" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Rueckspulgeschwindigkeit fuer den Rueckspulbetrieb und fuer Ruecksetzbewegungen nach Fehlern bzw. Entnahmekontrolle. Dieser Wert ist prozesskritisch fuer den ESP, weil die Rueckspulung damit weich und reproduzierbar laufen soll. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
+          <t>KI: Ich verstehe diesen Parameter als Rueckspulgeschwindigkeit fuer den Rueckspulbetrieb und fuer Ruecksetzbewegungen nach Fehlern bzw. Entnahmekontrolle. Dieser Wert ist prozesskritisch fuer den ESP, weil die Rueckspulung damit weich und reproduzierbar laufen soll. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="135" customHeight="1">
       <c r="A624" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47560,7 +47560,7 @@
       </c>
       <c r="H624" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I624" s="15" t="inlineStr">
@@ -47589,11 +47589,11 @@
       <c r="P624" s="24" t="n"/>
       <c r="Q624" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Auswahl zwischen TTO und Laser. Es darf immer nur eines der beiden Drucksysteme fuehrend aktiv sein; davon haengen Triggerweg, Bypasslogik und die nachfolgenden Bewertungsbits im Label-Schieberegister ab. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="625" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Auswahl zwischen TTO und Laser. Es darf immer nur eines der beiden Drucksysteme fuehrend aktiv sein; davon haengen Triggerweg, Bypasslogik und die nachfolgenden Bewertungsbits im Label-Schieberegister ab. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="135" customHeight="1">
       <c r="A625" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47631,7 +47631,7 @@
       </c>
       <c r="H625" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I625" s="15" t="inlineStr">
@@ -47660,11 +47660,11 @@
       <c r="P625" s="24" t="n"/>
       <c r="Q625" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Material-Kontrollkamera. Diese Distanz ist ein fester Wegbezug im Label-Schieberegister, damit die Kamera fuer jedes bereits eingelesene Label an der richtigen Stelle getriggert wird. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="626" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Material-Kontrollkamera. Diese Distanz ist ein fester Wegbezug im Label-Schieberegister, damit die Kamera fuer jedes bereits eingelesene Label an der richtigen Stelle getriggert wird. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="135" customHeight="1">
       <c r="A626" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47702,7 +47702,7 @@
       </c>
       <c r="H626" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I626" s="31" t="inlineStr">
@@ -47731,11 +47731,11 @@
       <c r="P626" s="38" t="n"/>
       <c r="Q626" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Druckposition des Lasers. Nur wenn MAP0016 auf Laser steht und kein Bypass aktiv ist, darf der ESP an genau dieser Wegposition den Laser-Trigger ausloesen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="627" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Druckposition des Lasers. Nur wenn MAP0016 auf Laser steht und kein Bypass aktiv ist, darf der ESP an genau dieser Wegposition den Laser-Trigger ausloesen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627" ht="120" customHeight="1">
       <c r="A627" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47773,7 +47773,7 @@
       </c>
       <c r="H627" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I627" s="15" t="inlineStr">
@@ -47802,11 +47802,11 @@
       <c r="P627" s="24" t="n"/>
       <c r="Q627" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Druckposition des TTO. Nur wenn MAP0016 auf TTO steht und kein Bypass aktiv ist, darf der ESP an genau dieser Wegposition den TTO-Trigger ausloesen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="628" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur Druckposition des TTO. Nur wenn MAP0016 auf TTO steht und kein Bypass aktiv ist, darf der ESP an genau dieser Wegposition den TTO-Trigger ausloesen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="135" customHeight="1">
       <c r="A628" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47844,7 +47844,7 @@
       </c>
       <c r="H628" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I628" s="31" t="inlineStr">
@@ -47873,11 +47873,11 @@
       <c r="P628" s="38" t="n"/>
       <c r="Q628" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur OCR-/Verifizierungs-Kamera. Dieser Wegwert wird im Label-Schieberegister fuer den spaeteren OCR-Trigger und die Rueckmeldung von Verifizierung OK gebraucht. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="629" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur OCR-/Verifizierungs-Kamera. Dieser Wegwert wird im Label-Schieberegister fuer den spaeteren OCR-Trigger und die Rueckmeldung von Verifizierung OK gebraucht. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="120" customHeight="1">
       <c r="A629" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47915,7 +47915,7 @@
       </c>
       <c r="H629" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I629" s="15" t="inlineStr">
@@ -47944,11 +47944,11 @@
       <c r="P629" s="24" t="n"/>
       <c r="Q629" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zum Kontrollsensor am Tischende. Dort wird geprueft, ob ein gutes Label vorhanden bleiben durfte bzw. ein schlechtes Label entnommen wurde. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="630" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zum Kontrollsensor am Tischende. Dort wird geprueft, ob ein gutes Label vorhanden bleiben durfte bzw. ein schlechtes Label entnommen wurde. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="150" customHeight="1">
       <c r="A630" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47986,7 +47986,7 @@
       </c>
       <c r="H630" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I630" s="31" t="inlineStr">
@@ -48015,11 +48015,11 @@
       <c r="P630" s="38" t="n"/>
       <c r="Q630" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Rueckspuldistanz, wenn ein Label am Kontrollsensor haette entnommen sein muessen, aber noch erkannt wurde. Der ESP muss dann das Band kontrolliert zuruecksetzen, ohne bereits bearbeitete Labels im Schieberegister fachlich noch einmal neu zu behandeln. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
+          <t>KI: Ich verstehe diesen Parameter als Rueckspuldistanz, wenn ein Label am Kontrollsensor haette entnommen sein muessen, aber noch erkannt wurde. Der ESP muss dann das Band kontrolliert zuruecksetzen, ohne bereits bearbeitete Labels im Schieberegister fachlich noch einmal neu zu behandeln. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="105" customHeight="1">
       <c r="A631" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48057,7 +48057,7 @@
       </c>
       <c r="H631" s="29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I631" s="15" t="inlineStr">
@@ -48086,11 +48086,11 @@
       <c r="P631" s="24" t="n"/>
       <c r="Q631" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Abwickler in Prozent. Wenn MAS008 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende entstehen. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
+          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Abwickler in Prozent. Wenn MAS0008 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende entstehen. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="105" customHeight="1">
       <c r="A632" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48128,7 +48128,7 @@
       </c>
       <c r="H632" s="33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I632" s="31" t="inlineStr">
@@ -48157,11 +48157,11 @@
       <c r="P632" s="38" t="n"/>
       <c r="Q632" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Aufwickler in Prozent. Wenn MAS009 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende bzw. Rollenfuellstand entstehen. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="633" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Aufwickler in Prozent. Wenn MAS0009 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende bzw. Rollenfuellstand entstehen. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="135" customHeight="1">
       <c r="A633" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48232,7 +48232,7 @@
         </is>
       </c>
     </row>
-    <row r="634">
+    <row r="634" ht="90" customHeight="1">
       <c r="A634" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48270,7 +48270,7 @@
       </c>
       <c r="H634" s="33" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I634" s="31" t="inlineStr">
@@ -48299,11 +48299,11 @@
       <c r="P634" s="38" t="n"/>
       <c r="Q634" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0026 als MAP0026 Stopposition Spleissung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="635" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAP0026 als MAP0026 Stopposition Spleissung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635" ht="165" customHeight="1">
       <c r="A635" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48341,7 +48341,7 @@
       </c>
       <c r="H635" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I635" s="15" t="inlineStr">
@@ -48370,11 +48370,11 @@
       <c r="P635" s="24" t="n"/>
       <c r="Q635" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0027 als MAP0027 Grundstellung Portalachse X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="636" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse X. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle X-bezogenen Berechnungen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="165" customHeight="1">
       <c r="A636" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48412,7 +48412,7 @@
       </c>
       <c r="H636" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I636" s="15" t="inlineStr">
@@ -48441,11 +48441,11 @@
       <c r="P636" s="21" t="n"/>
       <c r="Q636" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0028 als MAP0028 Grundstellung Portalachse Z. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="637" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse Z. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle Z-bezogenen Berechnungen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="180" customHeight="1">
       <c r="A637" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48483,7 +48483,7 @@
       </c>
       <c r="H637" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I637" s="15" t="inlineStr">
@@ -48512,11 +48512,11 @@
       <c r="P637" s="24" t="n"/>
       <c r="Q637" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0029 als MAP0029 Grundstellung Positionierung Etikettensensor X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="638" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Etikettenerfassungs-Sensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638" ht="180" customHeight="1">
       <c r="A638" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48554,7 +48554,7 @@
       </c>
       <c r="H638" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I638" s="15" t="inlineStr">
@@ -48583,11 +48583,11 @@
       <c r="P638" s="21" t="n"/>
       <c r="Q638" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0030 als MAP0030 Grundstellung Positionierung Etikettenentnahmesensor X. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="639" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Entnahme-/Kontrollsensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="180" customHeight="1">
       <c r="A639" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48625,7 +48625,7 @@
       </c>
       <c r="H639" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I639" s="15" t="inlineStr">
@@ -48654,11 +48654,11 @@
       <c r="P639" s="24" t="n"/>
       <c r="Q639" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0031 als MAP0031 Grundstellung Positionierung Etikettenanschlag Einlauf. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="640" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Einlauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="180" customHeight="1">
       <c r="A640" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="H640" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I640" s="15" t="inlineStr">
@@ -48725,11 +48725,11 @@
       <c r="P640" s="21" t="n"/>
       <c r="Q640" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0032 als MAP0032 Grundstellung Positionierung Etikettenanschlag Auslauf. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="641" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Auslauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="180" customHeight="1">
       <c r="A641" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48767,7 +48767,7 @@
       </c>
       <c r="H641" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I641" s="15" t="inlineStr">
@@ -48796,11 +48796,11 @@
       <c r="P641" s="24" t="n"/>
       <c r="Q641" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0033 als MAP0033 Grundstellung Positionierung Material-Kontrollkamera. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="642" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Material-Kontrollkamera-Querachse. Die formatabhaengige Kameraposition wird relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="180" customHeight="1">
       <c r="A642" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48838,7 +48838,7 @@
       </c>
       <c r="H642" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I642" s="15" t="inlineStr">
@@ -48867,11 +48867,11 @@
       <c r="P642" s="21" t="n"/>
       <c r="Q642" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0034 als MAP0034 Grundstellung Positionierung Laserschutz. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Laser-Schutzblechs. Die Schutzblechachse bleibt parametrierbar, auch wenn der Laserprozess spaeter finalisiert wird. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643" ht="135" customHeight="1">
       <c r="A643" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48909,7 +48909,7 @@
       </c>
       <c r="H643" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I643" s="15" t="inlineStr">
@@ -48938,11 +48938,11 @@
       <c r="P643" s="24" t="n"/>
       <c r="Q643" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass fuer das aktive Drucksystem. Wenn er gesetzt ist, darf das jeweilige Drucksystem den Prozess nicht blockieren; die Druckbewertung im Labelregister muss dann fachlich als gebypasst behandelt werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
+          <t>KI: Ich verstehe diesen Parameter als Bypass fuer das aktive Drucksystem. Wenn er gesetzt ist, darf das jeweilige Drucksystem den Prozess nicht blockieren; die Druckbewertung im Labelregister muss dann fachlich als gebypasst behandelt werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644" ht="120" customHeight="1">
       <c r="A644" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48980,7 +48980,7 @@
       </c>
       <c r="H644" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I644" s="15" t="inlineStr">
@@ -49009,11 +49009,11 @@
       <c r="P644" s="21" t="n"/>
       <c r="Q644" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass der Material-Kontrollkamera. Wenn der Bypass aktiv ist, darf fehlendes Kamerafeedback nicht zu einem schlechten Material-OK-Bit fuehren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
+          <t>KI: Ich verstehe diesen Parameter als Bypass der Material-Kontrollkamera. Wenn der Bypass aktiv ist, darf fehlendes Kamerafeedback nicht zu einem schlechten Material-OK-Bit fuehren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="120" customHeight="1">
       <c r="A645" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49051,7 +49051,7 @@
       </c>
       <c r="H645" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I645" s="15" t="inlineStr">
@@ -49080,11 +49080,11 @@
       <c r="P645" s="24" t="n"/>
       <c r="Q645" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass der Verifizierungs-/OCR-Kamera. Wenn der Bypass aktiv ist, darf fehlendes OCR-Feedback das Label nicht als schlecht markieren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
+          <t>KI: Ich verstehe diesen Parameter als Bypass der Verifizierungs-/OCR-Kamera. Wenn der Bypass aktiv ist, darf fehlendes OCR-Feedback das Label nicht als schlecht markieren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646" ht="120" customHeight="1">
       <c r="A646" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49122,7 +49122,7 @@
       </c>
       <c r="H646" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I646" s="15" t="inlineStr">
@@ -49151,11 +49151,11 @@
       <c r="P646" s="24" t="n"/>
       <c r="Q646" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass fuer den Etiketten-Kontrollsensor am Auslauf. Wenn der Bypass aktiv ist, darf die Anlage fehlende Entnahmekontrolle nicht als Produktionsfehler werten. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
+          <t>KI: Ich verstehe diesen Parameter als Bypass fuer den Etiketten-Kontrollsensor am Auslauf. Wenn der Bypass aktiv ist, darf die Anlage fehlende Entnahmekontrolle nicht als Produktionsfehler werten. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647" ht="165" customHeight="1">
       <c r="A647" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49193,7 +49193,7 @@
       </c>
       <c r="H647" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I647" s="15" t="inlineStr">
@@ -49222,11 +49222,11 @@
       <c r="P647" s="24" t="n"/>
       <c r="Q647" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0039 als MAP0039 Rückspulung nach Produktionsstop. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="648" ht="30" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Freigabe fuer automatische Rueckspulung nach Produktionsstop. Wenn der Wert 1 ist, wird nach Produktionsstop und Rueckspul-Taster bis zum Ursprungspunkt zurueckgespult und erst danach die Produktion abgeschlossen; bei 0 gilt die Produktion ohne Rueckspulung als abgeschlossen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Ist dieser Wert 1, wird nach dem Produktionsstop automatisch (nach drücken des Rückspul-Tasters) die Etiektte an den Ursprungspunkt zurückgespult und erst dann wird die Produktion abgeschlossen. Ist der Wert 0, erfolgt keine Rückspulung und die Produktion gilt nach dem Produktionsstop als abgeschlossen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="105" customHeight="1">
       <c r="A648" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49264,7 +49264,7 @@
       </c>
       <c r="H648" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I648" s="15" t="inlineStr">
@@ -49293,11 +49293,11 @@
       <c r="P648" s="24" t="n"/>
       <c r="Q648" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0040 als MAP0040 Maximale Abweichung gemessene Labellänge. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
+          <t>KI: Ich verstehe MAP0040 als MAP0040 Maximale Abweichung gemessene Labellänge. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" ht="90" customHeight="1">
       <c r="A649" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49335,7 +49335,7 @@
       </c>
       <c r="H649" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I649" s="15" t="inlineStr">
@@ -49364,11 +49364,11 @@
       <c r="P649" s="24" t="n"/>
       <c r="Q649" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0041 als MAP0041 Triggerdauer Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
+          <t>KI: Ich verstehe MAP0041 als MAP0041 Triggerdauer Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="90" customHeight="1">
       <c r="A650" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49406,7 +49406,7 @@
       </c>
       <c r="H650" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I650" s="15" t="inlineStr">
@@ -49435,11 +49435,11 @@
       <c r="P650" s="24" t="n"/>
       <c r="Q650" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0042 als MAP0042 Triggerdauer TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
+          <t>KI: Ich verstehe MAP0042 als MAP0042 Triggerdauer TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="90" customHeight="1">
       <c r="A651" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49477,7 +49477,7 @@
       </c>
       <c r="H651" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I651" s="15" t="inlineStr">
@@ -49506,11 +49506,11 @@
       <c r="P651" s="24" t="n"/>
       <c r="Q651" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0043 als MAP0043 Material Kontrollkamera. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
+          <t>KI: Ich verstehe MAP0043 als MAP0043 Material Kontrollkamera. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="90" customHeight="1">
       <c r="A652" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49548,7 +49548,7 @@
       </c>
       <c r="H652" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I652" s="15" t="inlineStr">
@@ -49577,11 +49577,11 @@
       <c r="P652" s="24" t="n"/>
       <c r="Q652" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0044 als MAP0044 Triggerdauer Verifizierungs-Kamera. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
+          <t>KI: Ich verstehe MAP0044 als MAP0044 Triggerdauer Verifizierungs-Kamera. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: ms. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653" ht="90" customHeight="1">
       <c r="A653" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="H653" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I653" s="15" t="inlineStr">
@@ -49648,11 +49648,11 @@
       <c r="P653" s="21" t="n"/>
       <c r="Q653" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0045 als MAP0045 Entprellung Etikettenerfassungs-Sensor. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
+          <t>KI: Ich verstehe MAP0045 als MAP0045 Entprellung Etikettenerfassungs-Sensor. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="90" customHeight="1">
       <c r="A654" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49690,7 +49690,7 @@
       </c>
       <c r="H654" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I654" s="15" t="inlineStr">
@@ -49719,11 +49719,11 @@
       <c r="P654" s="23" t="n"/>
       <c r="Q654" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0046 als MAP0046 Entprellung Etikettenkontroll-Sensor. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
+          <t>KI: Ich verstehe MAP0046 als MAP0046 Entprellung Etikettenkontroll-Sensor. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655" ht="120" customHeight="1">
       <c r="A655" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49790,11 +49790,11 @@
       <c r="P655" s="41" t="n"/>
       <c r="Q655" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorgabe, ob innen- oder aussengewickeltes Material verarbeitet wird. Daraus ergeben sich die Drehrichtungen fuer Auf- und Abwickler; der ESP soll diesen Wert lesen und fuer die Wicklerlogik umsetzen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn nur lesen bzw. intern verwenden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
+          <t>KI: Ich verstehe diesen Parameter als Vorgabe, ob innen- oder aussengewickeltes Material verarbeitet wird. Daraus ergeben sich die Drehrichtungen fuer Auf- und Abwickler; der ESP soll diesen Wert lesen und fuer die Wicklerlogik umsetzen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" ht="90" customHeight="1">
       <c r="A656" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49832,7 +49832,7 @@
       </c>
       <c r="H656" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I656" s="15" t="inlineStr">
@@ -49861,11 +49861,11 @@
       <c r="P656" s="23" t="n"/>
       <c r="Q656" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0048 als MAP0048 IP Adresse Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
+          <t>KI: Ich verstehe MAP0048 als MAP0048 IP Adresse Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657" ht="90" customHeight="1">
       <c r="A657" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49903,7 +49903,7 @@
       </c>
       <c r="H657" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I657" s="15" t="inlineStr">
@@ -49932,11 +49932,11 @@
       <c r="P657" s="22" t="n"/>
       <c r="Q657" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0049 als MAP0049 Subnet Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
+          <t>KI: Ich verstehe MAP0049 als MAP0049 Subnet Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658" ht="90" customHeight="1">
       <c r="A658" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49974,7 +49974,7 @@
       </c>
       <c r="H658" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I658" s="15" t="inlineStr">
@@ -50003,11 +50003,11 @@
       <c r="P658" s="22" t="n"/>
       <c r="Q658" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0050 als MAP0050 Gateway Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="659" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAP0050 als MAP0050 Gateway Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: IP. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659" ht="90" customHeight="1">
       <c r="A659" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50045,7 +50045,7 @@
       </c>
       <c r="H659" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I659" s="15" t="inlineStr">
@@ -50074,11 +50074,11 @@
       <c r="P659" s="22" t="n"/>
       <c r="Q659" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0051 als MAP0051 Kommunikationsport Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
+          <t>KI: Ich verstehe MAP0051 als MAP0051 Kommunikationsport Produktionsanlage. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660" ht="90" customHeight="1">
       <c r="A660" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="H660" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I660" s="15" t="inlineStr">
@@ -50145,11 +50145,11 @@
       <c r="P660" s="22" t="n"/>
       <c r="Q660" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0052 als MAP0052 Druckdaten Port TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
+          <t>KI: Ich verstehe MAP0052 als MAP0052 Druckdaten Port TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661" ht="90" customHeight="1">
       <c r="A661" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50187,7 +50187,7 @@
       </c>
       <c r="H661" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I661" s="15" t="inlineStr">
@@ -50216,11 +50216,11 @@
       <c r="P661" s="22" t="n"/>
       <c r="Q661" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0053 als MAP0053 Webinterface Port TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
+          <t>KI: Ich verstehe MAP0053 als MAP0053 Webinterface Port TTO. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662" ht="90" customHeight="1">
       <c r="A662" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50258,7 +50258,7 @@
       </c>
       <c r="H662" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I662" s="15" t="inlineStr">
@@ -50287,11 +50287,11 @@
       <c r="P662" s="22" t="n"/>
       <c r="Q662" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0054 als MAP0054 Druckdaten Port Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
+          <t>KI: Ich verstehe MAP0054 als MAP0054 Druckdaten Port Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663" ht="90" customHeight="1">
       <c r="A663" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50329,7 +50329,7 @@
       </c>
       <c r="H663" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I663" s="15" t="inlineStr">
@@ -50358,11 +50358,11 @@
       <c r="P663" s="22" t="n"/>
       <c r="Q663" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAP0055 als MAP0055 Webinterface Port Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
+          <t>KI: Ich verstehe MAP0055 als MAP0055 Webinterface Port Laser. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Port. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664" ht="120" customHeight="1">
       <c r="A664" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50417,7 +50417,7 @@
       </c>
       <c r="M664" s="22" t="inlineStr">
         <is>
-          <t>Soll-Position Portalachse X (Querrichtung)</t>
+          <t>Soll-Position Portalachse X (Horizonal, Quer zur Etiekttenlaufrichtung)</t>
         </is>
       </c>
       <c r="N664" s="22" t="n"/>
@@ -50429,7 +50429,7 @@
         </is>
       </c>
     </row>
-    <row r="665">
+    <row r="665" ht="120" customHeight="1">
       <c r="A665" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50484,7 +50484,7 @@
       </c>
       <c r="M665" s="22" t="inlineStr">
         <is>
-          <t>Soll- Position Portalachse Z (Längsrichtung)</t>
+          <t>Soll- Position Portalachse Z (Vertikale Richtung)</t>
         </is>
       </c>
       <c r="N665" s="22" t="n"/>
@@ -50496,7 +50496,7 @@
         </is>
       </c>
     </row>
-    <row r="666">
+    <row r="666" ht="135" customHeight="1">
       <c r="A666" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50565,7 +50565,7 @@
         </is>
       </c>
     </row>
-    <row r="667">
+    <row r="667" ht="135" customHeight="1">
       <c r="A667" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50632,7 +50632,7 @@
         </is>
       </c>
     </row>
-    <row r="668" ht="30" customHeight="1">
+    <row r="668" ht="120" customHeight="1">
       <c r="A668" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50699,7 +50699,7 @@
         </is>
       </c>
     </row>
-    <row r="669">
+    <row r="669" ht="120" customHeight="1">
       <c r="A669" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50766,7 +50766,7 @@
         </is>
       </c>
     </row>
-    <row r="670" ht="30" customHeight="1">
+    <row r="670" ht="120" customHeight="1">
       <c r="A670" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50833,7 +50833,7 @@
         </is>
       </c>
     </row>
-    <row r="671" ht="30" customHeight="1">
+    <row r="671" ht="120" customHeight="1">
       <c r="A671" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50900,7 +50900,7 @@
         </is>
       </c>
     </row>
-    <row r="672" ht="30" customHeight="1">
+    <row r="672" ht="120" customHeight="1">
       <c r="A672" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50967,7 +50967,7 @@
         </is>
       </c>
     </row>
-    <row r="673">
+    <row r="673" hidden="1">
       <c r="A673" s="15" t="n"/>
       <c r="B673" s="22" t="n"/>
       <c r="C673" s="3" t="n"/>
@@ -51060,11 +51060,11 @@
       <c r="P674" s="22" t="n"/>
       <c r="Q674" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bitmaske fuer die Freigabe der Maschinen-Tasten je nach Microtom-Benutzerlevel. Der Raspi nutzt diese Bitmaske, um Tastereingaben zu erlauben oder zu sperren und um die zugehoerigen Taster-LEDs nur dann zu signalisieren, wenn die Bedienhandlung fachlich und rechtebezogen erlaubt ist. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn nur lesen bzw. intern verwenden. Einheit bzw. Wertebereich laut Tabelle: Button - Access. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
+          <t>KI: Ich verstehe diesen Parameter als Bitmaske fuer die Freigabe der Maschinen-Tasten je nach Microtom-Benutzerlevel. Der Raspi nutzt diese Bitmaske, um Tastereingaben zu erlauben oder zu sperren und um die zugehoerigen Taster-LEDs nur dann zu signalisieren, wenn die Bedienhandlung fachlich und rechtebezogen erlaubt ist. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: Button - Access. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675" ht="135" customHeight="1">
       <c r="A675" s="10" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -51087,7 +51087,7 @@
       </c>
       <c r="E675" s="12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F675" s="29" t="inlineStr">
@@ -51102,7 +51102,7 @@
       </c>
       <c r="H675" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I675" s="29" t="inlineStr">
@@ -51131,14 +51131,14 @@
       <c r="P675" s="28" t="n"/>
       <c r="Q675" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur ersten LED des 1-m-LED-Streifens. Der ESP braucht diesen Wegbezug, um den Labelstatus entlang des Streifens korrekt anzuzeigen; der exakte Default muss spaeter an der realen Maschine verifiziert werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur ersten LED des 1-m-LED-Streifens. Der aktuelle Default 8000 entspricht 800.0 mm. Der ESP braucht diesen Wegbezug, um den Labelstatus entlang des Streifens korrekt anzuzeigen; der exakte Wert muss bei der realen Inbetriebnahme mechanisch verifiziert werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="R675" s="4" t="n"/>
       <c r="S675" s="4" t="n"/>
       <c r="T675" s="4" t="n"/>
     </row>
-    <row r="676" ht="345" customHeight="1">
+    <row r="676" hidden="1" ht="345" customHeight="1">
       <c r="A676" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51225,7 +51225,7 @@
         </is>
       </c>
     </row>
-    <row r="677" ht="150" customHeight="1">
+    <row r="677" hidden="1" ht="150" customHeight="1">
       <c r="A677" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
     </row>
-    <row r="678" ht="120" customHeight="1">
+    <row r="678" hidden="1" ht="120" customHeight="1">
       <c r="A678" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51371,7 +51371,7 @@
         </is>
       </c>
     </row>
-    <row r="679">
+    <row r="679" hidden="1" ht="90" customHeight="1">
       <c r="A679" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51438,7 +51438,7 @@
         </is>
       </c>
     </row>
-    <row r="680">
+    <row r="680" hidden="1" ht="90" customHeight="1">
       <c r="A680" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51505,7 +51505,7 @@
         </is>
       </c>
     </row>
-    <row r="681">
+    <row r="681" hidden="1" ht="90" customHeight="1">
       <c r="A681" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51572,7 +51572,7 @@
         </is>
       </c>
     </row>
-    <row r="682">
+    <row r="682" hidden="1" ht="90" customHeight="1">
       <c r="A682" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51639,7 +51639,7 @@
         </is>
       </c>
     </row>
-    <row r="683">
+    <row r="683" hidden="1" ht="90" customHeight="1">
       <c r="A683" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51706,7 +51706,7 @@
         </is>
       </c>
     </row>
-    <row r="684">
+    <row r="684" hidden="1" ht="90" customHeight="1">
       <c r="A684" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51773,7 +51773,7 @@
         </is>
       </c>
     </row>
-    <row r="685" ht="30" customHeight="1">
+    <row r="685" hidden="1" ht="30" customHeight="1">
       <c r="A685" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51840,7 +51840,7 @@
         </is>
       </c>
     </row>
-    <row r="686">
+    <row r="686" hidden="1" ht="90" customHeight="1">
       <c r="A686" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51907,7 +51907,7 @@
         </is>
       </c>
     </row>
-    <row r="687">
+    <row r="687" hidden="1" ht="90" customHeight="1">
       <c r="A687" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51974,7 +51974,7 @@
         </is>
       </c>
     </row>
-    <row r="688">
+    <row r="688" hidden="1" ht="90" customHeight="1">
       <c r="A688" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52041,7 +52041,7 @@
         </is>
       </c>
     </row>
-    <row r="689" ht="30" customHeight="1">
+    <row r="689" hidden="1" ht="30" customHeight="1">
       <c r="A689" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52108,7 +52108,7 @@
         </is>
       </c>
     </row>
-    <row r="690" ht="30" customHeight="1">
+    <row r="690" hidden="1" ht="30" customHeight="1">
       <c r="A690" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52175,7 +52175,7 @@
         </is>
       </c>
     </row>
-    <row r="691" ht="30" customHeight="1">
+    <row r="691" hidden="1" ht="30" customHeight="1">
       <c r="A691" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52242,7 +52242,7 @@
         </is>
       </c>
     </row>
-    <row r="692" ht="30" customHeight="1">
+    <row r="692" hidden="1" ht="30" customHeight="1">
       <c r="A692" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52309,7 +52309,7 @@
         </is>
       </c>
     </row>
-    <row r="693">
+    <row r="693" hidden="1" ht="90" customHeight="1">
       <c r="A693" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
     </row>
-    <row r="694">
+    <row r="694" hidden="1" ht="90" customHeight="1">
       <c r="A694" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52441,7 +52441,7 @@
         </is>
       </c>
     </row>
-    <row r="695">
+    <row r="695" hidden="1" ht="90" customHeight="1">
       <c r="A695" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52506,7 +52506,7 @@
         </is>
       </c>
     </row>
-    <row r="696">
+    <row r="696" hidden="1" ht="90" customHeight="1">
       <c r="A696" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
     </row>
-    <row r="697" ht="409.5" customHeight="1">
+    <row r="697" hidden="1" ht="409.5" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52670,7 +52670,7 @@
         </is>
       </c>
     </row>
-    <row r="698" ht="409.5" customHeight="1">
+    <row r="698" hidden="1" ht="409.5" customHeight="1">
       <c r="A698" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52768,7 +52768,7 @@
         </is>
       </c>
     </row>
-    <row r="699" ht="409.5" customHeight="1">
+    <row r="699" hidden="1" ht="409.5" customHeight="1">
       <c r="A699" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52867,7 +52867,7 @@
         </is>
       </c>
     </row>
-    <row r="700" ht="409.5" customHeight="1">
+    <row r="700" hidden="1" ht="409.5" customHeight="1">
       <c r="A700" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52966,7 +52966,7 @@
         </is>
       </c>
     </row>
-    <row r="701" ht="105" customHeight="1">
+    <row r="701" hidden="1" ht="105" customHeight="1">
       <c r="A701" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53039,7 +53039,7 @@
         </is>
       </c>
     </row>
-    <row r="702" ht="90" customHeight="1">
+    <row r="702" hidden="1" ht="90" customHeight="1">
       <c r="A702" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53111,7 +53111,7 @@
         </is>
       </c>
     </row>
-    <row r="703">
+    <row r="703" hidden="1" ht="135" customHeight="1">
       <c r="A703" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53178,7 +53178,7 @@
         </is>
       </c>
     </row>
-    <row r="704" ht="60" customHeight="1">
+    <row r="704" hidden="1" ht="60" customHeight="1">
       <c r="A704" s="29" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53244,7 +53244,7 @@
       <c r="S704" s="4" t="n"/>
       <c r="T704" s="4" t="n"/>
     </row>
-    <row r="705" ht="60" customHeight="1">
+    <row r="705" hidden="1" ht="60" customHeight="1">
       <c r="A705" s="29" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53313,7 +53313,7 @@
       <c r="S705" s="4" t="n"/>
       <c r="T705" s="4" t="n"/>
     </row>
-    <row r="706">
+    <row r="706" hidden="1" ht="90" customHeight="1">
       <c r="A706" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53382,7 +53382,7 @@
         </is>
       </c>
     </row>
-    <row r="707">
+    <row r="707" hidden="1" ht="90" customHeight="1">
       <c r="A707" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53449,7 +53449,7 @@
         </is>
       </c>
     </row>
-    <row r="708">
+    <row r="708" hidden="1">
       <c r="A708" s="15" t="n"/>
       <c r="B708" s="22" t="n"/>
       <c r="C708" s="3" t="n"/>
@@ -53472,7 +53472,7 @@
       <c r="P708" s="22" t="n"/>
       <c r="Q708" s="22" t="n"/>
     </row>
-    <row r="709" ht="30" customHeight="1">
+    <row r="709" hidden="1" ht="30" customHeight="1">
       <c r="A709" s="15" t="inlineStr">
         <is>
           <t>MAW</t>
@@ -53539,7 +53539,7 @@
         </is>
       </c>
     </row>
-    <row r="710" ht="30" customHeight="1">
+    <row r="710" hidden="1" ht="30" customHeight="1">
       <c r="A710" s="15" t="inlineStr">
         <is>
           <t>MAW</t>
@@ -53606,7 +53606,7 @@
         </is>
       </c>
     </row>
-    <row r="711">
+    <row r="711" hidden="1">
       <c r="A711" s="15" t="n"/>
       <c r="B711" s="8" t="n"/>
       <c r="C711" s="3" t="n"/>
@@ -53629,7 +53629,7 @@
       <c r="P711" s="22" t="n"/>
       <c r="Q711" s="22" t="n"/>
     </row>
-    <row r="712">
+    <row r="712" hidden="1">
       <c r="A712" s="15" t="n"/>
       <c r="B712" s="8" t="n"/>
       <c r="C712" s="3" t="n"/>
@@ -53652,7 +53652,7 @@
       <c r="P712" s="22" t="n"/>
       <c r="Q712" s="22" t="n"/>
     </row>
-    <row r="713" ht="45" customHeight="1">
+    <row r="713" hidden="1" ht="45" customHeight="1">
       <c r="A713" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -53728,7 +53728,7 @@
         </is>
       </c>
     </row>
-    <row r="714" ht="30" customHeight="1">
+    <row r="714" hidden="1" ht="30" customHeight="1">
       <c r="A714" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -53803,7 +53803,7 @@
         </is>
       </c>
     </row>
-    <row r="715">
+    <row r="715" hidden="1" ht="90" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -53878,7 +53878,7 @@
         </is>
       </c>
     </row>
-    <row r="716" ht="45" customHeight="1">
+    <row r="716" hidden="1" ht="45" customHeight="1">
       <c r="A716" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -53953,7 +53953,7 @@
         </is>
       </c>
     </row>
-    <row r="717" ht="45" customHeight="1">
+    <row r="717" hidden="1" ht="45" customHeight="1">
       <c r="A717" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54028,7 +54028,7 @@
         </is>
       </c>
     </row>
-    <row r="718" ht="45" customHeight="1">
+    <row r="718" hidden="1" ht="45" customHeight="1">
       <c r="A718" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54103,7 +54103,7 @@
         </is>
       </c>
     </row>
-    <row r="719" ht="45" customHeight="1">
+    <row r="719" hidden="1" ht="45" customHeight="1">
       <c r="A719" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54178,7 +54178,7 @@
         </is>
       </c>
     </row>
-    <row r="720" ht="45" customHeight="1">
+    <row r="720" hidden="1" ht="45" customHeight="1">
       <c r="A720" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54253,7 +54253,7 @@
         </is>
       </c>
     </row>
-    <row r="721" ht="45" customHeight="1">
+    <row r="721" hidden="1" ht="45" customHeight="1">
       <c r="A721" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54328,7 +54328,7 @@
         </is>
       </c>
     </row>
-    <row r="722" ht="45" customHeight="1">
+    <row r="722" hidden="1" ht="45" customHeight="1">
       <c r="A722" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54403,7 +54403,7 @@
         </is>
       </c>
     </row>
-    <row r="723">
+    <row r="723" hidden="1" ht="90" customHeight="1">
       <c r="A723" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54478,7 +54478,7 @@
         </is>
       </c>
     </row>
-    <row r="724">
+    <row r="724" hidden="1" ht="90" customHeight="1">
       <c r="A724" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54553,7 +54553,7 @@
         </is>
       </c>
     </row>
-    <row r="725">
+    <row r="725" hidden="1" ht="90" customHeight="1">
       <c r="A725" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
     </row>
-    <row r="726">
+    <row r="726" hidden="1" ht="90" customHeight="1">
       <c r="A726" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54703,7 +54703,7 @@
         </is>
       </c>
     </row>
-    <row r="727" ht="30" customHeight="1">
+    <row r="727" hidden="1" ht="30" customHeight="1">
       <c r="A727" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54778,7 +54778,7 @@
         </is>
       </c>
     </row>
-    <row r="728">
+    <row r="728" hidden="1" ht="90" customHeight="1">
       <c r="A728" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54853,7 +54853,7 @@
         </is>
       </c>
     </row>
-    <row r="729">
+    <row r="729" hidden="1" ht="90" customHeight="1">
       <c r="A729" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54928,7 +54928,7 @@
         </is>
       </c>
     </row>
-    <row r="730" ht="45" customHeight="1">
+    <row r="730" hidden="1" ht="45" customHeight="1">
       <c r="A730" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55003,7 +55003,7 @@
         </is>
       </c>
     </row>
-    <row r="731">
+    <row r="731" hidden="1" ht="90" customHeight="1">
       <c r="A731" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55078,7 +55078,7 @@
         </is>
       </c>
     </row>
-    <row r="732">
+    <row r="732" hidden="1" ht="90" customHeight="1">
       <c r="A732" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55153,7 +55153,7 @@
         </is>
       </c>
     </row>
-    <row r="733" ht="30" customHeight="1">
+    <row r="733" hidden="1" ht="30" customHeight="1">
       <c r="A733" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55228,7 +55228,7 @@
         </is>
       </c>
     </row>
-    <row r="734" ht="30" customHeight="1">
+    <row r="734" hidden="1" ht="30" customHeight="1">
       <c r="A734" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55303,7 +55303,7 @@
         </is>
       </c>
     </row>
-    <row r="735" ht="45" customHeight="1">
+    <row r="735" hidden="1" ht="45" customHeight="1">
       <c r="A735" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55379,7 +55379,7 @@
         </is>
       </c>
     </row>
-    <row r="736">
+    <row r="736" hidden="1" ht="90" customHeight="1">
       <c r="A736" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55454,7 +55454,7 @@
         </is>
       </c>
     </row>
-    <row r="737">
+    <row r="737" hidden="1" ht="90" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55529,7 +55529,7 @@
         </is>
       </c>
     </row>
-    <row r="738">
+    <row r="738" hidden="1" ht="90" customHeight="1">
       <c r="A738" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55604,7 +55604,7 @@
         </is>
       </c>
     </row>
-    <row r="739" ht="30" customHeight="1">
+    <row r="739" hidden="1" ht="30" customHeight="1">
       <c r="A739" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55680,7 +55680,7 @@
         </is>
       </c>
     </row>
-    <row r="740" ht="30" customHeight="1">
+    <row r="740" hidden="1" ht="30" customHeight="1">
       <c r="A740" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55751,11 +55751,11 @@
       </c>
       <c r="Q740" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0028 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0028 Störung Abwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
+          <t>KI: Ich verstehe MAE0028 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0028 Störung Abwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741" hidden="1" ht="75" customHeight="1">
       <c r="A741" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55826,11 +55826,11 @@
       </c>
       <c r="Q741" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0029 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0029 Störung Abwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="742" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAE0029 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0029 Störung Abwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" hidden="1" ht="30" customHeight="1">
       <c r="A742" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55901,11 +55901,11 @@
       </c>
       <c r="Q742" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0030 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0030 Störung Abwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="743" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAE0030 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0030 Störung Abwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" hidden="1" ht="30" customHeight="1">
       <c r="A743" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55976,11 +55976,11 @@
       </c>
       <c r="Q743" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0032 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0032 Störung Aufwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
+          <t>KI: Ich verstehe MAE0032 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0032 Störung Aufwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" hidden="1" ht="75" customHeight="1">
       <c r="A744" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56051,11 +56051,11 @@
       </c>
       <c r="Q744" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0033 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0033 Störung Aufwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="745" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAE0033 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0033 Störung Aufwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" hidden="1" ht="30" customHeight="1">
       <c r="A745" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56126,11 +56126,11 @@
       </c>
       <c r="Q745" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0034 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0034 Störung Aufwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn nur lesen bzw. intern verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="746" ht="30" customHeight="1">
+          <t>KI: Ich verstehe MAE0034 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0034 Störung Aufwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" hidden="1" ht="30" customHeight="1">
       <c r="A746" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56205,7 +56205,7 @@
         </is>
       </c>
     </row>
-    <row r="747" ht="30" customHeight="1">
+    <row r="747" hidden="1" ht="30" customHeight="1">
       <c r="A747" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56280,7 +56280,7 @@
         </is>
       </c>
     </row>
-    <row r="748">
+    <row r="748" hidden="1" ht="90" customHeight="1">
       <c r="A748" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56351,7 +56351,7 @@
         </is>
       </c>
     </row>
-    <row r="749">
+    <row r="749" hidden="1" ht="90" customHeight="1">
       <c r="A749" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56422,7 +56422,7 @@
         </is>
       </c>
     </row>
-    <row r="750">
+    <row r="750" hidden="1" ht="90" customHeight="1">
       <c r="A750" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56493,7 +56493,7 @@
         </is>
       </c>
     </row>
-    <row r="751">
+    <row r="751" hidden="1" ht="90" customHeight="1">
       <c r="A751" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56564,7 +56564,7 @@
         </is>
       </c>
     </row>
-    <row r="752">
+    <row r="752" hidden="1" ht="90" customHeight="1">
       <c r="A752" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56635,7 +56635,7 @@
         </is>
       </c>
     </row>
-    <row r="753" ht="30" customHeight="1">
+    <row r="753" hidden="1" ht="30" customHeight="1">
       <c r="A753" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56710,7 +56710,7 @@
         </is>
       </c>
     </row>
-    <row r="754">
+    <row r="754" hidden="1" ht="90" customHeight="1">
       <c r="A754" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56781,7 +56781,7 @@
         </is>
       </c>
     </row>
-    <row r="755" ht="30" customHeight="1">
+    <row r="755" hidden="1" ht="30" customHeight="1">
       <c r="A755" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56856,7 +56856,7 @@
         </is>
       </c>
     </row>
-    <row r="756" ht="45" customHeight="1">
+    <row r="756" hidden="1" ht="45" customHeight="1">
       <c r="A756" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56931,7 +56931,7 @@
         </is>
       </c>
     </row>
-    <row r="757" ht="45" customHeight="1">
+    <row r="757" hidden="1" ht="45" customHeight="1">
       <c r="A757" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57006,7 +57006,7 @@
         </is>
       </c>
     </row>
-    <row r="758">
+    <row r="758" hidden="1">
       <c r="A758" s="10" t="n"/>
       <c r="B758" s="8" t="n"/>
       <c r="C758" s="43" t="n"/>
@@ -57025,7 +57025,7 @@
       <c r="P758" s="22" t="n"/>
       <c r="Q758" s="22" t="n"/>
     </row>
-    <row r="759">
+    <row r="759" hidden="1">
       <c r="A759" s="10" t="n"/>
       <c r="B759" s="8" t="n"/>
       <c r="C759" s="43" t="n"/>
@@ -57044,7 +57044,7 @@
       <c r="P759" s="22" t="n"/>
       <c r="Q759" s="22" t="n"/>
     </row>
-    <row r="760">
+    <row r="760" hidden="1">
       <c r="A760" s="10" t="n"/>
       <c r="B760" s="8" t="n"/>
       <c r="C760" s="43" t="n"/>
@@ -57063,7 +57063,7 @@
       <c r="P760" s="22" t="n"/>
       <c r="Q760" s="22" t="n"/>
     </row>
-    <row r="761">
+    <row r="761" hidden="1">
       <c r="A761" s="10" t="n"/>
       <c r="B761" s="8" t="n"/>
       <c r="C761" s="43" t="n"/>
@@ -57082,7 +57082,7 @@
       <c r="P761" s="22" t="n"/>
       <c r="Q761" s="22" t="n"/>
     </row>
-    <row r="762">
+    <row r="762" hidden="1">
       <c r="A762" s="10" t="n"/>
       <c r="B762" s="8" t="n"/>
       <c r="C762" s="43" t="n"/>
@@ -57101,7 +57101,7 @@
       <c r="P762" s="22" t="n"/>
       <c r="Q762" s="22" t="n"/>
     </row>
-    <row r="763">
+    <row r="763" hidden="1">
       <c r="A763" s="10" t="n"/>
       <c r="B763" s="8" t="n"/>
       <c r="C763" s="43" t="n"/>
@@ -57120,7 +57120,7 @@
       <c r="P763" s="22" t="n"/>
       <c r="Q763" s="22" t="n"/>
     </row>
-    <row r="764">
+    <row r="764" hidden="1">
       <c r="A764" s="10" t="n"/>
       <c r="B764" s="8" t="n"/>
       <c r="C764" s="43" t="n"/>
@@ -57139,7 +57139,7 @@
       <c r="P764" s="22" t="n"/>
       <c r="Q764" s="22" t="n"/>
     </row>
-    <row r="765">
+    <row r="765" hidden="1">
       <c r="A765" s="10" t="n"/>
       <c r="B765" s="8" t="n"/>
       <c r="C765" s="43" t="n"/>
@@ -57158,7 +57158,7 @@
       <c r="P765" s="22" t="n"/>
       <c r="Q765" s="22" t="n"/>
     </row>
-    <row r="766">
+    <row r="766" hidden="1">
       <c r="A766" s="10" t="n"/>
       <c r="B766" s="8" t="n"/>
       <c r="C766" s="43" t="n"/>
@@ -57177,7 +57177,7 @@
       <c r="P766" s="22" t="n"/>
       <c r="Q766" s="22" t="n"/>
     </row>
-    <row r="767">
+    <row r="767" hidden="1">
       <c r="A767" s="10" t="n"/>
       <c r="B767" s="8" t="n"/>
       <c r="C767" s="43" t="n"/>
@@ -57196,7 +57196,7 @@
       <c r="P767" s="22" t="n"/>
       <c r="Q767" s="22" t="n"/>
     </row>
-    <row r="768">
+    <row r="768" hidden="1">
       <c r="A768" s="10" t="n"/>
       <c r="B768" s="8" t="n"/>
       <c r="C768" s="43" t="n"/>
@@ -57215,7 +57215,7 @@
       <c r="P768" s="22" t="n"/>
       <c r="Q768" s="22" t="n"/>
     </row>
-    <row r="769">
+    <row r="769" hidden="1">
       <c r="A769" s="10" t="n"/>
       <c r="B769" s="8" t="n"/>
       <c r="C769" s="43" t="n"/>
@@ -57234,7 +57234,7 @@
       <c r="P769" s="22" t="n"/>
       <c r="Q769" s="22" t="n"/>
     </row>
-    <row r="770">
+    <row r="770" hidden="1">
       <c r="A770" s="10" t="n"/>
       <c r="B770" s="8" t="n"/>
       <c r="C770" s="43" t="n"/>
@@ -57253,7 +57253,7 @@
       <c r="P770" s="22" t="n"/>
       <c r="Q770" s="22" t="n"/>
     </row>
-    <row r="771">
+    <row r="771" hidden="1">
       <c r="A771" s="10" t="n"/>
       <c r="B771" s="8" t="n"/>
       <c r="C771" s="43" t="n"/>
@@ -57272,7 +57272,7 @@
       <c r="P771" s="22" t="n"/>
       <c r="Q771" s="22" t="n"/>
     </row>
-    <row r="772">
+    <row r="772" hidden="1">
       <c r="A772" s="10" t="n"/>
       <c r="B772" s="8" t="n"/>
       <c r="C772" s="43" t="n"/>
@@ -57291,7 +57291,7 @@
       <c r="P772" s="22" t="n"/>
       <c r="Q772" s="22" t="n"/>
     </row>
-    <row r="773">
+    <row r="773" hidden="1">
       <c r="A773" s="10" t="n"/>
       <c r="B773" s="8" t="n"/>
       <c r="C773" s="43" t="n"/>
@@ -57310,7 +57310,7 @@
       <c r="P773" s="22" t="n"/>
       <c r="Q773" s="22" t="n"/>
     </row>
-    <row r="774">
+    <row r="774" hidden="1">
       <c r="A774" s="10" t="n"/>
       <c r="B774" s="8" t="n"/>
       <c r="C774" s="43" t="n"/>
@@ -57329,7 +57329,7 @@
       <c r="P774" s="22" t="n"/>
       <c r="Q774" s="22" t="n"/>
     </row>
-    <row r="775">
+    <row r="775" hidden="1">
       <c r="A775" s="10" t="n"/>
       <c r="B775" s="8" t="n"/>
       <c r="C775" s="43" t="n"/>
@@ -57348,7 +57348,7 @@
       <c r="P775" s="22" t="n"/>
       <c r="Q775" s="22" t="n"/>
     </row>
-    <row r="776">
+    <row r="776" hidden="1">
       <c r="A776" s="10" t="n"/>
       <c r="B776" s="8" t="n"/>
       <c r="C776" s="43" t="n"/>
@@ -57367,7 +57367,7 @@
       <c r="P776" s="22" t="n"/>
       <c r="Q776" s="22" t="n"/>
     </row>
-    <row r="777">
+    <row r="777" hidden="1">
       <c r="A777" s="10" t="n"/>
       <c r="B777" s="8" t="n"/>
       <c r="C777" s="43" t="n"/>
@@ -57386,7 +57386,7 @@
       <c r="P777" s="22" t="n"/>
       <c r="Q777" s="22" t="n"/>
     </row>
-    <row r="778">
+    <row r="778" hidden="1">
       <c r="A778" s="10" t="n"/>
       <c r="B778" s="8" t="n"/>
       <c r="C778" s="43" t="n"/>
@@ -57406,7 +57406,7 @@
       <c r="Q778" s="22" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation sqref="L1:L1048576 O2:O119" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -57420,296 +57420,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B0F64AD-B99C-4871-926C-E219C34FB48E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B68565-0F38-4DCC-BE22-5ECD6C59FC6A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B32450-7DE8-42CF-8C5E-3C247F3FAE57}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -57420,4 +57420,296 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD8B92E4-A62E-4C3D-ABB7-B1C8056BB11B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EEC841-3638-4C83-A17D-B41FFD8905C4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37AD3F2D-24B3-4F2A-92A9-16CAFF700971}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -46457,7 +46457,7 @@
       <c r="S608" s="4" t="n"/>
       <c r="T608" s="4" t="n"/>
     </row>
-    <row r="609" ht="180" customHeight="1">
+    <row r="609" ht="270" customHeight="1">
       <c r="A609" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46524,11 +46524,11 @@
       <c r="P609" s="24" t="n"/>
       <c r="Q609" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Etiketten- bzw. Traegerbandbreite in 1/10 mm. Der Wert definiert zugleich die Sollposition der beiden Etikettenanschlaege: der rechte Nullpunkt liegt von oben gesehen an der rechten Bandkante, daher entspricht 20.0 mm dem Sollwert 200 und 55.0 mm dem Sollwert 550 fuer Einlauf- und Auslaufanschlag. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Der Wert definiert auch wo die beiden Etiekttenanschläge positioniert werden. Stelle Dir vor dass die Etikette von oben gesehen im Produktionsbetrieb von unten nach oben läuft und dass der 0-Punkt der Bahn auf der das Etikettenträgerband läuft ganz rechts ist. Wenn eine 20mm breite Etikette hier im format angegeben wird, müssen die beiden anschläge auf 200 (20mm) fahren, bei einer 55mm Etikette auf 550 usw.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="610" ht="150" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Etiketten- bzw. Traegerbandbreite in 1/10 mm. Der Wert definiert zugleich die Sollposition der beiden Etikettenanschlaege: der rechte Nullpunkt liegt von oben gesehen an der rechten Bandkante, daher entspricht 20.0 mm dem Sollwert 200 und 55.0 mm dem Sollwert 550 fuer Einlauf- und Auslaufanschlag. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="225" customHeight="1">
       <c r="A610" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46595,11 +46595,11 @@
       <c r="P610" s="38" t="n"/>
       <c r="Q610" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Soll-Etikettenlaenge ohne Gap in 1/10 mm. Der ESP muss die real gemessene Etikettenlaenge mit MAP0040 vergleichen; bei zu kurzer Laenge wird MAE0025 gesetzt, bei zu langer Laenge MAE0026. Der Raspi behandelt diese beiden Fehler als Produktionspause statt als Purge/Not-Stop. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Etikettenlänge wird für die Erfassungs/Sensorüberwachung der Etiekttenlänge verwendet. Der Parameter hängt zusammen mit MAP0040. Weicht die gemessene Länge im System mehr als MAP0040 nach oben/unten ab, wird ein entsprechender Fehler ausgelöst und die Produktion pausiert.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="611" ht="210" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Soll-Etikettenlaenge ohne Gap in 1/10 mm. Der ESP muss die real gemessene Etikettenlaenge mit MAP0040 vergleichen; bei zu kurzer Laenge wird MAE0025 gesetzt, bei zu langer Laenge MAE0026. Der Raspi behandelt diese beiden Fehler als Produktionspause statt als Purge/Not-Stop. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="285" customHeight="1">
       <c r="A611" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46666,11 +46666,11 @@
       <c r="P611" s="24" t="n"/>
       <c r="Q611" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Druckposition in X-/Querrichtung auf dem Etikett. Fuer die Portalachse X gilt eine Umkehrlogik: ein positiver Druckpositionswert verschiebt den Tisch in negative X-Richtung, ein negativer Wert in positive X-Richtung. Die zusaetzliche Korrektur MAP0005 wird vorher auf den Druckpositionswert addiert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dies ist die Druckposition auf der Etikette in Querrichtung (wieder von oben gesehen rechts)ist der 0-Punkt. Das hat in der Steuerung folgende Funktion: Je nachdem welcher drucker (Laser/TTO) aktiv ist (bestimmt durch MAP0016) wird der tisch in X-Richtung weiter nach vorne bewegt. 0 heisst dabei dass die X-Achse im Produktionsbetrieb auf 0 geht und ein wert vom parameter hier von 20 bedeutet dass die X-Achse auf -20 (-2mmgeht ) und bei einem Wert von -20 muss die X-achse um 20 (2mm) nach vorne hier herrscht also ein Umkehrwert.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="612" ht="240" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Druckposition in X-/Querrichtung auf dem Etikett. Fuer die Portalachse X gilt eine Umkehrlogik: ein positiver Druckpositionswert verschiebt den Tisch in negative X-Richtung, ein negativer Wert in positive X-Richtung. Die zusaetzliche Korrektur MAP0005 wird vorher auf den Druckpositionswert addiert. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="285" customHeight="1">
       <c r="A612" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46737,11 +46737,11 @@
       <c r="P612" s="38" t="n"/>
       <c r="Q612" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Druckposition in Y-/Laufrichtung auf dem Etikett. Der konkrete Stopppunkt ergibt sich aus MAP0018 fuer Laser oder MAP0019 fuer TTO plus MAP0004 und plus Korrektur MAP0006. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dies ist die Druckposition auf der Etikette in Längsrichtung (wieder von oben gesehen oben)ist der 0-Punkt. Das hat in der Steuerung folgende Funktion: Die Distanz MAP0018 bzw. MAP0019 (je nach aktivem Drucker) beschreibt die Position der Etikette in laufrichtung ganz am anfang (von oben gesehen). Der Wert 0 bedeutet somit, dass das Etiekttenband zum drucken bei genau Erfassungsanfang+MAP0018 oder MAP0019 + 0 stoppen muss. Steht hier z.b.50, soll der druck von oben gesehen in laufrichtung 5mm nach unten versetzt werden, was bedeutet, dass der stop-punkt zum drucken nun bei Erfassungsanfang des jewiligen Etiketts+MAP0018 oder MAP0019 + 50 stoppen muss.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="613" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Druckposition in Y-/Laufrichtung auf dem Etikett. Der konkrete Stopppunkt ergibt sich aus MAP0018 fuer Laser oder MAP0019 fuer TTO plus MAP0004 und plus Korrektur MAP0006. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="150" customHeight="1">
       <c r="A613" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46808,11 +46808,11 @@
       <c r="P613" s="24" t="n"/>
       <c r="Q613" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die X-Druckposition. Er wird auf MAP0003 addiert, bevor daraus die invertierte X-Achskorrektur fuer den Tisch gebildet wird. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Hier kann eine zusätliche Korrektur auf den X-Wert vorgenommen werden (dieser wird auf den X-Wert aufaddiert).. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="614" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die X-Druckposition. Er wird auf MAP0003 addiert, bevor daraus die invertierte X-Achskorrektur fuer den Tisch gebildet wird. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="150" customHeight="1">
       <c r="A614" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46879,11 +46879,11 @@
       <c r="P614" s="38" t="n"/>
       <c r="Q614" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die Y-Druckposition. Er wird auf MAP0004 addiert und beeinflusst damit den exakten Druck-Stoppweg in Laufrichtung. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Hier kann eine zusätliche Korrektur auf den Y-Wert vorgenommen werden (dieser wird auf den Y-Wert aufaddiert).. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="615" ht="150" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als zusaetzliche Korrektur auf die Y-Druckposition. Er wird auf MAP0004 addiert und beeinflusst damit den exakten Druck-Stoppweg in Laufrichtung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="195" customHeight="1">
       <c r="A615" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -46950,11 +46950,11 @@
       <c r="P615" s="24" t="n"/>
       <c r="Q615" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Materialdicke bzw. Produktions-Z-Position des Tisches in 1/10 mm. Zusammen mit der Nullpunktkorrektur MAP0028 ergibt er den Z-Sollwert fuer den Produktionsbetrieb. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Dieser wert Steuert die Z-Achse vom Tisch im Produktionsbetrieb und beschreibt die Etiekttendicke. Ein Wert von 1 bedeutet die Z-Achse muss im Produktionsbetrieb auf 1 fahren, ein wert von 50 bedeutet die Z-Achse muss im Produktionsbetrieb auf 50 fahren,. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="616" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Materialdicke bzw. Produktions-Z-Position des Tisches in 1/10 mm. Zusammen mit der Nullpunktkorrektur MAP0028 ergibt er den Z-Sollwert fuer den Produktionsbetrieb. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="180" customHeight="1">
       <c r="A616" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47021,11 +47021,11 @@
       <c r="P616" s="38" t="n"/>
       <c r="Q616" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Querposition des Etikettenerfassungs-Sensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0029 kombiniert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den Etiekttenerfassungssensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="617" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Querposition des Etikettenerfassungs-Sensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0029 kombiniert. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="165" customHeight="1">
       <c r="A617" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47092,11 +47092,11 @@
       <c r="P617" s="24" t="n"/>
       <c r="Q617" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Querposition des Entnahme-/Kontrollsensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0030 kombiniert. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den ENtnahme/Kontrollensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="618" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Querposition des Entnahme-/Kontrollsensors im Produktionsbetrieb in mm. Fuer die Motor-/Achslogik wird er in 1/10 mm umgerechnet und mit der Nullpunktkorrektur MAP0030 kombiniert. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="180" customHeight="1">
       <c r="A618" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47163,11 +47163,11 @@
       <c r="P618" s="38" t="n"/>
       <c r="Q618" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als X-/Quer-Leseposition der Material-Kontrollkamera. Er beschreibt die formatabhaengige Kameraposition; die mechanische Achskorrektur fuer diese Kamera wird separat ueber MAP0033 bzw. die Motor-Sollposition MAP0060 beruecksichtigt. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für den Etiekttenerfassungssensor im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="619" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als X-/Quer-Leseposition der Material-Kontrollkamera. Er beschreibt die formatabhaengige Kameraposition; die mechanische Achskorrektur fuer diese Kamera wird separat ueber MAP0033 bzw. die Motor-Sollposition MAP0060 beruecksichtigt. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="165" customHeight="1">
       <c r="A619" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47234,11 +47234,11 @@
       <c r="P619" s="24" t="n"/>
       <c r="Q619" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der Material-Kontrollkamera. Der Wert ist ein Prozessbezug fuer Trigger-/Auswertefenster und nicht die Motor-ID-5-Querachse selbst. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für die Materialkontrollkamera im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="620" ht="120" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der Material-Kontrollkamera. Der Wert ist ein Prozessbezug fuer Trigger-/Auswertefenster und nicht die Motor-ID-5-Querachse selbst. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="165" customHeight="1">
       <c r="A620" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47305,11 +47305,11 @@
       <c r="P620" s="38" t="n"/>
       <c r="Q620" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der OCR-/Verifizierungs-Kamera. Die Kamera ist aktuell nicht als eigene Verstellachse modelliert; der Wert bleibt aber fuer Prozessfenster und spaetere Verifikation relevant. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist die Position der Verstellachse für OCE Verifikationskamera im Produktionsbetrieb in mm.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="621" ht="210" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Y-/Laengs-Leseposition der OCR-/Verifizierungs-Kamera. Die Kamera ist aktuell nicht als eigene Verstellachse modelliert; der Wert bleibt aber fuer Prozessfenster und spaetere Verifikation relevant. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="315" customHeight="1">
       <c r="A621" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47376,11 +47376,11 @@
       <c r="P621" s="24" t="n"/>
       <c r="Q621" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Rollenkern-Typ fuer Auf- und Abwicklung (0=76 mm, 1=100 mm). Die vorhandene Hardware kann den Kern nicht sicher direkt erkennen; eine Plausibilisierung ueber Wicklerbewegung und Rollenfuellstand ist theoretisch denkbar, aber noch nicht freigegeben. Deshalb wird der Wert vorerst nur als lesbarer Format-/Materialhinweis an den ESP gespiegelt und nicht aktiv fuer Regelentscheidungen verwendet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Das ist der Parameter für den Typ des aufgespannten Etiekttenrollenkerns auf der Auf-und ABwicklung. Momentan wird das noch nicht verwendet und es ist auch nicht sicher ob der Parameter drin bleibt., da nicht sicher ist, ob anhand der Bewegungen des auf-und abwicklers kontrolliert werden kann, welcher Kern (76 oder 100mm) aktuell aufgespannt ist. Aufgabe: Finde heraus ob das technisch machbar ist mit der vorhandenen Hardware und schreibe hier das Ergebnis rein, verändere noch nichts am Code diesbezüglich.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="622" ht="225" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Rollenkern-Typ fuer Auf- und Abwicklung (0=76 mm, 1=100 mm). Die vorhandene Hardware kann den Kern nicht sicher direkt erkennen; eine Plausibilisierung ueber Wicklerbewegung und Rollenfuellstand ist theoretisch denkbar, aber noch nicht freigegeben. Deshalb wird der Wert vorerst nur als lesbarer Format-/Materialhinweis an den ESP gespiegelt und nicht aktiv fuer Regelentscheidungen verwendet. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="255" customHeight="1">
       <c r="A622" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -47447,7 +47447,7 @@
       <c r="P622" s="38" t="n"/>
       <c r="Q622" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Soll-Transportgeschwindigkeit des Etikettenbands. Im kontinuierlichen Lasermodus ist er die Druck-/Bandgeschwindigkeit; in allen getakteten Modi ist er die Vorzugsgeschwindigkeit zwischen den Druckpositionen. Der ESP nutzt ihn fuer Taktbewegungen und dynamische Nachregelung, der Raspi fuer Transparenz, Logging und Bedienung. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Der Parameter ist hier noch nicht vollständig korrekt beschrieben. IM Kontinuierlichen Lasermodus (nicht getakteter Betrieb) ist dies die Vorzugsgeschwindigkeit der Eteikette über den Etiekttenantrieb. In jedem anderen Modus ist dieser Parameter die Vorzugsgeschwindigkeit zwischen den Druckpositionen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+          <t>KI: Ich verstehe diesen Parameter als Soll-Transportgeschwindigkeit des Etikettenbands. Im kontinuierlichen Lasermodus ist er die Druck-/Bandgeschwindigkeit; in allen getakteten Modi ist er die Vorzugsgeschwindigkeit zwischen den Druckpositionen. Der ESP nutzt ihn fuer Taktbewegungen und dynamische Nachregelung, der Raspi fuer Transparenz, Logging und Bedienung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
         </is>
       </c>
     </row>
@@ -48019,7 +48019,7 @@
         </is>
       </c>
     </row>
-    <row r="631" ht="105" customHeight="1">
+    <row r="631" ht="135" customHeight="1">
       <c r="A631" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48078,7 +48078,7 @@
       </c>
       <c r="M631" s="23" t="inlineStr">
         <is>
-          <t>Vorwarnung Etikettenfüllstand bei Abwicklung</t>
+          <t>Vorwarnung Etikettenfuellstand bei Abwicklung (bald leer)</t>
         </is>
       </c>
       <c r="N631" s="23" t="n"/>
@@ -48086,11 +48086,11 @@
       <c r="P631" s="24" t="n"/>
       <c r="Q631" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Abwickler in Prozent. Wenn MAS0008 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende entstehen. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="632" ht="105" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Abwickler in Prozent Restfuellstand. Wenn MAS0008 kleiner/gleich diesem Wert ist, ist die Abwickelrolle bald leer und die passende Wickler-/Materialwarnung muss aktiv werden. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="150" customHeight="1">
       <c r="A632" s="31" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48103,17 +48103,17 @@
       </c>
       <c r="C632" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F632" s="31" t="inlineStr">
@@ -48149,7 +48149,7 @@
       </c>
       <c r="M632" s="39" t="inlineStr">
         <is>
-          <t>Vorwarnung Etikettenfüllstand bei Aufwicklung</t>
+          <t>Vorwarnung Etikettenfuellstand bei Aufwicklung (bald voll)</t>
         </is>
       </c>
       <c r="N632" s="37" t="n"/>
@@ -48157,7 +48157,7 @@
       <c r="P632" s="38" t="n"/>
       <c r="Q632" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Aufwickler in Prozent. Wenn MAS0009 unter diesen Wert faellt, soll daraus die passende Warnung fuer Materialende bzw. Rollenfuellstand entstehen. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Vorwarnschwelle fuer den Aufwickler in Prozent Rollenfuellstand. Wenn MAS0009 groesser/gleich diesem Wert ist, ist die Aufwickelrolle bald voll und die passende Wickler-/Materialwarnung muss aktiv werden. Default ist 95 %, also Warnung im Bereich 95-100 %. Alte/gespiegelte Werte kleiner/gleich 50 werden in der Wickler-Firmware uebergangsweise als Restreserve bis voll interpretiert, z.B. 5 bedeutet Warnung ab 95 %. Der ESP liest diesen Wert fuer die Wickler-/Prozesslogik, Microtom liest ihn als eingestellte Schwelle. Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -48303,7 +48303,7 @@
         </is>
       </c>
     </row>
-    <row r="635" ht="165" customHeight="1">
+    <row r="635" ht="225" customHeight="1">
       <c r="A635" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48370,11 +48370,11 @@
       <c r="P635" s="24" t="n"/>
       <c r="Q635" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse X. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle X-bezogenen Berechnungen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="636" ht="165" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse X. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle X-bezogenen Berechnungen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="225" customHeight="1">
       <c r="A636" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48441,11 +48441,11 @@
       <c r="P636" s="21" t="n"/>
       <c r="Q636" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse Z. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle Z-bezogenen Berechnungen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="637" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Portalachse Z. Die programmierte Motor-Nullposition bleibt die Grundstellung; dieser Wert verschiebt den fachlichen Nullpunkt fuer alle Z-bezogenen Berechnungen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="225" customHeight="1">
       <c r="A637" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48512,11 +48512,11 @@
       <c r="P637" s="24" t="n"/>
       <c r="Q637" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Etikettenerfassungs-Sensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="638" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Etikettenerfassungs-Sensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638" ht="210" customHeight="1">
       <c r="A638" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48583,11 +48583,11 @@
       <c r="P638" s="21" t="n"/>
       <c r="Q638" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Entnahme-/Kontrollsensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="639" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Querachse fuer den Entnahme-/Kontrollsensor. Alle Sensorpositionen fuer diese Achse werden relativ zu diesem korrigierten Nullpunkt betrachtet. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="210" customHeight="1">
       <c r="A639" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48654,11 +48654,11 @@
       <c r="P639" s="24" t="n"/>
       <c r="Q639" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Einlauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="640" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Einlauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="210" customHeight="1">
       <c r="A640" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48725,11 +48725,11 @@
       <c r="P640" s="21" t="n"/>
       <c r="Q640" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Auslauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="641" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Etikettenanschlags am Auslauf. Die aus MAP0001 abgeleitete Bandbreitenposition wird um diese Korrektur verschoben. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="210" customHeight="1">
       <c r="A641" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48796,11 +48796,11 @@
       <c r="P641" s="24" t="n"/>
       <c r="Q641" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Material-Kontrollkamera-Querachse. Die formatabhaengige Kameraposition wird relativ zu diesem korrigierten Nullpunkt betrachtet. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="642" ht="180" customHeight="1">
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur der Material-Kontrollkamera-Querachse. Die formatabhaengige Kameraposition wird relativ zu diesem korrigierten Nullpunkt betrachtet. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="210" customHeight="1">
       <c r="A642" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -48867,7 +48867,7 @@
       <c r="P642" s="21" t="n"/>
       <c r="Q642" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Laser-Schutzblechs. Die Schutzblechachse bleibt parametrierbar, auch wenn der Laserprozess spaeter finalisiert wird. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Die Grundstellung ist eigentlich immer bei der programmierten 0 - Position des jeweiligen Motors. Dieser Wert versteht sich als korrekturangabe auf den eigentlichen 0-Punkt. Wird hier ein anderer Wert als 0 eingegeben, gild dieser korrigierte wert als 0-Punkt für alle anderen Parameter und Funktionen, welche sich auf diesen 0 Punkt beziehen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Nullpunktkorrektur des Laser-Schutzblechs. Die Schutzblechachse bleibt parametrierbar, auch wenn der Laserprozess spaeter finalisiert wird. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -49155,7 +49155,7 @@
         </is>
       </c>
     </row>
-    <row r="647" ht="165" customHeight="1">
+    <row r="647" ht="240" customHeight="1">
       <c r="A647" s="15" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -49222,7 +49222,7 @@
       <c r="P647" s="24" t="n"/>
       <c r="Q647" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Freigabe fuer automatische Rueckspulung nach Produktionsstop. Wenn der Wert 1 ist, wird nach Produktionsstop und Rueckspul-Taster bis zum Ursprungspunkt zurueckgespult und erst danach die Produktion abgeschlossen; bei 0 gilt die Produktion ohne Rueckspulung als abgeschlossen. Aus der ergaenzten Fachbeschreibung wurde ausgewertet: Ist dieser Wert 1, wird nach dem Produktionsstop automatisch (nach drücken des Rückspul-Tasters) die Etiektte an den Ursprungspunkt zurückgespult und erst dann wird die Produktion abgeschlossen. Ist der Wert 0, erfolgt keine Rückspulung und die Produktion gilt nach dem Produktionsstop als abgeschlossen.. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+          <t>KI: Ich verstehe diesen Parameter als Freigabe fuer automatische Rueckspulung nach Produktionsstop. Wenn der Wert 1 ist, wird nach Produktionsstop und Rueckspul-Taster bis zum Ursprungspunkt zurueckgespult und erst danach die Produktion abgeschlossen; bei 0 gilt die Produktion ohne Rueckspulung als abgeschlossen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
         </is>
       </c>
     </row>
@@ -49723,7 +49723,7 @@
         </is>
       </c>
     </row>
-    <row r="655" ht="120" customHeight="1">
+    <row r="655" ht="135" customHeight="1">
       <c r="A655" s="8" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -50990,7 +50990,7 @@
       <c r="P673" s="22" t="n"/>
       <c r="Q673" s="22" t="n"/>
     </row>
-    <row r="674" ht="135" customHeight="1">
+    <row r="674" ht="150" customHeight="1">
       <c r="A674" s="10" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -51064,7 +51064,7 @@
         </is>
       </c>
     </row>
-    <row r="675" ht="135" customHeight="1">
+    <row r="675" ht="150" customHeight="1">
       <c r="A675" s="10" t="inlineStr">
         <is>
           <t>MAP</t>
@@ -57007,118 +57007,408 @@
       </c>
     </row>
     <row r="758" hidden="1">
-      <c r="A758" s="10" t="n"/>
-      <c r="B758" s="8" t="n"/>
-      <c r="C758" s="43" t="n"/>
-      <c r="D758" s="11" t="n"/>
-      <c r="E758" s="11" t="n"/>
-      <c r="F758" s="15" t="n"/>
-      <c r="G758" s="15" t="n"/>
-      <c r="H758" s="15" t="n"/>
-      <c r="I758" s="15" t="n"/>
-      <c r="J758" s="15" t="n"/>
-      <c r="K758" s="22" t="n"/>
-      <c r="L758" s="22" t="n"/>
-      <c r="M758" s="22" t="n"/>
-      <c r="N758" s="22" t="n"/>
-      <c r="O758" s="22" t="n"/>
-      <c r="P758" s="22" t="n"/>
-      <c r="Q758" s="22" t="n"/>
+      <c r="A758" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B758" s="8" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="C758" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D758" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E758" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F758" s="29" t="n"/>
+      <c r="G758" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H758" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I758" s="29" t="inlineStr">
+        <is>
+          <t>uint8</t>
+        </is>
+      </c>
+      <c r="J758" s="29" t="inlineStr">
+        <is>
+          <t>Temporaerer IBN/Test Prozessbefehl</t>
+        </is>
+      </c>
+      <c r="K758" s="28" t="n"/>
+      <c r="L758" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M758" s="28" t="inlineStr">
+        <is>
+          <t>0=Stop, 1=Wickler einmessen+Messfahrt, 2=Taktbetrieb, 3=Vorziehen kontinuierlich, 4=Zurueckspulen kontinuierlich</t>
+        </is>
+      </c>
+      <c r="N758" s="28" t="n"/>
+      <c r="O758" s="28" t="n"/>
+      <c r="P758" s="28" t="n"/>
+      <c r="Q758" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0001 als temporaeren IBN-/Testbefehl von Microtom an den Raspi. Der Raspi uebersetzt diesen Wert in produktionsnahe Startkommandos fuer ESP32-PLC und Wickler. Dieser Parameter ist ausdruecklich nur fuer Inbetriebnahme/Test vorgesehen und muss spaeter entfernt oder durch produktive MAS/MAP-Ablaufbefehle ersetzt werden. Der ESP soll ihn gemaess Masterliste nicht direkt als normalen Parameter verwenden. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R758" s="4" t="n"/>
+      <c r="S758" s="4" t="n"/>
+      <c r="T758" s="4" t="n"/>
     </row>
     <row r="759" hidden="1">
-      <c r="A759" s="10" t="n"/>
-      <c r="B759" s="8" t="n"/>
-      <c r="C759" s="43" t="n"/>
-      <c r="D759" s="11" t="n"/>
-      <c r="E759" s="11" t="n"/>
-      <c r="F759" s="15" t="n"/>
-      <c r="G759" s="15" t="n"/>
-      <c r="H759" s="15" t="n"/>
-      <c r="I759" s="15" t="n"/>
-      <c r="J759" s="15" t="n"/>
-      <c r="K759" s="22" t="n"/>
-      <c r="L759" s="22" t="n"/>
-      <c r="M759" s="22" t="n"/>
-      <c r="N759" s="22" t="n"/>
-      <c r="O759" s="22" t="n"/>
-      <c r="P759" s="22" t="n"/>
-      <c r="Q759" s="22" t="n"/>
+      <c r="A759" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B759" s="8" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="C759" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D759" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E759" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F759" s="29" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G759" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H759" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I759" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="J759" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere Takt-/Labellaenge</t>
+        </is>
+      </c>
+      <c r="K759" s="28" t="n"/>
+      <c r="L759" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M759" s="28" t="inlineStr">
+        <is>
+          <t>Labelweg fuer getakteten Testbetrieb in 1/10 mm</t>
+        </is>
+      </c>
+      <c r="N759" s="28" t="n"/>
+      <c r="O759" s="28" t="n"/>
+      <c r="P759" s="28" t="n"/>
+      <c r="Q759" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0002 als temporaere Labellaenge bzw. Taktstrecke fuer den IBN-Test. Default 1000 bedeutet 100.0 mm. Spaeter kommt dieser Wert aus Rezept-/Formatdaten und Etiketteneinmessung, nicht mehr aus einem MAC-Testparameter. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R759" s="4" t="n"/>
+      <c r="S759" s="4" t="n"/>
+      <c r="T759" s="4" t="n"/>
     </row>
     <row r="760" hidden="1">
-      <c r="A760" s="10" t="n"/>
-      <c r="B760" s="8" t="n"/>
-      <c r="C760" s="43" t="n"/>
-      <c r="D760" s="11" t="n"/>
-      <c r="E760" s="11" t="n"/>
-      <c r="F760" s="15" t="n"/>
-      <c r="G760" s="15" t="n"/>
-      <c r="H760" s="15" t="n"/>
-      <c r="I760" s="15" t="n"/>
-      <c r="J760" s="15" t="n"/>
-      <c r="K760" s="22" t="n"/>
-      <c r="L760" s="22" t="n"/>
-      <c r="M760" s="22" t="n"/>
-      <c r="N760" s="22" t="n"/>
-      <c r="O760" s="22" t="n"/>
-      <c r="P760" s="22" t="n"/>
-      <c r="Q760" s="22" t="n"/>
+      <c r="A760" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B760" s="8" t="inlineStr">
+        <is>
+          <t>0003</t>
+        </is>
+      </c>
+      <c r="C760" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D760" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="E760" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F760" s="29" t="inlineStr">
+        <is>
+          <t>mm/s</t>
+        </is>
+      </c>
+      <c r="G760" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H760" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I760" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="J760" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere Vorzugsgeschwindigkeit</t>
+        </is>
+      </c>
+      <c r="K760" s="28" t="n"/>
+      <c r="L760" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M760" s="28" t="inlineStr">
+        <is>
+          <t>Sollgeschwindigkeit fuer kontinuierlichen und getakteten IBN-Testbetrieb</t>
+        </is>
+      </c>
+      <c r="N760" s="28" t="n"/>
+      <c r="O760" s="28" t="n"/>
+      <c r="P760" s="28" t="n"/>
+      <c r="Q760" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0003 als temporaere Vorzugsgeschwindigkeit fuer Motor 3 im IBN-Test. Wird kein neuer Wert gesetzt, verwendet der Raspi den zuletzt gespeicherten Wert. Produktiv wird die Geschwindigkeit ueber MAP0014 bzw. die Betriebsart vorgegeben. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R760" s="4" t="n"/>
+      <c r="S760" s="4" t="n"/>
+      <c r="T760" s="4" t="n"/>
     </row>
     <row r="761" hidden="1">
-      <c r="A761" s="10" t="n"/>
-      <c r="B761" s="8" t="n"/>
-      <c r="C761" s="43" t="n"/>
-      <c r="D761" s="11" t="n"/>
-      <c r="E761" s="11" t="n"/>
-      <c r="F761" s="15" t="n"/>
-      <c r="G761" s="15" t="n"/>
-      <c r="H761" s="15" t="n"/>
-      <c r="I761" s="15" t="n"/>
-      <c r="J761" s="15" t="n"/>
-      <c r="K761" s="22" t="n"/>
-      <c r="L761" s="22" t="n"/>
-      <c r="M761" s="22" t="n"/>
-      <c r="N761" s="22" t="n"/>
-      <c r="O761" s="22" t="n"/>
-      <c r="P761" s="22" t="n"/>
-      <c r="Q761" s="22" t="n"/>
+      <c r="A761" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B761" s="8" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="C761" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D761" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E761" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F761" s="29" t="inlineStr">
+        <is>
+          <t>mm/s2</t>
+        </is>
+      </c>
+      <c r="G761" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H761" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I761" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="J761" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere Transport-Rampe</t>
+        </is>
+      </c>
+      <c r="K761" s="28" t="n"/>
+      <c r="L761" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M761" s="28" t="inlineStr">
+        <is>
+          <t>Beschleunigung/Verzoegerung fuer Motor 3 im IBN-Testbetrieb</t>
+        </is>
+      </c>
+      <c r="N761" s="28" t="n"/>
+      <c r="O761" s="28" t="n"/>
+      <c r="P761" s="28" t="n"/>
+      <c r="Q761" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0004 als temporaere Rampe fuer Beschleunigung und Bremsung des Etikettenantriebs im IBN-Test. Produktiv wird diese Vorgabe aus Maschinen- bzw. Formatparametern abgeleitet und darf den Etikettenschlupf nicht erhoehen. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s2. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R761" s="4" t="n"/>
+      <c r="S761" s="4" t="n"/>
+      <c r="T761" s="4" t="n"/>
     </row>
     <row r="762" hidden="1">
-      <c r="A762" s="10" t="n"/>
-      <c r="B762" s="8" t="n"/>
-      <c r="C762" s="43" t="n"/>
-      <c r="D762" s="11" t="n"/>
-      <c r="E762" s="11" t="n"/>
-      <c r="F762" s="15" t="n"/>
-      <c r="G762" s="15" t="n"/>
-      <c r="H762" s="15" t="n"/>
-      <c r="I762" s="15" t="n"/>
-      <c r="J762" s="15" t="n"/>
-      <c r="K762" s="22" t="n"/>
-      <c r="L762" s="22" t="n"/>
-      <c r="M762" s="22" t="n"/>
-      <c r="N762" s="22" t="n"/>
-      <c r="O762" s="22" t="n"/>
-      <c r="P762" s="22" t="n"/>
-      <c r="Q762" s="22" t="n"/>
+      <c r="A762" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B762" s="8" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="C762" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D762" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E762" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F762" s="29" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G762" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H762" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I762" s="29" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="J762" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere kontinuierliche Weglaenge</t>
+        </is>
+      </c>
+      <c r="K762" s="28" t="n"/>
+      <c r="L762" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M762" s="28" t="inlineStr">
+        <is>
+          <t>Weg fuer kontinuierliches Vorziehen/Rueckspulen; 0=endlos bis Stop</t>
+        </is>
+      </c>
+      <c r="N762" s="28" t="n"/>
+      <c r="O762" s="28" t="n"/>
+      <c r="P762" s="28" t="n"/>
+      <c r="Q762" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0005 als temporaere Wegvorgabe fuer kontinuierliches Vorziehen oder Rueckspulen. Default 0 bedeutet endlos fahren bis MAC0001=0. Produktiv wird diese Laenge aus Ablaufzustand, Rueckspulweg oder Bedienhandlung bestimmt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R762" s="4" t="n"/>
+      <c r="S762" s="4" t="n"/>
+      <c r="T762" s="4" t="n"/>
     </row>
     <row r="763" hidden="1">
-      <c r="A763" s="10" t="n"/>
-      <c r="B763" s="8" t="n"/>
-      <c r="C763" s="43" t="n"/>
-      <c r="D763" s="11" t="n"/>
-      <c r="E763" s="11" t="n"/>
-      <c r="F763" s="15" t="n"/>
-      <c r="G763" s="15" t="n"/>
-      <c r="H763" s="15" t="n"/>
-      <c r="I763" s="15" t="n"/>
-      <c r="J763" s="15" t="n"/>
-      <c r="K763" s="22" t="n"/>
-      <c r="L763" s="22" t="n"/>
-      <c r="M763" s="22" t="n"/>
-      <c r="N763" s="22" t="n"/>
-      <c r="O763" s="22" t="n"/>
-      <c r="P763" s="22" t="n"/>
-      <c r="Q763" s="22" t="n"/>
+      <c r="A763" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B763" s="8" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="C763" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D763" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E763" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F763" s="29" t="inlineStr">
+        <is>
+          <t>Zyklen</t>
+        </is>
+      </c>
+      <c r="G763" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H763" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I763" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="J763" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere Taktzyklus-Anzahl</t>
+        </is>
+      </c>
+      <c r="K763" s="28" t="n"/>
+      <c r="L763" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M763" s="28" t="inlineStr">
+        <is>
+          <t>Anzahl Takte im Testbetrieb; 0=endlos bis Stop</t>
+        </is>
+      </c>
+      <c r="N763" s="28" t="n"/>
+      <c r="O763" s="28" t="n"/>
+      <c r="P763" s="28" t="n"/>
+      <c r="Q763" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0006 als temporaere Zyklusanzahl fuer den getakteten IBN-Test. Default 20 entspricht einem kurzen Stabilitaetstest; 0 bedeutet laufender Taktbetrieb bis MAC0001=0. Spaeter wird diese Logik durch den echten Produktionsablauf und das Schieberegister ersetzt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Zyklen. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="R763" s="4" t="n"/>
+      <c r="S763" s="4" t="n"/>
+      <c r="T763" s="4" t="n"/>
     </row>
     <row r="764" hidden="1">
       <c r="A764" s="10" t="n"/>
@@ -57703,13 +57993,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD8B92E4-A62E-4C3D-ABB7-B1C8056BB11B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AD463D1-E757-4D31-B8E8-0F1FA0DA293A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EEC841-3638-4C83-A17D-B41FFD8905C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67F1944-362D-43F5-BE44-588BA96467B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37AD3F2D-24B3-4F2A-92A9-16CAFF700971}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A096BF9-12F5-4E2F-802A-25F1F6BC033C}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
@@ -269,6 +269,7 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
@@ -296,7 +297,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
@@ -474,9 +474,8 @@
   <autoFilter ref="A1:R778">
     <filterColumn colId="0" hiddenButton="0" showButton="1">
       <filters>
+        <filter val="MAE"/>
         <filter val="MAP"/>
-        <filter val="MAS"/>
-        <filter val="TTP"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -490,18 +489,18 @@
     <tableColumn id="2" name="Max.:" dataDxfId="14"/>
     <tableColumn id="10" name="Default Value:" dataDxfId="13"/>
     <tableColumn id="4" name="Einheit:" dataDxfId="12"/>
-    <tableColumn id="8" name="Microtom User Range:" dataDxfId="0"/>
-    <tableColumn id="5" name="R/W:" dataDxfId="11"/>
-    <tableColumn id="6" name="ESP32 R/W:" dataDxfId="10"/>
-    <tableColumn id="14" name="Data Type:" dataDxfId="9"/>
-    <tableColumn id="15" name="Name:" dataDxfId="8"/>
-    <tableColumn id="7" name="ZBC Mapping:" dataDxfId="7"/>
-    <tableColumn id="11" name="Format relevant?:" dataDxfId="6"/>
-    <tableColumn id="12" name="Message:" dataDxfId="5"/>
-    <tableColumn id="13" name="Possible Cause:" dataDxfId="4"/>
-    <tableColumn id="17" name="Effects:" dataDxfId="3"/>
-    <tableColumn id="18" name="Remedy:" dataDxfId="2"/>
-    <tableColumn id="19" name="KI-Anweisungen:" dataDxfId="1"/>
+    <tableColumn id="8" name="Microtom User Range:" dataDxfId="11"/>
+    <tableColumn id="5" name="R/W:" dataDxfId="10"/>
+    <tableColumn id="6" name="ESP32 R/W:" dataDxfId="9"/>
+    <tableColumn id="14" name="Data Type:" dataDxfId="8"/>
+    <tableColumn id="15" name="Name:" dataDxfId="7"/>
+    <tableColumn id="7" name="ZBC Mapping:" dataDxfId="6"/>
+    <tableColumn id="11" name="Format relevant?:" dataDxfId="5"/>
+    <tableColumn id="12" name="Message:" dataDxfId="4"/>
+    <tableColumn id="13" name="Possible Cause:" dataDxfId="3"/>
+    <tableColumn id="17" name="Effects:" dataDxfId="2"/>
+    <tableColumn id="18" name="Remedy:" dataDxfId="1"/>
+    <tableColumn id="19" name="KI-Anweisungen:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -41439,7 +41438,7 @@
         </is>
       </c>
     </row>
-    <row r="528" ht="60" customHeight="1">
+    <row r="528" hidden="1" ht="60" customHeight="1">
       <c r="A528" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41509,7 +41508,7 @@
         </is>
       </c>
     </row>
-    <row r="529" ht="60" customHeight="1">
+    <row r="529" hidden="1" ht="60" customHeight="1">
       <c r="A529" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41581,7 +41580,7 @@
         </is>
       </c>
     </row>
-    <row r="530" ht="60" customHeight="1">
+    <row r="530" hidden="1" ht="60" customHeight="1">
       <c r="A530" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41653,7 +41652,7 @@
         </is>
       </c>
     </row>
-    <row r="531" ht="75" customHeight="1">
+    <row r="531" hidden="1" ht="75" customHeight="1">
       <c r="A531" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41727,7 +41726,7 @@
         </is>
       </c>
     </row>
-    <row r="532" ht="60" customHeight="1">
+    <row r="532" hidden="1" ht="60" customHeight="1">
       <c r="A532" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41799,7 +41798,7 @@
         </is>
       </c>
     </row>
-    <row r="533" ht="45" customHeight="1">
+    <row r="533" hidden="1" ht="45" customHeight="1">
       <c r="A533" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41869,7 +41868,7 @@
         </is>
       </c>
     </row>
-    <row r="534" ht="60" customHeight="1">
+    <row r="534" hidden="1" ht="60" customHeight="1">
       <c r="A534" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -41939,7 +41938,7 @@
         </is>
       </c>
     </row>
-    <row r="535" ht="60" customHeight="1">
+    <row r="535" hidden="1" ht="60" customHeight="1">
       <c r="A535" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42009,7 +42008,7 @@
         </is>
       </c>
     </row>
-    <row r="536" ht="60" customHeight="1">
+    <row r="536" hidden="1" ht="60" customHeight="1">
       <c r="A536" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42079,7 +42078,7 @@
         </is>
       </c>
     </row>
-    <row r="537" ht="75" customHeight="1">
+    <row r="537" hidden="1" ht="75" customHeight="1">
       <c r="A537" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42147,7 +42146,7 @@
         </is>
       </c>
     </row>
-    <row r="538" ht="60" customHeight="1">
+    <row r="538" hidden="1" ht="60" customHeight="1">
       <c r="A538" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42217,7 +42216,7 @@
         </is>
       </c>
     </row>
-    <row r="539" ht="60" customHeight="1">
+    <row r="539" hidden="1" ht="60" customHeight="1">
       <c r="A539" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42289,7 +42288,7 @@
         </is>
       </c>
     </row>
-    <row r="540" ht="60" customHeight="1">
+    <row r="540" hidden="1" ht="60" customHeight="1">
       <c r="A540" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42359,7 +42358,7 @@
         </is>
       </c>
     </row>
-    <row r="541" ht="60" customHeight="1">
+    <row r="541" hidden="1" ht="60" customHeight="1">
       <c r="A541" s="15" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42431,7 +42430,7 @@
         </is>
       </c>
     </row>
-    <row r="542" ht="60" customHeight="1">
+    <row r="542" hidden="1" ht="60" customHeight="1">
       <c r="A542" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42503,7 +42502,7 @@
         </is>
       </c>
     </row>
-    <row r="543" ht="75" customHeight="1">
+    <row r="543" hidden="1" ht="75" customHeight="1">
       <c r="A543" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42575,7 +42574,7 @@
         </is>
       </c>
     </row>
-    <row r="544" ht="60" customHeight="1">
+    <row r="544" hidden="1" ht="60" customHeight="1">
       <c r="A544" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42647,7 +42646,7 @@
         </is>
       </c>
     </row>
-    <row r="545" ht="60" customHeight="1">
+    <row r="545" hidden="1" ht="60" customHeight="1">
       <c r="A545" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42723,7 +42722,7 @@
         </is>
       </c>
     </row>
-    <row r="546" ht="60" customHeight="1">
+    <row r="546" hidden="1" ht="60" customHeight="1">
       <c r="A546" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42799,7 +42798,7 @@
         </is>
       </c>
     </row>
-    <row r="547" ht="60" customHeight="1">
+    <row r="547" hidden="1" ht="60" customHeight="1">
       <c r="A547" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42871,7 +42870,7 @@
         </is>
       </c>
     </row>
-    <row r="548" ht="60" customHeight="1">
+    <row r="548" hidden="1" ht="60" customHeight="1">
       <c r="A548" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -42947,7 +42946,7 @@
         </is>
       </c>
     </row>
-    <row r="549" ht="60" customHeight="1">
+    <row r="549" hidden="1" ht="60" customHeight="1">
       <c r="A549" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43017,7 +43016,7 @@
         </is>
       </c>
     </row>
-    <row r="550" ht="60" customHeight="1">
+    <row r="550" hidden="1" ht="60" customHeight="1">
       <c r="A550" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43090,7 +43089,7 @@
         </is>
       </c>
     </row>
-    <row r="551" ht="60" customHeight="1">
+    <row r="551" hidden="1" ht="60" customHeight="1">
       <c r="A551" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43158,7 +43157,7 @@
         </is>
       </c>
     </row>
-    <row r="552" ht="60" customHeight="1">
+    <row r="552" hidden="1" ht="60" customHeight="1">
       <c r="A552" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43230,7 +43229,7 @@
         </is>
       </c>
     </row>
-    <row r="553" ht="75" customHeight="1">
+    <row r="553" hidden="1" ht="75" customHeight="1">
       <c r="A553" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43300,7 +43299,7 @@
         </is>
       </c>
     </row>
-    <row r="554" ht="60" customHeight="1">
+    <row r="554" hidden="1" ht="60" customHeight="1">
       <c r="A554" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43372,7 +43371,7 @@
         </is>
       </c>
     </row>
-    <row r="555" ht="60" customHeight="1">
+    <row r="555" hidden="1" ht="60" customHeight="1">
       <c r="A555" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43444,7 +43443,7 @@
         </is>
       </c>
     </row>
-    <row r="556" ht="60" customHeight="1">
+    <row r="556" hidden="1" ht="60" customHeight="1">
       <c r="A556" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43514,7 +43513,7 @@
         </is>
       </c>
     </row>
-    <row r="557" ht="60" customHeight="1">
+    <row r="557" hidden="1" ht="60" customHeight="1">
       <c r="A557" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43586,7 +43585,7 @@
         </is>
       </c>
     </row>
-    <row r="558" ht="60" customHeight="1">
+    <row r="558" hidden="1" ht="60" customHeight="1">
       <c r="A558" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43658,7 +43657,7 @@
         </is>
       </c>
     </row>
-    <row r="559" ht="60" customHeight="1">
+    <row r="559" hidden="1" ht="60" customHeight="1">
       <c r="A559" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43730,7 +43729,7 @@
         </is>
       </c>
     </row>
-    <row r="560" ht="60" customHeight="1">
+    <row r="560" hidden="1" ht="60" customHeight="1">
       <c r="A560" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43803,7 +43802,7 @@
         </is>
       </c>
     </row>
-    <row r="561" ht="45" customHeight="1">
+    <row r="561" hidden="1" ht="45" customHeight="1">
       <c r="A561" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43875,7 +43874,7 @@
         </is>
       </c>
     </row>
-    <row r="562" ht="60" customHeight="1">
+    <row r="562" hidden="1" ht="60" customHeight="1">
       <c r="A562" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -43943,7 +43942,7 @@
         </is>
       </c>
     </row>
-    <row r="563" ht="45" customHeight="1">
+    <row r="563" hidden="1" ht="45" customHeight="1">
       <c r="A563" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44013,7 +44012,7 @@
         </is>
       </c>
     </row>
-    <row r="564" ht="45" customHeight="1">
+    <row r="564" hidden="1" ht="45" customHeight="1">
       <c r="A564" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44083,7 +44082,7 @@
         </is>
       </c>
     </row>
-    <row r="565" ht="45" customHeight="1">
+    <row r="565" hidden="1" ht="45" customHeight="1">
       <c r="A565" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44153,7 +44152,7 @@
         </is>
       </c>
     </row>
-    <row r="566" ht="60" customHeight="1">
+    <row r="566" hidden="1" ht="60" customHeight="1">
       <c r="A566" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44223,7 +44222,7 @@
         </is>
       </c>
     </row>
-    <row r="567" ht="60" customHeight="1">
+    <row r="567" hidden="1" ht="60" customHeight="1">
       <c r="A567" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44293,7 +44292,7 @@
         </is>
       </c>
     </row>
-    <row r="568" ht="60" customHeight="1">
+    <row r="568" hidden="1" ht="60" customHeight="1">
       <c r="A568" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44365,7 +44364,7 @@
         </is>
       </c>
     </row>
-    <row r="569" ht="45" customHeight="1">
+    <row r="569" hidden="1" ht="45" customHeight="1">
       <c r="A569" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44437,7 +44436,7 @@
         </is>
       </c>
     </row>
-    <row r="570" ht="45" customHeight="1">
+    <row r="570" hidden="1" ht="45" customHeight="1">
       <c r="A570" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44507,7 +44506,7 @@
         </is>
       </c>
     </row>
-    <row r="571" ht="45" customHeight="1">
+    <row r="571" hidden="1" ht="45" customHeight="1">
       <c r="A571" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44577,7 +44576,7 @@
         </is>
       </c>
     </row>
-    <row r="572" ht="45" customHeight="1">
+    <row r="572" hidden="1" ht="45" customHeight="1">
       <c r="A572" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44649,7 +44648,7 @@
         </is>
       </c>
     </row>
-    <row r="573" ht="60" customHeight="1">
+    <row r="573" hidden="1" ht="60" customHeight="1">
       <c r="A573" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44721,7 +44720,7 @@
         </is>
       </c>
     </row>
-    <row r="574" ht="45" customHeight="1">
+    <row r="574" hidden="1" ht="45" customHeight="1">
       <c r="A574" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44791,7 +44790,7 @@
         </is>
       </c>
     </row>
-    <row r="575" ht="60" customHeight="1">
+    <row r="575" hidden="1" ht="60" customHeight="1">
       <c r="A575" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44863,7 +44862,7 @@
         </is>
       </c>
     </row>
-    <row r="576" ht="45" customHeight="1">
+    <row r="576" hidden="1" ht="45" customHeight="1">
       <c r="A576" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -44935,7 +44934,7 @@
         </is>
       </c>
     </row>
-    <row r="577" ht="75" customHeight="1">
+    <row r="577" hidden="1" ht="75" customHeight="1">
       <c r="A577" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45007,7 +45006,7 @@
         </is>
       </c>
     </row>
-    <row r="578" ht="60" customHeight="1">
+    <row r="578" hidden="1" ht="60" customHeight="1">
       <c r="A578" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45077,7 +45076,7 @@
         </is>
       </c>
     </row>
-    <row r="579" ht="75" customHeight="1">
+    <row r="579" hidden="1" ht="75" customHeight="1">
       <c r="A579" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45147,7 +45146,7 @@
         </is>
       </c>
     </row>
-    <row r="580" ht="60" customHeight="1">
+    <row r="580" hidden="1" ht="60" customHeight="1">
       <c r="A580" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45219,7 +45218,7 @@
         </is>
       </c>
     </row>
-    <row r="581" ht="60" customHeight="1">
+    <row r="581" hidden="1" ht="60" customHeight="1">
       <c r="A581" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45291,7 +45290,7 @@
         </is>
       </c>
     </row>
-    <row r="582" ht="60" customHeight="1">
+    <row r="582" hidden="1" ht="60" customHeight="1">
       <c r="A582" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45359,7 +45358,7 @@
         </is>
       </c>
     </row>
-    <row r="583" ht="60" customHeight="1">
+    <row r="583" hidden="1" ht="60" customHeight="1">
       <c r="A583" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45429,7 +45428,7 @@
         </is>
       </c>
     </row>
-    <row r="584" ht="60" customHeight="1">
+    <row r="584" hidden="1" ht="60" customHeight="1">
       <c r="A584" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45499,7 +45498,7 @@
         </is>
       </c>
     </row>
-    <row r="585" ht="60" customHeight="1">
+    <row r="585" hidden="1" ht="60" customHeight="1">
       <c r="A585" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45569,7 +45568,7 @@
         </is>
       </c>
     </row>
-    <row r="586" ht="60" customHeight="1">
+    <row r="586" hidden="1" ht="60" customHeight="1">
       <c r="A586" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45639,7 +45638,7 @@
         </is>
       </c>
     </row>
-    <row r="587" ht="45" customHeight="1">
+    <row r="587" hidden="1" ht="45" customHeight="1">
       <c r="A587" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45709,7 +45708,7 @@
         </is>
       </c>
     </row>
-    <row r="588" ht="60" customHeight="1">
+    <row r="588" hidden="1" ht="60" customHeight="1">
       <c r="A588" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45779,7 +45778,7 @@
         </is>
       </c>
     </row>
-    <row r="589" ht="45" customHeight="1">
+    <row r="589" hidden="1" ht="45" customHeight="1">
       <c r="A589" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45849,7 +45848,7 @@
         </is>
       </c>
     </row>
-    <row r="590" ht="60" customHeight="1">
+    <row r="590" hidden="1" ht="60" customHeight="1">
       <c r="A590" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -45975,7 +45974,7 @@
       <c r="Q592" s="22" t="n"/>
       <c r="R592" s="22" t="n"/>
     </row>
-    <row r="593" ht="60" customHeight="1">
+    <row r="593" hidden="1" ht="60" customHeight="1">
       <c r="A593" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46046,7 +46045,7 @@
       <c r="T593" s="4" t="n"/>
       <c r="U593" s="4" t="n"/>
     </row>
-    <row r="594" ht="45" customHeight="1">
+    <row r="594" hidden="1" ht="45" customHeight="1">
       <c r="A594" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46117,7 +46116,7 @@
       <c r="T594" s="4" t="n"/>
       <c r="U594" s="4" t="n"/>
     </row>
-    <row r="595" ht="105" customHeight="1">
+    <row r="595" hidden="1" ht="105" customHeight="1">
       <c r="A595" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46184,7 +46183,7 @@
       <c r="T595" s="4" t="n"/>
       <c r="U595" s="4" t="n"/>
     </row>
-    <row r="596" ht="90" customHeight="1">
+    <row r="596" hidden="1" ht="90" customHeight="1">
       <c r="A596" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46255,7 +46254,7 @@
       <c r="T596" s="4" t="n"/>
       <c r="U596" s="4" t="n"/>
     </row>
-    <row r="597" ht="60" customHeight="1">
+    <row r="597" hidden="1" ht="60" customHeight="1">
       <c r="A597" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46326,7 +46325,7 @@
       <c r="T597" s="4" t="n"/>
       <c r="U597" s="4" t="n"/>
     </row>
-    <row r="598" ht="75" customHeight="1">
+    <row r="598" hidden="1" ht="75" customHeight="1">
       <c r="A598" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46401,7 +46400,7 @@
       <c r="T598" s="4" t="n"/>
       <c r="U598" s="4" t="n"/>
     </row>
-    <row r="599" ht="60" customHeight="1">
+    <row r="599" hidden="1" ht="60" customHeight="1">
       <c r="A599" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46476,7 +46475,7 @@
       <c r="T599" s="4" t="n"/>
       <c r="U599" s="4" t="n"/>
     </row>
-    <row r="600" ht="45" customHeight="1">
+    <row r="600" hidden="1" ht="45" customHeight="1">
       <c r="A600" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46551,7 +46550,7 @@
       <c r="T600" s="4" t="n"/>
       <c r="U600" s="4" t="n"/>
     </row>
-    <row r="601" ht="45" customHeight="1">
+    <row r="601" hidden="1" ht="45" customHeight="1">
       <c r="A601" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46622,7 +46621,7 @@
       <c r="T601" s="4" t="n"/>
       <c r="U601" s="4" t="n"/>
     </row>
-    <row r="602" ht="30" customHeight="1">
+    <row r="602" hidden="1" ht="30" customHeight="1">
       <c r="A602" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46689,7 +46688,7 @@
       <c r="T602" s="4" t="n"/>
       <c r="U602" s="4" t="n"/>
     </row>
-    <row r="603" ht="30" customHeight="1">
+    <row r="603" hidden="1" ht="30" customHeight="1">
       <c r="A603" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46756,7 +46755,7 @@
       <c r="T603" s="4" t="n"/>
       <c r="U603" s="4" t="n"/>
     </row>
-    <row r="604" ht="30" customHeight="1">
+    <row r="604" hidden="1" ht="30" customHeight="1">
       <c r="A604" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46823,7 +46822,7 @@
       <c r="T604" s="4" t="n"/>
       <c r="U604" s="4" t="n"/>
     </row>
-    <row r="605" ht="30" customHeight="1">
+    <row r="605" hidden="1" ht="30" customHeight="1">
       <c r="A605" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46890,7 +46889,7 @@
       <c r="T605" s="4" t="n"/>
       <c r="U605" s="4" t="n"/>
     </row>
-    <row r="606" ht="45" customHeight="1">
+    <row r="606" hidden="1" ht="45" customHeight="1">
       <c r="A606" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -46957,7 +46956,7 @@
       <c r="T606" s="4" t="n"/>
       <c r="U606" s="4" t="n"/>
     </row>
-    <row r="607" ht="105" customHeight="1">
+    <row r="607" hidden="1" ht="105" customHeight="1">
       <c r="A607" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -47024,7 +47023,7 @@
       <c r="T607" s="4" t="n"/>
       <c r="U607" s="4" t="n"/>
     </row>
-    <row r="608" ht="30" customHeight="1">
+    <row r="608" hidden="1" ht="30" customHeight="1">
       <c r="A608" s="8" t="inlineStr">
         <is>
           <t>TTP</t>
@@ -48288,17 +48287,17 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D625" s="6" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E625" s="6" t="inlineStr">
+        <is>
           <t>1000</t>
-        </is>
-      </c>
-      <c r="D625" s="6" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="E625" s="6" t="inlineStr">
-        <is>
-          <t>2200</t>
         </is>
       </c>
       <c r="F625" s="15" t="inlineStr">
@@ -48360,17 +48359,17 @@
       </c>
       <c r="C626" s="7" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D626" s="7" t="inlineStr">
+        <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="D626" s="7" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
       <c r="E626" s="7" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F626" s="31" t="inlineStr">
@@ -48432,17 +48431,17 @@
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="E627" s="6" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="F627" s="15" t="inlineStr">
@@ -48504,7 +48503,7 @@
       </c>
       <c r="C628" s="7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D628" s="7" t="inlineStr">
@@ -48514,7 +48513,7 @@
       </c>
       <c r="E628" s="7" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="F628" s="31" t="inlineStr">
@@ -48576,17 +48575,17 @@
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E629" s="6" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="F629" s="15" t="inlineStr">
@@ -51098,16 +51097,14 @@
           <t>0056</t>
         </is>
       </c>
-      <c r="C664" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C664" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D664" s="11" t="n">
         <v>2100</v>
       </c>
       <c r="E664" s="11" t="n">
-        <v>100</v>
+        <v>1550</v>
       </c>
       <c r="F664" s="15" t="inlineStr">
         <is>
@@ -51166,16 +51163,14 @@
           <t>0057</t>
         </is>
       </c>
-      <c r="C665" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C665" s="3" t="n">
+        <v>-10000</v>
       </c>
       <c r="D665" s="11" t="n">
-        <v>2100</v>
+        <v>10000</v>
       </c>
       <c r="E665" s="11" t="n">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="F665" s="15" t="inlineStr">
         <is>
@@ -51304,16 +51299,14 @@
           <t>0059</t>
         </is>
       </c>
-      <c r="C667" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C667" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D667" s="11" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="E667" s="11" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F667" s="15" t="inlineStr">
         <is>
@@ -51372,16 +51365,14 @@
           <t>0060</t>
         </is>
       </c>
-      <c r="C668" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C668" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D668" s="11" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E668" s="11" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F668" s="15" t="inlineStr">
         <is>
@@ -51440,13 +51431,11 @@
           <t>0061</t>
         </is>
       </c>
-      <c r="C669" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C669" s="3" t="n">
+        <v>-200</v>
       </c>
       <c r="D669" s="11" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E669" s="11" t="n">
         <v>300</v>
@@ -51508,16 +51497,14 @@
           <t>0062</t>
         </is>
       </c>
-      <c r="C670" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C670" s="3" t="n">
+        <v>-200</v>
       </c>
       <c r="D670" s="11" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E670" s="11" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F670" s="15" t="inlineStr">
         <is>
@@ -51576,16 +51563,14 @@
           <t>0063</t>
         </is>
       </c>
-      <c r="C671" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C671" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="D671" s="11" t="n">
-        <v>1100</v>
+        <v>910</v>
       </c>
       <c r="E671" s="11" t="n">
-        <v>600</v>
+        <v>910</v>
       </c>
       <c r="F671" s="15" t="inlineStr">
         <is>
@@ -51644,16 +51629,14 @@
           <t>0064</t>
         </is>
       </c>
-      <c r="C672" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C672" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="D672" s="11" t="n">
-        <v>1100</v>
+        <v>910</v>
       </c>
       <c r="E672" s="11" t="n">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="F672" s="15" t="inlineStr">
         <is>
@@ -51813,18 +51796,14 @@
       </c>
       <c r="C675" s="46" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D675" s="12" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="E675" s="12" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="D675" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E675" s="12" t="n">
+        <v>9600</v>
       </c>
       <c r="F675" s="29" t="inlineStr">
         <is>
@@ -51875,7 +51854,7 @@
       <c r="T675" s="4" t="n"/>
       <c r="U675" s="4" t="n"/>
     </row>
-    <row r="676" ht="345" customHeight="1">
+    <row r="676" hidden="1" ht="345" customHeight="1">
       <c r="A676" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -51963,7 +51942,7 @@
         </is>
       </c>
     </row>
-    <row r="677" ht="150" customHeight="1">
+    <row r="677" hidden="1" ht="150" customHeight="1">
       <c r="A677" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52037,7 +52016,7 @@
         </is>
       </c>
     </row>
-    <row r="678" ht="120" customHeight="1">
+    <row r="678" hidden="1" ht="120" customHeight="1">
       <c r="A678" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52111,7 +52090,7 @@
         </is>
       </c>
     </row>
-    <row r="679" ht="90" customHeight="1">
+    <row r="679" hidden="1" ht="90" customHeight="1">
       <c r="A679" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52179,7 +52158,7 @@
         </is>
       </c>
     </row>
-    <row r="680" ht="90" customHeight="1">
+    <row r="680" hidden="1" ht="90" customHeight="1">
       <c r="A680" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52247,7 +52226,7 @@
         </is>
       </c>
     </row>
-    <row r="681" ht="90" customHeight="1">
+    <row r="681" hidden="1" ht="90" customHeight="1">
       <c r="A681" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52315,7 +52294,7 @@
         </is>
       </c>
     </row>
-    <row r="682" ht="90" customHeight="1">
+    <row r="682" hidden="1" ht="90" customHeight="1">
       <c r="A682" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52383,7 +52362,7 @@
         </is>
       </c>
     </row>
-    <row r="683" ht="90" customHeight="1">
+    <row r="683" hidden="1" ht="90" customHeight="1">
       <c r="A683" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52451,7 +52430,7 @@
         </is>
       </c>
     </row>
-    <row r="684" ht="90" customHeight="1">
+    <row r="684" hidden="1" ht="90" customHeight="1">
       <c r="A684" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52519,7 +52498,7 @@
         </is>
       </c>
     </row>
-    <row r="685" ht="30" customHeight="1">
+    <row r="685" hidden="1" ht="30" customHeight="1">
       <c r="A685" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52587,7 +52566,7 @@
         </is>
       </c>
     </row>
-    <row r="686" ht="90" customHeight="1">
+    <row r="686" hidden="1" ht="90" customHeight="1">
       <c r="A686" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52598,16 +52577,14 @@
           <t>0011</t>
         </is>
       </c>
-      <c r="C686" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C686" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D686" s="11" t="n">
         <v>2100</v>
       </c>
       <c r="E686" s="11" t="n">
-        <v>100</v>
+        <v>1550</v>
       </c>
       <c r="F686" s="15" t="inlineStr">
         <is>
@@ -52655,7 +52632,7 @@
         </is>
       </c>
     </row>
-    <row r="687" ht="90" customHeight="1">
+    <row r="687" hidden="1" ht="90" customHeight="1">
       <c r="A687" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52666,16 +52643,14 @@
           <t>0012</t>
         </is>
       </c>
-      <c r="C687" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C687" s="3" t="n">
+        <v>-10000</v>
       </c>
       <c r="D687" s="11" t="n">
-        <v>1100</v>
+        <v>10000</v>
       </c>
       <c r="E687" s="11" t="n">
-        <v>200</v>
+        <v>980</v>
       </c>
       <c r="F687" s="15" t="inlineStr">
         <is>
@@ -52723,7 +52698,7 @@
         </is>
       </c>
     </row>
-    <row r="688" ht="90" customHeight="1">
+    <row r="688" hidden="1" ht="90" customHeight="1">
       <c r="A688" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52734,13 +52709,11 @@
           <t>0013</t>
         </is>
       </c>
-      <c r="C688" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C688" s="3" t="n">
+        <v>-200</v>
       </c>
       <c r="D688" s="11" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E688" s="11" t="n">
         <v>300</v>
@@ -52791,7 +52764,7 @@
         </is>
       </c>
     </row>
-    <row r="689" ht="30" customHeight="1">
+    <row r="689" hidden="1" ht="30" customHeight="1">
       <c r="A689" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52802,16 +52775,14 @@
           <t>0014</t>
         </is>
       </c>
-      <c r="C689" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C689" s="3" t="n">
+        <v>-200</v>
       </c>
       <c r="D689" s="11" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E689" s="11" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F689" s="15" t="inlineStr">
         <is>
@@ -52859,7 +52830,7 @@
         </is>
       </c>
     </row>
-    <row r="690" ht="30" customHeight="1">
+    <row r="690" hidden="1" ht="30" customHeight="1">
       <c r="A690" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52870,16 +52841,14 @@
           <t>0015</t>
         </is>
       </c>
-      <c r="C690" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C690" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="D690" s="11" t="n">
-        <v>1100</v>
+        <v>910</v>
       </c>
       <c r="E690" s="11" t="n">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="F690" s="15" t="inlineStr">
         <is>
@@ -52927,7 +52896,7 @@
         </is>
       </c>
     </row>
-    <row r="691" ht="30" customHeight="1">
+    <row r="691" hidden="1" ht="30" customHeight="1">
       <c r="A691" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -52938,16 +52907,14 @@
           <t>0016</t>
         </is>
       </c>
-      <c r="C691" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C691" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="D691" s="11" t="n">
-        <v>1100</v>
+        <v>910</v>
       </c>
       <c r="E691" s="11" t="n">
-        <v>600</v>
+        <v>910</v>
       </c>
       <c r="F691" s="15" t="inlineStr">
         <is>
@@ -52995,7 +52962,7 @@
         </is>
       </c>
     </row>
-    <row r="692" ht="30" customHeight="1">
+    <row r="692" hidden="1" ht="30" customHeight="1">
       <c r="A692" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53006,16 +52973,14 @@
           <t>0017</t>
         </is>
       </c>
-      <c r="C692" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C692" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D692" s="11" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E692" s="11" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F692" s="15" t="inlineStr">
         <is>
@@ -53063,7 +53028,7 @@
         </is>
       </c>
     </row>
-    <row r="693" ht="90" customHeight="1">
+    <row r="693" hidden="1" ht="90" customHeight="1">
       <c r="A693" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53131,7 +53096,7 @@
         </is>
       </c>
     </row>
-    <row r="694" ht="90" customHeight="1">
+    <row r="694" hidden="1" ht="90" customHeight="1">
       <c r="A694" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53197,7 +53162,7 @@
         </is>
       </c>
     </row>
-    <row r="695" ht="90" customHeight="1">
+    <row r="695" hidden="1" ht="90" customHeight="1">
       <c r="A695" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53263,7 +53228,7 @@
         </is>
       </c>
     </row>
-    <row r="696" ht="90" customHeight="1">
+    <row r="696" hidden="1" ht="90" customHeight="1">
       <c r="A696" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53329,7 +53294,7 @@
         </is>
       </c>
     </row>
-    <row r="697" ht="409.5" customHeight="1">
+    <row r="697" hidden="1" ht="409.5" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53429,7 +53394,7 @@
         </is>
       </c>
     </row>
-    <row r="698" ht="409.5" customHeight="1">
+    <row r="698" hidden="1" ht="409.5" customHeight="1">
       <c r="A698" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53528,7 +53493,7 @@
         </is>
       </c>
     </row>
-    <row r="699" ht="409.5" customHeight="1">
+    <row r="699" hidden="1" ht="409.5" customHeight="1">
       <c r="A699" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53628,7 +53593,7 @@
         </is>
       </c>
     </row>
-    <row r="700" ht="409.5" customHeight="1">
+    <row r="700" hidden="1" ht="409.5" customHeight="1">
       <c r="A700" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53728,7 +53693,7 @@
         </is>
       </c>
     </row>
-    <row r="701" ht="105" customHeight="1">
+    <row r="701" hidden="1" ht="105" customHeight="1">
       <c r="A701" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53802,7 +53767,7 @@
         </is>
       </c>
     </row>
-    <row r="702" ht="90" customHeight="1">
+    <row r="702" hidden="1" ht="90" customHeight="1">
       <c r="A702" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53875,7 +53840,7 @@
         </is>
       </c>
     </row>
-    <row r="703" ht="135" customHeight="1">
+    <row r="703" hidden="1" ht="135" customHeight="1">
       <c r="A703" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -53943,7 +53908,7 @@
         </is>
       </c>
     </row>
-    <row r="704" ht="60" customHeight="1">
+    <row r="704" hidden="1" ht="60" customHeight="1">
       <c r="A704" s="29" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -54010,7 +53975,7 @@
       <c r="T704" s="4" t="n"/>
       <c r="U704" s="4" t="n"/>
     </row>
-    <row r="705" ht="60" customHeight="1">
+    <row r="705" hidden="1" ht="60" customHeight="1">
       <c r="A705" s="29" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -54080,7 +54045,7 @@
       <c r="T705" s="4" t="n"/>
       <c r="U705" s="4" t="n"/>
     </row>
-    <row r="706" ht="90" customHeight="1">
+    <row r="706" hidden="1" ht="90" customHeight="1">
       <c r="A706" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -54150,7 +54115,7 @@
         </is>
       </c>
     </row>
-    <row r="707" ht="90" customHeight="1">
+    <row r="707" hidden="1" ht="90" customHeight="1">
       <c r="A707" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
@@ -54161,16 +54126,14 @@
           <t>0032</t>
         </is>
       </c>
-      <c r="C707" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C707" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D707" s="11" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="E707" s="11" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F707" s="15" t="inlineStr">
         <is>
@@ -54426,7 +54389,7 @@
       <c r="Q712" s="22" t="n"/>
       <c r="R712" s="22" t="n"/>
     </row>
-    <row r="713" hidden="1" ht="45" customHeight="1">
+    <row r="713" ht="45" customHeight="1">
       <c r="A713" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54503,7 +54466,7 @@
         </is>
       </c>
     </row>
-    <row r="714" hidden="1" ht="30" customHeight="1">
+    <row r="714" ht="30" customHeight="1">
       <c r="A714" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54579,7 +54542,7 @@
         </is>
       </c>
     </row>
-    <row r="715" hidden="1" ht="90" customHeight="1">
+    <row r="715" ht="90" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54655,7 +54618,7 @@
         </is>
       </c>
     </row>
-    <row r="716" hidden="1" ht="45" customHeight="1">
+    <row r="716" ht="45" customHeight="1">
       <c r="A716" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54666,10 +54629,8 @@
           <t>0004</t>
         </is>
       </c>
-      <c r="C716" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C716" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D716" s="11" t="n">
         <v>1</v>
@@ -54731,7 +54692,7 @@
         </is>
       </c>
     </row>
-    <row r="717" hidden="1" ht="45" customHeight="1">
+    <row r="717" ht="45" customHeight="1">
       <c r="A717" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54742,10 +54703,8 @@
           <t>0005</t>
         </is>
       </c>
-      <c r="C717" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C717" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D717" s="11" t="n">
         <v>1</v>
@@ -54807,7 +54766,7 @@
         </is>
       </c>
     </row>
-    <row r="718" hidden="1" ht="45" customHeight="1">
+    <row r="718" ht="45" customHeight="1">
       <c r="A718" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54818,10 +54777,8 @@
           <t>0006</t>
         </is>
       </c>
-      <c r="C718" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C718" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D718" s="11" t="n">
         <v>1</v>
@@ -54883,7 +54840,7 @@
         </is>
       </c>
     </row>
-    <row r="719" hidden="1" ht="45" customHeight="1">
+    <row r="719" ht="45" customHeight="1">
       <c r="A719" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54894,10 +54851,8 @@
           <t>0007</t>
         </is>
       </c>
-      <c r="C719" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C719" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D719" s="11" t="n">
         <v>1</v>
@@ -54959,7 +54914,7 @@
         </is>
       </c>
     </row>
-    <row r="720" hidden="1" ht="45" customHeight="1">
+    <row r="720" ht="45" customHeight="1">
       <c r="A720" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -54970,10 +54925,8 @@
           <t>0008</t>
         </is>
       </c>
-      <c r="C720" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C720" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D720" s="11" t="n">
         <v>1</v>
@@ -55035,7 +54988,7 @@
         </is>
       </c>
     </row>
-    <row r="721" hidden="1" ht="45" customHeight="1">
+    <row r="721" ht="45" customHeight="1">
       <c r="A721" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55046,10 +54999,8 @@
           <t>0009</t>
         </is>
       </c>
-      <c r="C721" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C721" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D721" s="11" t="n">
         <v>1</v>
@@ -55111,7 +55062,7 @@
         </is>
       </c>
     </row>
-    <row r="722" hidden="1" ht="45" customHeight="1">
+    <row r="722" ht="45" customHeight="1">
       <c r="A722" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55122,10 +55073,8 @@
           <t>0010</t>
         </is>
       </c>
-      <c r="C722" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C722" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D722" s="11" t="n">
         <v>1</v>
@@ -55187,7 +55136,7 @@
         </is>
       </c>
     </row>
-    <row r="723" hidden="1" ht="90" customHeight="1">
+    <row r="723" ht="90" customHeight="1">
       <c r="A723" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55263,7 +55212,7 @@
         </is>
       </c>
     </row>
-    <row r="724" hidden="1" ht="90" customHeight="1">
+    <row r="724" ht="90" customHeight="1">
       <c r="A724" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55339,7 +55288,7 @@
         </is>
       </c>
     </row>
-    <row r="725" hidden="1" ht="90" customHeight="1">
+    <row r="725" ht="90" customHeight="1">
       <c r="A725" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55415,7 +55364,7 @@
         </is>
       </c>
     </row>
-    <row r="726" hidden="1" ht="90" customHeight="1">
+    <row r="726" ht="90" customHeight="1">
       <c r="A726" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55491,7 +55440,7 @@
         </is>
       </c>
     </row>
-    <row r="727" hidden="1" ht="30" customHeight="1">
+    <row r="727" ht="30" customHeight="1">
       <c r="A727" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55567,7 +55516,7 @@
         </is>
       </c>
     </row>
-    <row r="728" hidden="1" ht="90" customHeight="1">
+    <row r="728" ht="90" customHeight="1">
       <c r="A728" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55643,7 +55592,7 @@
         </is>
       </c>
     </row>
-    <row r="729" hidden="1" ht="90" customHeight="1">
+    <row r="729" ht="90" customHeight="1">
       <c r="A729" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55719,7 +55668,7 @@
         </is>
       </c>
     </row>
-    <row r="730" hidden="1" ht="45" customHeight="1">
+    <row r="730" ht="45" customHeight="1">
       <c r="A730" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55795,7 +55744,7 @@
         </is>
       </c>
     </row>
-    <row r="731" hidden="1" ht="90" customHeight="1">
+    <row r="731" ht="90" customHeight="1">
       <c r="A731" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55871,7 +55820,7 @@
         </is>
       </c>
     </row>
-    <row r="732" hidden="1" ht="90" customHeight="1">
+    <row r="732" ht="90" customHeight="1">
       <c r="A732" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -55947,7 +55896,7 @@
         </is>
       </c>
     </row>
-    <row r="733" hidden="1" ht="30" customHeight="1">
+    <row r="733" ht="30" customHeight="1">
       <c r="A733" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56023,7 +55972,7 @@
         </is>
       </c>
     </row>
-    <row r="734" hidden="1" ht="30" customHeight="1">
+    <row r="734" ht="30" customHeight="1">
       <c r="A734" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56099,7 +56048,7 @@
         </is>
       </c>
     </row>
-    <row r="735" hidden="1" ht="45" customHeight="1">
+    <row r="735" ht="45" customHeight="1">
       <c r="A735" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56176,7 +56125,7 @@
         </is>
       </c>
     </row>
-    <row r="736" hidden="1" ht="90" customHeight="1">
+    <row r="736" ht="90" customHeight="1">
       <c r="A736" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56252,7 +56201,7 @@
         </is>
       </c>
     </row>
-    <row r="737" hidden="1" ht="90" customHeight="1">
+    <row r="737" ht="90" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56328,7 +56277,7 @@
         </is>
       </c>
     </row>
-    <row r="738" hidden="1" ht="90" customHeight="1">
+    <row r="738" ht="90" customHeight="1">
       <c r="A738" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56404,7 +56353,7 @@
         </is>
       </c>
     </row>
-    <row r="739" hidden="1" ht="30" customHeight="1">
+    <row r="739" ht="30" customHeight="1">
       <c r="A739" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56481,7 +56430,7 @@
         </is>
       </c>
     </row>
-    <row r="740" hidden="1" ht="30" customHeight="1">
+    <row r="740" ht="30" customHeight="1">
       <c r="A740" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56557,7 +56506,7 @@
         </is>
       </c>
     </row>
-    <row r="741" hidden="1" ht="75" customHeight="1">
+    <row r="741" ht="75" customHeight="1">
       <c r="A741" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56633,7 +56582,7 @@
         </is>
       </c>
     </row>
-    <row r="742" hidden="1" ht="30" customHeight="1">
+    <row r="742" ht="30" customHeight="1">
       <c r="A742" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56709,7 +56658,7 @@
         </is>
       </c>
     </row>
-    <row r="743" hidden="1" ht="30" customHeight="1">
+    <row r="743" ht="30" customHeight="1">
       <c r="A743" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56788,7 +56737,7 @@
       <c r="T743" s="4" t="n"/>
       <c r="U743" s="4" t="n"/>
     </row>
-    <row r="744" hidden="1" ht="75" customHeight="1">
+    <row r="744" ht="75" customHeight="1">
       <c r="A744" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56864,7 +56813,7 @@
         </is>
       </c>
     </row>
-    <row r="745" hidden="1" ht="30" customHeight="1">
+    <row r="745" ht="30" customHeight="1">
       <c r="A745" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -56940,7 +56889,7 @@
         </is>
       </c>
     </row>
-    <row r="746" hidden="1" ht="30" customHeight="1">
+    <row r="746" ht="30" customHeight="1">
       <c r="A746" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57016,7 +56965,7 @@
         </is>
       </c>
     </row>
-    <row r="747" hidden="1" ht="30" customHeight="1">
+    <row r="747" ht="30" customHeight="1">
       <c r="A747" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57095,7 +57044,7 @@
       <c r="T747" s="4" t="n"/>
       <c r="U747" s="4" t="n"/>
     </row>
-    <row r="748" hidden="1" ht="90" customHeight="1">
+    <row r="748" ht="90" customHeight="1">
       <c r="A748" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57171,7 +57120,7 @@
         </is>
       </c>
     </row>
-    <row r="749" hidden="1" ht="90" customHeight="1">
+    <row r="749" ht="90" customHeight="1">
       <c r="A749" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57247,7 +57196,7 @@
         </is>
       </c>
     </row>
-    <row r="750" hidden="1" ht="90" customHeight="1">
+    <row r="750" ht="90" customHeight="1">
       <c r="A750" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57319,7 +57268,7 @@
         </is>
       </c>
     </row>
-    <row r="751" hidden="1" ht="90" customHeight="1">
+    <row r="751" ht="90" customHeight="1">
       <c r="A751" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57391,7 +57340,7 @@
         </is>
       </c>
     </row>
-    <row r="752" hidden="1" ht="90" customHeight="1">
+    <row r="752" ht="90" customHeight="1">
       <c r="A752" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57463,7 +57412,7 @@
         </is>
       </c>
     </row>
-    <row r="753" hidden="1" ht="30" customHeight="1">
+    <row r="753" ht="30" customHeight="1">
       <c r="A753" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57535,7 +57484,7 @@
         </is>
       </c>
     </row>
-    <row r="754" hidden="1" ht="90" customHeight="1">
+    <row r="754" ht="90" customHeight="1">
       <c r="A754" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57607,7 +57556,7 @@
         </is>
       </c>
     </row>
-    <row r="755" hidden="1" ht="30" customHeight="1">
+    <row r="755" ht="30" customHeight="1">
       <c r="A755" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57683,7 +57632,7 @@
         </is>
       </c>
     </row>
-    <row r="756" hidden="1" ht="45" customHeight="1">
+    <row r="756" ht="45" customHeight="1">
       <c r="A756" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57755,7 +57704,7 @@
         </is>
       </c>
     </row>
-    <row r="757" hidden="1" ht="45" customHeight="1">
+    <row r="757" ht="45" customHeight="1">
       <c r="A757" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57831,7 +57780,7 @@
         </is>
       </c>
     </row>
-    <row r="758" hidden="1" ht="150" customHeight="1">
+    <row r="758" ht="150" customHeight="1">
       <c r="A758" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57842,10 +57791,8 @@
           <t>0046</t>
         </is>
       </c>
-      <c r="C758" s="43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C758" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="D758" s="11" t="n">
         <v>1</v>
@@ -57907,7 +57854,7 @@
         </is>
       </c>
     </row>
-    <row r="759" hidden="1" ht="120" customHeight="1">
+    <row r="759" ht="120" customHeight="1">
       <c r="A759" s="10" t="inlineStr">
         <is>
           <t>MAE</t>
@@ -57918,10 +57865,8 @@
           <t>0047</t>
         </is>
       </c>
-      <c r="C759" s="43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C759" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="D759" s="11" t="n">
         <v>1</v>
@@ -58255,7 +58200,7 @@
       <c r="T763" s="4" t="n"/>
       <c r="U763" s="4" t="n"/>
     </row>
-    <row r="764" hidden="1">
+    <row r="764" hidden="1" ht="135" customHeight="1">
       <c r="A764" s="10" t="inlineStr">
         <is>
           <t>MAC</t>
@@ -58324,7 +58269,7 @@
       <c r="T764" s="4" t="n"/>
       <c r="U764" s="4" t="n"/>
     </row>
-    <row r="765" hidden="1">
+    <row r="765" hidden="1" ht="135" customHeight="1">
       <c r="A765" s="10" t="inlineStr">
         <is>
           <t>MAC</t>
@@ -58708,4 +58653,296 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19930CF4-2EE6-43B1-B275-7A602E166EFE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64468085-42FE-47F1-A7E2-4F975A580B50}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0AB6D09-120D-4712-8811-F293FA38E8C9}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="rng_Lieferanten">#REF!</definedName>
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U780"/>
+  <dimension ref="A1:U781"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="16.140625" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
@@ -57928,22 +57928,22 @@
         </is>
       </c>
     </row>
-    <row r="760" hidden="1" ht="135" customHeight="1">
+    <row r="760" hidden="1" ht="120" customHeight="1">
       <c r="A760" s="10" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>MAE</t>
         </is>
       </c>
       <c r="B760" s="8" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0048</t>
         </is>
       </c>
       <c r="C760" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D760" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E760" s="12" t="n">
         <v>0</v>
@@ -57952,22 +57952,22 @@
       <c r="G760" s="29" t="n"/>
       <c r="H760" s="29" t="inlineStr">
         <is>
-          <t>R/W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I760" s="29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J760" s="29" t="inlineStr">
         <is>
-          <t>uint8</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="K760" s="29" t="inlineStr">
         <is>
-          <t>Temporaerer IBN/Test Prozessbefehl</t>
+          <t>MAE0048 Etikettenantrieb Nachpositionierung Toleranz nicht erreicht</t>
         </is>
       </c>
       <c r="L760" s="28" t="n"/>
@@ -57978,15 +57978,27 @@
       </c>
       <c r="N760" s="28" t="inlineStr">
         <is>
-          <t>0=Stop, 1=Wickler einmessen+Messfahrt, 2=Taktbetrieb, 3=Vorziehen kontinuierlich, 4=Zurueckspulen kontinuierlich</t>
-        </is>
-      </c>
-      <c r="O760" s="28" t="n"/>
-      <c r="P760" s="28" t="n"/>
-      <c r="Q760" s="28" t="n"/>
+          <t>Etikettenantrieb Nachpositionierung: Toleranz +/-0.05 mm nach 3 Versuchen nicht erreicht</t>
+        </is>
+      </c>
+      <c r="O760" s="28" t="inlineStr">
+        <is>
+          <t>Schlupf, mechanische Blockade, falsche Motoraufl?sung, Encoderabweichung oder AZD-Parameter ausserhalb des stabilen Bereichs</t>
+        </is>
+      </c>
+      <c r="P760" s="28" t="inlineStr">
+        <is>
+          <t>Mess-/Taktposition wird verworfen; Produktion oder Einrichten wird abgebrochen, weil die Druckposition nicht garantiert werden kann</t>
+        </is>
+      </c>
+      <c r="Q760" s="28" t="inlineStr">
+        <is>
+          <t>Mechanik, Bandspannung, Motoraufl?sung, Encoderwerte und AZD-Parameter pr?fen; danach Reset und erneutes Einrichten ausf?hren</t>
+        </is>
+      </c>
       <c r="R760" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0001 als temporaeren IBN-/Testbefehl von Microtom an den Raspi. Der Raspi uebersetzt diesen Wert in produktionsnahe Startkommandos fuer ESP32-PLC und Wickler. Dieser Parameter ist ausdruecklich nur fuer Inbetriebnahme/Test vorgesehen und muss spaeter entfernt oder durch produktive MAS/MAP-Ablaufbefehle ersetzt werden. Der ESP soll ihn gemaess Masterliste nicht direkt als normalen Parameter verwenden. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0048 als Stoerungsmeldung, wenn Motor 3 nach einer Mess- oder Taktposition seine Sollposition trotz maximal drei Nachpositionierungen nicht innerhalb von +/-0.05 mm erreicht. Waehrend dieser Nachpositionierung muessen Abwickler und Aufwickler stillstehen und duerfen nicht selbst nachregeln.</t>
         </is>
       </c>
       <c r="S760" s="4" t="n"/>
@@ -58001,23 +58013,19 @@
       </c>
       <c r="B761" s="8" t="inlineStr">
         <is>
-          <t>0002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="C761" s="46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D761" s="12" t="n">
-        <v>5000</v>
+        <v>4</v>
       </c>
       <c r="E761" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F761" s="29" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F761" s="29" t="n"/>
       <c r="G761" s="29" t="n"/>
       <c r="H761" s="29" t="inlineStr">
         <is>
@@ -58031,12 +58039,12 @@
       </c>
       <c r="J761" s="29" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="K761" s="29" t="inlineStr">
         <is>
-          <t>Temporaere Takt-/Labellaenge</t>
+          <t>Temporaerer IBN/Test Prozessbefehl</t>
         </is>
       </c>
       <c r="L761" s="28" t="n"/>
@@ -58047,7 +58055,7 @@
       </c>
       <c r="N761" s="28" t="inlineStr">
         <is>
-          <t>Labelweg fuer getakteten Testbetrieb in 1/10 mm</t>
+          <t>0=Stop, 1=Wickler einmessen+Messfahrt, 2=Taktbetrieb, 3=Vorziehen kontinuierlich, 4=Zurueckspulen kontinuierlich</t>
         </is>
       </c>
       <c r="O761" s="28" t="n"/>
@@ -58055,7 +58063,7 @@
       <c r="Q761" s="28" t="n"/>
       <c r="R761" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0002 als temporaere Labellaenge bzw. Taktstrecke fuer den IBN-Test. Default 1000 bedeutet 100.0 mm. Spaeter kommt dieser Wert aus Rezept-/Formatdaten und Etiketteneinmessung, nicht mehr aus einem MAC-Testparameter. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAC0001 als temporaeren IBN-/Testbefehl von Microtom an den Raspi. Der Raspi uebersetzt diesen Wert in produktionsnahe Startkommandos fuer ESP32-PLC und Wickler. Dieser Parameter ist ausdruecklich nur fuer Inbetriebnahme/Test vorgesehen und muss spaeter entfernt oder durch produktive MAS/MAP-Ablaufbefehle ersetzt werden. Der ESP soll ihn gemaess Masterliste nicht direkt als normalen Parameter verwenden. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="S761" s="4" t="n"/>
@@ -58070,21 +58078,21 @@
       </c>
       <c r="B762" s="8" t="inlineStr">
         <is>
-          <t>0003</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="C762" s="46" t="n">
         <v>1</v>
       </c>
       <c r="D762" s="12" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="E762" s="12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F762" s="29" t="inlineStr">
         <is>
-          <t>mm/s</t>
+          <t>1/10mm</t>
         </is>
       </c>
       <c r="G762" s="29" t="n"/>
@@ -58105,7 +58113,7 @@
       </c>
       <c r="K762" s="29" t="inlineStr">
         <is>
-          <t>Temporaere Vorzugsgeschwindigkeit</t>
+          <t>Temporaere Takt-/Labellaenge</t>
         </is>
       </c>
       <c r="L762" s="28" t="n"/>
@@ -58116,7 +58124,7 @@
       </c>
       <c r="N762" s="28" t="inlineStr">
         <is>
-          <t>Sollgeschwindigkeit fuer kontinuierlichen und getakteten IBN-Testbetrieb</t>
+          <t>Labelweg fuer getakteten Testbetrieb in 1/10 mm</t>
         </is>
       </c>
       <c r="O762" s="28" t="n"/>
@@ -58124,7 +58132,7 @@
       <c r="Q762" s="28" t="n"/>
       <c r="R762" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0003 als temporaere Vorzugsgeschwindigkeit fuer Motor 3 im IBN-Test. Wird kein neuer Wert gesetzt, verwendet der Raspi den zuletzt gespeicherten Wert. Produktiv wird die Geschwindigkeit ueber MAP0014 bzw. die Betriebsart vorgegeben. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAC0002 als temporaere Labellaenge bzw. Taktstrecke fuer den IBN-Test. Default 1000 bedeutet 100.0 mm. Spaeter kommt dieser Wert aus Rezept-/Formatdaten und Etiketteneinmessung, nicht mehr aus einem MAC-Testparameter. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="S762" s="4" t="n"/>
@@ -58139,21 +58147,21 @@
       </c>
       <c r="B763" s="8" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="C763" s="46" t="n">
         <v>1</v>
       </c>
       <c r="D763" s="12" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
       <c r="E763" s="12" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F763" s="29" t="inlineStr">
         <is>
-          <t>mm/s2</t>
+          <t>mm/s</t>
         </is>
       </c>
       <c r="G763" s="29" t="n"/>
@@ -58174,7 +58182,7 @@
       </c>
       <c r="K763" s="29" t="inlineStr">
         <is>
-          <t>Temporaere Transport-Rampe</t>
+          <t>Temporaere Vorzugsgeschwindigkeit</t>
         </is>
       </c>
       <c r="L763" s="28" t="n"/>
@@ -58185,7 +58193,7 @@
       </c>
       <c r="N763" s="28" t="inlineStr">
         <is>
-          <t>Beschleunigung/Verzoegerung fuer Motor 3 im IBN-Testbetrieb</t>
+          <t>Sollgeschwindigkeit fuer kontinuierlichen und getakteten IBN-Testbetrieb</t>
         </is>
       </c>
       <c r="O763" s="28" t="n"/>
@@ -58193,7 +58201,7 @@
       <c r="Q763" s="28" t="n"/>
       <c r="R763" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0004 als temporaere Rampe fuer Beschleunigung und Bremsung des Etikettenantriebs im IBN-Test. Produktiv wird diese Vorgabe aus Maschinen- bzw. Formatparametern abgeleitet und darf den Etikettenschlupf nicht erhoehen. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s2. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAC0003 als temporaere Vorzugsgeschwindigkeit fuer Motor 3 im IBN-Test. Wird kein neuer Wert gesetzt, verwendet der Raspi den zuletzt gespeicherten Wert. Produktiv wird die Geschwindigkeit ueber MAP0014 bzw. die Betriebsart vorgegeben. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="S763" s="4" t="n"/>
@@ -58208,21 +58216,21 @@
       </c>
       <c r="B764" s="8" t="inlineStr">
         <is>
-          <t>0005</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="C764" s="46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D764" s="12" t="n">
-        <v>100000</v>
+        <v>6000</v>
       </c>
       <c r="E764" s="12" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F764" s="29" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>mm/s2</t>
         </is>
       </c>
       <c r="G764" s="29" t="n"/>
@@ -58238,12 +58246,12 @@
       </c>
       <c r="J764" s="29" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K764" s="29" t="inlineStr">
         <is>
-          <t>Temporaere kontinuierliche Weglaenge</t>
+          <t>Temporaere Transport-Rampe</t>
         </is>
       </c>
       <c r="L764" s="28" t="n"/>
@@ -58254,7 +58262,7 @@
       </c>
       <c r="N764" s="28" t="inlineStr">
         <is>
-          <t>Weg fuer kontinuierliches Vorziehen/Rueckspulen; 0=endlos bis Stop</t>
+          <t>Beschleunigung/Verzoegerung fuer Motor 3 im IBN-Testbetrieb</t>
         </is>
       </c>
       <c r="O764" s="28" t="n"/>
@@ -58262,7 +58270,7 @@
       <c r="Q764" s="28" t="n"/>
       <c r="R764" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0005 als temporaere Wegvorgabe fuer kontinuierliches Vorziehen oder Rueckspulen. Default 0 bedeutet endlos fahren bis MAC0001=0. Produktiv wird diese Laenge aus Ablaufzustand, Rueckspulweg oder Bedienhandlung bestimmt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAC0004 als temporaere Rampe fuer Beschleunigung und Bremsung des Etikettenantriebs im IBN-Test. Produktiv wird diese Vorgabe aus Maschinen- bzw. Formatparametern abgeleitet und darf den Etikettenschlupf nicht erhoehen. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s2. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="S764" s="4" t="n"/>
@@ -58277,21 +58285,21 @@
       </c>
       <c r="B765" s="8" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>0005</t>
         </is>
       </c>
       <c r="C765" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D765" s="12" t="n">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="E765" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F765" s="29" t="inlineStr">
         <is>
-          <t>Zyklen</t>
+          <t>1/10mm</t>
         </is>
       </c>
       <c r="G765" s="29" t="n"/>
@@ -58307,12 +58315,12 @@
       </c>
       <c r="J765" s="29" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="K765" s="29" t="inlineStr">
         <is>
-          <t>Temporaere Taktzyklus-Anzahl</t>
+          <t>Temporaere kontinuierliche Weglaenge</t>
         </is>
       </c>
       <c r="L765" s="28" t="n"/>
@@ -58323,7 +58331,7 @@
       </c>
       <c r="N765" s="28" t="inlineStr">
         <is>
-          <t>Anzahl Takte im Testbetrieb; 0=endlos bis Stop</t>
+          <t>Weg fuer kontinuierliches Vorziehen/Rueckspulen; 0=endlos bis Stop</t>
         </is>
       </c>
       <c r="O765" s="28" t="n"/>
@@ -58331,7 +58339,7 @@
       <c r="Q765" s="28" t="n"/>
       <c r="R765" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAC0006 als temporaere Zyklusanzahl fuer den getakteten IBN-Test. Default 20 entspricht einem kurzen Stabilitaetstest; 0 bedeutet laufender Taktbetrieb bis MAC0001=0. Spaeter wird diese Logik durch den echten Produktionsablauf und das Schieberegister ersetzt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Zyklen. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAC0005 als temporaere Wegvorgabe fuer kontinuierliches Vorziehen oder Rueckspulen. Default 0 bedeutet endlos fahren bis MAC0001=0. Produktiv wird diese Laenge aus Ablaufzustand, Rueckspulweg oder Bedienhandlung bestimmt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
       <c r="S765" s="4" t="n"/>
@@ -58339,24 +58347,73 @@
       <c r="U765" s="4" t="n"/>
     </row>
     <row r="766" hidden="1">
-      <c r="A766" s="10" t="n"/>
-      <c r="B766" s="8" t="n"/>
-      <c r="C766" s="43" t="n"/>
-      <c r="D766" s="11" t="n"/>
-      <c r="E766" s="11" t="n"/>
-      <c r="F766" s="15" t="n"/>
-      <c r="G766" s="15" t="n"/>
-      <c r="H766" s="15" t="n"/>
-      <c r="I766" s="15" t="n"/>
-      <c r="J766" s="15" t="n"/>
-      <c r="K766" s="15" t="n"/>
-      <c r="L766" s="22" t="n"/>
-      <c r="M766" s="22" t="n"/>
-      <c r="N766" s="22" t="n"/>
-      <c r="O766" s="22" t="n"/>
-      <c r="P766" s="22" t="n"/>
-      <c r="Q766" s="22" t="n"/>
-      <c r="R766" s="22" t="n"/>
+      <c r="A766" s="10" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="B766" s="8" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="C766" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D766" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E766" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F766" s="29" t="inlineStr">
+        <is>
+          <t>Zyklen</t>
+        </is>
+      </c>
+      <c r="G766" s="29" t="n"/>
+      <c r="H766" s="29" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="I766" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J766" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K766" s="29" t="inlineStr">
+        <is>
+          <t>Temporaere Taktzyklus-Anzahl</t>
+        </is>
+      </c>
+      <c r="L766" s="28" t="n"/>
+      <c r="M766" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N766" s="28" t="inlineStr">
+        <is>
+          <t>Anzahl Takte im Testbetrieb; 0=endlos bis Stop</t>
+        </is>
+      </c>
+      <c r="O766" s="28" t="n"/>
+      <c r="P766" s="28" t="n"/>
+      <c r="Q766" s="28" t="n"/>
+      <c r="R766" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAC0006 als temporaere Zyklusanzahl fuer den getakteten IBN-Test. Default 20 entspricht einem kurzen Stabilitaetstest; 0 bedeutet laufender Taktbetrieb bis MAC0001=0. Spaeter wird diese Logik durch den echten Produktionsablauf und das Schieberegister ersetzt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Zyklen. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="S766" s="4" t="n"/>
+      <c r="T766" s="4" t="n"/>
+      <c r="U766" s="4" t="n"/>
     </row>
     <row r="767" hidden="1">
       <c r="A767" s="10" t="n"/>
@@ -58638,6 +58695,26 @@
       <c r="Q780" s="22" t="n"/>
       <c r="R780" s="22" t="n"/>
     </row>
+    <row r="781">
+      <c r="A781" s="10" t="n"/>
+      <c r="B781" s="8" t="n"/>
+      <c r="C781" s="43" t="n"/>
+      <c r="D781" s="11" t="n"/>
+      <c r="E781" s="11" t="n"/>
+      <c r="F781" s="15" t="n"/>
+      <c r="G781" s="15" t="n"/>
+      <c r="H781" s="15" t="n"/>
+      <c r="I781" s="15" t="n"/>
+      <c r="J781" s="15" t="n"/>
+      <c r="K781" s="15" t="n"/>
+      <c r="L781" s="22" t="n"/>
+      <c r="M781" s="22" t="n"/>
+      <c r="N781" s="22" t="n"/>
+      <c r="O781" s="22" t="n"/>
+      <c r="P781" s="22" t="n"/>
+      <c r="Q781" s="22" t="n"/>
+      <c r="R781" s="22" t="n"/>
+    </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation sqref="M1:M1048576 P2:P119" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -58653,296 +58730,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19930CF4-2EE6-43B1-B275-7A602E166EFE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64468085-42FE-47F1-A7E2-4F975A580B50}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0AB6D09-120D-4712-8811-F293FA38E8C9}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U781"/>
+  <dimension ref="A1:U775"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="16.140625" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
@@ -58006,414 +58006,124 @@
       <c r="U760" s="4" t="n"/>
     </row>
     <row r="761" hidden="1" ht="120" customHeight="1">
-      <c r="A761" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B761" s="8" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="C761" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D761" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E761" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F761" s="29" t="n"/>
-      <c r="G761" s="29" t="n"/>
-      <c r="H761" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I761" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J761" s="29" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="K761" s="29" t="inlineStr">
-        <is>
-          <t>Temporaerer IBN/Test Prozessbefehl</t>
-        </is>
-      </c>
-      <c r="L761" s="28" t="n"/>
-      <c r="M761" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N761" s="28" t="inlineStr">
-        <is>
-          <t>0=Stop, 1=Wickler einmessen+Messfahrt, 2=Taktbetrieb, 3=Vorziehen kontinuierlich, 4=Zurueckspulen kontinuierlich</t>
-        </is>
-      </c>
-      <c r="O761" s="28" t="n"/>
-      <c r="P761" s="28" t="n"/>
-      <c r="Q761" s="28" t="n"/>
-      <c r="R761" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0001 als temporaeren IBN-/Testbefehl von Microtom an den Raspi. Der Raspi uebersetzt diesen Wert in produktionsnahe Startkommandos fuer ESP32-PLC und Wickler. Dieser Parameter ist ausdruecklich nur fuer Inbetriebnahme/Test vorgesehen und muss spaeter entfernt oder durch produktive MAS/MAP-Ablaufbefehle ersetzt werden. Der ESP soll ihn gemaess Masterliste nicht direkt als normalen Parameter verwenden. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S761" s="4" t="n"/>
-      <c r="T761" s="4" t="n"/>
-      <c r="U761" s="4" t="n"/>
+      <c r="A761" s="10" t="n"/>
+      <c r="B761" s="8" t="n"/>
+      <c r="C761" s="43" t="n"/>
+      <c r="D761" s="11" t="n"/>
+      <c r="E761" s="11" t="n"/>
+      <c r="F761" s="15" t="n"/>
+      <c r="G761" s="15" t="n"/>
+      <c r="H761" s="15" t="n"/>
+      <c r="I761" s="15" t="n"/>
+      <c r="J761" s="15" t="n"/>
+      <c r="K761" s="15" t="n"/>
+      <c r="L761" s="22" t="n"/>
+      <c r="M761" s="22" t="n"/>
+      <c r="N761" s="22" t="n"/>
+      <c r="O761" s="22" t="n"/>
+      <c r="P761" s="22" t="n"/>
+      <c r="Q761" s="22" t="n"/>
+      <c r="R761" s="22" t="n"/>
     </row>
     <row r="762" hidden="1" ht="135" customHeight="1">
-      <c r="A762" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B762" s="8" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="C762" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D762" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E762" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F762" s="29" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G762" s="29" t="n"/>
-      <c r="H762" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I762" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J762" s="29" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K762" s="29" t="inlineStr">
-        <is>
-          <t>Temporaere Takt-/Labellaenge</t>
-        </is>
-      </c>
-      <c r="L762" s="28" t="n"/>
-      <c r="M762" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N762" s="28" t="inlineStr">
-        <is>
-          <t>Labelweg fuer getakteten Testbetrieb in 1/10 mm</t>
-        </is>
-      </c>
-      <c r="O762" s="28" t="n"/>
-      <c r="P762" s="28" t="n"/>
-      <c r="Q762" s="28" t="n"/>
-      <c r="R762" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0002 als temporaere Labellaenge bzw. Taktstrecke fuer den IBN-Test. Default 1000 bedeutet 100.0 mm. Spaeter kommt dieser Wert aus Rezept-/Formatdaten und Etiketteneinmessung, nicht mehr aus einem MAC-Testparameter. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S762" s="4" t="n"/>
-      <c r="T762" s="4" t="n"/>
-      <c r="U762" s="4" t="n"/>
+      <c r="A762" s="10" t="n"/>
+      <c r="B762" s="8" t="n"/>
+      <c r="C762" s="43" t="n"/>
+      <c r="D762" s="11" t="n"/>
+      <c r="E762" s="11" t="n"/>
+      <c r="F762" s="15" t="n"/>
+      <c r="G762" s="15" t="n"/>
+      <c r="H762" s="15" t="n"/>
+      <c r="I762" s="15" t="n"/>
+      <c r="J762" s="15" t="n"/>
+      <c r="K762" s="15" t="n"/>
+      <c r="L762" s="22" t="n"/>
+      <c r="M762" s="22" t="n"/>
+      <c r="N762" s="22" t="n"/>
+      <c r="O762" s="22" t="n"/>
+      <c r="P762" s="22" t="n"/>
+      <c r="Q762" s="22" t="n"/>
+      <c r="R762" s="22" t="n"/>
     </row>
     <row r="763" hidden="1" ht="135" customHeight="1">
-      <c r="A763" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B763" s="8" t="inlineStr">
-        <is>
-          <t>0003</t>
-        </is>
-      </c>
-      <c r="C763" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D763" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="E763" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="F763" s="29" t="inlineStr">
-        <is>
-          <t>mm/s</t>
-        </is>
-      </c>
-      <c r="G763" s="29" t="n"/>
-      <c r="H763" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I763" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J763" s="29" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K763" s="29" t="inlineStr">
-        <is>
-          <t>Temporaere Vorzugsgeschwindigkeit</t>
-        </is>
-      </c>
-      <c r="L763" s="28" t="n"/>
-      <c r="M763" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N763" s="28" t="inlineStr">
-        <is>
-          <t>Sollgeschwindigkeit fuer kontinuierlichen und getakteten IBN-Testbetrieb</t>
-        </is>
-      </c>
-      <c r="O763" s="28" t="n"/>
-      <c r="P763" s="28" t="n"/>
-      <c r="Q763" s="28" t="n"/>
-      <c r="R763" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0003 als temporaere Vorzugsgeschwindigkeit fuer Motor 3 im IBN-Test. Wird kein neuer Wert gesetzt, verwendet der Raspi den zuletzt gespeicherten Wert. Produktiv wird die Geschwindigkeit ueber MAP0014 bzw. die Betriebsart vorgegeben. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S763" s="4" t="n"/>
-      <c r="T763" s="4" t="n"/>
-      <c r="U763" s="4" t="n"/>
+      <c r="A763" s="10" t="n"/>
+      <c r="B763" s="8" t="n"/>
+      <c r="C763" s="43" t="n"/>
+      <c r="D763" s="11" t="n"/>
+      <c r="E763" s="11" t="n"/>
+      <c r="F763" s="15" t="n"/>
+      <c r="G763" s="15" t="n"/>
+      <c r="H763" s="15" t="n"/>
+      <c r="I763" s="15" t="n"/>
+      <c r="J763" s="15" t="n"/>
+      <c r="K763" s="15" t="n"/>
+      <c r="L763" s="22" t="n"/>
+      <c r="M763" s="22" t="n"/>
+      <c r="N763" s="22" t="n"/>
+      <c r="O763" s="22" t="n"/>
+      <c r="P763" s="22" t="n"/>
+      <c r="Q763" s="22" t="n"/>
+      <c r="R763" s="22" t="n"/>
     </row>
     <row r="764" hidden="1" ht="135" customHeight="1">
-      <c r="A764" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B764" s="8" t="inlineStr">
-        <is>
-          <t>0004</t>
-        </is>
-      </c>
-      <c r="C764" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D764" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E764" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="F764" s="29" t="inlineStr">
-        <is>
-          <t>mm/s2</t>
-        </is>
-      </c>
-      <c r="G764" s="29" t="n"/>
-      <c r="H764" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I764" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J764" s="29" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K764" s="29" t="inlineStr">
-        <is>
-          <t>Temporaere Transport-Rampe</t>
-        </is>
-      </c>
-      <c r="L764" s="28" t="n"/>
-      <c r="M764" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N764" s="28" t="inlineStr">
-        <is>
-          <t>Beschleunigung/Verzoegerung fuer Motor 3 im IBN-Testbetrieb</t>
-        </is>
-      </c>
-      <c r="O764" s="28" t="n"/>
-      <c r="P764" s="28" t="n"/>
-      <c r="Q764" s="28" t="n"/>
-      <c r="R764" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0004 als temporaere Rampe fuer Beschleunigung und Bremsung des Etikettenantriebs im IBN-Test. Produktiv wird diese Vorgabe aus Maschinen- bzw. Formatparametern abgeleitet und darf den Etikettenschlupf nicht erhoehen. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: mm/s2. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S764" s="4" t="n"/>
-      <c r="T764" s="4" t="n"/>
-      <c r="U764" s="4" t="n"/>
+      <c r="A764" s="10" t="n"/>
+      <c r="B764" s="8" t="n"/>
+      <c r="C764" s="43" t="n"/>
+      <c r="D764" s="11" t="n"/>
+      <c r="E764" s="11" t="n"/>
+      <c r="F764" s="15" t="n"/>
+      <c r="G764" s="15" t="n"/>
+      <c r="H764" s="15" t="n"/>
+      <c r="I764" s="15" t="n"/>
+      <c r="J764" s="15" t="n"/>
+      <c r="K764" s="15" t="n"/>
+      <c r="L764" s="22" t="n"/>
+      <c r="M764" s="22" t="n"/>
+      <c r="N764" s="22" t="n"/>
+      <c r="O764" s="22" t="n"/>
+      <c r="P764" s="22" t="n"/>
+      <c r="Q764" s="22" t="n"/>
+      <c r="R764" s="22" t="n"/>
     </row>
     <row r="765" hidden="1" ht="135" customHeight="1">
-      <c r="A765" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B765" s="8" t="inlineStr">
-        <is>
-          <t>0005</t>
-        </is>
-      </c>
-      <c r="C765" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D765" s="12" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E765" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F765" s="29" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G765" s="29" t="n"/>
-      <c r="H765" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I765" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J765" s="29" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K765" s="29" t="inlineStr">
-        <is>
-          <t>Temporaere kontinuierliche Weglaenge</t>
-        </is>
-      </c>
-      <c r="L765" s="28" t="n"/>
-      <c r="M765" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N765" s="28" t="inlineStr">
-        <is>
-          <t>Weg fuer kontinuierliches Vorziehen/Rueckspulen; 0=endlos bis Stop</t>
-        </is>
-      </c>
-      <c r="O765" s="28" t="n"/>
-      <c r="P765" s="28" t="n"/>
-      <c r="Q765" s="28" t="n"/>
-      <c r="R765" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0005 als temporaere Wegvorgabe fuer kontinuierliches Vorziehen oder Rueckspulen. Default 0 bedeutet endlos fahren bis MAC0001=0. Produktiv wird diese Laenge aus Ablaufzustand, Rueckspulweg oder Bedienhandlung bestimmt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S765" s="4" t="n"/>
-      <c r="T765" s="4" t="n"/>
-      <c r="U765" s="4" t="n"/>
+      <c r="A765" s="10" t="n"/>
+      <c r="B765" s="8" t="n"/>
+      <c r="C765" s="43" t="n"/>
+      <c r="D765" s="11" t="n"/>
+      <c r="E765" s="11" t="n"/>
+      <c r="F765" s="15" t="n"/>
+      <c r="G765" s="15" t="n"/>
+      <c r="H765" s="15" t="n"/>
+      <c r="I765" s="15" t="n"/>
+      <c r="J765" s="15" t="n"/>
+      <c r="K765" s="15" t="n"/>
+      <c r="L765" s="22" t="n"/>
+      <c r="M765" s="22" t="n"/>
+      <c r="N765" s="22" t="n"/>
+      <c r="O765" s="22" t="n"/>
+      <c r="P765" s="22" t="n"/>
+      <c r="Q765" s="22" t="n"/>
+      <c r="R765" s="22" t="n"/>
     </row>
     <row r="766" hidden="1">
-      <c r="A766" s="10" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="B766" s="8" t="inlineStr">
-        <is>
-          <t>0006</t>
-        </is>
-      </c>
-      <c r="C766" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D766" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E766" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="F766" s="29" t="inlineStr">
-        <is>
-          <t>Zyklen</t>
-        </is>
-      </c>
-      <c r="G766" s="29" t="n"/>
-      <c r="H766" s="29" t="inlineStr">
-        <is>
-          <t>R/W</t>
-        </is>
-      </c>
-      <c r="I766" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J766" s="29" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K766" s="29" t="inlineStr">
-        <is>
-          <t>Temporaere Taktzyklus-Anzahl</t>
-        </is>
-      </c>
-      <c r="L766" s="28" t="n"/>
-      <c r="M766" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N766" s="28" t="inlineStr">
-        <is>
-          <t>Anzahl Takte im Testbetrieb; 0=endlos bis Stop</t>
-        </is>
-      </c>
-      <c r="O766" s="28" t="n"/>
-      <c r="P766" s="28" t="n"/>
-      <c r="Q766" s="28" t="n"/>
-      <c r="R766" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAC0006 als temporaere Zyklusanzahl fuer den getakteten IBN-Test. Default 20 entspricht einem kurzen Stabilitaetstest; 0 bedeutet laufender Taktbetrieb bis MAC0001=0. Spaeter wird diese Logik durch den echten Produktionsablauf und das Schieberegister ersetzt. Microtom soll diesen Wert lesen und bei Bedarf auch schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Zyklen. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S766" s="4" t="n"/>
-      <c r="T766" s="4" t="n"/>
-      <c r="U766" s="4" t="n"/>
+      <c r="A766" s="10" t="n"/>
+      <c r="B766" s="8" t="n"/>
+      <c r="C766" s="43" t="n"/>
+      <c r="D766" s="11" t="n"/>
+      <c r="E766" s="11" t="n"/>
+      <c r="F766" s="15" t="n"/>
+      <c r="G766" s="15" t="n"/>
+      <c r="H766" s="15" t="n"/>
+      <c r="I766" s="15" t="n"/>
+      <c r="J766" s="15" t="n"/>
+      <c r="K766" s="15" t="n"/>
+      <c r="L766" s="22" t="n"/>
+      <c r="M766" s="22" t="n"/>
+      <c r="N766" s="22" t="n"/>
+      <c r="O766" s="22" t="n"/>
+      <c r="P766" s="22" t="n"/>
+      <c r="Q766" s="22" t="n"/>
+      <c r="R766" s="22" t="n"/>
     </row>
     <row r="767" hidden="1">
       <c r="A767" s="10" t="n"/>
@@ -58595,126 +58305,9 @@
       <c r="Q775" s="22" t="n"/>
       <c r="R775" s="22" t="n"/>
     </row>
-    <row r="776" hidden="1">
-      <c r="A776" s="10" t="n"/>
-      <c r="B776" s="8" t="n"/>
-      <c r="C776" s="43" t="n"/>
-      <c r="D776" s="11" t="n"/>
-      <c r="E776" s="11" t="n"/>
-      <c r="F776" s="15" t="n"/>
-      <c r="G776" s="15" t="n"/>
-      <c r="H776" s="15" t="n"/>
-      <c r="I776" s="15" t="n"/>
-      <c r="J776" s="15" t="n"/>
-      <c r="K776" s="15" t="n"/>
-      <c r="L776" s="22" t="n"/>
-      <c r="M776" s="22" t="n"/>
-      <c r="N776" s="22" t="n"/>
-      <c r="O776" s="22" t="n"/>
-      <c r="P776" s="22" t="n"/>
-      <c r="Q776" s="22" t="n"/>
-      <c r="R776" s="22" t="n"/>
-    </row>
-    <row r="777" hidden="1">
-      <c r="A777" s="10" t="n"/>
-      <c r="B777" s="8" t="n"/>
-      <c r="C777" s="43" t="n"/>
-      <c r="D777" s="11" t="n"/>
-      <c r="E777" s="11" t="n"/>
-      <c r="F777" s="15" t="n"/>
-      <c r="G777" s="15" t="n"/>
-      <c r="H777" s="15" t="n"/>
-      <c r="I777" s="15" t="n"/>
-      <c r="J777" s="15" t="n"/>
-      <c r="K777" s="15" t="n"/>
-      <c r="L777" s="22" t="n"/>
-      <c r="M777" s="22" t="n"/>
-      <c r="N777" s="22" t="n"/>
-      <c r="O777" s="22" t="n"/>
-      <c r="P777" s="22" t="n"/>
-      <c r="Q777" s="22" t="n"/>
-      <c r="R777" s="22" t="n"/>
-    </row>
-    <row r="778" hidden="1">
-      <c r="A778" s="10" t="n"/>
-      <c r="B778" s="8" t="n"/>
-      <c r="C778" s="43" t="n"/>
-      <c r="D778" s="11" t="n"/>
-      <c r="E778" s="11" t="n"/>
-      <c r="F778" s="15" t="n"/>
-      <c r="G778" s="15" t="n"/>
-      <c r="H778" s="15" t="n"/>
-      <c r="I778" s="15" t="n"/>
-      <c r="J778" s="15" t="n"/>
-      <c r="K778" s="15" t="n"/>
-      <c r="L778" s="22" t="n"/>
-      <c r="M778" s="22" t="n"/>
-      <c r="N778" s="22" t="n"/>
-      <c r="O778" s="22" t="n"/>
-      <c r="P778" s="22" t="n"/>
-      <c r="Q778" s="22" t="n"/>
-      <c r="R778" s="22" t="n"/>
-    </row>
-    <row r="779">
-      <c r="A779" s="10" t="n"/>
-      <c r="B779" s="8" t="n"/>
-      <c r="C779" s="43" t="n"/>
-      <c r="D779" s="11" t="n"/>
-      <c r="E779" s="11" t="n"/>
-      <c r="F779" s="15" t="n"/>
-      <c r="G779" s="15" t="n"/>
-      <c r="H779" s="15" t="n"/>
-      <c r="I779" s="15" t="n"/>
-      <c r="J779" s="15" t="n"/>
-      <c r="K779" s="15" t="n"/>
-      <c r="L779" s="22" t="n"/>
-      <c r="M779" s="22" t="n"/>
-      <c r="N779" s="22" t="n"/>
-      <c r="O779" s="22" t="n"/>
-      <c r="P779" s="22" t="n"/>
-      <c r="Q779" s="22" t="n"/>
-      <c r="R779" s="22" t="n"/>
-    </row>
-    <row r="780">
-      <c r="A780" s="10" t="n"/>
-      <c r="B780" s="8" t="n"/>
-      <c r="C780" s="43" t="n"/>
-      <c r="D780" s="11" t="n"/>
-      <c r="E780" s="11" t="n"/>
-      <c r="F780" s="15" t="n"/>
-      <c r="G780" s="15" t="n"/>
-      <c r="H780" s="15" t="n"/>
-      <c r="I780" s="15" t="n"/>
-      <c r="J780" s="15" t="n"/>
-      <c r="K780" s="15" t="n"/>
-      <c r="L780" s="22" t="n"/>
-      <c r="M780" s="22" t="n"/>
-      <c r="N780" s="22" t="n"/>
-      <c r="O780" s="22" t="n"/>
-      <c r="P780" s="22" t="n"/>
-      <c r="Q780" s="22" t="n"/>
-      <c r="R780" s="22" t="n"/>
-    </row>
-    <row r="781">
-      <c r="A781" s="10" t="n"/>
-      <c r="B781" s="8" t="n"/>
-      <c r="C781" s="43" t="n"/>
-      <c r="D781" s="11" t="n"/>
-      <c r="E781" s="11" t="n"/>
-      <c r="F781" s="15" t="n"/>
-      <c r="G781" s="15" t="n"/>
-      <c r="H781" s="15" t="n"/>
-      <c r="I781" s="15" t="n"/>
-      <c r="J781" s="15" t="n"/>
-      <c r="K781" s="15" t="n"/>
-      <c r="L781" s="22" t="n"/>
-      <c r="M781" s="22" t="n"/>
-      <c r="N781" s="22" t="n"/>
-      <c r="O781" s="22" t="n"/>
-      <c r="P781" s="22" t="n"/>
-      <c r="Q781" s="22" t="n"/>
-      <c r="R781" s="22" t="n"/>
-    </row>
+    <row r="776" hidden="1"/>
+    <row r="777" hidden="1"/>
+    <row r="778" hidden="1"/>
   </sheetData>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation sqref="M1:M1048576 P2:P119" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -58730,4 +58323,296 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFC6A37-2F19-49DF-87E6-AB5652B8C8E4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC4971B4-DAD3-46DF-A3E3-9AF4554EE247}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B6A060-7507-475D-9722-2354344567E1}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -51101,10 +51101,10 @@
         <v>0</v>
       </c>
       <c r="D664" s="11" t="n">
-        <v>2100</v>
+        <v>1540</v>
       </c>
       <c r="E664" s="11" t="n">
-        <v>1550</v>
+        <v>1535</v>
       </c>
       <c r="F664" s="15" t="inlineStr">
         <is>
@@ -51164,13 +51164,13 @@
         </is>
       </c>
       <c r="C665" s="3" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="D665" s="11" t="n">
-        <v>10000</v>
+        <v>990</v>
       </c>
       <c r="E665" s="11" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="F665" s="15" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>650</v>
       </c>
       <c r="E669" s="11" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="F669" s="15" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>650</v>
       </c>
       <c r="E670" s="11" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="F670" s="15" t="inlineStr">
         <is>
@@ -51567,10 +51567,10 @@
         <v>100</v>
       </c>
       <c r="D671" s="11" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="E671" s="11" t="n">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="F671" s="15" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>100</v>
       </c>
       <c r="D672" s="11" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="E672" s="11" t="n">
         <v>910</v>
@@ -52581,10 +52581,10 @@
         <v>0</v>
       </c>
       <c r="D686" s="11" t="n">
-        <v>2100</v>
+        <v>1540</v>
       </c>
       <c r="E686" s="11" t="n">
-        <v>1550</v>
+        <v>1535</v>
       </c>
       <c r="F686" s="15" t="inlineStr">
         <is>
@@ -52644,13 +52644,13 @@
         </is>
       </c>
       <c r="C687" s="3" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="D687" s="11" t="n">
-        <v>10000</v>
+        <v>990</v>
       </c>
       <c r="E687" s="11" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="F687" s="15" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>650</v>
       </c>
       <c r="E688" s="11" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="F688" s="15" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>650</v>
       </c>
       <c r="E689" s="11" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="F689" s="15" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>100</v>
       </c>
       <c r="D690" s="11" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="E690" s="11" t="n">
         <v>910</v>
@@ -52911,10 +52911,10 @@
         <v>100</v>
       </c>
       <c r="D691" s="11" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="E691" s="11" t="n">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="F691" s="15" t="inlineStr">
         <is>
@@ -58606,13 +58606,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFC6A37-2F19-49DF-87E6-AB5652B8C8E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{581018F7-B077-41F8-932C-95F125681D77}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC4971B4-DAD3-46DF-A3E3-9AF4554EE247}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BA8AE4-C304-4D21-904A-1D0430EAC1A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B6A060-7507-475D-9722-2354344567E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A4D9519-4D37-46AB-809E-0405F788D2A2}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="rng_Lieferanten">#REF!</definedName>
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U775"/>
+  <dimension ref="A1:U784"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="16.140625" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
@@ -48122,7 +48122,7 @@
       <c r="Q622" s="38" t="n"/>
       <c r="R622" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Soll-Transportgeschwindigkeit des Etikettenbands. Im kontinuierlichen Lasermodus ist er die Druck-/Bandgeschwindigkeit; in allen getakteten Modi ist er die Vorzugsgeschwindigkeit zwischen den Druckpositionen. Der ESP nutzt ihn fuer Taktbewegungen und dynamische Nachregelung, der Raspi fuer Transparenz, Logging und Bedienung. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: mm/s. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+          <t>KI: Transportgeschwindigkeit des Etikettenbands in mm/s. Positive Werte bedeuten Vorzugsrichtung/Produktionsfeed. Rueckspulen wird in der Runtime als negative Bewegung ausgefuehrt, nicht durch negative Formatgeschwindigkeit. Der Raspi startet den ESP-Produktionsrunner mit diesem Wert als SPEED_MM_S. Microtom schreibt fuehrend; ESP/Raspi spiegeln und verwenden den Wert fuer Prozess, Logging und Diagnose. Formatrelevant.</t>
         </is>
       </c>
     </row>
@@ -49634,7 +49634,7 @@
       </c>
       <c r="N643" s="23" t="inlineStr">
         <is>
-          <t>Bypass Drucksystem (TTO bzw. Laser)</t>
+          <t>Bypass Drucksystem (TTO bzw. Laser), Druckdauer wird ueber MAP0069/MAP0070 simuliert</t>
         </is>
       </c>
       <c r="O643" s="23" t="n"/>
@@ -49642,7 +49642,7 @@
       <c r="Q643" s="24" t="n"/>
       <c r="R643" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass fuer das aktive Drucksystem. Wenn er gesetzt ist, darf das jeweilige Drucksystem den Prozess nicht blockieren; die Druckbewertung im Labelregister muss dann fachlich als gebypasst behandelt werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Bypass fuer das aktive Drucksystem (TTO oder Laser). Wenn er gesetzt ist, wird der echte Drucker nicht getriggert und dessen Status-/Druckfertig-Signale werden ignoriert. Stattdessen wartet die ESP-Prozesslogik die passende Simulationsdauer MAP0069 (Laser) oder MAP0070 (TTO) ab und setzt das Druckergebnis intern als erledigt. Das Label bleibt im Schieberegister als gebypasst erkennbar; ein Bypass darf die Produktion nicht faelschlich als regulaer OK ausweisen.</t>
         </is>
       </c>
     </row>
@@ -49706,7 +49706,7 @@
       </c>
       <c r="N644" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bypass Material-Kontrollkamera </t>
+          <t>Bypass Material-Kontrollkamera mit Trigger und simuliertem Ergebnis ueber MAP0067</t>
         </is>
       </c>
       <c r="O644" s="20" t="n"/>
@@ -49714,7 +49714,7 @@
       <c r="Q644" s="21" t="n"/>
       <c r="R644" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass der Material-Kontrollkamera. Wenn der Bypass aktiv ist, darf fehlendes Kamerafeedback nicht zu einem schlechten Material-OK-Bit fuehren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Bypass der Material-Kontrollkamera. Bei aktivem Bypass wird der Kameratrigger weiterhin wie im Produktionsbetrieb ausgegeben, aber Bereit-/Gut-Schlecht-Rueckmelde-IOs werden ignoriert. Das simulierte Gut/Schlecht-Ergebnis wird ueber MAP0067 gebildet und in das Etiketten-Schieberegister geschrieben.</t>
         </is>
       </c>
     </row>
@@ -49778,7 +49778,7 @@
       </c>
       <c r="N645" s="23" t="inlineStr">
         <is>
-          <t>Bypass Verifizierungs-Kamera</t>
+          <t>Bypass Verifizierungs-Kamera mit Trigger und simuliertem Ergebnis ueber MAP0068</t>
         </is>
       </c>
       <c r="O645" s="23" t="n"/>
@@ -49786,7 +49786,7 @@
       <c r="Q645" s="24" t="n"/>
       <c r="R645" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass der Verifizierungs-/OCR-Kamera. Wenn der Bypass aktiv ist, darf fehlendes OCR-Feedback das Label nicht als schlecht markieren. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Bypass der Druck-Verifikations-/OCR-Kamera. Bei aktivem Bypass wird der Kameratrigger weiterhin wie im Produktionsbetrieb ausgegeben, aber Bereit-/Gut-Schlecht-Rueckmelde-IOs werden ignoriert. Das simulierte Gut/Schlecht-Ergebnis wird ueber MAP0068 gebildet und in das Etiketten-Schieberegister geschrieben.</t>
         </is>
       </c>
     </row>
@@ -49850,7 +49850,7 @@
       </c>
       <c r="N646" s="23" t="inlineStr">
         <is>
-          <t>Bypass Etiketten Kontrollsensor</t>
+          <t>Bypass Etiketten Kontrollsensor ohne Entnahme-/Rueckspulpflicht</t>
         </is>
       </c>
       <c r="O646" s="23" t="n"/>
@@ -49858,7 +49858,7 @@
       <c r="Q646" s="24" t="n"/>
       <c r="R646" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Bypass fuer den Etiketten-Kontrollsensor am Auslauf. Wenn der Bypass aktiv ist, darf die Anlage fehlende Entnahmekontrolle nicht als Produktionsfehler werten. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Bypass fuer den Etiketten-Kontrollsensor am Auslauf. Bei aktivem Bypass wird keine Entnahme-/Rueckspulpflicht fuer schlechte Labels erzwungen; die Statuswerte der Labels bleiben aber im Schieberegister erhalten, damit der Produktionslauf nachvollziehbar bleibt.</t>
         </is>
       </c>
     </row>
@@ -50506,7 +50506,7 @@
       <c r="Q655" s="41" t="n"/>
       <c r="R655" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Vorgabe, ob innen- oder aussengewickeltes Material verarbeitet wird. Daraus ergeben sich die Drehrichtungen fuer Auf- und Abwickler; der ESP soll diesen Wert lesen und fuer die Wicklerlogik umsetzen. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist formatrelevant und muss beim Formatwechsel konsistent mitgezogen werden.</t>
+          <t>KI: Vorgabe innen-/aussengewickeltes Material. Dieser Wert beeinflusst die Wickler-Drehrichtung, aber nicht die globale Prozesskoordinate: Vorzugsrichtung bleibt fuer Motor 3 und beide Prozessencoder positiv, Rueckspulen negativ. Microtom schreibt fuehrend; Wickler/Raspi/ESP muessen den Wert konsistent gespiegelt verwenden. Formatrelevant.</t>
         </is>
       </c>
     </row>
@@ -51103,8 +51103,10 @@
       <c r="D664" s="11" t="n">
         <v>1540</v>
       </c>
-      <c r="E664" s="11" t="n">
-        <v>1535</v>
+      <c r="E664" s="11" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
       </c>
       <c r="F664" s="15" t="inlineStr">
         <is>
@@ -51169,8 +51171,10 @@
       <c r="D665" s="11" t="n">
         <v>990</v>
       </c>
-      <c r="E665" s="11" t="n">
-        <v>990</v>
+      <c r="E665" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="F665" s="15" t="inlineStr">
         <is>
@@ -51284,7 +51288,7 @@
       <c r="Q666" s="22" t="n"/>
       <c r="R666" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Sollbewegung bzw. Sollposition des Etikettenantriebs in 1/10 mm. Dieser Parameter ist im Produktionsprozess besonders sensibel, weil daraus die genaue Bandposition fuer Druck und Kameratrigger entsteht. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Soll-/Prozesswert des Etikettenantriebs Motor ID3 in 1/10 mm in Maschinenkoordinaten. Positive Werte bedeuten Vorzugsrichtung/Produktionsfeed, negative Werte Rueckspulen. ID3 ist keine Positionsachse wie ID1/2/4-9; seine logische 0 wird beim Einrichten/Messfahrtstart und vor dem Produktionsstart neu erfasst. Microtom liest nur; ESP fuehrt den Prozesswert.</t>
         </is>
       </c>
     </row>
@@ -51305,8 +51309,10 @@
       <c r="D667" s="11" t="n">
         <v>800</v>
       </c>
-      <c r="E667" s="11" t="n">
-        <v>800</v>
+      <c r="E667" s="11" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="F667" s="15" t="inlineStr">
         <is>
@@ -51371,8 +51377,10 @@
       <c r="D668" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="E668" s="11" t="n">
-        <v>0</v>
+      <c r="E668" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F668" s="15" t="inlineStr">
         <is>
@@ -51437,8 +51445,10 @@
       <c r="D669" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="E669" s="11" t="n">
-        <v>-200</v>
+      <c r="E669" s="11" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="F669" s="15" t="inlineStr">
         <is>
@@ -51503,8 +51513,10 @@
       <c r="D670" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="E670" s="11" t="n">
-        <v>-200</v>
+      <c r="E670" s="11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="F670" s="15" t="inlineStr">
         <is>
@@ -51569,8 +51581,10 @@
       <c r="D671" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="E671" s="11" t="n">
-        <v>925</v>
+      <c r="E671" s="11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
       </c>
       <c r="F671" s="15" t="inlineStr">
         <is>
@@ -51635,8 +51649,10 @@
       <c r="D672" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="E672" s="11" t="n">
-        <v>910</v>
+      <c r="E672" s="11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
       </c>
       <c r="F672" s="15" t="inlineStr">
         <is>
@@ -51847,66 +51863,717 @@
       <c r="Q675" s="28" t="n"/>
       <c r="R675" s="28" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur ersten LED des 1-m-LED-Streifens. Der aktuelle Default 8000 entspricht 800.0 mm. Der ESP braucht diesen Wegbezug, um den Labelstatus entlang des Streifens korrekt anzuzeigen; der exakte Wert muss bei der realen Inbetriebnahme mechanisch verifiziert werden. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Distanz vom Einlese-Sensor bis zur ersten LED des externen LED-Streifens. Der ESP braucht diesen Wegbezug, um den Labelstatus entlang des Streifens korrekt anzuzeigen; der exakte Wert muss bei der realen Inbetriebnahme mechanisch verifiziert werden.</t>
         </is>
       </c>
       <c r="S675" s="4" t="n"/>
       <c r="T675" s="4" t="n"/>
       <c r="U675" s="4" t="n"/>
     </row>
-    <row r="676" hidden="1" ht="345" customHeight="1">
-      <c r="A676" s="15" t="inlineStr">
+    <row r="676" hidden="1" ht="150" customHeight="1">
+      <c r="A676" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B676" s="8" t="inlineStr">
+        <is>
+          <t>0067</t>
+        </is>
+      </c>
+      <c r="C676" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D676" s="12" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E676" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F676" s="29" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G676" s="28" t="n"/>
+      <c r="H676" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I676" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J676" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K676" s="29" t="inlineStr">
+        <is>
+          <t>MAP0067 Materialkamera Bypass-Simulation</t>
+        </is>
+      </c>
+      <c r="L676" s="28" t="n"/>
+      <c r="M676" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N676" s="28" t="inlineStr">
+        <is>
+          <t>Simulation Rueckmeldung Material-Kontrollkamera bei aktivem Bypass: 0=alle Etiketten gut, 1=alle schlecht, n=jede n-te Etikette schlecht.</t>
+        </is>
+      </c>
+      <c r="O676" s="28" t="n"/>
+      <c r="P676" s="28" t="n"/>
+      <c r="Q676" s="28" t="n"/>
+      <c r="R676" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Simulationsmuster fuer die Material-Kontrollkamera bei aktivem MAP0036. 0 bedeutet: jedes Etikett wird im Schieberegister als Material OK bewertet. 1 bedeutet: jedes Etikett wird als schlecht bewertet. Werte groesser 1 bedeuten: jede n-te Etikette wird als schlecht markiert. Der reale Kameratrigger bleibt aktiv, die Rueckmelde-IOs werden aber ignoriert.</t>
+        </is>
+      </c>
+      <c r="S676" s="4" t="n"/>
+      <c r="T676" s="4" t="n"/>
+      <c r="U676" s="4" t="n"/>
+    </row>
+    <row r="677" hidden="1" ht="150" customHeight="1">
+      <c r="A677" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B677" s="8" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="C677" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D677" s="12" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E677" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F677" s="29" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G677" s="28" t="n"/>
+      <c r="H677" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I677" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J677" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K677" s="29" t="inlineStr">
+        <is>
+          <t>MAP0068 Verifikationskamera Bypass-Simulation</t>
+        </is>
+      </c>
+      <c r="L677" s="28" t="n"/>
+      <c r="M677" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N677" s="28" t="inlineStr">
+        <is>
+          <t>Simulation Rueckmeldung Druck-Verifikationskamera bei aktivem Bypass: 0=alle Etiketten gut, 1=alle schlecht, n=jede n-te Etikette schlecht.</t>
+        </is>
+      </c>
+      <c r="O677" s="28" t="n"/>
+      <c r="P677" s="28" t="n"/>
+      <c r="Q677" s="28" t="n"/>
+      <c r="R677" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Simulationsmuster fuer die Druck-Verifikations-/OCR-Kamera bei aktivem MAP0037. 0 bedeutet: jedes Etikett wird im Schieberegister als Verifizierung OK bewertet. 1 bedeutet: jedes Etikett wird als schlecht bewertet. Werte groesser 1 bedeuten: jede n-te Etikette wird als schlecht markiert. Der reale Kameratrigger bleibt aktiv, die Rueckmelde-IOs werden aber ignoriert.</t>
+        </is>
+      </c>
+      <c r="S677" s="4" t="n"/>
+      <c r="T677" s="4" t="n"/>
+      <c r="U677" s="4" t="n"/>
+    </row>
+    <row r="678" hidden="1" ht="150" customHeight="1">
+      <c r="A678" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B678" s="8" t="inlineStr">
+        <is>
+          <t>0069</t>
+        </is>
+      </c>
+      <c r="C678" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D678" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E678" s="12" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="F678" s="29" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="G678" s="28" t="n"/>
+      <c r="H678" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I678" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J678" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K678" s="29" t="inlineStr">
+        <is>
+          <t>MAP0069 Laser Bypass-Druckdauer</t>
+        </is>
+      </c>
+      <c r="L678" s="28" t="n"/>
+      <c r="M678" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N678" s="28" t="inlineStr">
+        <is>
+          <t>Simulierte Druckdauer Laser in ms bei aktivem Drucksystem-Bypass.</t>
+        </is>
+      </c>
+      <c r="O678" s="28" t="n"/>
+      <c r="P678" s="28" t="n"/>
+      <c r="Q678" s="28" t="n"/>
+      <c r="R678" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Wartezeit fuer den Laser-Druckpfad, wenn MAP0035 aktiv ist und MAP0016 den Laser auswaehlt. Der Laser wird dann nicht getriggert, Status-/Fertigsignale werden ignoriert, und nach dieser Zeit wird der Druck intern als beendet betrachtet.</t>
+        </is>
+      </c>
+      <c r="S678" s="4" t="n"/>
+      <c r="T678" s="4" t="n"/>
+      <c r="U678" s="4" t="n"/>
+    </row>
+    <row r="679" hidden="1" ht="150" customHeight="1">
+      <c r="A679" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B679" s="8" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="C679" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D679" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E679" s="12" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="F679" s="29" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="G679" s="28" t="n"/>
+      <c r="H679" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I679" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J679" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K679" s="29" t="inlineStr">
+        <is>
+          <t>MAP0070 TTO Bypass-Druckdauer</t>
+        </is>
+      </c>
+      <c r="L679" s="28" t="n"/>
+      <c r="M679" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N679" s="28" t="inlineStr">
+        <is>
+          <t>Simulierte Druckdauer TTO in ms bei aktivem Drucksystem-Bypass.</t>
+        </is>
+      </c>
+      <c r="O679" s="28" t="n"/>
+      <c r="P679" s="28" t="n"/>
+      <c r="Q679" s="28" t="n"/>
+      <c r="R679" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Wartezeit fuer den TTO-Druckpfad, wenn MAP0035 aktiv ist und MAP0016 den TTO auswaehlt. Der TTO wird dann nicht getriggert, Status-/Fertigsignale werden ignoriert, und nach dieser Zeit wird der Druck intern als beendet betrachtet.</t>
+        </is>
+      </c>
+      <c r="S679" s="4" t="n"/>
+      <c r="T679" s="4" t="n"/>
+      <c r="U679" s="4" t="n"/>
+    </row>
+    <row r="680" hidden="1" ht="90" customHeight="1">
+      <c r="A680" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B680" s="8" t="inlineStr">
+        <is>
+          <t>0071</t>
+        </is>
+      </c>
+      <c r="C680" s="46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D680" s="12" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="E680" s="12" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="F680" s="29" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G680" s="28" t="n"/>
+      <c r="H680" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I680" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J680" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K680" s="29" t="inlineStr">
+        <is>
+          <t>MAP0071 LED-Streifen aktive Laenge</t>
+        </is>
+      </c>
+      <c r="L680" s="28" t="n"/>
+      <c r="M680" s="28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N680" s="28" t="inlineStr">
+        <is>
+          <t>Aktive Laenge des externen LED-Streifens in 1/10 mm</t>
+        </is>
+      </c>
+      <c r="O680" s="28" t="n"/>
+      <c r="P680" s="28" t="n"/>
+      <c r="Q680" s="28" t="n"/>
+      <c r="R680" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als aktive Laenge des externen LED-Streifens in 1/10 mm. Aktuell ist der Streifen auf 520.0 mm gekuerzt; der ESP rendert dafuer 75 Pixel und sendet sie an den externen LED-Controller.</t>
+        </is>
+      </c>
+      <c r="S680" s="4" t="n"/>
+      <c r="T680" s="4" t="n"/>
+      <c r="U680" s="4" t="n"/>
+    </row>
+    <row r="681" hidden="1" ht="90" customHeight="1">
+      <c r="A681" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B681" s="8" t="inlineStr">
+        <is>
+          <t>0072</t>
+        </is>
+      </c>
+      <c r="C681" s="46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D681" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E681" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F681" s="29" t="inlineStr"/>
+      <c r="G681" s="28" t="n"/>
+      <c r="H681" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I681" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J681" s="29" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K681" s="29" t="inlineStr">
+        <is>
+          <t>MAP0072 LED-Controller UDP aktiv</t>
+        </is>
+      </c>
+      <c r="L681" s="28" t="n"/>
+      <c r="M681" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N681" s="28" t="inlineStr">
+        <is>
+          <t>Freigabe des ESP32-PLC UDP-Datenstroms zum externen LED-Controller</t>
+        </is>
+      </c>
+      <c r="O681" s="28" t="n"/>
+      <c r="P681" s="28" t="n"/>
+      <c r="Q681" s="28" t="n"/>
+      <c r="R681" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Freigabe des externen LED-Controller-Datenstroms. Bei 1 sendet der ESP32-PLC Prozess fertige RGB-Frames per UDP, bei 0 bleibt der LED-Datenstrom aus.</t>
+        </is>
+      </c>
+      <c r="S681" s="4" t="n"/>
+      <c r="T681" s="4" t="n"/>
+      <c r="U681" s="4" t="n"/>
+    </row>
+    <row r="682" hidden="1" ht="90" customHeight="1">
+      <c r="A682" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B682" s="8" t="inlineStr">
+        <is>
+          <t>0073</t>
+        </is>
+      </c>
+      <c r="C682" s="46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D682" s="12" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E682" s="12" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="F682" s="29" t="inlineStr"/>
+      <c r="G682" s="28" t="n"/>
+      <c r="H682" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I682" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J682" s="29" t="inlineStr">
+        <is>
+          <t>uint8</t>
+        </is>
+      </c>
+      <c r="K682" s="29" t="inlineStr">
+        <is>
+          <t>MAP0073 LED-Controller Ziel-IP letztes Oktett</t>
+        </is>
+      </c>
+      <c r="L682" s="28" t="n"/>
+      <c r="M682" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N682" s="28" t="inlineStr">
+        <is>
+          <t>Letztes Oktett der LED-Controller-Ziel-IP im ESP-Netz 192.168.2.x</t>
+        </is>
+      </c>
+      <c r="O682" s="28" t="n"/>
+      <c r="P682" s="28" t="n"/>
+      <c r="Q682" s="28" t="n"/>
+      <c r="R682" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als letztes Oktett der Ziel-IP fuer den externen LED-Controller im ESP-Netz 192.168.2.x. Der Default 255 nutzt Broadcast, damit der Controller ohne feste IP-Konfiguration Frames empfangen kann.</t>
+        </is>
+      </c>
+      <c r="S682" s="4" t="n"/>
+      <c r="T682" s="4" t="n"/>
+      <c r="U682" s="4" t="n"/>
+    </row>
+    <row r="683" hidden="1" ht="90" customHeight="1">
+      <c r="A683" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B683" s="8" t="inlineStr">
+        <is>
+          <t>0074</t>
+        </is>
+      </c>
+      <c r="C683" s="46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D683" s="12" t="inlineStr">
+        <is>
+          <t>65535</t>
+        </is>
+      </c>
+      <c r="E683" s="12" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="F683" s="29" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="G683" s="28" t="n"/>
+      <c r="H683" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I683" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J683" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K683" s="29" t="inlineStr">
+        <is>
+          <t>MAP0074 LED-Controller UDP-Port</t>
+        </is>
+      </c>
+      <c r="L683" s="28" t="n"/>
+      <c r="M683" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N683" s="28" t="inlineStr">
+        <is>
+          <t>UDP-Zielport fuer MAS004-LED-UDP/v1 Frames</t>
+        </is>
+      </c>
+      <c r="O683" s="28" t="n"/>
+      <c r="P683" s="28" t="n"/>
+      <c r="Q683" s="28" t="n"/>
+      <c r="R683" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als UDP-Zielport fuer das MAS004-LED-UDP/v1 Protokoll zum externen LED-Controller.</t>
+        </is>
+      </c>
+      <c r="S683" s="4" t="n"/>
+      <c r="T683" s="4" t="n"/>
+      <c r="U683" s="4" t="n"/>
+    </row>
+    <row r="684" hidden="1" ht="90" customHeight="1">
+      <c r="A684" s="10" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="B684" s="8" t="inlineStr">
+        <is>
+          <t>0075</t>
+        </is>
+      </c>
+      <c r="C684" s="46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D684" s="12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E684" s="12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F684" s="29" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="G684" s="28" t="n"/>
+      <c r="H684" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I684" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J684" s="29" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K684" s="29" t="inlineStr">
+        <is>
+          <t>MAP0075 LED-Controller Frame-Intervall</t>
+        </is>
+      </c>
+      <c r="L684" s="28" t="n"/>
+      <c r="M684" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N684" s="28" t="inlineStr">
+        <is>
+          <t>Minimales Sendeintervall fuer LED-Frames an den externen Controller</t>
+        </is>
+      </c>
+      <c r="O684" s="28" t="n"/>
+      <c r="P684" s="28" t="n"/>
+      <c r="Q684" s="28" t="n"/>
+      <c r="R684" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als minimales Sendeintervall fuer LED-Frames in ms. Der Default 33 ms entspricht etwa 30 Hz und ist fuer die Positionsanzeige ausreichend schnell.</t>
+        </is>
+      </c>
+      <c r="S684" s="4" t="n"/>
+      <c r="T684" s="4" t="n"/>
+      <c r="U684" s="4" t="n"/>
+    </row>
+    <row r="685" hidden="1" ht="30" customHeight="1">
+      <c r="A685" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B676" s="22" t="inlineStr">
+      <c r="B685" s="22" t="inlineStr">
         <is>
           <t>0001</t>
         </is>
       </c>
-      <c r="C676" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D676" s="11" t="n">
+      <c r="C685" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D685" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="E676" s="11" t="n"/>
-      <c r="F676" s="15" t="inlineStr">
+      <c r="E685" s="11" t="n"/>
+      <c r="F685" s="15" t="inlineStr">
         <is>
           <t>Status - Read</t>
         </is>
       </c>
-      <c r="G676" s="22" t="n"/>
-      <c r="H676" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I676" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J676" s="15" t="inlineStr">
+      <c r="G685" s="22" t="n"/>
+      <c r="H685" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I685" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J685" s="15" t="inlineStr">
         <is>
           <t>uint8</t>
         </is>
       </c>
-      <c r="K676" s="15" t="inlineStr">
+      <c r="K685" s="15" t="inlineStr">
         <is>
           <t>MAS0001 Statusmeldung Anlage</t>
         </is>
       </c>
-      <c r="L676" s="29" t="n"/>
-      <c r="M676" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N676" s="22" t="inlineStr">
+      <c r="L685" s="29" t="n"/>
+      <c r="M685" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N685" s="22" t="inlineStr">
         <is>
           <t>Status-Byte-Wert der Produktionsanlge:
 0 - Anlage Augeschaltet
@@ -51933,68 +52600,68 @@
 21 - Not-Stop/ Störung</t>
         </is>
       </c>
-      <c r="O676" s="22" t="n"/>
-      <c r="P676" s="22" t="n"/>
-      <c r="Q676" s="22" t="n"/>
-      <c r="R676" s="22" t="inlineStr">
+      <c r="O685" s="22" t="n"/>
+      <c r="P685" s="22" t="n"/>
+      <c r="Q685" s="22" t="n"/>
+      <c r="R685" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe diesen Parameter als fuehrenden Anlagenstatus, den der Raspi gegenueber Microtom meldet. Die eigentliche Statuslogik entsteht aus Bedienbefehlen, Sicherheitsbedingungen und Maschinenfortschritt; der ESP liefert dafuer harte Prozessereignisse zu. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status - Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="677" hidden="1" ht="150" customHeight="1">
-      <c r="A677" s="15" t="inlineStr">
+    <row r="686" hidden="1" ht="90" customHeight="1">
+      <c r="A686" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B677" s="22" t="inlineStr">
+      <c r="B686" s="22" t="inlineStr">
         <is>
           <t>0002</t>
         </is>
       </c>
-      <c r="C677" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D677" s="11" t="n">
+      <c r="C686" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D686" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="E677" s="11" t="n"/>
-      <c r="F677" s="15" t="inlineStr">
+      <c r="E686" s="11" t="n"/>
+      <c r="F686" s="15" t="inlineStr">
         <is>
           <t>Status - Write</t>
         </is>
       </c>
-      <c r="G677" s="22" t="n"/>
-      <c r="H677" s="15" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I677" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J677" s="15" t="inlineStr">
+      <c r="G686" s="22" t="n"/>
+      <c r="H686" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I686" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J686" s="15" t="inlineStr">
         <is>
           <t>uint8</t>
         </is>
       </c>
-      <c r="K677" s="15" t="inlineStr">
+      <c r="K686" s="15" t="inlineStr">
         <is>
           <t>MAS0002 Status-Steuerung Anlage von Microtom</t>
         </is>
       </c>
-      <c r="L677" s="29" t="n"/>
-      <c r="M677" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N677" s="22" t="inlineStr">
+      <c r="L686" s="29" t="n"/>
+      <c r="M686" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N686" s="22" t="inlineStr">
         <is>
           <t>Status Steuer-Byte Mikrotom zur Produktionsanlage
 0 - Keine Anforderung
@@ -52007,70 +52674,70 @@
 7 - Pause</t>
         </is>
       </c>
-      <c r="O677" s="22" t="n"/>
-      <c r="P677" s="22" t="n"/>
-      <c r="Q677" s="22" t="n"/>
-      <c r="R677" s="22" t="inlineStr">
+      <c r="O686" s="22" t="n"/>
+      <c r="P686" s="22" t="n"/>
+      <c r="Q686" s="22" t="n"/>
+      <c r="R686" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe diesen Parameter nicht als Status, sondern als Befehlsbyte von Microtom an die Anlage. Der Raspi muss diesen Befehlswert in den passenden internen Zielzustand uebersetzen, zum Beispiel Start, Stop, Einrichten, Synchronisieren, Leerfahren, Rueckspulen oder Pause. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status - Write. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="678" hidden="1" ht="120" customHeight="1">
-      <c r="A678" s="15" t="inlineStr">
+    <row r="687" hidden="1" ht="90" customHeight="1">
+      <c r="A687" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B678" s="22" t="inlineStr">
+      <c r="B687" s="22" t="inlineStr">
         <is>
           <t>0003</t>
         </is>
       </c>
-      <c r="C678" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D678" s="11" t="inlineStr">
+      <c r="C687" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D687" s="11" t="inlineStr">
         <is>
           <t>21Bit</t>
         </is>
       </c>
-      <c r="E678" s="11" t="n"/>
-      <c r="F678" s="15" t="inlineStr">
+      <c r="E687" s="11" t="n"/>
+      <c r="F687" s="15" t="inlineStr">
         <is>
           <t>Label-Info</t>
         </is>
       </c>
-      <c r="G678" s="22" t="n"/>
-      <c r="H678" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I678" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J678" s="15" t="inlineStr">
+      <c r="G687" s="22" t="n"/>
+      <c r="H687" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I687" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J687" s="15" t="inlineStr">
         <is>
           <t>unint32</t>
         </is>
       </c>
-      <c r="K678" s="15" t="inlineStr">
+      <c r="K687" s="15" t="inlineStr">
         <is>
           <t>MAS003 Label Produktions-Info</t>
         </is>
       </c>
-      <c r="L678" s="29" t="n"/>
-      <c r="M678" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N678" s="22" t="inlineStr">
+      <c r="L687" s="29" t="n"/>
+      <c r="M687" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N687" s="22" t="inlineStr">
         <is>
           <t>Produktions Info für fertige Etiketten:
 Bit  0–15 : Etikettennummer (16 Bit - max 65536 Labels)
@@ -52081,620 +52748,12 @@
 Bit 20    : Produktion OK</t>
         </is>
       </c>
-      <c r="O678" s="22" t="n"/>
-      <c r="P678" s="22" t="n"/>
-      <c r="Q678" s="22" t="n"/>
-      <c r="R678" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als verdichtete Produktionsrueckmeldung pro fertig behandeltem Label. Der ESP baut die Einzelinformationen im Schieberegister auf; der Raspi packt sie in das definierte Bitfeld und meldet den Wert an Microtom sowie in das Label-Produktionslog. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Label-Info. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="679" hidden="1" ht="90" customHeight="1">
-      <c r="A679" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B679" s="22" t="inlineStr">
-        <is>
-          <t>0004</t>
-        </is>
-      </c>
-      <c r="C679" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D679" s="11" t="n">
-        <v>65536</v>
-      </c>
-      <c r="E679" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F679" s="15" t="inlineStr">
-        <is>
-          <t>Stk.</t>
-        </is>
-      </c>
-      <c r="G679" s="22" t="n"/>
-      <c r="H679" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I679" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J679" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K679" s="15" t="inlineStr">
-        <is>
-          <t>MAS004 Verarbeitete Labels</t>
-        </is>
-      </c>
-      <c r="L679" s="29" t="n"/>
-      <c r="M679" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N679" s="22" t="inlineStr">
-        <is>
-          <t>Anzahl der Verarbeiteten Labels im Batch</t>
-        </is>
-      </c>
-      <c r="O679" s="22" t="n"/>
-      <c r="P679" s="22" t="n"/>
-      <c r="Q679" s="22" t="n"/>
-      <c r="R679" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0004 als MAS004 Verarbeitete Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="680" hidden="1" ht="90" customHeight="1">
-      <c r="A680" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B680" s="22" t="inlineStr">
-        <is>
-          <t>0005</t>
-        </is>
-      </c>
-      <c r="C680" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D680" s="11" t="n">
-        <v>65536</v>
-      </c>
-      <c r="E680" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F680" s="15" t="inlineStr">
-        <is>
-          <t>Stk.</t>
-        </is>
-      </c>
-      <c r="G680" s="22" t="n"/>
-      <c r="H680" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I680" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J680" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K680" s="15" t="inlineStr">
-        <is>
-          <t>MAS005 Anzahl gute Labels</t>
-        </is>
-      </c>
-      <c r="L680" s="29" t="n"/>
-      <c r="M680" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N680" s="22" t="inlineStr">
-        <is>
-          <t>Anzahl der gut Verarbeiteten Labels im Batch</t>
-        </is>
-      </c>
-      <c r="O680" s="22" t="n"/>
-      <c r="P680" s="22" t="n"/>
-      <c r="Q680" s="22" t="n"/>
-      <c r="R680" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0005 als MAS005 Anzahl gute Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="681" hidden="1" ht="90" customHeight="1">
-      <c r="A681" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B681" s="22" t="inlineStr">
-        <is>
-          <t>0006</t>
-        </is>
-      </c>
-      <c r="C681" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D681" s="11" t="n">
-        <v>65536</v>
-      </c>
-      <c r="E681" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F681" s="15" t="inlineStr">
-        <is>
-          <t>Stk.</t>
-        </is>
-      </c>
-      <c r="G681" s="22" t="n"/>
-      <c r="H681" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I681" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J681" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K681" s="15" t="inlineStr">
-        <is>
-          <t>MAS006 Anzahl schlechte Labels</t>
-        </is>
-      </c>
-      <c r="L681" s="29" t="n"/>
-      <c r="M681" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N681" s="22" t="inlineStr">
-        <is>
-          <t>Anzahl der schlechten Labels im Batch</t>
-        </is>
-      </c>
-      <c r="O681" s="22" t="n"/>
-      <c r="P681" s="22" t="n"/>
-      <c r="Q681" s="22" t="n"/>
-      <c r="R681" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0006 als MAS006 Anzahl schlechte Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="682" hidden="1" ht="90" customHeight="1">
-      <c r="A682" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B682" s="22" t="inlineStr">
-        <is>
-          <t>0007</t>
-        </is>
-      </c>
-      <c r="C682" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D682" s="11" t="n">
-        <v>999999999</v>
-      </c>
-      <c r="E682" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F682" s="15" t="inlineStr">
-        <is>
-          <t>Stk.</t>
-        </is>
-      </c>
-      <c r="G682" s="22" t="n"/>
-      <c r="H682" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I682" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J682" s="15" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K682" s="15" t="inlineStr">
-        <is>
-          <t>MAS007 Labelzähler Global</t>
-        </is>
-      </c>
-      <c r="L682" s="29" t="n"/>
-      <c r="M682" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N682" s="22" t="inlineStr">
-        <is>
-          <t>Globalzähler erfasste Labels</t>
-        </is>
-      </c>
-      <c r="O682" s="22" t="n"/>
-      <c r="P682" s="22" t="n"/>
-      <c r="Q682" s="22" t="n"/>
-      <c r="R682" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0007 als MAS007 Labelzähler Global. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="683" hidden="1" ht="90" customHeight="1">
-      <c r="A683" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B683" s="22" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
-      <c r="C683" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D683" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E683" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F683" s="15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G683" s="22" t="n"/>
-      <c r="H683" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I683" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J683" s="15" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="K683" s="15" t="inlineStr">
-        <is>
-          <t>MAS008 Füllstand Abwicklung</t>
-        </is>
-      </c>
-      <c r="L683" s="29" t="n"/>
-      <c r="M683" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N683" s="22" t="inlineStr">
-        <is>
-          <t>Füllstand Abwickeleinheit</t>
-        </is>
-      </c>
-      <c r="O683" s="22" t="n"/>
-      <c r="P683" s="22" t="n"/>
-      <c r="Q683" s="22" t="n"/>
-      <c r="R683" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als Fuellstand des Abwicklers in Prozent. Microtom liest ihn nur; der Wert wird aus der Wicklerlogik abgeleitet. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="684" hidden="1" ht="90" customHeight="1">
-      <c r="A684" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B684" s="22" t="inlineStr">
-        <is>
-          <t>0009</t>
-        </is>
-      </c>
-      <c r="C684" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D684" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E684" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F684" s="15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G684" s="22" t="n"/>
-      <c r="H684" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I684" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J684" s="15" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="K684" s="15" t="inlineStr">
-        <is>
-          <t>MAS009 Füllstand Aufwicklung</t>
-        </is>
-      </c>
-      <c r="L684" s="29" t="n"/>
-      <c r="M684" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N684" s="22" t="inlineStr">
-        <is>
-          <t>Füllstand Aufwickeleinheit</t>
-        </is>
-      </c>
-      <c r="O684" s="22" t="n"/>
-      <c r="P684" s="22" t="n"/>
-      <c r="Q684" s="22" t="n"/>
-      <c r="R684" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als Fuellstand des Aufwicklers in Prozent. Microtom liest ihn nur; der Wert wird aus der Wicklerlogik abgeleitet. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="685" hidden="1" ht="30" customHeight="1">
-      <c r="A685" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B685" s="22" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
-      <c r="C685" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D685" s="11" t="n">
-        <v>65536</v>
-      </c>
-      <c r="E685" s="11" t="n">
-        <v>1002</v>
-      </c>
-      <c r="F685" s="15" t="inlineStr">
-        <is>
-          <t>Stk.</t>
-        </is>
-      </c>
-      <c r="G685" s="22" t="n"/>
-      <c r="H685" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I685" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J685" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K685" s="15" t="inlineStr">
-        <is>
-          <t>MAS0010 Verbleibende Labels (geschätzt)</t>
-        </is>
-      </c>
-      <c r="L685" s="29" t="n"/>
-      <c r="M685" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N685" s="22" t="inlineStr">
-        <is>
-          <t>Anzahl verbelibende Labels auf der Labelrolle (geschätzt)</t>
-        </is>
-      </c>
-      <c r="O685" s="22" t="n"/>
-      <c r="P685" s="22" t="n"/>
-      <c r="Q685" s="22" t="n"/>
-      <c r="R685" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0010 als MAS0010 Verbleibende Labels (geschätzt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="686" hidden="1" ht="90" customHeight="1">
-      <c r="A686" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B686" s="22" t="inlineStr">
-        <is>
-          <t>0011</t>
-        </is>
-      </c>
-      <c r="C686" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D686" s="11" t="n">
-        <v>1540</v>
-      </c>
-      <c r="E686" s="11" t="n">
-        <v>1535</v>
-      </c>
-      <c r="F686" s="15" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G686" s="22" t="n"/>
-      <c r="H686" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I686" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J686" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K686" s="15" t="inlineStr">
-        <is>
-          <t>MAS0011 Ist Position Portalachse X</t>
-        </is>
-      </c>
-      <c r="L686" s="29" t="n"/>
-      <c r="M686" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N686" s="22" t="inlineStr">
-        <is>
-          <t>Ist Position Portalachse X (Querrichtung)</t>
-        </is>
-      </c>
-      <c r="O686" s="22" t="n"/>
-      <c r="P686" s="22" t="n"/>
-      <c r="Q686" s="22" t="n"/>
-      <c r="R686" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0011 als MAS0011 Ist Position Portalachse X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="687" hidden="1" ht="90" customHeight="1">
-      <c r="A687" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B687" s="22" t="inlineStr">
-        <is>
-          <t>0012</t>
-        </is>
-      </c>
-      <c r="C687" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D687" s="11" t="n">
-        <v>990</v>
-      </c>
-      <c r="E687" s="11" t="n">
-        <v>990</v>
-      </c>
-      <c r="F687" s="15" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G687" s="22" t="n"/>
-      <c r="H687" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I687" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J687" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K687" s="15" t="inlineStr">
-        <is>
-          <t>MAS0012 Ist Position Portalachse Z</t>
-        </is>
-      </c>
-      <c r="L687" s="29" t="n"/>
-      <c r="M687" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N687" s="22" t="inlineStr">
-        <is>
-          <t>Ist Position Portalachse Z (Vertikal)</t>
-        </is>
-      </c>
       <c r="O687" s="22" t="n"/>
       <c r="P687" s="22" t="n"/>
       <c r="Q687" s="22" t="n"/>
       <c r="R687" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0012 als MAS0012 Ist Position Portalachse Z. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als verdichtete Produktionsrueckmeldung pro fertig behandeltem Label. Der ESP baut die Einzelinformationen im Schieberegister auf; der Raspi packt sie in das definierte Bitfeld und meldet den Wert an Microtom sowie in das Label-Produktionslog. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Label-Info. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -52706,21 +52765,23 @@
       </c>
       <c r="B688" s="22" t="inlineStr">
         <is>
-          <t>0013</t>
-        </is>
-      </c>
-      <c r="C688" s="3" t="n">
-        <v>-200</v>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="C688" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D688" s="11" t="n">
-        <v>650</v>
+        <v>65536</v>
       </c>
       <c r="E688" s="11" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F688" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>Stk.</t>
         </is>
       </c>
       <c r="G688" s="22" t="n"/>
@@ -52741,7 +52802,7 @@
       </c>
       <c r="K688" s="15" t="inlineStr">
         <is>
-          <t>MAS0013 Ist Position Etikettensensor X</t>
+          <t>MAS004 Verarbeitete Labels</t>
         </is>
       </c>
       <c r="L688" s="29" t="n"/>
@@ -52752,7 +52813,7 @@
       </c>
       <c r="N688" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Etikettensensor X (Querrichtung)</t>
+          <t>Anzahl der Verarbeiteten Labels im Batch</t>
         </is>
       </c>
       <c r="O688" s="22" t="n"/>
@@ -52760,7 +52821,7 @@
       <c r="Q688" s="22" t="n"/>
       <c r="R688" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0013 als MAS0013 Ist Position Etikettensensor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0004 als MAS004 Verarbeitete Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -52772,21 +52833,23 @@
       </c>
       <c r="B689" s="22" t="inlineStr">
         <is>
-          <t>0014</t>
-        </is>
-      </c>
-      <c r="C689" s="3" t="n">
-        <v>-200</v>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D689" s="11" t="n">
-        <v>650</v>
+        <v>65536</v>
       </c>
       <c r="E689" s="11" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F689" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>Stk.</t>
         </is>
       </c>
       <c r="G689" s="22" t="n"/>
@@ -52807,7 +52870,7 @@
       </c>
       <c r="K689" s="15" t="inlineStr">
         <is>
-          <t>MAS0014 Ist Position Etikettenentnahmesensor X</t>
+          <t>MAS005 Anzahl gute Labels</t>
         </is>
       </c>
       <c r="L689" s="29" t="n"/>
@@ -52818,7 +52881,7 @@
       </c>
       <c r="N689" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Etikettenentnahmesensor X (Querrichtung)</t>
+          <t>Anzahl der gut Verarbeiteten Labels im Batch</t>
         </is>
       </c>
       <c r="O689" s="22" t="n"/>
@@ -52826,7 +52889,7 @@
       <c r="Q689" s="22" t="n"/>
       <c r="R689" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0014 als MAS0014 Ist Position Etikettenentnahmesensor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0005 als MAS005 Anzahl gute Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -52838,21 +52901,23 @@
       </c>
       <c r="B690" s="22" t="inlineStr">
         <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="C690" s="3" t="n">
-        <v>100</v>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="C690" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D690" s="11" t="n">
-        <v>1000</v>
+        <v>65536</v>
       </c>
       <c r="E690" s="11" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="F690" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>Stk.</t>
         </is>
       </c>
       <c r="G690" s="22" t="n"/>
@@ -52873,7 +52938,7 @@
       </c>
       <c r="K690" s="15" t="inlineStr">
         <is>
-          <t>MAS0015 Ist Position Etikettenanschlag Einlauf X</t>
+          <t>MAS006 Anzahl schlechte Labels</t>
         </is>
       </c>
       <c r="L690" s="29" t="n"/>
@@ -52884,7 +52949,7 @@
       </c>
       <c r="N690" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Etikettenanschlag Einlauf X (Querrichtung)</t>
+          <t>Anzahl der schlechten Labels im Batch</t>
         </is>
       </c>
       <c r="O690" s="22" t="n"/>
@@ -52892,7 +52957,7 @@
       <c r="Q690" s="22" t="n"/>
       <c r="R690" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0015 als MAS0015 Ist Position Etikettenanschlag Einlauf X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0006 als MAS006 Anzahl schlechte Labels. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -52904,21 +52969,23 @@
       </c>
       <c r="B691" s="22" t="inlineStr">
         <is>
-          <t>0016</t>
-        </is>
-      </c>
-      <c r="C691" s="3" t="n">
+          <t>0007</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D691" s="11" t="n">
+        <v>999999999</v>
+      </c>
+      <c r="E691" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="D691" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E691" s="11" t="n">
-        <v>925</v>
-      </c>
       <c r="F691" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>Stk.</t>
         </is>
       </c>
       <c r="G691" s="22" t="n"/>
@@ -52934,12 +53001,12 @@
       </c>
       <c r="J691" s="15" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="K691" s="15" t="inlineStr">
         <is>
-          <t>MAS0016 Ist Position Etikettenanschlag Auslauf X</t>
+          <t>MAS007 Labelzähler Global</t>
         </is>
       </c>
       <c r="L691" s="29" t="n"/>
@@ -52950,7 +53017,7 @@
       </c>
       <c r="N691" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Etikettenanschlag Auslauf X (Querrichtung)</t>
+          <t>Globalzähler erfasste Labels</t>
         </is>
       </c>
       <c r="O691" s="22" t="n"/>
@@ -52958,7 +53025,7 @@
       <c r="Q691" s="22" t="n"/>
       <c r="R691" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0016 als MAS0016 Ist Position Etikettenanschlag Auslauf X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0007 als MAS007 Labelzähler Global. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -52970,21 +53037,23 @@
       </c>
       <c r="B692" s="22" t="inlineStr">
         <is>
-          <t>0017</t>
-        </is>
-      </c>
-      <c r="C692" s="3" t="n">
-        <v>0</v>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="C692" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D692" s="11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E692" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F692" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G692" s="22" t="n"/>
@@ -52995,17 +53064,17 @@
       </c>
       <c r="I692" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J692" s="15" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="K692" s="15" t="inlineStr">
         <is>
-          <t>MAS0017 Ist Position Material-Kontrollkamera X</t>
+          <t>MAS008 Füllstand Abwicklung</t>
         </is>
       </c>
       <c r="L692" s="29" t="n"/>
@@ -53016,7 +53085,7 @@
       </c>
       <c r="N692" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Material-Kontrollkamera X (Querrichtung)</t>
+          <t>Füllstand Abwickeleinheit</t>
         </is>
       </c>
       <c r="O692" s="22" t="n"/>
@@ -53024,7 +53093,7 @@
       <c r="Q692" s="22" t="n"/>
       <c r="R692" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0017 als MAS0017 Ist Position Material-Kontrollkamera X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Fuellstand des Abwicklers in Prozent. Microtom liest ihn nur; der Wert wird aus der Wicklerlogik abgeleitet. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -53036,7 +53105,7 @@
       </c>
       <c r="B693" s="22" t="inlineStr">
         <is>
-          <t>0018</t>
+          <t>0009</t>
         </is>
       </c>
       <c r="C693" s="3" t="inlineStr">
@@ -53045,14 +53114,14 @@
         </is>
       </c>
       <c r="D693" s="11" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="E693" s="11" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F693" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G693" s="22" t="n"/>
@@ -53063,17 +53132,17 @@
       </c>
       <c r="I693" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J693" s="15" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="K693" s="15" t="inlineStr">
         <is>
-          <t>MAS0018 Ist Position Laserschutz X</t>
+          <t>MAS009 Füllstand Aufwicklung</t>
         </is>
       </c>
       <c r="L693" s="29" t="n"/>
@@ -53084,7 +53153,7 @@
       </c>
       <c r="N693" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Laserschutz X (Querrichtung)</t>
+          <t>Füllstand Aufwickeleinheit</t>
         </is>
       </c>
       <c r="O693" s="22" t="n"/>
@@ -53092,7 +53161,7 @@
       <c r="Q693" s="22" t="n"/>
       <c r="R693" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0018 als MAS0018 Ist Position Laserschutz X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe diesen Parameter als Fuellstand des Aufwicklers in Prozent. Microtom liest ihn nur; der Wert wird aus der Wicklerlogik abgeleitet. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: %. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -53104,21 +53173,23 @@
       </c>
       <c r="B694" s="22" t="inlineStr">
         <is>
-          <t>0019</t>
-        </is>
-      </c>
-      <c r="C694" s="16" t="n">
-        <v>-67465000</v>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="C694" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D694" s="11" t="n">
-        <v>67465000</v>
+        <v>65536</v>
       </c>
       <c r="E694" s="11" t="n">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="F694" s="15" t="inlineStr">
         <is>
-          <t>1/10mm</t>
+          <t>Stk.</t>
         </is>
       </c>
       <c r="G694" s="22" t="n"/>
@@ -53134,12 +53205,12 @@
       </c>
       <c r="J694" s="15" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K694" s="15" t="inlineStr">
         <is>
-          <t>MAS0019 Position Etikettenband</t>
+          <t>MAS0010 Verbleibende Labels (geschätzt)</t>
         </is>
       </c>
       <c r="L694" s="29" t="n"/>
@@ -53150,7 +53221,7 @@
       </c>
       <c r="N694" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Etikettenband</t>
+          <t>Anzahl verbelibende Labels auf der Labelrolle (geschätzt)</t>
         </is>
       </c>
       <c r="O694" s="22" t="n"/>
@@ -53158,7 +53229,7 @@
       <c r="Q694" s="22" t="n"/>
       <c r="R694" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0019 als MAS0019 Position Etikettenband. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0010 als MAS0010 Verbleibende Labels (geschätzt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Stk.. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -53170,21 +53241,23 @@
       </c>
       <c r="B695" s="22" t="inlineStr">
         <is>
-          <t>0020</t>
-        </is>
-      </c>
-      <c r="C695" s="16" t="n">
-        <v>-2147483647</v>
+          <t>0011</t>
+        </is>
+      </c>
+      <c r="C695" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D695" s="11" t="n">
-        <v>2147483647</v>
-      </c>
-      <c r="E695" s="11" t="n">
-        <v>0</v>
+        <v>1540</v>
+      </c>
+      <c r="E695" s="11" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
       </c>
       <c r="F695" s="15" t="inlineStr">
         <is>
-          <t>pulse</t>
+          <t>1/10mm</t>
         </is>
       </c>
       <c r="G695" s="22" t="n"/>
@@ -53200,12 +53273,12 @@
       </c>
       <c r="J695" s="15" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K695" s="15" t="inlineStr">
         <is>
-          <t>MAS0020 Position Encoder Einlauf</t>
+          <t>MAS0011 Ist Position Portalachse X</t>
         </is>
       </c>
       <c r="L695" s="29" t="n"/>
@@ -53216,7 +53289,7 @@
       </c>
       <c r="N695" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Encoder Einlauf</t>
+          <t>Ist Position Portalachse X (Querrichtung)</t>
         </is>
       </c>
       <c r="O695" s="22" t="n"/>
@@ -53224,7 +53297,7 @@
       <c r="Q695" s="22" t="n"/>
       <c r="R695" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0020 als MAS0020 Position Encoder Einlauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: pulse. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0011 als MAS0011 Ist Position Portalachse X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -53236,21 +53309,23 @@
       </c>
       <c r="B696" s="22" t="inlineStr">
         <is>
-          <t>0021</t>
-        </is>
-      </c>
-      <c r="C696" s="16" t="n">
-        <v>-2147483647</v>
+          <t>0012</t>
+        </is>
+      </c>
+      <c r="C696" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D696" s="11" t="n">
-        <v>2147483647</v>
-      </c>
-      <c r="E696" s="11" t="n">
-        <v>0</v>
+        <v>990</v>
+      </c>
+      <c r="E696" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="F696" s="15" t="inlineStr">
         <is>
-          <t>pulse</t>
+          <t>1/10mm</t>
         </is>
       </c>
       <c r="G696" s="22" t="n"/>
@@ -53266,12 +53341,12 @@
       </c>
       <c r="J696" s="15" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K696" s="15" t="inlineStr">
         <is>
-          <t>MAS0021 Position Encoder Auslauf</t>
+          <t>MAS0012 Ist Position Portalachse Z</t>
         </is>
       </c>
       <c r="L696" s="29" t="n"/>
@@ -53282,7 +53357,7 @@
       </c>
       <c r="N696" s="22" t="inlineStr">
         <is>
-          <t>Ist Position Encoder Auslauf</t>
+          <t>Ist Position Portalachse Z (Vertikal)</t>
         </is>
       </c>
       <c r="O696" s="22" t="n"/>
@@ -53290,7 +53365,7 @@
       <c r="Q696" s="22" t="n"/>
       <c r="R696" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAS0021 als MAS0021 Position Encoder Auslauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: pulse. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0012 als MAS0012 Ist Position Portalachse Z. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -53302,23 +53377,23 @@
       </c>
       <c r="B697" s="22" t="inlineStr">
         <is>
-          <t>0022</t>
-        </is>
-      </c>
-      <c r="C697" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0013</t>
+        </is>
+      </c>
+      <c r="C697" s="3" t="n">
+        <v>-200</v>
       </c>
       <c r="D697" s="11" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="E697" s="11" t="n">
-        <v>1200</v>
+        <v>650</v>
+      </c>
+      <c r="E697" s="11" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="F697" s="15" t="inlineStr">
         <is>
-          <t>Status-Read</t>
+          <t>1/10mm</t>
         </is>
       </c>
       <c r="G697" s="22" t="n"/>
@@ -53334,12 +53409,12 @@
       </c>
       <c r="J697" s="15" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K697" s="15" t="inlineStr">
         <is>
-          <t>MAS0022 SPS-IO Status (0)</t>
+          <t>MAS0013 Ist Position Etikettensensor X</t>
         </is>
       </c>
       <c r="L697" s="29" t="n"/>
@@ -53349,6 +53424,612 @@
         </is>
       </c>
       <c r="N697" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etikettensensor X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O697" s="22" t="n"/>
+      <c r="P697" s="22" t="n"/>
+      <c r="Q697" s="22" t="n"/>
+      <c r="R697" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0013 als MAS0013 Ist Position Etikettensensor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" hidden="1" ht="409.5" customHeight="1">
+      <c r="A698" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B698" s="22" t="inlineStr">
+        <is>
+          <t>0014</t>
+        </is>
+      </c>
+      <c r="C698" s="3" t="n">
+        <v>-200</v>
+      </c>
+      <c r="D698" s="11" t="n">
+        <v>650</v>
+      </c>
+      <c r="E698" s="11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F698" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G698" s="22" t="n"/>
+      <c r="H698" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I698" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J698" s="15" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K698" s="15" t="inlineStr">
+        <is>
+          <t>MAS0014 Ist Position Etikettenentnahmesensor X</t>
+        </is>
+      </c>
+      <c r="L698" s="29" t="n"/>
+      <c r="M698" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N698" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etikettenentnahmesensor X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O698" s="22" t="n"/>
+      <c r="P698" s="22" t="n"/>
+      <c r="Q698" s="22" t="n"/>
+      <c r="R698" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0014 als MAS0014 Ist Position Etikettenentnahmesensor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" hidden="1" ht="409.5" customHeight="1">
+      <c r="A699" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B699" s="22" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="C699" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D699" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E699" s="11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F699" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G699" s="22" t="n"/>
+      <c r="H699" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I699" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J699" s="15" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K699" s="15" t="inlineStr">
+        <is>
+          <t>MAS0015 Ist Position Etikettenanschlag Einlauf X</t>
+        </is>
+      </c>
+      <c r="L699" s="29" t="n"/>
+      <c r="M699" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N699" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etikettenanschlag Einlauf X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O699" s="22" t="n"/>
+      <c r="P699" s="22" t="n"/>
+      <c r="Q699" s="22" t="n"/>
+      <c r="R699" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0015 als MAS0015 Ist Position Etikettenanschlag Einlauf X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700" hidden="1" ht="409.5" customHeight="1">
+      <c r="A700" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B700" s="22" t="inlineStr">
+        <is>
+          <t>0016</t>
+        </is>
+      </c>
+      <c r="C700" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D700" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E700" s="11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F700" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G700" s="22" t="n"/>
+      <c r="H700" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I700" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J700" s="15" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K700" s="15" t="inlineStr">
+        <is>
+          <t>MAS0016 Ist Position Etikettenanschlag Auslauf X</t>
+        </is>
+      </c>
+      <c r="L700" s="29" t="n"/>
+      <c r="M700" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N700" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etikettenanschlag Auslauf X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O700" s="22" t="n"/>
+      <c r="P700" s="22" t="n"/>
+      <c r="Q700" s="22" t="n"/>
+      <c r="R700" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0016 als MAS0016 Ist Position Etikettenanschlag Auslauf X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701" hidden="1" ht="105" customHeight="1">
+      <c r="A701" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B701" s="22" t="inlineStr">
+        <is>
+          <t>0017</t>
+        </is>
+      </c>
+      <c r="C701" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D701" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E701" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F701" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G701" s="22" t="n"/>
+      <c r="H701" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I701" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J701" s="15" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K701" s="15" t="inlineStr">
+        <is>
+          <t>MAS0017 Ist Position Material-Kontrollkamera X</t>
+        </is>
+      </c>
+      <c r="L701" s="29" t="n"/>
+      <c r="M701" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N701" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Material-Kontrollkamera X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O701" s="22" t="n"/>
+      <c r="P701" s="22" t="n"/>
+      <c r="Q701" s="22" t="n"/>
+      <c r="R701" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0017 als MAS0017 Ist Position Material-Kontrollkamera X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702" hidden="1" ht="90" customHeight="1">
+      <c r="A702" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B702" s="22" t="inlineStr">
+        <is>
+          <t>0018</t>
+        </is>
+      </c>
+      <c r="C702" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D702" s="11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E702" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="F702" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G702" s="22" t="n"/>
+      <c r="H702" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I702" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J702" s="15" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="K702" s="15" t="inlineStr">
+        <is>
+          <t>MAS0018 Ist Position Laserschutz X</t>
+        </is>
+      </c>
+      <c r="L702" s="29" t="n"/>
+      <c r="M702" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N702" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Laserschutz X (Querrichtung)</t>
+        </is>
+      </c>
+      <c r="O702" s="22" t="n"/>
+      <c r="P702" s="22" t="n"/>
+      <c r="Q702" s="22" t="n"/>
+      <c r="R702" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0018 als MAS0018 Ist Position Laserschutz X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" hidden="1" ht="135" customHeight="1">
+      <c r="A703" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B703" s="22" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="C703" s="16" t="n">
+        <v>-67465000</v>
+      </c>
+      <c r="D703" s="11" t="n">
+        <v>67465000</v>
+      </c>
+      <c r="E703" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F703" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G703" s="22" t="n"/>
+      <c r="H703" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I703" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J703" s="15" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="K703" s="15" t="inlineStr">
+        <is>
+          <t>MAS0019 Position Etikettenband</t>
+        </is>
+      </c>
+      <c r="L703" s="29" t="n"/>
+      <c r="M703" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N703" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etikettenband</t>
+        </is>
+      </c>
+      <c r="O703" s="22" t="n"/>
+      <c r="P703" s="22" t="n"/>
+      <c r="Q703" s="22" t="n"/>
+      <c r="R703" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAS0019 als MAS0019 Position Etikettenband. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704" hidden="1" ht="60" customHeight="1">
+      <c r="A704" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B704" s="22" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="C704" s="16" t="n">
+        <v>-2147483647</v>
+      </c>
+      <c r="D704" s="11" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="E704" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F704" s="15" t="inlineStr">
+        <is>
+          <t>pulse</t>
+        </is>
+      </c>
+      <c r="G704" s="22" t="n"/>
+      <c r="H704" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I704" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J704" s="15" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="K704" s="15" t="inlineStr">
+        <is>
+          <t>MAS0020 Position Encoder Einlauf</t>
+        </is>
+      </c>
+      <c r="L704" s="29" t="n"/>
+      <c r="M704" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N704" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Encoder Einlauf</t>
+        </is>
+      </c>
+      <c r="O704" s="22" t="n"/>
+      <c r="P704" s="22" t="n"/>
+      <c r="Q704" s="22" t="n"/>
+      <c r="R704" s="22" t="inlineStr">
+        <is>
+          <t>KI: Istposition Encoder Einlauf in Pulsen. Die ESP-Firmware normalisiert die Zaehlerichtung so, dass physische Vorzugsrichtung/Produktionsfeed positiv zaehlt und Rueckspulen negativ. Dieser Rohzaehler muss mit den Prozess-mm-Werten und dem Label-Schieberegister dieselbe Vorzeichenlogik haben. Microtom liest nur; ESP fuehrt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705" hidden="1" ht="60" customHeight="1">
+      <c r="A705" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B705" s="22" t="inlineStr">
+        <is>
+          <t>0021</t>
+        </is>
+      </c>
+      <c r="C705" s="16" t="n">
+        <v>-2147483647</v>
+      </c>
+      <c r="D705" s="11" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="E705" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F705" s="15" t="inlineStr">
+        <is>
+          <t>pulse</t>
+        </is>
+      </c>
+      <c r="G705" s="22" t="n"/>
+      <c r="H705" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I705" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J705" s="15" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="K705" s="15" t="inlineStr">
+        <is>
+          <t>MAS0021 Position Encoder Auslauf</t>
+        </is>
+      </c>
+      <c r="L705" s="29" t="n"/>
+      <c r="M705" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N705" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Encoder Auslauf</t>
+        </is>
+      </c>
+      <c r="O705" s="22" t="n"/>
+      <c r="P705" s="22" t="n"/>
+      <c r="Q705" s="22" t="n"/>
+      <c r="R705" s="22" t="inlineStr">
+        <is>
+          <t>KI: Istposition Encoder Auslauf/Drive in Pulsen. Die ESP-Firmware normalisiert die Zaehlerichtung so, dass physische Vorzugsrichtung/Produktionsfeed positiv zaehlt und Rueckspulen negativ. Dieser Rohzaehler muss mit Motor ID3 und dem Einlaufencoder dieselbe Vorzeichenlogik haben. Microtom liest nur; ESP fuehrt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" hidden="1" ht="90" customHeight="1">
+      <c r="A706" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B706" s="22" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
+      <c r="C706" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D706" s="11" t="n">
+        <v>4294967295</v>
+      </c>
+      <c r="E706" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F706" s="15" t="inlineStr">
+        <is>
+          <t>Status-Read</t>
+        </is>
+      </c>
+      <c r="G706" s="22" t="n"/>
+      <c r="H706" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I706" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J706" s="15" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="K706" s="15" t="inlineStr">
+        <is>
+          <t>MAS0022 SPS-IO Status (0)</t>
+        </is>
+      </c>
+      <c r="L706" s="29" t="n"/>
+      <c r="M706" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N706" s="22" t="inlineStr">
         <is>
           <t>IO-Status0 von ESP32-SPS0
 Bit  0 = I0.0   TTO Drucker Status
@@ -53385,70 +54066,70 @@
 Bit 31 = I2.5   Interrupt Encoder CH A Umlenkrolle hinten</t>
         </is>
       </c>
-      <c r="O697" s="22" t="n"/>
-      <c r="P697" s="22" t="n"/>
-      <c r="Q697" s="22" t="n"/>
-      <c r="R697" s="22" t="inlineStr">
+      <c r="O706" s="22" t="n"/>
+      <c r="P706" s="22" t="n"/>
+      <c r="Q706" s="22" t="n"/>
+      <c r="R706" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe MAS0022 als MAS0022 SPS-IO Status (0). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="698" hidden="1" ht="409.5" customHeight="1">
-      <c r="A698" s="15" t="inlineStr">
+    <row r="707" hidden="1" ht="90" customHeight="1">
+      <c r="A707" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B698" s="22" t="inlineStr">
+      <c r="B707" s="22" t="inlineStr">
         <is>
           <t>0023</t>
         </is>
       </c>
-      <c r="C698" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D698" s="11" t="n">
+      <c r="C707" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D707" s="11" t="n">
         <v>4294967295</v>
       </c>
-      <c r="E698" s="11" t="n">
+      <c r="E707" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="F698" s="15" t="inlineStr">
+      <c r="F707" s="15" t="inlineStr">
         <is>
           <t>Status-Read</t>
         </is>
       </c>
-      <c r="G698" s="22" t="n"/>
-      <c r="H698" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I698" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J698" s="15" t="inlineStr">
+      <c r="G707" s="22" t="n"/>
+      <c r="H707" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I707" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J707" s="15" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="K698" s="15" t="inlineStr">
+      <c r="K707" s="15" t="inlineStr">
         <is>
           <t>MAS0023 SPS-IO Status (1)</t>
         </is>
       </c>
-      <c r="L698" s="29" t="n"/>
-      <c r="M698" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N698" s="22" t="inlineStr">
+      <c r="L707" s="29" t="n"/>
+      <c r="M707" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N707" s="22" t="inlineStr">
         <is>
           <t>IO-Status1 von ESP32-SPS:Bit 32 = I2.6   Interrupt Encoder CH B Umlenkrolle hinten
 Bit 33 = I2.7   SEAVision Materialkontrolle Daten bereit
@@ -53484,70 +54165,70 @@
 Bit 63 = DO2    Reserve 2 Motor X-Achse</t>
         </is>
       </c>
-      <c r="O698" s="22" t="n"/>
-      <c r="P698" s="22" t="n"/>
-      <c r="Q698" s="22" t="n"/>
-      <c r="R698" s="22" t="inlineStr">
+      <c r="O707" s="22" t="n"/>
+      <c r="P707" s="22" t="n"/>
+      <c r="Q707" s="22" t="n"/>
+      <c r="R707" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe MAS0023 als MAS0023 SPS-IO Status (1). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="699" hidden="1" ht="409.5" customHeight="1">
-      <c r="A699" s="15" t="inlineStr">
+    <row r="708" hidden="1">
+      <c r="A708" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B699" s="22" t="inlineStr">
+      <c r="B708" s="22" t="inlineStr">
         <is>
           <t>0024</t>
         </is>
       </c>
-      <c r="C699" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D699" s="11" t="n">
+      <c r="C708" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D708" s="11" t="n">
         <v>4294967295</v>
       </c>
-      <c r="E699" s="11" t="n">
+      <c r="E708" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="F699" s="15" t="inlineStr">
+      <c r="F708" s="15" t="inlineStr">
         <is>
           <t>Status-Read</t>
         </is>
       </c>
-      <c r="G699" s="22" t="n"/>
-      <c r="H699" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I699" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J699" s="15" t="inlineStr">
+      <c r="G708" s="22" t="n"/>
+      <c r="H708" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I708" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J708" s="15" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="K699" s="15" t="inlineStr">
+      <c r="K708" s="15" t="inlineStr">
         <is>
           <t>MAS0024 SPS-IO Status (2)</t>
         </is>
       </c>
-      <c r="L699" s="29" t="n"/>
-      <c r="M699" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N699" s="22" t="inlineStr">
+      <c r="L708" s="29" t="n"/>
+      <c r="M708" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N708" s="22" t="inlineStr">
         <is>
           <t>IO-Status2 von ESP32-SPS:
 Bit 64 = DO3    Start Motor Z-Achse (IN0)
@@ -53584,70 +54265,70 @@
 Bit 95 = n.a.</t>
         </is>
       </c>
-      <c r="O699" s="22" t="n"/>
-      <c r="P699" s="22" t="n"/>
-      <c r="Q699" s="22" t="n"/>
-      <c r="R699" s="22" t="inlineStr">
+      <c r="O708" s="22" t="n"/>
+      <c r="P708" s="22" t="n"/>
+      <c r="Q708" s="22" t="n"/>
+      <c r="R708" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe MAS0024 als MAS0024 SPS-IO Status (2). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="700" hidden="1" ht="409.5" customHeight="1">
-      <c r="A700" s="15" t="inlineStr">
+    <row r="709" hidden="1" ht="30" customHeight="1">
+      <c r="A709" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B700" s="22" t="inlineStr">
+      <c r="B709" s="22" t="inlineStr">
         <is>
           <t>0025</t>
         </is>
       </c>
-      <c r="C700" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D700" s="11" t="n">
+      <c r="C709" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D709" s="11" t="n">
         <v>4294967295</v>
       </c>
-      <c r="E700" s="11" t="n">
+      <c r="E709" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F700" s="15" t="inlineStr">
+      <c r="F709" s="15" t="inlineStr">
         <is>
           <t>Status-Read</t>
         </is>
       </c>
-      <c r="G700" s="22" t="n"/>
-      <c r="H700" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I700" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J700" s="15" t="inlineStr">
+      <c r="G709" s="22" t="n"/>
+      <c r="H709" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I709" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J709" s="15" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="K700" s="15" t="inlineStr">
+      <c r="K709" s="15" t="inlineStr">
         <is>
           <t>MAS0025 SPS-IO Status (3)</t>
         </is>
       </c>
-      <c r="L700" s="29" t="n"/>
-      <c r="M700" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N700" s="22" t="inlineStr">
+      <c r="L709" s="29" t="n"/>
+      <c r="M709" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N709" s="22" t="inlineStr">
         <is>
           <t>IO-Status 3 von RPI-SPS:
 Bit  96 = I0.0   Reserve
@@ -53684,70 +54365,70 @@
 Bit 127 = n.a.</t>
         </is>
       </c>
-      <c r="O700" s="22" t="n"/>
-      <c r="P700" s="22" t="n"/>
-      <c r="Q700" s="22" t="n"/>
-      <c r="R700" s="22" t="inlineStr">
+      <c r="O709" s="22" t="n"/>
+      <c r="P709" s="22" t="n"/>
+      <c r="Q709" s="22" t="n"/>
+      <c r="R709" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe MAS0025 als MAS0025 SPS-IO Status (3). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="701" hidden="1" ht="105" customHeight="1">
-      <c r="A701" s="15" t="inlineStr">
+    <row r="710" hidden="1" ht="30" customHeight="1">
+      <c r="A710" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B701" s="22" t="inlineStr">
+      <c r="B710" s="22" t="inlineStr">
         <is>
           <t>0026</t>
         </is>
       </c>
-      <c r="C701" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D701" s="11" t="n">
+      <c r="C710" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D710" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="E701" s="11" t="n">
+      <c r="E710" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F701" s="15" t="inlineStr">
+      <c r="F710" s="15" t="inlineStr">
         <is>
           <t>Status-Read</t>
         </is>
       </c>
-      <c r="G701" s="22" t="n"/>
-      <c r="H701" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I701" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J701" s="15" t="inlineStr">
+      <c r="G710" s="22" t="n"/>
+      <c r="H710" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I710" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J710" s="15" t="inlineStr">
         <is>
           <t>uint8</t>
         </is>
       </c>
-      <c r="K701" s="25" t="inlineStr">
+      <c r="K710" s="25" t="inlineStr">
         <is>
           <t>MAS0026 Status Abwickler</t>
         </is>
       </c>
-      <c r="L701" s="29" t="n"/>
-      <c r="M701" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N701" s="22" t="inlineStr">
+      <c r="L710" s="29" t="n"/>
+      <c r="M710" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N710" s="22" t="inlineStr">
         <is>
           <t>Status Byte Abwickeleinheit:
 0 = Ausgeschaltet
@@ -53758,70 +54439,70 @@
 5 = Warnung</t>
         </is>
       </c>
-      <c r="O701" s="22" t="n"/>
-      <c r="P701" s="22" t="n"/>
-      <c r="Q701" s="22" t="n"/>
-      <c r="R701" s="22" t="inlineStr">
+      <c r="O710" s="22" t="n"/>
+      <c r="P710" s="22" t="n"/>
+      <c r="Q710" s="22" t="n"/>
+      <c r="R710" s="22" t="inlineStr">
         <is>
           <t>KI: Ich verstehe diesen Parameter als Status des Abwicklers. Der Wert wird von der Wicklersteuerung fuehrend geliefert und vom ESP/Raspi fuer die Gesamtanlage weiterverwendet. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
-    <row r="702" hidden="1" ht="90" customHeight="1">
-      <c r="A702" s="15" t="inlineStr">
+    <row r="711" hidden="1">
+      <c r="A711" s="15" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>
       </c>
-      <c r="B702" s="22" t="inlineStr">
+      <c r="B711" s="22" t="inlineStr">
         <is>
           <t>0027</t>
         </is>
       </c>
-      <c r="C702" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D702" s="11" t="n">
+      <c r="C711" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D711" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="E702" s="11" t="n">
+      <c r="E711" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="F702" s="15" t="inlineStr">
+      <c r="F711" s="15" t="inlineStr">
         <is>
           <t>Status-Read</t>
         </is>
       </c>
-      <c r="G702" s="22" t="n"/>
-      <c r="H702" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I702" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J702" s="15" t="inlineStr">
+      <c r="G711" s="22" t="n"/>
+      <c r="H711" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I711" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J711" s="15" t="inlineStr">
         <is>
           <t>uint8</t>
         </is>
       </c>
-      <c r="K702" s="25" t="inlineStr">
+      <c r="K711" s="25" t="inlineStr">
         <is>
           <t>MAS0027 Status Aufwickler</t>
         </is>
       </c>
-      <c r="L702" s="29" t="n"/>
-      <c r="M702" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N702" s="22" t="inlineStr">
+      <c r="L711" s="29" t="n"/>
+      <c r="M711" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N711" s="22" t="inlineStr">
         <is>
           <t>Status Byte Aufwickeleinheit:
 0 = Ausgeschaltet
@@ -53831,741 +54512,250 @@
 4 = Störung</t>
         </is>
       </c>
-      <c r="O702" s="22" t="n"/>
-      <c r="P702" s="22" t="n"/>
-      <c r="Q702" s="22" t="n"/>
-      <c r="R702" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als Status des Aufwicklers. Der Wert wird von der Wicklersteuerung fuehrend geliefert und vom ESP/Raspi fuer die Gesamtanlage weiterverwendet. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="703" hidden="1" ht="135" customHeight="1">
-      <c r="A703" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B703" s="22" t="inlineStr">
-        <is>
-          <t>0028</t>
-        </is>
-      </c>
-      <c r="C703" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D703" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E703" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F703" s="15" t="inlineStr">
-        <is>
-          <t>Status - Write</t>
-        </is>
-      </c>
-      <c r="G703" s="22" t="n"/>
-      <c r="H703" s="15" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I703" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J703" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K703" s="25" t="inlineStr">
-        <is>
-          <t>MAS0028 PurgeEvent (1=Event ausgelöst; 0=zurückgesetzt)</t>
-        </is>
-      </c>
-      <c r="L703" s="29" t="n"/>
-      <c r="M703" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N703" s="22" t="inlineStr">
-        <is>
-          <t>Purge Event ausgelöst</t>
-        </is>
-      </c>
-      <c r="O703" s="22" t="n"/>
-      <c r="P703" s="22" t="n"/>
-      <c r="Q703" s="22" t="n"/>
-      <c r="R703" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als Purge- bzw. Abbruchereignis, das eine saubere Fortsetzung der laufenden Produktion verhindert. Solche Ereignisse muessen in den Not-Stop-/Stoerungszustand fuehren und sind fachlich staerker als eine normale Pause. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status - Write. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="704" hidden="1" ht="60" customHeight="1">
-      <c r="A704" s="29" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B704" s="28" t="inlineStr">
-        <is>
-          <t>0029</t>
-        </is>
-      </c>
-      <c r="C704" s="5" t="n"/>
-      <c r="D704" s="12" t="n"/>
-      <c r="E704" s="11" t="inlineStr">
-        <is>
-          <t>ProduxtionX</t>
-        </is>
-      </c>
-      <c r="F704" s="29" t="inlineStr">
-        <is>
-          <t>String - Write</t>
-        </is>
-      </c>
-      <c r="G704" s="28" t="n"/>
-      <c r="H704" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I704" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J704" s="29" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="K704" s="30" t="inlineStr">
-        <is>
-          <t>MAS0029 Produktions-Auftrags-ID / Logfile-Name</t>
-        </is>
-      </c>
-      <c r="L704" s="29" t="n"/>
-      <c r="M704" s="29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N704" s="28" t="inlineStr">
-        <is>
-          <t>String-ID der aktuellen Produktion. Dieser Wert wird beim Start (MAS0002=1) als Dateinamenszusatz fuer die Produktions-Logfiles verwendet.</t>
-        </is>
-      </c>
-      <c r="O704" s="28" t="n"/>
-      <c r="P704" s="28" t="n"/>
-      <c r="Q704" s="28" t="n"/>
-      <c r="R704" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als aktuelle Produktions- bzw. Auftrags-ID fuer Logfiles und Rueckverfolgbarkeit. Gemass Masterliste ist er fuer den ESP nicht relevant; fuehrend verwaltet wird er auf Raspi-/Microtom-Seite. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: String - Write. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S704" s="4" t="n"/>
-      <c r="T704" s="4" t="n"/>
-      <c r="U704" s="4" t="n"/>
-    </row>
-    <row r="705" hidden="1" ht="60" customHeight="1">
-      <c r="A705" s="29" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B705" s="28" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
-      <c r="C705" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D705" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E705" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F705" s="29" t="inlineStr">
-        <is>
-          <t>Status - Read</t>
-        </is>
-      </c>
-      <c r="G705" s="28" t="n"/>
-      <c r="H705" s="29" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I705" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J705" s="29" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="K705" s="30" t="inlineStr">
-        <is>
-          <t>MAS0030 Produktions-Logfiles abholbereit</t>
-        </is>
-      </c>
-      <c r="L705" s="29" t="n"/>
-      <c r="M705" s="29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N705" s="28" t="inlineStr">
-        <is>
-          <t>0 - keine Produktions-Logfiles abholbereit
-1 - Produktions-Logfiles der letzten Produktion sind ueber /api/production/logfiles/* abholbereit</t>
-        </is>
-      </c>
-      <c r="O705" s="28" t="n"/>
-      <c r="P705" s="28" t="n"/>
-      <c r="Q705" s="28" t="n"/>
-      <c r="R705" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe diesen Parameter als Status, ob Produktionslogfiles der letzten Produktion noch abholbereit sind. Auch dieser Wert ist gemaess Masterliste Raspi-/Microtom-seitig und soll nicht in den ESP gespiegelt werden. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Status - Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S705" s="4" t="n"/>
-      <c r="T705" s="4" t="n"/>
-      <c r="U705" s="4" t="n"/>
-    </row>
-    <row r="706" hidden="1" ht="90" customHeight="1">
-      <c r="A706" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B706" s="22" t="inlineStr">
-        <is>
-          <t>0031</t>
-        </is>
-      </c>
-      <c r="C706" s="3" t="inlineStr">
-        <is>
-          <t>-2’147’483’648</t>
-        </is>
-      </c>
-      <c r="D706" s="11" t="inlineStr">
-        <is>
-          <t>2’147’483’647</t>
-        </is>
-      </c>
-      <c r="E706" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F706" s="15" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G706" s="22" t="n"/>
-      <c r="H706" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I706" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J706" s="15" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="K706" s="15" t="inlineStr">
-        <is>
-          <t>MAS0031 Ist Position Etikettenantrieb</t>
-        </is>
-      </c>
-      <c r="L706" s="29" t="n"/>
-      <c r="M706" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N706" s="22" t="inlineStr">
-        <is>
-          <t>Ist Position Etiekttenantrieb in 1/10mm</t>
-        </is>
-      </c>
-      <c r="O706" s="22" t="n"/>
-      <c r="P706" s="22" t="n"/>
-      <c r="Q706" s="22" t="n"/>
-      <c r="R706" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0031 als MAS0031 Ist Position Etikettenantrieb. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="707" hidden="1" ht="90" customHeight="1">
-      <c r="A707" s="15" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="B707" s="22" t="inlineStr">
-        <is>
-          <t>0032</t>
-        </is>
-      </c>
-      <c r="C707" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D707" s="11" t="n">
-        <v>800</v>
-      </c>
-      <c r="E707" s="11" t="n">
-        <v>800</v>
-      </c>
-      <c r="F707" s="15" t="inlineStr">
-        <is>
-          <t>1/10mm</t>
-        </is>
-      </c>
-      <c r="G707" s="22" t="n"/>
-      <c r="H707" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I707" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J707" s="15" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="K707" s="15" t="inlineStr">
-        <is>
-          <t>MAS0032 Ist Position Schutzblech Laser</t>
-        </is>
-      </c>
-      <c r="L707" s="29" t="n"/>
-      <c r="M707" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N707" s="22" t="inlineStr">
-        <is>
-          <t>Ist Position Schutzblech Laser in 1/10mm</t>
-        </is>
-      </c>
-      <c r="O707" s="22" t="n"/>
-      <c r="P707" s="22" t="n"/>
-      <c r="Q707" s="22" t="n"/>
-      <c r="R707" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAS0032 als MAS0032 Ist Position Schutzblech Laser. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="708" hidden="1">
-      <c r="A708" s="15" t="n"/>
-      <c r="B708" s="22" t="n"/>
-      <c r="C708" s="3" t="n"/>
-      <c r="D708" s="11" t="n"/>
-      <c r="E708" s="11" t="n"/>
-      <c r="F708" s="15" t="n"/>
-      <c r="G708" s="15" t="n"/>
-      <c r="H708" s="15" t="n"/>
-      <c r="I708" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J708" s="15" t="n"/>
-      <c r="K708" s="25" t="n"/>
-      <c r="L708" s="29" t="n"/>
-      <c r="M708" s="15" t="n"/>
-      <c r="N708" s="22" t="n"/>
-      <c r="O708" s="22" t="n"/>
-      <c r="P708" s="22" t="n"/>
-      <c r="Q708" s="22" t="n"/>
-      <c r="R708" s="22" t="n"/>
-    </row>
-    <row r="709" hidden="1" ht="30" customHeight="1">
-      <c r="A709" s="15" t="inlineStr">
-        <is>
-          <t>MAW</t>
-        </is>
-      </c>
-      <c r="B709" s="22" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="C709" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D709" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E709" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F709" s="15" t="inlineStr">
-        <is>
-          <t>OFF/ON</t>
-        </is>
-      </c>
-      <c r="G709" s="15" t="n"/>
-      <c r="H709" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I709" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J709" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K709" s="15" t="inlineStr">
-        <is>
-          <t>MAW0001 Warnung Etikettenfüllstand Abwicklung</t>
-        </is>
-      </c>
-      <c r="L709" s="29" t="n"/>
-      <c r="M709" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N709" s="22" t="inlineStr">
-        <is>
-          <t>Der Füllstand der Etiketten Abwickeleinheit ist tiefer als der eingestellte Wert</t>
-        </is>
-      </c>
-      <c r="O709" s="22" t="n"/>
-      <c r="P709" s="22" t="n"/>
-      <c r="Q709" s="22" t="n"/>
-      <c r="R709" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAW0001 als Warnungsbit bzw. Vorwarnung fuer MAW0001 Warnung Etikettenfüllstand Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="710" hidden="1" ht="30" customHeight="1">
-      <c r="A710" s="15" t="inlineStr">
-        <is>
-          <t>MAW</t>
-        </is>
-      </c>
-      <c r="B710" s="22" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="C710" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D710" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E710" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F710" s="15" t="inlineStr">
-        <is>
-          <t>OFF/ON</t>
-        </is>
-      </c>
-      <c r="G710" s="15" t="n"/>
-      <c r="H710" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I710" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J710" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K710" s="15" t="inlineStr">
-        <is>
-          <t>MAW0002 Warnung Etikettenfüllstand Aufwicklung</t>
-        </is>
-      </c>
-      <c r="L710" s="29" t="n"/>
-      <c r="M710" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N710" s="22" t="inlineStr">
-        <is>
-          <t>Der Füllstand der Etiketten Aufwickeleinheit ist tiefer als der eingestellte Wert</t>
-        </is>
-      </c>
-      <c r="O710" s="22" t="n"/>
-      <c r="P710" s="22" t="n"/>
-      <c r="Q710" s="22" t="n"/>
-      <c r="R710" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAW0002 als Warnungsbit bzw. Vorwarnung fuer MAW0002 Warnung Etikettenfüllstand Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="711" hidden="1">
-      <c r="A711" s="15" t="n"/>
-      <c r="B711" s="8" t="n"/>
-      <c r="C711" s="3" t="n"/>
-      <c r="D711" s="11" t="n"/>
-      <c r="E711" s="11" t="n"/>
-      <c r="F711" s="15" t="n"/>
-      <c r="G711" s="15" t="n"/>
-      <c r="H711" s="15" t="n"/>
-      <c r="I711" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J711" s="15" t="n"/>
-      <c r="K711" s="15" t="n"/>
-      <c r="L711" s="29" t="n"/>
-      <c r="M711" s="15" t="n"/>
-      <c r="N711" s="22" t="n"/>
       <c r="O711" s="22" t="n"/>
       <c r="P711" s="22" t="n"/>
       <c r="Q711" s="22" t="n"/>
-      <c r="R711" s="22" t="n"/>
+      <c r="R711" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Status des Aufwicklers. Der Wert wird von der Wicklersteuerung fuehrend geliefert und vom ESP/Raspi fuer die Gesamtanlage weiterverwendet. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status-Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="712" hidden="1">
-      <c r="A712" s="15" t="n"/>
-      <c r="B712" s="8" t="n"/>
-      <c r="C712" s="3" t="n"/>
-      <c r="D712" s="11" t="n"/>
-      <c r="E712" s="11" t="n"/>
-      <c r="F712" s="15" t="n"/>
-      <c r="G712" s="15" t="n"/>
-      <c r="H712" s="15" t="n"/>
+      <c r="A712" s="15" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B712" s="22" t="inlineStr">
+        <is>
+          <t>0028</t>
+        </is>
+      </c>
+      <c r="C712" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D712" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E712" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F712" s="15" t="inlineStr">
+        <is>
+          <t>Status - Write</t>
+        </is>
+      </c>
+      <c r="G712" s="22" t="n"/>
+      <c r="H712" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="I712" s="29" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J712" s="15" t="n"/>
-      <c r="K712" s="15" t="n"/>
+      <c r="J712" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K712" s="25" t="inlineStr">
+        <is>
+          <t>MAS0028 PurgeEvent (1=Event ausgelöst; 0=zurückgesetzt)</t>
+        </is>
+      </c>
       <c r="L712" s="29" t="n"/>
-      <c r="M712" s="15" t="n"/>
-      <c r="N712" s="22" t="n"/>
+      <c r="M712" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N712" s="22" t="inlineStr">
+        <is>
+          <t>Purge Event ausgelöst</t>
+        </is>
+      </c>
       <c r="O712" s="22" t="n"/>
       <c r="P712" s="22" t="n"/>
       <c r="Q712" s="22" t="n"/>
-      <c r="R712" s="22" t="n"/>
+      <c r="R712" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Purge- bzw. Abbruchereignis, das eine saubere Fortsetzung der laufenden Produktion verhindert. Solche Ereignisse muessen in den Not-Stop-/Stoerungszustand fuehren und sind fachlich staerker als eine normale Pause. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: Status - Write. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="713" ht="45" customHeight="1">
-      <c r="A713" s="15" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B713" s="8" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="C713" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D713" s="11" t="n">
+      <c r="A713" s="29" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B713" s="28" t="inlineStr">
+        <is>
+          <t>0029</t>
+        </is>
+      </c>
+      <c r="C713" s="5" t="n"/>
+      <c r="D713" s="12" t="n"/>
+      <c r="E713" s="11" t="inlineStr">
+        <is>
+          <t>ProduxtionX</t>
+        </is>
+      </c>
+      <c r="F713" s="29" t="inlineStr">
+        <is>
+          <t>String - Write</t>
+        </is>
+      </c>
+      <c r="G713" s="28" t="n"/>
+      <c r="H713" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I713" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J713" s="29" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K713" s="30" t="inlineStr">
+        <is>
+          <t>MAS0029 Produktions-Auftrags-ID / Logfile-Name</t>
+        </is>
+      </c>
+      <c r="L713" s="29" t="n"/>
+      <c r="M713" s="29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N713" s="28" t="inlineStr">
+        <is>
+          <t>String-ID der aktuellen Produktion. Dieser Wert wird beim Start (MAS0002=1) als Dateinamenszusatz fuer die Produktions-Logfiles verwendet.</t>
+        </is>
+      </c>
+      <c r="O713" s="28" t="n"/>
+      <c r="P713" s="28" t="n"/>
+      <c r="Q713" s="28" t="n"/>
+      <c r="R713" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als aktuelle Produktions- bzw. Auftrags-ID fuer Logfiles und Rueckverfolgbarkeit. Gemass Masterliste ist er fuer den ESP nicht relevant; fuehrend verwaltet wird er auf Raspi-/Microtom-Seite. Microtom soll diesen Wert fuehrend schreiben koennen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: String - Write. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="S713" s="4" t="n"/>
+      <c r="T713" s="4" t="n"/>
+      <c r="U713" s="4" t="n"/>
+    </row>
+    <row r="714" ht="30" customHeight="1">
+      <c r="A714" s="29" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B714" s="28" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="C714" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D714" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E713" s="11" t="n">
+      <c r="E714" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F713" s="15" t="n"/>
-      <c r="G713" s="15" t="n"/>
-      <c r="H713" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I713" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J713" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K713" s="15" t="inlineStr">
-        <is>
-          <t>MAE0001 Not-Aus ausgelöst</t>
-        </is>
-      </c>
-      <c r="L713" s="29" t="n"/>
-      <c r="M713" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N713" s="15" t="inlineStr">
-        <is>
-          <t>Not-Aus wurde betätigt</t>
-        </is>
-      </c>
-      <c r="O713" s="15" t="inlineStr">
-        <is>
-          <t>Not-Aus-Taster gedrückt, Sicherheitskreis unterbrochen</t>
-        </is>
-      </c>
-      <c r="P713" s="22" t="inlineStr">
-        <is>
-          <t>Produktionsstopp</t>
-        </is>
-      </c>
-      <c r="Q713" s="22" t="inlineStr">
-        <is>
-          <t>Not-Aus entriegeln, Sicherheitskreis prüfen, 
-Produktion neu starten</t>
-        </is>
-      </c>
-      <c r="R713" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0001 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0001 Not-Aus ausgelöst. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="714" ht="30" customHeight="1">
-      <c r="A714" s="15" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B714" s="8" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="C714" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D714" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E714" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F714" s="15" t="n"/>
-      <c r="G714" s="15" t="n"/>
-      <c r="H714" s="15" t="inlineStr">
+      <c r="F714" s="29" t="inlineStr">
+        <is>
+          <t>Status - Read</t>
+        </is>
+      </c>
+      <c r="G714" s="28" t="n"/>
+      <c r="H714" s="29" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="I714" s="29" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J714" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K714" s="15" t="inlineStr">
-        <is>
-          <t>MAE0002 Lichtgitter ausgelöst</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J714" s="29" t="inlineStr">
+        <is>
+          <t>uint8</t>
+        </is>
+      </c>
+      <c r="K714" s="30" t="inlineStr">
+        <is>
+          <t>MAS0030 Produktions-Logfiles abholbereit</t>
         </is>
       </c>
       <c r="L714" s="29" t="n"/>
-      <c r="M714" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N714" s="15" t="inlineStr">
-        <is>
-          <t>Lichtgitter unterbrochen</t>
-        </is>
-      </c>
-      <c r="O714" s="15" t="inlineStr">
-        <is>
-          <t>Person oder Objekt im Schutzbereich</t>
-        </is>
-      </c>
-      <c r="P714" s="22" t="inlineStr">
-        <is>
-          <t>Produktionspause</t>
-        </is>
-      </c>
-      <c r="Q714" s="22" t="inlineStr">
-        <is>
-          <t>Schutzbereich freimachen, Start drücken</t>
-        </is>
-      </c>
-      <c r="R714" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0002 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0002 Lichtgitter ausgelöst. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M714" s="29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N714" s="28" t="inlineStr">
+        <is>
+          <t>0 - keine Produktions-Logfiles abholbereit
+1 - Produktions-Logfiles der letzten Produktion sind ueber /api/production/logfiles/* abholbereit</t>
+        </is>
+      </c>
+      <c r="O714" s="28" t="n"/>
+      <c r="P714" s="28" t="n"/>
+      <c r="Q714" s="28" t="n"/>
+      <c r="R714" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe diesen Parameter als Status, ob Produktionslogfiles der letzten Produktion noch abholbereit sind. Auch dieser Wert ist gemaess Masterliste Raspi-/Microtom-seitig und soll nicht in den ESP gespiegelt werden. Microtom soll diesen Wert nur lesen. Der ESP soll ihn gemaess Masterliste nicht verwenden. Einheit bzw. Wertebereich laut Tabelle: Status - Read. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="S714" s="4" t="n"/>
+      <c r="T714" s="4" t="n"/>
+      <c r="U714" s="4" t="n"/>
     </row>
     <row r="715" ht="90" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B715" s="8" t="inlineStr">
-        <is>
-          <t>0003</t>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B715" s="22" t="inlineStr">
+        <is>
+          <t>0031</t>
         </is>
       </c>
       <c r="C715" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D715" s="11" t="n">
-        <v>1</v>
+          <t>-2’147’483’648</t>
+        </is>
+      </c>
+      <c r="D715" s="11" t="inlineStr">
+        <is>
+          <t>2’147’483’647</t>
+        </is>
       </c>
       <c r="E715" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F715" s="15" t="n"/>
-      <c r="G715" s="15" t="n"/>
+      <c r="F715" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G715" s="22" t="n"/>
       <c r="H715" s="15" t="inlineStr">
         <is>
           <t>R</t>
@@ -54578,12 +54768,12 @@
       </c>
       <c r="J715" s="15" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int32</t>
         </is>
       </c>
       <c r="K715" s="15" t="inlineStr">
         <is>
-          <t>MAE0003 Laserschutzgehäuse offen</t>
+          <t>MAS0031 Ist Position Etikettenantrieb</t>
         </is>
       </c>
       <c r="L715" s="29" t="n"/>
@@ -54592,54 +54782,48 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N715" s="15" t="inlineStr">
-        <is>
-          <t>Laserschutzgehäuse offen</t>
-        </is>
-      </c>
-      <c r="O715" s="15" t="inlineStr">
-        <is>
-          <t>Schutzschalter geöffnet</t>
-        </is>
-      </c>
-      <c r="P715" s="22" t="inlineStr">
-        <is>
-          <t>Produktionspause</t>
-        </is>
-      </c>
-      <c r="Q715" s="22" t="inlineStr">
-        <is>
-          <t>Sensorposition prüfen</t>
-        </is>
-      </c>
+      <c r="N715" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Etiekttenantrieb in 1/10mm</t>
+        </is>
+      </c>
+      <c r="O715" s="22" t="n"/>
+      <c r="P715" s="22" t="n"/>
+      <c r="Q715" s="22" t="n"/>
       <c r="R715" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0003 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0003 Laserschutzgehäuse offen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ist-/Prozessposition des Etikettenantriebs Motor ID3 in 1/10 mm in Maschinenkoordinaten. Positive Werte bedeuten Vorzugsrichtung/Produktionsfeed, negative Werte Rueckspulen. ID3 ist keine dauerhafte Positionsachse; die produktive Nullung erfolgt beim Einrichten/Messfahrtstart und erneut vor Pause/Produktionsstart ueber SET_POSITION_MM=0.000.</t>
         </is>
       </c>
     </row>
     <row r="716" ht="45" customHeight="1">
       <c r="A716" s="15" t="inlineStr">
         <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B716" s="8" t="inlineStr">
-        <is>
-          <t>0004</t>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="B716" s="22" t="inlineStr">
+        <is>
+          <t>0032</t>
         </is>
       </c>
       <c r="C716" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D716" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E716" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F716" s="15" t="n"/>
-      <c r="G716" s="15" t="n"/>
+        <v>800</v>
+      </c>
+      <c r="E716" s="11" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="F716" s="15" t="inlineStr">
+        <is>
+          <t>1/10mm</t>
+        </is>
+      </c>
+      <c r="G716" s="22" t="n"/>
       <c r="H716" s="15" t="inlineStr">
         <is>
           <t>R</t>
@@ -54652,12 +54836,12 @@
       </c>
       <c r="J716" s="15" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="K716" s="15" t="inlineStr">
         <is>
-          <t>MAE0004 Störung Portalachsenmotor X</t>
+          <t>MAS0032 Ist Position Schutzblech Laser</t>
         </is>
       </c>
       <c r="L716" s="29" t="n"/>
@@ -54666,119 +54850,59 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N716" s="15" t="inlineStr">
-        <is>
-          <t>Störung Motor X-Achse</t>
-        </is>
-      </c>
-      <c r="O716" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P716" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q716" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
+      <c r="N716" s="22" t="inlineStr">
+        <is>
+          <t>Ist Position Schutzblech Laser in 1/10mm</t>
+        </is>
+      </c>
+      <c r="O716" s="22" t="n"/>
+      <c r="P716" s="22" t="n"/>
+      <c r="Q716" s="22" t="n"/>
       <c r="R716" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0004 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0004 Störung Portalachsenmotor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAS0032 als MAS0032 Ist Position Schutzblech Laser. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: 1/10mm. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="717" ht="45" customHeight="1">
-      <c r="A717" s="15" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B717" s="8" t="inlineStr">
-        <is>
-          <t>0005</t>
-        </is>
-      </c>
-      <c r="C717" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D717" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E717" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A717" s="15" t="n"/>
+      <c r="B717" s="22" t="n"/>
+      <c r="C717" s="3" t="n"/>
+      <c r="D717" s="11" t="n"/>
+      <c r="E717" s="11" t="n"/>
       <c r="F717" s="15" t="n"/>
       <c r="G717" s="15" t="n"/>
-      <c r="H717" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H717" s="15" t="n"/>
       <c r="I717" s="29" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J717" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K717" s="15" t="inlineStr">
-        <is>
-          <t>MAE0005 Störung Portalachsenmotor Z</t>
-        </is>
-      </c>
+      <c r="J717" s="15" t="n"/>
+      <c r="K717" s="25" t="n"/>
       <c r="L717" s="29" t="n"/>
-      <c r="M717" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N717" s="15" t="inlineStr">
-        <is>
-          <t>Störung Motor Z-Achse</t>
-        </is>
-      </c>
-      <c r="O717" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P717" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q717" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
-      <c r="R717" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0005 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0005 Störung Portalachsenmotor Z. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M717" s="15" t="n"/>
+      <c r="N717" s="22" t="n"/>
+      <c r="O717" s="22" t="n"/>
+      <c r="P717" s="22" t="n"/>
+      <c r="Q717" s="22" t="n"/>
+      <c r="R717" s="22" t="n"/>
     </row>
     <row r="718" ht="45" customHeight="1">
       <c r="A718" s="15" t="inlineStr">
         <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B718" s="8" t="inlineStr">
-        <is>
-          <t>0006</t>
-        </is>
-      </c>
-      <c r="C718" s="3" t="n">
-        <v>0</v>
+          <t>MAW</t>
+        </is>
+      </c>
+      <c r="B718" s="22" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="C718" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D718" s="11" t="n">
         <v>1</v>
@@ -54786,7 +54910,11 @@
       <c r="E718" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F718" s="15" t="n"/>
+      <c r="F718" s="15" t="inlineStr">
+        <is>
+          <t>OFF/ON</t>
+        </is>
+      </c>
       <c r="G718" s="15" t="n"/>
       <c r="H718" s="15" t="inlineStr">
         <is>
@@ -54805,7 +54933,7 @@
       </c>
       <c r="K718" s="15" t="inlineStr">
         <is>
-          <t>MAE0006 Störung Positionsantrieb Etiketten Erfassungssensor</t>
+          <t>MAW0001 Warnung Etikettenfüllstand Abwicklung</t>
         </is>
       </c>
       <c r="L718" s="29" t="n"/>
@@ -54814,45 +54942,35 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N718" s="15" t="inlineStr">
-        <is>
-          <t>Positionsantrieb Erfassungssensor gestört</t>
-        </is>
-      </c>
-      <c r="O718" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P718" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q718" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
+      <c r="N718" s="22" t="inlineStr">
+        <is>
+          <t>Der Füllstand der Etiketten Abwickeleinheit ist tiefer als der eingestellte Wert</t>
+        </is>
+      </c>
+      <c r="O718" s="22" t="n"/>
+      <c r="P718" s="22" t="n"/>
+      <c r="Q718" s="22" t="n"/>
       <c r="R718" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0006 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0006 Störung Positionsantrieb Etiketten Erfassungssensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAW0001 als Warnungsbit bzw. Vorwarnung fuer MAW0001 Warnung Etikettenfüllstand Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="719" ht="45" customHeight="1">
       <c r="A719" s="15" t="inlineStr">
         <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B719" s="8" t="inlineStr">
-        <is>
-          <t>0007</t>
-        </is>
-      </c>
-      <c r="C719" s="3" t="n">
-        <v>0</v>
+          <t>MAW</t>
+        </is>
+      </c>
+      <c r="B719" s="22" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D719" s="11" t="n">
         <v>1</v>
@@ -54860,7 +54978,11 @@
       <c r="E719" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F719" s="15" t="n"/>
+      <c r="F719" s="15" t="inlineStr">
+        <is>
+          <t>OFF/ON</t>
+        </is>
+      </c>
       <c r="G719" s="15" t="n"/>
       <c r="H719" s="15" t="inlineStr">
         <is>
@@ -54879,7 +55001,7 @@
       </c>
       <c r="K719" s="15" t="inlineStr">
         <is>
-          <t>MAE0007 Störung Positionsantrieb Etiketten Entnahmesensor</t>
+          <t>MAW0002 Warnung Etikettenfüllstand Aufwicklung</t>
         </is>
       </c>
       <c r="L719" s="29" t="n"/>
@@ -54888,179 +55010,67 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N719" s="15" t="inlineStr">
-        <is>
-          <t>Positionsantrieb Entnahmesensor gestört</t>
-        </is>
-      </c>
-      <c r="O719" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P719" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q719" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
+      <c r="N719" s="22" t="inlineStr">
+        <is>
+          <t>Der Füllstand der Etiketten Aufwickeleinheit ist tiefer als der eingestellte Wert</t>
+        </is>
+      </c>
+      <c r="O719" s="22" t="n"/>
+      <c r="P719" s="22" t="n"/>
+      <c r="Q719" s="22" t="n"/>
       <c r="R719" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0007 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0007 Störung Positionsantrieb Etiketten Entnahmesensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAW0002 als Warnungsbit bzw. Vorwarnung fuer MAW0002 Warnung Etikettenfüllstand Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Einheit bzw. Wertebereich laut Tabelle: OFF/ON. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="720" ht="45" customHeight="1">
-      <c r="A720" s="15" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B720" s="8" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
-      <c r="C720" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D720" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E720" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A720" s="15" t="n"/>
+      <c r="B720" s="8" t="n"/>
+      <c r="C720" s="3" t="n"/>
+      <c r="D720" s="11" t="n"/>
+      <c r="E720" s="11" t="n"/>
       <c r="F720" s="15" t="n"/>
       <c r="G720" s="15" t="n"/>
-      <c r="H720" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H720" s="15" t="n"/>
       <c r="I720" s="29" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J720" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K720" s="15" t="inlineStr">
-        <is>
-          <t>MAE0008 Störung Positionsantrieb Etikettenführung Einlauf</t>
-        </is>
-      </c>
+      <c r="J720" s="15" t="n"/>
+      <c r="K720" s="15" t="n"/>
       <c r="L720" s="29" t="n"/>
-      <c r="M720" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N720" s="15" t="inlineStr">
-        <is>
-          <t>Etikettenführung Einlauf gestört</t>
-        </is>
-      </c>
-      <c r="O720" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P720" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q720" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
-      <c r="R720" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0008 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0008 Störung Positionsantrieb Etikettenführung Einlauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M720" s="15" t="n"/>
+      <c r="N720" s="22" t="n"/>
+      <c r="O720" s="22" t="n"/>
+      <c r="P720" s="22" t="n"/>
+      <c r="Q720" s="22" t="n"/>
+      <c r="R720" s="22" t="n"/>
     </row>
     <row r="721" ht="45" customHeight="1">
-      <c r="A721" s="15" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="B721" s="8" t="inlineStr">
-        <is>
-          <t>0009</t>
-        </is>
-      </c>
-      <c r="C721" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D721" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E721" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A721" s="15" t="n"/>
+      <c r="B721" s="8" t="n"/>
+      <c r="C721" s="3" t="n"/>
+      <c r="D721" s="11" t="n"/>
+      <c r="E721" s="11" t="n"/>
       <c r="F721" s="15" t="n"/>
       <c r="G721" s="15" t="n"/>
-      <c r="H721" s="15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H721" s="15" t="n"/>
       <c r="I721" s="29" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J721" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K721" s="15" t="inlineStr">
-        <is>
-          <t>MAE0009 Störung Positionsantrieb Etikettenführung Auslauf</t>
-        </is>
-      </c>
+      <c r="J721" s="15" t="n"/>
+      <c r="K721" s="15" t="n"/>
       <c r="L721" s="29" t="n"/>
-      <c r="M721" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N721" s="15" t="inlineStr">
-        <is>
-          <t>Etikettenführung Auslauf gestört</t>
-        </is>
-      </c>
-      <c r="O721" s="15" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
-      <c r="P721" s="22" t="inlineStr">
-        <is>
-          <t>Positionierung nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q721" s="22" t="inlineStr">
-        <is>
-          <t>Mechanik und Motor prüfen</t>
-        </is>
-      </c>
-      <c r="R721" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0009 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0009 Störung Positionsantrieb Etikettenführung Auslauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M721" s="15" t="n"/>
+      <c r="N721" s="22" t="n"/>
+      <c r="O721" s="22" t="n"/>
+      <c r="P721" s="22" t="n"/>
+      <c r="Q721" s="22" t="n"/>
+      <c r="R721" s="22" t="n"/>
     </row>
     <row r="722" ht="45" customHeight="1">
       <c r="A722" s="15" t="inlineStr">
@@ -55070,11 +55080,13 @@
       </c>
       <c r="B722" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
-        </is>
-      </c>
-      <c r="C722" s="3" t="n">
-        <v>0</v>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="C722" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D722" s="11" t="n">
         <v>1</v>
@@ -55101,7 +55113,7 @@
       </c>
       <c r="K722" s="15" t="inlineStr">
         <is>
-          <t>MAE0010 Störung Positionsantrieb Material Kontrollkamera</t>
+          <t>MAE0001 Not-Aus ausgelöst</t>
         </is>
       </c>
       <c r="L722" s="29" t="n"/>
@@ -55112,27 +55124,28 @@
       </c>
       <c r="N722" s="15" t="inlineStr">
         <is>
-          <t>Materialkontrollkamera Positionsantrieb meldet Störung</t>
+          <t>Not-Aus wurde betätigt</t>
         </is>
       </c>
       <c r="O722" s="15" t="inlineStr">
         <is>
-          <t>Überlast oder Blockade</t>
+          <t>Not-Aus-Taster gedrückt, Sicherheitskreis unterbrochen</t>
         </is>
       </c>
       <c r="P722" s="22" t="inlineStr">
         <is>
-          <t>Positionierung nicht möglich</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q722" s="22" t="inlineStr">
         <is>
-          <t>Mechanik und Motor prüfen</t>
+          <t>Not-Aus entriegeln, Sicherheitskreis prüfen, 
+Produktion neu starten</t>
         </is>
       </c>
       <c r="R722" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0010 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0010 Störung Positionsantrieb Material Kontrollkamera. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0001 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0001 Not-Aus ausgelöst. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55144,7 +55157,7 @@
       </c>
       <c r="B723" s="8" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="C723" s="3" t="inlineStr">
@@ -55177,7 +55190,7 @@
       </c>
       <c r="K723" s="15" t="inlineStr">
         <is>
-          <t>MAE0011 Störung Antriebsmotor Abwicklung</t>
+          <t>MAE0002 Lichtgitter ausgelöst</t>
         </is>
       </c>
       <c r="L723" s="29" t="n"/>
@@ -55188,12 +55201,12 @@
       </c>
       <c r="N723" s="15" t="inlineStr">
         <is>
-          <t>Abwicklungsmotor meldet Störung</t>
+          <t>Lichtgitter unterbrochen</t>
         </is>
       </c>
       <c r="O723" s="15" t="inlineStr">
         <is>
-          <t>Überlast oder Blockade</t>
+          <t>Person oder Objekt im Schutzbereich</t>
         </is>
       </c>
       <c r="P723" s="22" t="inlineStr">
@@ -55203,12 +55216,12 @@
       </c>
       <c r="Q723" s="22" t="inlineStr">
         <is>
-          <t>Mechanik und Motor prüfen</t>
+          <t>Schutzbereich freimachen, Start drücken</t>
         </is>
       </c>
       <c r="R723" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0011 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0011 Störung Antriebsmotor Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0002 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0002 Lichtgitter ausgelöst. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55220,7 +55233,7 @@
       </c>
       <c r="B724" s="8" t="inlineStr">
         <is>
-          <t>0012</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="C724" s="3" t="inlineStr">
@@ -55253,7 +55266,7 @@
       </c>
       <c r="K724" s="15" t="inlineStr">
         <is>
-          <t>MAE0012 Störung Antriebsmotor Aufwicklung</t>
+          <t>MAE0003 Laserschutzgehäuse offen</t>
         </is>
       </c>
       <c r="L724" s="29" t="n"/>
@@ -55264,12 +55277,12 @@
       </c>
       <c r="N724" s="15" t="inlineStr">
         <is>
-          <t>Aufwicklungsmotor meldet Störung</t>
+          <t>Laserschutzgehäuse offen</t>
         </is>
       </c>
       <c r="O724" s="15" t="inlineStr">
         <is>
-          <t>Überlast oder Blockade</t>
+          <t>Schutzschalter geöffnet</t>
         </is>
       </c>
       <c r="P724" s="22" t="inlineStr">
@@ -55279,12 +55292,12 @@
       </c>
       <c r="Q724" s="22" t="inlineStr">
         <is>
-          <t>Mechanik und Motor prüfen</t>
+          <t>Sensorposition prüfen</t>
         </is>
       </c>
       <c r="R724" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0012 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0012 Störung Antriebsmotor Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0003 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0003 Laserschutzgehäuse offen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55296,13 +55309,11 @@
       </c>
       <c r="B725" s="8" t="inlineStr">
         <is>
-          <t>0013</t>
-        </is>
-      </c>
-      <c r="C725" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D725" s="11" t="n">
         <v>1</v>
@@ -55329,7 +55340,7 @@
       </c>
       <c r="K725" s="15" t="inlineStr">
         <is>
-          <t>MAE0013 Störung Kommunikation mit Mikrotom</t>
+          <t>MAE0004 Störung Portalachsenmotor X</t>
         </is>
       </c>
       <c r="L725" s="29" t="n"/>
@@ -55340,27 +55351,27 @@
       </c>
       <c r="N725" s="15" t="inlineStr">
         <is>
-          <t>Kommunikation Mikrotom gestört</t>
+          <t>Störung Motor X-Achse</t>
         </is>
       </c>
       <c r="O725" s="15" t="inlineStr">
         <is>
-          <t>Netzwerkfehler</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P725" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q725" s="22" t="inlineStr">
         <is>
-          <t>Verbindung prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R725" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0013 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0013 Störung Kommunikation mit Mikrotom. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0004 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0004 Störung Portalachsenmotor X. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55372,13 +55383,11 @@
       </c>
       <c r="B726" s="8" t="inlineStr">
         <is>
-          <t>0014</t>
-        </is>
-      </c>
-      <c r="C726" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="C726" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D726" s="11" t="n">
         <v>1</v>
@@ -55405,7 +55414,7 @@
       </c>
       <c r="K726" s="15" t="inlineStr">
         <is>
-          <t>MAE0014 Störung Kommunikation mit TTO</t>
+          <t>MAE0005 Störung Portalachsenmotor Z</t>
         </is>
       </c>
       <c r="L726" s="29" t="n"/>
@@ -55416,27 +55425,27 @@
       </c>
       <c r="N726" s="15" t="inlineStr">
         <is>
-          <t>Kommunikation mit TTO gestört</t>
+          <t>Störung Motor Z-Achse</t>
         </is>
       </c>
       <c r="O726" s="15" t="inlineStr">
         <is>
-          <t>Netzwerkfehler</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P726" s="22" t="inlineStr">
         <is>
-          <t>Druck nicht möglich</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q726" s="22" t="inlineStr">
         <is>
-          <t>TTO prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R726" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0014 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0014 Störung Kommunikation mit TTO. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0005 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0005 Störung Portalachsenmotor Z. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55448,13 +55457,11 @@
       </c>
       <c r="B727" s="8" t="inlineStr">
         <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="C727" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D727" s="11" t="n">
         <v>1</v>
@@ -55481,7 +55488,7 @@
       </c>
       <c r="K727" s="15" t="inlineStr">
         <is>
-          <t>MAE0015 Störung Kommunikation mit LASER</t>
+          <t>MAE0006 Störung Positionsantrieb Etiketten Erfassungssensor</t>
         </is>
       </c>
       <c r="L727" s="29" t="n"/>
@@ -55492,27 +55499,27 @@
       </c>
       <c r="N727" s="15" t="inlineStr">
         <is>
-          <t>Kommunikation mit Laser gestört</t>
+          <t>Positionsantrieb Erfassungssensor gestört</t>
         </is>
       </c>
       <c r="O727" s="15" t="inlineStr">
         <is>
-          <t>Netzwerkfehler</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P727" s="22" t="inlineStr">
         <is>
-          <t>Laserbetrieb gestoppt</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q727" s="22" t="inlineStr">
         <is>
-          <t>Laser prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R727" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0015 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0015 Störung Kommunikation mit LASER. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0006 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0006 Störung Positionsantrieb Etiketten Erfassungssensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55524,13 +55531,11 @@
       </c>
       <c r="B728" s="8" t="inlineStr">
         <is>
-          <t>0016</t>
-        </is>
-      </c>
-      <c r="C728" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0007</t>
+        </is>
+      </c>
+      <c r="C728" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D728" s="11" t="n">
         <v>1</v>
@@ -55557,7 +55562,7 @@
       </c>
       <c r="K728" s="15" t="inlineStr">
         <is>
-          <t>MAE0016 Störung Kommunikation mit Abwicklung</t>
+          <t>MAE0007 Störung Positionsantrieb Etiketten Entnahmesensor</t>
         </is>
       </c>
       <c r="L728" s="29" t="n"/>
@@ -55568,27 +55573,27 @@
       </c>
       <c r="N728" s="15" t="inlineStr">
         <is>
-          <t>Kommunikation mit Abwicklung gestört</t>
+          <t>Positionsantrieb Entnahmesensor gestört</t>
         </is>
       </c>
       <c r="O728" s="15" t="inlineStr">
         <is>
-          <t>Netzwerkfehler</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P728" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q728" s="22" t="inlineStr">
         <is>
-          <t>Verbindung prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R728" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0016 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0016 Störung Kommunikation mit Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0007 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0007 Störung Positionsantrieb Etiketten Entnahmesensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55600,13 +55605,11 @@
       </c>
       <c r="B729" s="8" t="inlineStr">
         <is>
-          <t>0017</t>
-        </is>
-      </c>
-      <c r="C729" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="C729" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D729" s="11" t="n">
         <v>1</v>
@@ -55633,7 +55636,7 @@
       </c>
       <c r="K729" s="15" t="inlineStr">
         <is>
-          <t>MAE0017 Störung Kommunikation mit Aufwicklung</t>
+          <t>MAE0008 Störung Positionsantrieb Etikettenführung Einlauf</t>
         </is>
       </c>
       <c r="L729" s="29" t="n"/>
@@ -55644,27 +55647,27 @@
       </c>
       <c r="N729" s="15" t="inlineStr">
         <is>
-          <t>Kommunikation mit Aufwicklung gestört</t>
+          <t>Etikettenführung Einlauf gestört</t>
         </is>
       </c>
       <c r="O729" s="15" t="inlineStr">
         <is>
-          <t>Netzwerkfehler</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P729" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q729" s="22" t="inlineStr">
         <is>
-          <t>Verbindung prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R729" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0017 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0017 Störung Kommunikation mit Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0008 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0008 Störung Positionsantrieb Etikettenführung Einlauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55676,13 +55679,11 @@
       </c>
       <c r="B730" s="8" t="inlineStr">
         <is>
-          <t>0018</t>
-        </is>
-      </c>
-      <c r="C730" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0009</t>
+        </is>
+      </c>
+      <c r="C730" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D730" s="11" t="n">
         <v>1</v>
@@ -55709,7 +55710,7 @@
       </c>
       <c r="K730" s="15" t="inlineStr">
         <is>
-          <t>MAE0018 Störung Modbus-RTU</t>
+          <t>MAE0009 Störung Positionsantrieb Etikettenführung Auslauf</t>
         </is>
       </c>
       <c r="L730" s="29" t="n"/>
@@ -55720,27 +55721,27 @@
       </c>
       <c r="N730" s="15" t="inlineStr">
         <is>
-          <t>Modbus-RTU Fehler</t>
+          <t>Etikettenführung Auslauf gestört</t>
         </is>
       </c>
       <c r="O730" s="15" t="inlineStr">
         <is>
-          <t>Busunterbruch</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P730" s="22" t="inlineStr">
         <is>
-          <t>Mehrere Komponenten ohne Funktion</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q730" s="22" t="inlineStr">
         <is>
-          <t>Verbindung prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R730" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0018 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0018 Störung Modbus-RTU. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0009 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0009 Störung Positionsantrieb Etikettenführung Auslauf. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55752,13 +55753,11 @@
       </c>
       <c r="B731" s="8" t="inlineStr">
         <is>
-          <t>0019</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D731" s="11" t="n">
         <v>1</v>
@@ -55785,7 +55784,7 @@
       </c>
       <c r="K731" s="15" t="inlineStr">
         <is>
-          <t>MAE0019 Störung Encoder Abwicklung</t>
+          <t>MAE0010 Störung Positionsantrieb Material Kontrollkamera</t>
         </is>
       </c>
       <c r="L731" s="29" t="n"/>
@@ -55796,27 +55795,27 @@
       </c>
       <c r="N731" s="15" t="inlineStr">
         <is>
-          <t>Encoder Abwicklung fehlerhaft</t>
+          <t>Materialkontrollkamera Positionsantrieb meldet Störung</t>
         </is>
       </c>
       <c r="O731" s="15" t="inlineStr">
         <is>
-          <t>Signalverlust oder Blockade</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P731" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Positionierung nicht möglich</t>
         </is>
       </c>
       <c r="Q731" s="22" t="inlineStr">
         <is>
-          <t>Encoder prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R731" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0019 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0019 Störung Encoder Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0010 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0010 Störung Positionsantrieb Material Kontrollkamera. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55828,7 +55827,7 @@
       </c>
       <c r="B732" s="8" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="C732" s="3" t="inlineStr">
@@ -55861,7 +55860,7 @@
       </c>
       <c r="K732" s="15" t="inlineStr">
         <is>
-          <t>MAE0020 Störung Encoder Aufwicklung</t>
+          <t>MAE0011 Störung Antriebsmotor Abwicklung</t>
         </is>
       </c>
       <c r="L732" s="29" t="n"/>
@@ -55872,12 +55871,12 @@
       </c>
       <c r="N732" s="15" t="inlineStr">
         <is>
-          <t>Encoder Aufwicklung fehlerhaft</t>
+          <t>Abwicklungsmotor meldet Störung</t>
         </is>
       </c>
       <c r="O732" s="15" t="inlineStr">
         <is>
-          <t>Signalverlust oder Blockade</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P732" s="22" t="inlineStr">
@@ -55887,12 +55886,12 @@
       </c>
       <c r="Q732" s="22" t="inlineStr">
         <is>
-          <t>Encoder prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R732" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0020 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0020 Störung Encoder Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0011 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0011 Störung Antriebsmotor Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55904,7 +55903,7 @@
       </c>
       <c r="B733" s="8" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>0012</t>
         </is>
       </c>
       <c r="C733" s="3" t="inlineStr">
@@ -55937,7 +55936,7 @@
       </c>
       <c r="K733" s="15" t="inlineStr">
         <is>
-          <t>MAE0021 Störung Etiketten Erfassungs-Sensor</t>
+          <t>MAE0012 Störung Antriebsmotor Aufwicklung</t>
         </is>
       </c>
       <c r="L733" s="29" t="n"/>
@@ -55948,27 +55947,27 @@
       </c>
       <c r="N733" s="15" t="inlineStr">
         <is>
-          <t>Etiketten Erfassungs-Sensor gestört</t>
+          <t>Aufwicklungsmotor meldet Störung</t>
         </is>
       </c>
       <c r="O733" s="15" t="inlineStr">
         <is>
-          <t>Verschmutzt oder falsch positioniert</t>
+          <t>Überlast oder Blockade</t>
         </is>
       </c>
       <c r="P733" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q733" s="22" t="inlineStr">
         <is>
-          <t>Sensor reinigen und Positio in Format prüfen</t>
+          <t>Mechanik und Motor prüfen</t>
         </is>
       </c>
       <c r="R733" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0021 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0021 Störung Etiketten Erfassungs-Sensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0012 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0012 Störung Antriebsmotor Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -55980,7 +55979,7 @@
       </c>
       <c r="B734" s="8" t="inlineStr">
         <is>
-          <t>0022</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="C734" s="3" t="inlineStr">
@@ -56013,7 +56012,7 @@
       </c>
       <c r="K734" s="15" t="inlineStr">
         <is>
-          <t>MAE0022 Störung Etiketten Kontroll-Sensor</t>
+          <t>MAE0013 Störung Kommunikation mit Mikrotom</t>
         </is>
       </c>
       <c r="L734" s="29" t="n"/>
@@ -56024,12 +56023,12 @@
       </c>
       <c r="N734" s="15" t="inlineStr">
         <is>
-          <t>Etiketten Kontrollsensor gestört</t>
+          <t>Kommunikation Mikrotom gestört</t>
         </is>
       </c>
       <c r="O734" s="15" t="inlineStr">
         <is>
-          <t>Verschmutzt oder falsch positioniert</t>
+          <t>Netzwerkfehler</t>
         </is>
       </c>
       <c r="P734" s="22" t="inlineStr">
@@ -56039,12 +56038,12 @@
       </c>
       <c r="Q734" s="22" t="inlineStr">
         <is>
-          <t>Sensor reinigen und Positio in Format prüfen</t>
+          <t>Verbindung prüfen</t>
         </is>
       </c>
       <c r="R734" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0022 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0022 Störung Etiketten Kontroll-Sensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0013 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0013 Störung Kommunikation mit Mikrotom. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -56056,7 +56055,7 @@
       </c>
       <c r="B735" s="8" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0014</t>
         </is>
       </c>
       <c r="C735" s="3" t="inlineStr">
@@ -56089,7 +56088,7 @@
       </c>
       <c r="K735" s="15" t="inlineStr">
         <is>
-          <t>MAE0023 Inkonsistente Bewegung zwischen Auf- und Abwichlung</t>
+          <t>MAE0014 Störung Kommunikation mit TTO</t>
         </is>
       </c>
       <c r="L735" s="29" t="n"/>
@@ -56100,28 +56099,27 @@
       </c>
       <c r="N735" s="15" t="inlineStr">
         <is>
-          <t>Inkonsistente Wickelbewegung</t>
+          <t>Kommunikation mit TTO gestört</t>
         </is>
       </c>
       <c r="O735" s="15" t="inlineStr">
         <is>
-          <t>Encoderabweichung (Schlupf zwischen Ab und 
-Aufwicklung)</t>
+          <t>Netzwerkfehler</t>
         </is>
       </c>
       <c r="P735" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Druck nicht möglich</t>
         </is>
       </c>
       <c r="Q735" s="22" t="inlineStr">
         <is>
-          <t>Rollen Reinigen, Format prüfen</t>
+          <t>TTO prüfen</t>
         </is>
       </c>
       <c r="R735" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0023 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0023 Inkonsistente Bewegung zwischen Auf- und Abwichlung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0014 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0014 Störung Kommunikation mit TTO. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -56133,7 +56131,7 @@
       </c>
       <c r="B736" s="8" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="C736" s="3" t="inlineStr">
@@ -56166,7 +56164,7 @@
       </c>
       <c r="K736" s="15" t="inlineStr">
         <is>
-          <t>MAE0024 Etikettenbandriss</t>
+          <t>MAE0015 Störung Kommunikation mit LASER</t>
         </is>
       </c>
       <c r="L736" s="29" t="n"/>
@@ -56177,27 +56175,27 @@
       </c>
       <c r="N736" s="15" t="inlineStr">
         <is>
-          <t>Etikettenband gerissen</t>
+          <t>Kommunikation mit Laser gestört</t>
         </is>
       </c>
       <c r="O736" s="15" t="inlineStr">
         <is>
-          <t>Zu hohe Spannung</t>
+          <t>Netzwerkfehler</t>
         </is>
       </c>
       <c r="P736" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Laserbetrieb gestoppt</t>
         </is>
       </c>
       <c r="Q736" s="22" t="inlineStr">
         <is>
-          <t>Band neu einfädeln</t>
+          <t>Laser prüfen</t>
         </is>
       </c>
       <c r="R736" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0024 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0024 Etikettenbandriss. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0015 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0015 Störung Kommunikation mit LASER. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -56209,7 +56207,7 @@
       </c>
       <c r="B737" s="8" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>0016</t>
         </is>
       </c>
       <c r="C737" s="3" t="inlineStr">
@@ -56242,7 +56240,7 @@
       </c>
       <c r="K737" s="15" t="inlineStr">
         <is>
-          <t>MAE0025 Störung Etikettenerfassung (Label zu kurz)</t>
+          <t>MAE0016 Störung Kommunikation mit Abwicklung</t>
         </is>
       </c>
       <c r="L737" s="29" t="n"/>
@@ -56253,27 +56251,27 @@
       </c>
       <c r="N737" s="15" t="inlineStr">
         <is>
-          <t>Label zu kurz</t>
+          <t>Kommunikation mit Abwicklung gestört</t>
         </is>
       </c>
       <c r="O737" s="15" t="inlineStr">
         <is>
-          <t>Sensor falsch eingestellt</t>
+          <t>Netzwerkfehler</t>
         </is>
       </c>
       <c r="P737" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q737" s="22" t="inlineStr">
         <is>
-          <t>Parameter prüfen, Sensor neu einmessen</t>
+          <t>Verbindung prüfen</t>
         </is>
       </c>
       <c r="R737" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0025 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0025 Störung Etikettenerfassung (Label zu kurz). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0016 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0016 Störung Kommunikation mit Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -56285,7 +56283,7 @@
       </c>
       <c r="B738" s="8" t="inlineStr">
         <is>
-          <t>0026</t>
+          <t>0017</t>
         </is>
       </c>
       <c r="C738" s="3" t="inlineStr">
@@ -56318,7 +56316,7 @@
       </c>
       <c r="K738" s="15" t="inlineStr">
         <is>
-          <t>MAE0026 Störung Etikettenerfassung (Label zu lang)</t>
+          <t>MAE0017 Störung Kommunikation mit Aufwicklung</t>
         </is>
       </c>
       <c r="L738" s="29" t="n"/>
@@ -56329,42 +56327,42 @@
       </c>
       <c r="N738" s="15" t="inlineStr">
         <is>
-          <t>Label zu lang</t>
+          <t>Kommunikation mit Aufwicklung gestört</t>
         </is>
       </c>
       <c r="O738" s="15" t="inlineStr">
         <is>
-          <t>Sensor falsch eingestellt</t>
+          <t>Netzwerkfehler</t>
         </is>
       </c>
       <c r="P738" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q738" s="22" t="inlineStr">
         <is>
-          <t>Parameter prüfen, Sensor neu einmessen</t>
+          <t>Verbindung prüfen</t>
         </is>
       </c>
       <c r="R738" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0026 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0026 Störung Etikettenerfassung (Label zu lang). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0017 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0017 Störung Kommunikation mit Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="739" ht="30" customHeight="1">
-      <c r="A739" s="10" t="inlineStr">
+      <c r="A739" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B739" s="8" t="inlineStr">
         <is>
-          <t>0027</t>
-        </is>
-      </c>
-      <c r="C739" s="43" t="inlineStr">
+          <t>0018</t>
+        </is>
+      </c>
+      <c r="C739" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56394,54 +56392,53 @@
       </c>
       <c r="K739" s="15" t="inlineStr">
         <is>
-          <t>MAE0027 Störung Etikettenerfassung (Sensor prellt)</t>
-        </is>
-      </c>
-      <c r="L739" s="28" t="n"/>
-      <c r="M739" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N739" s="22" t="inlineStr">
-        <is>
-          <t>Etikettenerfassungs-Sensor prellt</t>
-        </is>
-      </c>
-      <c r="O739" s="22" t="inlineStr">
-        <is>
-          <t>Sensor falsch eingestellt</t>
+          <t>MAE0018 Störung Modbus-RTU</t>
+        </is>
+      </c>
+      <c r="L739" s="29" t="n"/>
+      <c r="M739" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N739" s="15" t="inlineStr">
+        <is>
+          <t>Modbus-RTU Fehler</t>
+        </is>
+      </c>
+      <c r="O739" s="15" t="inlineStr">
+        <is>
+          <t>Busunterbruch</t>
         </is>
       </c>
       <c r="P739" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Mehrere Komponenten ohne Funktion</t>
         </is>
       </c>
       <c r="Q739" s="22" t="inlineStr">
         <is>
-          <t>Sensor reinigen, neu einstellen, 
-Formatparameter prüfen</t>
+          <t>Verbindung prüfen</t>
         </is>
       </c>
       <c r="R739" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0027 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0027 Störung Etikettenerfassung (Sensor prellt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0018 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0018 Störung Modbus-RTU. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="740" ht="30" customHeight="1">
-      <c r="A740" s="10" t="inlineStr">
+      <c r="A740" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B740" s="8" t="inlineStr">
         <is>
-          <t>0028</t>
-        </is>
-      </c>
-      <c r="C740" s="43" t="inlineStr">
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="C740" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56461,7 +56458,7 @@
       </c>
       <c r="I740" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J740" s="15" t="inlineStr">
@@ -56471,53 +56468,53 @@
       </c>
       <c r="K740" s="15" t="inlineStr">
         <is>
-          <t>MAE0028 Störung Abwicklung (Tänzerarm blockiert)</t>
-        </is>
-      </c>
-      <c r="L740" s="28" t="n"/>
-      <c r="M740" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N740" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Abwicklung blockiert</t>
-        </is>
-      </c>
-      <c r="O740" s="22" t="inlineStr">
-        <is>
-          <t>Mechanische Blockade</t>
+          <t>MAE0019 Störung Encoder Abwicklung</t>
+        </is>
+      </c>
+      <c r="L740" s="29" t="n"/>
+      <c r="M740" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N740" s="15" t="inlineStr">
+        <is>
+          <t>Encoder Abwicklung fehlerhaft</t>
+        </is>
+      </c>
+      <c r="O740" s="15" t="inlineStr">
+        <is>
+          <t>Signalverlust oder Blockade</t>
         </is>
       </c>
       <c r="P740" s="22" t="inlineStr">
         <is>
-          <t>Bandregelung gestört</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q740" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Encoder prüfen</t>
         </is>
       </c>
       <c r="R740" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0028 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0028 Störung Abwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0019 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0019 Störung Encoder Abwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="741" ht="75" customHeight="1">
-      <c r="A741" s="10" t="inlineStr">
+      <c r="A741" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B741" s="8" t="inlineStr">
         <is>
-          <t>0029</t>
-        </is>
-      </c>
-      <c r="C741" s="43" t="inlineStr">
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56537,7 +56534,7 @@
       </c>
       <c r="I741" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J741" s="15" t="inlineStr">
@@ -56547,53 +56544,53 @@
       </c>
       <c r="K741" s="15" t="inlineStr">
         <is>
-          <t>MAE0029 Störung Abwicklung (Tänzeram zu hoch)</t>
-        </is>
-      </c>
-      <c r="L741" s="28" t="n"/>
-      <c r="M741" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N741" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Abwicklung zu hoch</t>
-        </is>
-      </c>
-      <c r="O741" s="22" t="inlineStr">
-        <is>
-          <t>Spannung zu gering</t>
+          <t>MAE0020 Störung Encoder Aufwicklung</t>
+        </is>
+      </c>
+      <c r="L741" s="29" t="n"/>
+      <c r="M741" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N741" s="15" t="inlineStr">
+        <is>
+          <t>Encoder Aufwicklung fehlerhaft</t>
+        </is>
+      </c>
+      <c r="O741" s="15" t="inlineStr">
+        <is>
+          <t>Signalverlust oder Blockade</t>
         </is>
       </c>
       <c r="P741" s="22" t="inlineStr">
         <is>
-          <t>Bandrissgefahr</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q741" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Encoder prüfen</t>
         </is>
       </c>
       <c r="R741" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0029 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0029 Störung Abwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0020 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0020 Störung Encoder Aufwicklung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="742" ht="30" customHeight="1">
-      <c r="A742" s="10" t="inlineStr">
+      <c r="A742" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B742" s="8" t="inlineStr">
         <is>
-          <t>0030</t>
-        </is>
-      </c>
-      <c r="C742" s="43" t="inlineStr">
+          <t>0021</t>
+        </is>
+      </c>
+      <c r="C742" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56613,7 +56610,7 @@
       </c>
       <c r="I742" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J742" s="15" t="inlineStr">
@@ -56623,66 +56620,66 @@
       </c>
       <c r="K742" s="15" t="inlineStr">
         <is>
-          <t>MAE0030 Störung Abwicklung (Tänzeram zu tief)</t>
-        </is>
-      </c>
-      <c r="L742" s="28" t="n"/>
-      <c r="M742" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N742" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Abwicklung zu tief</t>
-        </is>
-      </c>
-      <c r="O742" s="22" t="inlineStr">
-        <is>
-          <t>Spannung zu hoch</t>
+          <t>MAE0021 Störung Etiketten Erfassungs-Sensor</t>
+        </is>
+      </c>
+      <c r="L742" s="29" t="n"/>
+      <c r="M742" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N742" s="15" t="inlineStr">
+        <is>
+          <t>Etiketten Erfassungs-Sensor gestört</t>
+        </is>
+      </c>
+      <c r="O742" s="15" t="inlineStr">
+        <is>
+          <t>Verschmutzt oder falsch positioniert</t>
         </is>
       </c>
       <c r="P742" s="22" t="inlineStr">
         <is>
-          <t>Bandspannun nicht stuerbar</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q742" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Sensor reinigen und Positio in Format prüfen</t>
         </is>
       </c>
       <c r="R742" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0030 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0030 Störung Abwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0021 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0021 Störung Etiketten Erfassungs-Sensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="743" ht="30" customHeight="1">
-      <c r="A743" s="10" t="inlineStr">
+      <c r="A743" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B743" s="8" t="inlineStr">
         <is>
-          <t>0031</t>
-        </is>
-      </c>
-      <c r="C743" s="46" t="n">
+          <t>0022</t>
+        </is>
+      </c>
+      <c r="C743" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D743" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E743" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D743" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E743" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F743" s="29" t="n"/>
-      <c r="G743" s="29" t="n"/>
-      <c r="H743" s="29" t="inlineStr">
+      <c r="F743" s="15" t="n"/>
+      <c r="G743" s="15" t="n"/>
+      <c r="H743" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -56692,63 +56689,60 @@
           <t>W</t>
         </is>
       </c>
-      <c r="J743" s="29" t="inlineStr">
+      <c r="J743" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K743" s="29" t="inlineStr">
-        <is>
-          <t>MAE0031 Störung Abwicklung (Falscher Kernadapter eingelegt)</t>
-        </is>
-      </c>
-      <c r="L743" s="28" t="n"/>
-      <c r="M743" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N743" s="28" t="inlineStr">
-        <is>
-          <t>Falschen Kernadapter auf Abwicklung erkannt</t>
-        </is>
-      </c>
-      <c r="O743" s="28" t="inlineStr">
-        <is>
-          <t>Falscher Adapter eingesetzt</t>
-        </is>
-      </c>
-      <c r="P743" s="28" t="inlineStr">
-        <is>
-          <t>Wickeln nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q743" s="28" t="inlineStr">
-        <is>
-          <t>Adapter tauschen</t>
-        </is>
-      </c>
-      <c r="R743" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0031 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0031 Störung Abwicklung (Falscher Kernadapter eingelegt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S743" s="4" t="n"/>
-      <c r="T743" s="4" t="n"/>
-      <c r="U743" s="4" t="n"/>
+      <c r="K743" s="15" t="inlineStr">
+        <is>
+          <t>MAE0022 Störung Etiketten Kontroll-Sensor</t>
+        </is>
+      </c>
+      <c r="L743" s="29" t="n"/>
+      <c r="M743" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N743" s="15" t="inlineStr">
+        <is>
+          <t>Etiketten Kontrollsensor gestört</t>
+        </is>
+      </c>
+      <c r="O743" s="15" t="inlineStr">
+        <is>
+          <t>Verschmutzt oder falsch positioniert</t>
+        </is>
+      </c>
+      <c r="P743" s="22" t="inlineStr">
+        <is>
+          <t>Produktionsstopp</t>
+        </is>
+      </c>
+      <c r="Q743" s="22" t="inlineStr">
+        <is>
+          <t>Sensor reinigen und Positio in Format prüfen</t>
+        </is>
+      </c>
+      <c r="R743" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0022 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0022 Störung Etiketten Kontroll-Sensor. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="744" ht="75" customHeight="1">
-      <c r="A744" s="10" t="inlineStr">
+      <c r="A744" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B744" s="8" t="inlineStr">
         <is>
-          <t>0032</t>
-        </is>
-      </c>
-      <c r="C744" s="43" t="inlineStr">
+          <t>0023</t>
+        </is>
+      </c>
+      <c r="C744" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56768,7 +56762,7 @@
       </c>
       <c r="I744" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J744" s="15" t="inlineStr">
@@ -56778,53 +56772,54 @@
       </c>
       <c r="K744" s="15" t="inlineStr">
         <is>
-          <t>MAE0032 Störung Aufwicklung (Tänzerarm blockiert)</t>
-        </is>
-      </c>
-      <c r="L744" s="28" t="n"/>
-      <c r="M744" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N744" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Aufwicklung blockiert</t>
-        </is>
-      </c>
-      <c r="O744" s="22" t="inlineStr">
-        <is>
-          <t>Mechanische Blockade</t>
+          <t>MAE0023 Inkonsistente Bewegung zwischen Auf- und Abwichlung</t>
+        </is>
+      </c>
+      <c r="L744" s="29" t="n"/>
+      <c r="M744" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N744" s="15" t="inlineStr">
+        <is>
+          <t>Inkonsistente Wickelbewegung</t>
+        </is>
+      </c>
+      <c r="O744" s="15" t="inlineStr">
+        <is>
+          <t>Encoderabweichung (Schlupf zwischen Ab und 
+Aufwicklung)</t>
         </is>
       </c>
       <c r="P744" s="22" t="inlineStr">
         <is>
-          <t>Bandregelung gestört</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q744" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Rollen Reinigen, Format prüfen</t>
         </is>
       </c>
       <c r="R744" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0032 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0032 Störung Aufwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0023 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0023 Inkonsistente Bewegung zwischen Auf- und Abwichlung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="745" ht="30" customHeight="1">
-      <c r="A745" s="10" t="inlineStr">
+      <c r="A745" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B745" s="8" t="inlineStr">
         <is>
-          <t>0033</t>
-        </is>
-      </c>
-      <c r="C745" s="43" t="inlineStr">
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C745" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56844,7 +56839,7 @@
       </c>
       <c r="I745" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J745" s="15" t="inlineStr">
@@ -56854,53 +56849,53 @@
       </c>
       <c r="K745" s="15" t="inlineStr">
         <is>
-          <t>MAE0033 Störung Aufwicklung (Tänzeram zu hoch)</t>
-        </is>
-      </c>
-      <c r="L745" s="28" t="n"/>
-      <c r="M745" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N745" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Aufwicklung zu hoch</t>
-        </is>
-      </c>
-      <c r="O745" s="22" t="inlineStr">
-        <is>
-          <t>Spannung zu gering</t>
+          <t>MAE0024 Etikettenbandriss</t>
+        </is>
+      </c>
+      <c r="L745" s="29" t="n"/>
+      <c r="M745" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N745" s="15" t="inlineStr">
+        <is>
+          <t>Etikettenband gerissen</t>
+        </is>
+      </c>
+      <c r="O745" s="15" t="inlineStr">
+        <is>
+          <t>Zu hohe Spannung</t>
         </is>
       </c>
       <c r="P745" s="22" t="inlineStr">
         <is>
-          <t>Bandrissgefahr</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q745" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Band neu einfädeln</t>
         </is>
       </c>
       <c r="R745" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0033 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0033 Störung Aufwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0024 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0024 Etikettenbandriss. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="746" ht="30" customHeight="1">
-      <c r="A746" s="10" t="inlineStr">
+      <c r="A746" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B746" s="8" t="inlineStr">
         <is>
-          <t>0034</t>
-        </is>
-      </c>
-      <c r="C746" s="43" t="inlineStr">
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="C746" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56920,7 +56915,7 @@
       </c>
       <c r="I746" s="29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J746" s="15" t="inlineStr">
@@ -56930,66 +56925,66 @@
       </c>
       <c r="K746" s="15" t="inlineStr">
         <is>
-          <t>MAE0034 Störung Aufwicklung (Tänzeram zu tief)</t>
-        </is>
-      </c>
-      <c r="L746" s="28" t="n"/>
-      <c r="M746" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N746" s="22" t="inlineStr">
-        <is>
-          <t>Tänzerarm der Aufwicklung zu tief</t>
-        </is>
-      </c>
-      <c r="O746" s="22" t="inlineStr">
-        <is>
-          <t>Spannung zu hoch</t>
+          <t>MAE0025 Störung Etikettenerfassung (Label zu kurz)</t>
+        </is>
+      </c>
+      <c r="L746" s="29" t="n"/>
+      <c r="M746" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N746" s="15" t="inlineStr">
+        <is>
+          <t>Label zu kurz</t>
+        </is>
+      </c>
+      <c r="O746" s="15" t="inlineStr">
+        <is>
+          <t>Sensor falsch eingestellt</t>
         </is>
       </c>
       <c r="P746" s="22" t="inlineStr">
         <is>
-          <t>Bandspannun nicht stuerbar</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q746" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Parameter prüfen, Sensor neu einmessen</t>
         </is>
       </c>
       <c r="R746" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0034 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0034 Störung Aufwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0025 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0025 Störung Etikettenerfassung (Label zu kurz). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
     <row r="747" ht="30" customHeight="1">
-      <c r="A747" s="10" t="inlineStr">
+      <c r="A747" s="15" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
       <c r="B747" s="8" t="inlineStr">
         <is>
-          <t>0035</t>
-        </is>
-      </c>
-      <c r="C747" s="46" t="n">
+          <t>0026</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D747" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E747" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D747" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E747" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F747" s="29" t="n"/>
-      <c r="G747" s="29" t="n"/>
-      <c r="H747" s="29" t="inlineStr">
+      <c r="F747" s="15" t="n"/>
+      <c r="G747" s="15" t="n"/>
+      <c r="H747" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -56999,50 +56994,47 @@
           <t>W</t>
         </is>
       </c>
-      <c r="J747" s="29" t="inlineStr">
+      <c r="J747" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K747" s="29" t="inlineStr">
-        <is>
-          <t>MAE0035 Störung Aufwicklung (Falscher Kernadapter eingelegt)</t>
-        </is>
-      </c>
-      <c r="L747" s="28" t="n"/>
-      <c r="M747" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N747" s="28" t="inlineStr">
-        <is>
-          <t>Falschen Kernadapter auf Aufwicklung erkannt</t>
-        </is>
-      </c>
-      <c r="O747" s="28" t="inlineStr">
-        <is>
-          <t>Falscher Adapter eingesetzt</t>
-        </is>
-      </c>
-      <c r="P747" s="28" t="inlineStr">
-        <is>
-          <t>Wickeln nicht möglich</t>
-        </is>
-      </c>
-      <c r="Q747" s="28" t="inlineStr">
-        <is>
-          <t>Adapter tauschen</t>
-        </is>
-      </c>
-      <c r="R747" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0035 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0035 Störung Aufwicklung (Falscher Kernadapter eingelegt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
-      <c r="S747" s="4" t="n"/>
-      <c r="T747" s="4" t="n"/>
-      <c r="U747" s="4" t="n"/>
+      <c r="K747" s="15" t="inlineStr">
+        <is>
+          <t>MAE0026 Störung Etikettenerfassung (Label zu lang)</t>
+        </is>
+      </c>
+      <c r="L747" s="29" t="n"/>
+      <c r="M747" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N747" s="15" t="inlineStr">
+        <is>
+          <t>Label zu lang</t>
+        </is>
+      </c>
+      <c r="O747" s="15" t="inlineStr">
+        <is>
+          <t>Sensor falsch eingestellt</t>
+        </is>
+      </c>
+      <c r="P747" s="22" t="inlineStr">
+        <is>
+          <t>Produktionspause</t>
+        </is>
+      </c>
+      <c r="Q747" s="22" t="inlineStr">
+        <is>
+          <t>Parameter prüfen, Sensor neu einmessen</t>
+        </is>
+      </c>
+      <c r="R747" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0026 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0026 Störung Etikettenerfassung (Label zu lang). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="748" ht="90" customHeight="1">
       <c r="A748" s="10" t="inlineStr">
@@ -57052,7 +57044,7 @@
       </c>
       <c r="B748" s="8" t="inlineStr">
         <is>
-          <t>0036</t>
+          <t>0027</t>
         </is>
       </c>
       <c r="C748" s="43" t="inlineStr">
@@ -57085,7 +57077,7 @@
       </c>
       <c r="K748" s="15" t="inlineStr">
         <is>
-          <t>MAE0036 Wechsel zu Einrichtbetrieb fehlgeschlagen</t>
+          <t>MAE0027 Störung Etikettenerfassung (Sensor prellt)</t>
         </is>
       </c>
       <c r="L748" s="28" t="n"/>
@@ -57096,27 +57088,28 @@
       </c>
       <c r="N748" s="22" t="inlineStr">
         <is>
-          <t>Einrichtbetrieb nicht erreichbar</t>
+          <t>Etikettenerfassungs-Sensor prellt</t>
         </is>
       </c>
       <c r="O748" s="22" t="inlineStr">
         <is>
-          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
+          <t>Sensor falsch eingestellt</t>
         </is>
       </c>
       <c r="P748" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q748" s="22" t="inlineStr">
         <is>
-          <t>Auf Blockade prüfen</t>
+          <t>Sensor reinigen, neu einstellen, 
+Formatparameter prüfen</t>
         </is>
       </c>
       <c r="R748" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0036 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0036 Wechsel zu Einrichtbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0027 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0027 Störung Etikettenerfassung (Sensor prellt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57128,7 +57121,7 @@
       </c>
       <c r="B749" s="8" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>0028</t>
         </is>
       </c>
       <c r="C749" s="43" t="inlineStr">
@@ -57151,7 +57144,7 @@
       </c>
       <c r="I749" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J749" s="15" t="inlineStr">
@@ -57161,7 +57154,7 @@
       </c>
       <c r="K749" s="15" t="inlineStr">
         <is>
-          <t>MAE0037 Wechsel zu Produktionsbetrieb fehlgeschlagen</t>
+          <t>MAE0028 Störung Abwicklung (Tänzerarm blockiert)</t>
         </is>
       </c>
       <c r="L749" s="28" t="n"/>
@@ -57172,17 +57165,17 @@
       </c>
       <c r="N749" s="22" t="inlineStr">
         <is>
-          <t>Produktionsbetrieb nicht erreichbar</t>
+          <t>Tänzerarm der Abwicklung blockiert</t>
         </is>
       </c>
       <c r="O749" s="22" t="inlineStr">
         <is>
-          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
+          <t>Mechanische Blockade</t>
         </is>
       </c>
       <c r="P749" s="22" t="inlineStr">
         <is>
-          <t>Produktion startet nicht</t>
+          <t>Bandregelung gestört</t>
         </is>
       </c>
       <c r="Q749" s="22" t="inlineStr">
@@ -57192,7 +57185,7 @@
       </c>
       <c r="R749" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0037 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0037 Wechsel zu Produktionsbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0028 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0028 Störung Abwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57204,7 +57197,7 @@
       </c>
       <c r="B750" s="8" t="inlineStr">
         <is>
-          <t>0038</t>
+          <t>0029</t>
         </is>
       </c>
       <c r="C750" s="43" t="inlineStr">
@@ -57227,7 +57220,7 @@
       </c>
       <c r="I750" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J750" s="15" t="inlineStr">
@@ -57237,7 +57230,7 @@
       </c>
       <c r="K750" s="15" t="inlineStr">
         <is>
-          <t>MAE0038 Wechsel zu Pause Fehlgeschlagen</t>
+          <t>MAE0029 Störung Abwicklung (Tänzeram zu hoch)</t>
         </is>
       </c>
       <c r="L750" s="28" t="n"/>
@@ -57248,13 +57241,17 @@
       </c>
       <c r="N750" s="22" t="inlineStr">
         <is>
-          <t>Pause nicht erreichbar</t>
-        </is>
-      </c>
-      <c r="O750" s="22" t="n"/>
+          <t>Tänzerarm der Abwicklung zu hoch</t>
+        </is>
+      </c>
+      <c r="O750" s="22" t="inlineStr">
+        <is>
+          <t>Spannung zu gering</t>
+        </is>
+      </c>
       <c r="P750" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Bandrissgefahr</t>
         </is>
       </c>
       <c r="Q750" s="22" t="inlineStr">
@@ -57264,7 +57261,7 @@
       </c>
       <c r="R750" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0038 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0038 Wechsel zu Pause Fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0029 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0029 Störung Abwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57276,7 +57273,7 @@
       </c>
       <c r="B751" s="8" t="inlineStr">
         <is>
-          <t>0039</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="C751" s="43" t="inlineStr">
@@ -57299,7 +57296,7 @@
       </c>
       <c r="I751" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J751" s="15" t="inlineStr">
@@ -57309,7 +57306,7 @@
       </c>
       <c r="K751" s="15" t="inlineStr">
         <is>
-          <t>MAE0039 Wechsel zu Produktionsstop fehlgeschlagen</t>
+          <t>MAE0030 Störung Abwicklung (Tänzeram zu tief)</t>
         </is>
       </c>
       <c r="L751" s="28" t="n"/>
@@ -57320,13 +57317,17 @@
       </c>
       <c r="N751" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp nicht möglich</t>
-        </is>
-      </c>
-      <c r="O751" s="22" t="n"/>
+          <t>Tänzerarm der Abwicklung zu tief</t>
+        </is>
+      </c>
+      <c r="O751" s="22" t="inlineStr">
+        <is>
+          <t>Spannung zu hoch</t>
+        </is>
+      </c>
       <c r="P751" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Bandspannun nicht stuerbar</t>
         </is>
       </c>
       <c r="Q751" s="22" t="inlineStr">
@@ -57336,7 +57337,7 @@
       </c>
       <c r="R751" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0039 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0039 Wechsel zu Produktionsstop fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0030 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0030 Störung Abwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57348,23 +57349,23 @@
       </c>
       <c r="B752" s="8" t="inlineStr">
         <is>
-          <t>0040</t>
-        </is>
-      </c>
-      <c r="C752" s="43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D752" s="11" t="n">
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="C752" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D752" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E752" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F752" s="15" t="n"/>
-      <c r="G752" s="15" t="n"/>
-      <c r="H752" s="15" t="inlineStr">
+      <c r="E752" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F752" s="29" t="n"/>
+      <c r="G752" s="29" t="n"/>
+      <c r="H752" s="29" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -57374,43 +57375,50 @@
           <t>W</t>
         </is>
       </c>
-      <c r="J752" s="15" t="inlineStr">
+      <c r="J752" s="29" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K752" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MAE0040 Wechsel zu Rückspulbetrieb fehlgeschlagen </t>
+      <c r="K752" s="29" t="inlineStr">
+        <is>
+          <t>MAE0031 Störung Abwicklung (Falscher Kernadapter eingelegt)</t>
         </is>
       </c>
       <c r="L752" s="28" t="n"/>
-      <c r="M752" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N752" s="22" t="inlineStr">
-        <is>
-          <t>Rückspulbetrieb nicht möglich</t>
-        </is>
-      </c>
-      <c r="O752" s="22" t="n"/>
-      <c r="P752" s="22" t="inlineStr">
-        <is>
-          <t>Rückspulen blockiert</t>
-        </is>
-      </c>
-      <c r="Q752" s="22" t="inlineStr">
-        <is>
-          <t>Auf Blockade prüfen</t>
-        </is>
-      </c>
-      <c r="R752" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0040 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0040 Wechsel zu Rückspulbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M752" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N752" s="28" t="inlineStr">
+        <is>
+          <t>Falschen Kernadapter auf Abwicklung erkannt</t>
+        </is>
+      </c>
+      <c r="O752" s="28" t="inlineStr">
+        <is>
+          <t>Falscher Adapter eingesetzt</t>
+        </is>
+      </c>
+      <c r="P752" s="28" t="inlineStr">
+        <is>
+          <t>Wickeln nicht möglich</t>
+        </is>
+      </c>
+      <c r="Q752" s="28" t="inlineStr">
+        <is>
+          <t>Adapter tauschen</t>
+        </is>
+      </c>
+      <c r="R752" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0031 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0031 Störung Abwicklung (Falscher Kernadapter eingelegt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="S752" s="4" t="n"/>
+      <c r="T752" s="4" t="n"/>
+      <c r="U752" s="4" t="n"/>
     </row>
     <row r="753" ht="30" customHeight="1">
       <c r="A753" s="10" t="inlineStr">
@@ -57420,7 +57428,7 @@
       </c>
       <c r="B753" s="8" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C753" s="43" t="inlineStr">
@@ -57443,7 +57451,7 @@
       </c>
       <c r="I753" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J753" s="15" t="inlineStr">
@@ -57453,7 +57461,7 @@
       </c>
       <c r="K753" s="15" t="inlineStr">
         <is>
-          <t>MAE0041 Wechsel zu Etikettenentnahme</t>
+          <t>MAE0032 Störung Aufwicklung (Tänzerarm blockiert)</t>
         </is>
       </c>
       <c r="L753" s="28" t="n"/>
@@ -57464,13 +57472,17 @@
       </c>
       <c r="N753" s="22" t="inlineStr">
         <is>
-          <t>Wechsel zu Etikettenentnahme nicht möglich</t>
-        </is>
-      </c>
-      <c r="O753" s="22" t="n"/>
+          <t>Tänzerarm der Aufwicklung blockiert</t>
+        </is>
+      </c>
+      <c r="O753" s="22" t="inlineStr">
+        <is>
+          <t>Mechanische Blockade</t>
+        </is>
+      </c>
       <c r="P753" s="22" t="inlineStr">
         <is>
-          <t>Produktionspause</t>
+          <t>Bandregelung gestört</t>
         </is>
       </c>
       <c r="Q753" s="22" t="inlineStr">
@@ -57480,7 +57492,7 @@
       </c>
       <c r="R753" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0041 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0041 Wechsel zu Etikettenentnahme. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0032 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0032 Störung Aufwicklung (Tänzerarm blockiert). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57492,7 +57504,7 @@
       </c>
       <c r="B754" s="8" t="inlineStr">
         <is>
-          <t>0042</t>
+          <t>0033</t>
         </is>
       </c>
       <c r="C754" s="43" t="inlineStr">
@@ -57515,7 +57527,7 @@
       </c>
       <c r="I754" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J754" s="15" t="inlineStr">
@@ -57525,7 +57537,7 @@
       </c>
       <c r="K754" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAE0042 Wechsel zu Spleissen fehlgeschlagen </t>
+          <t>MAE0033 Störung Aufwicklung (Tänzeram zu hoch)</t>
         </is>
       </c>
       <c r="L754" s="28" t="n"/>
@@ -57536,13 +57548,17 @@
       </c>
       <c r="N754" s="22" t="inlineStr">
         <is>
-          <t>Spleissbetrieb nicht möglich</t>
-        </is>
-      </c>
-      <c r="O754" s="22" t="n"/>
+          <t>Tänzerarm der Aufwicklung zu hoch</t>
+        </is>
+      </c>
+      <c r="O754" s="22" t="inlineStr">
+        <is>
+          <t>Spannung zu gering</t>
+        </is>
+      </c>
       <c r="P754" s="22" t="inlineStr">
         <is>
-          <t>Spleissen blockiert</t>
+          <t>Bandrissgefahr</t>
         </is>
       </c>
       <c r="Q754" s="22" t="inlineStr">
@@ -57552,7 +57568,7 @@
       </c>
       <c r="R754" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0042 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0042 Wechsel zu Spleissen fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0033 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0033 Störung Aufwicklung (Tänzeram zu hoch). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57564,7 +57580,7 @@
       </c>
       <c r="B755" s="8" t="inlineStr">
         <is>
-          <t>0043</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C755" s="43" t="inlineStr">
@@ -57587,7 +57603,7 @@
       </c>
       <c r="I755" s="29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J755" s="15" t="inlineStr">
@@ -57597,7 +57613,7 @@
       </c>
       <c r="K755" s="15" t="inlineStr">
         <is>
-          <t>MAE0043 Wechsel zu Synchronisieren fehlgeschlagen</t>
+          <t>MAE0034 Störung Aufwicklung (Tänzeram zu tief)</t>
         </is>
       </c>
       <c r="L755" s="28" t="n"/>
@@ -57608,17 +57624,17 @@
       </c>
       <c r="N755" s="22" t="inlineStr">
         <is>
-          <t>Synchronisieren fehlgeschlagen</t>
+          <t>Tänzerarm der Aufwicklung zu tief</t>
         </is>
       </c>
       <c r="O755" s="22" t="inlineStr">
         <is>
-          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
+          <t>Spannung zu hoch</t>
         </is>
       </c>
       <c r="P755" s="22" t="inlineStr">
         <is>
-          <t>Produktionsstopp</t>
+          <t>Bandspannun nicht stuerbar</t>
         </is>
       </c>
       <c r="Q755" s="22" t="inlineStr">
@@ -57628,7 +57644,7 @@
       </c>
       <c r="R755" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0043 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0043 Wechsel zu Synchronisieren fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0034 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0034 Störung Aufwicklung (Tänzeram zu tief). Microtom soll diesen Wert nur lesen. Der ESP soll ihn aus der Raspi-/Microtom-Seite lesen bzw. gespiegelt bekommen, aber nicht fuehrend schreiben. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57640,23 +57656,23 @@
       </c>
       <c r="B756" s="8" t="inlineStr">
         <is>
-          <t>0044</t>
-        </is>
-      </c>
-      <c r="C756" s="43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D756" s="11" t="n">
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="C756" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D756" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E756" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F756" s="15" t="n"/>
-      <c r="G756" s="15" t="n"/>
-      <c r="H756" s="15" t="inlineStr">
+      <c r="E756" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F756" s="29" t="n"/>
+      <c r="G756" s="29" t="n"/>
+      <c r="H756" s="29" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -57666,43 +57682,50 @@
           <t>W</t>
         </is>
       </c>
-      <c r="J756" s="15" t="inlineStr">
+      <c r="J756" s="29" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K756" s="15" t="inlineStr">
-        <is>
-          <t>MAE0044 Wechsel zu Produktion abgeschlossen fehlgeschlagen</t>
+      <c r="K756" s="29" t="inlineStr">
+        <is>
+          <t>MAE0035 Störung Aufwicklung (Falscher Kernadapter eingelegt)</t>
         </is>
       </c>
       <c r="L756" s="28" t="n"/>
-      <c r="M756" s="22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N756" s="22" t="inlineStr">
-        <is>
-          <t>Produktion abgeschlossen fehlgeschlagen</t>
-        </is>
-      </c>
-      <c r="O756" s="22" t="n"/>
-      <c r="P756" s="22" t="inlineStr">
-        <is>
-          <t>Produktionspause</t>
-        </is>
-      </c>
-      <c r="Q756" s="22" t="inlineStr">
-        <is>
-          <t>Auf Blockade prüfen</t>
-        </is>
-      </c>
-      <c r="R756" s="22" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0044 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0044 Wechsel zu Produktion abgeschlossen fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
-        </is>
-      </c>
+      <c r="M756" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N756" s="28" t="inlineStr">
+        <is>
+          <t>Falschen Kernadapter auf Aufwicklung erkannt</t>
+        </is>
+      </c>
+      <c r="O756" s="28" t="inlineStr">
+        <is>
+          <t>Falscher Adapter eingesetzt</t>
+        </is>
+      </c>
+      <c r="P756" s="28" t="inlineStr">
+        <is>
+          <t>Wickeln nicht möglich</t>
+        </is>
+      </c>
+      <c r="Q756" s="28" t="inlineStr">
+        <is>
+          <t>Adapter tauschen</t>
+        </is>
+      </c>
+      <c r="R756" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0035 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0035 Störung Aufwicklung (Falscher Kernadapter eingelegt). Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+      <c r="S756" s="4" t="n"/>
+      <c r="T756" s="4" t="n"/>
+      <c r="U756" s="4" t="n"/>
     </row>
     <row r="757" ht="45" customHeight="1">
       <c r="A757" s="10" t="inlineStr">
@@ -57712,7 +57735,7 @@
       </c>
       <c r="B757" s="8" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0036</t>
         </is>
       </c>
       <c r="C757" s="43" t="inlineStr">
@@ -57745,7 +57768,7 @@
       </c>
       <c r="K757" s="15" t="inlineStr">
         <is>
-          <t>MAE0045 Störung während Rückspulung</t>
+          <t>MAE0036 Wechsel zu Einrichtbetrieb fehlgeschlagen</t>
         </is>
       </c>
       <c r="L757" s="28" t="n"/>
@@ -57756,27 +57779,27 @@
       </c>
       <c r="N757" s="22" t="inlineStr">
         <is>
-          <t>Fehler während Rückspulung</t>
+          <t>Einrichtbetrieb nicht erreichbar</t>
         </is>
       </c>
       <c r="O757" s="22" t="inlineStr">
         <is>
-          <t>Blockade oder Encoder-Fehler</t>
+          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
         </is>
       </c>
       <c r="P757" s="22" t="inlineStr">
         <is>
-          <t>Rückspulung abgebrochen</t>
+          <t>Produktionsstopp</t>
         </is>
       </c>
       <c r="Q757" s="22" t="inlineStr">
         <is>
-          <t>Encoder und Etikettenlauf prüfen</t>
+          <t>Auf Blockade prüfen</t>
         </is>
       </c>
       <c r="R757" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0045 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0045 Störung während Rückspulung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0036 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0036 Wechsel zu Einrichtbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57788,11 +57811,13 @@
       </c>
       <c r="B758" s="8" t="inlineStr">
         <is>
-          <t>0046</t>
-        </is>
-      </c>
-      <c r="C758" s="43" t="n">
-        <v>0</v>
+          <t>0037</t>
+        </is>
+      </c>
+      <c r="C758" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D758" s="11" t="n">
         <v>1</v>
@@ -57819,7 +57844,7 @@
       </c>
       <c r="K758" s="15" t="inlineStr">
         <is>
-          <t>MAE0045 Störung Motor Etiekttenantrieb</t>
+          <t>MAE0037 Wechsel zu Produktionsbetrieb fehlgeschlagen</t>
         </is>
       </c>
       <c r="L758" s="28" t="n"/>
@@ -57830,27 +57855,27 @@
       </c>
       <c r="N758" s="22" t="inlineStr">
         <is>
-          <t>Störung Motor Etiekttenantrieb</t>
+          <t>Produktionsbetrieb nicht erreichbar</t>
         </is>
       </c>
       <c r="O758" s="22" t="inlineStr">
         <is>
-          <t>Überlast oder Blockade</t>
+          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
         </is>
       </c>
       <c r="P758" s="22" t="inlineStr">
         <is>
-          <t>Etiektten-Antrieb nicht möglich</t>
+          <t>Produktion startet nicht</t>
         </is>
       </c>
       <c r="Q758" s="22" t="inlineStr">
         <is>
-          <t>Mechanik und Motor prüfen</t>
+          <t>Auf Blockade prüfen</t>
         </is>
       </c>
       <c r="R758" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0046 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0045 Störung Motor Etiekttenantrieb. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0037 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0037 Wechsel zu Produktionsbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57862,11 +57887,13 @@
       </c>
       <c r="B759" s="8" t="inlineStr">
         <is>
-          <t>0047</t>
-        </is>
-      </c>
-      <c r="C759" s="43" t="n">
-        <v>0</v>
+          <t>0038</t>
+        </is>
+      </c>
+      <c r="C759" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D759" s="11" t="n">
         <v>1</v>
@@ -57893,7 +57920,7 @@
       </c>
       <c r="K759" s="15" t="inlineStr">
         <is>
-          <t>MAE0047 Störung Positionsantrieb Schutzblech Laser</t>
+          <t>MAE0038 Wechsel zu Pause Fehlgeschlagen</t>
         </is>
       </c>
       <c r="L759" s="28" t="n"/>
@@ -57904,27 +57931,23 @@
       </c>
       <c r="N759" s="22" t="inlineStr">
         <is>
-          <t>Schutzblech-Laser Positionsantrieb meldet Störung</t>
-        </is>
-      </c>
-      <c r="O759" s="22" t="inlineStr">
-        <is>
-          <t>Überlast oder Blockade</t>
-        </is>
-      </c>
+          <t>Pause nicht erreichbar</t>
+        </is>
+      </c>
+      <c r="O759" s="22" t="n"/>
       <c r="P759" s="22" t="inlineStr">
         <is>
-          <t>Positionierung nicht möglich</t>
+          <t>Produktionspause</t>
         </is>
       </c>
       <c r="Q759" s="22" t="inlineStr">
         <is>
-          <t>Mechanik und Motor prüfen</t>
+          <t>Auf Blockade prüfen</t>
         </is>
       </c>
       <c r="R759" s="22" t="inlineStr">
         <is>
-          <t>KI: Ich verstehe MAE0047 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0047 Störung Positionsantrieb Schutzblech Laser. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+          <t>KI: Ich verstehe MAE0038 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0038 Wechsel zu Pause Fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
         </is>
       </c>
     </row>
@@ -57936,254 +57959,734 @@
       </c>
       <c r="B760" s="8" t="inlineStr">
         <is>
-          <t>0048</t>
-        </is>
-      </c>
-      <c r="C760" s="46" t="n">
+          <t>0039</t>
+        </is>
+      </c>
+      <c r="C760" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D760" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E760" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D760" s="12" t="n">
+      <c r="F760" s="15" t="n"/>
+      <c r="G760" s="15" t="n"/>
+      <c r="H760" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I760" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J760" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K760" s="15" t="inlineStr">
+        <is>
+          <t>MAE0039 Wechsel zu Produktionsstop fehlgeschlagen</t>
+        </is>
+      </c>
+      <c r="L760" s="28" t="n"/>
+      <c r="M760" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N760" s="22" t="inlineStr">
+        <is>
+          <t>Produktionsstopp nicht möglich</t>
+        </is>
+      </c>
+      <c r="O760" s="22" t="n"/>
+      <c r="P760" s="22" t="inlineStr">
+        <is>
+          <t>Produktionspause</t>
+        </is>
+      </c>
+      <c r="Q760" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R760" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0039 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0039 Wechsel zu Produktionsstop fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761" hidden="1" ht="120" customHeight="1">
+      <c r="A761" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B761" s="8" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="C761" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D761" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E760" s="12" t="n">
+      <c r="E761" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F760" s="29" t="n"/>
-      <c r="G760" s="29" t="n"/>
-      <c r="H760" s="29" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I760" s="29" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="J760" s="29" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="K760" s="29" t="inlineStr">
-        <is>
-          <t>MAE0048 Etikettenantrieb Nachpositionierung Toleranz nicht erreicht</t>
-        </is>
-      </c>
-      <c r="L760" s="28" t="n"/>
-      <c r="M760" s="28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N760" s="28" t="inlineStr">
-        <is>
-          <t>Etikettenantrieb Nachpositionierung: Toleranz +/-0.05 mm nach 3 Versuchen nicht erreicht</t>
-        </is>
-      </c>
-      <c r="O760" s="28" t="inlineStr">
-        <is>
-          <t>Schlupf, mechanische Blockade, falsche Motoraufl?sung, Encoderabweichung oder AZD-Parameter ausserhalb des stabilen Bereichs</t>
-        </is>
-      </c>
-      <c r="P760" s="28" t="inlineStr">
-        <is>
-          <t>Mess-/Taktposition wird verworfen; Produktion oder Einrichten wird abgebrochen, weil die Druckposition nicht garantiert werden kann</t>
-        </is>
-      </c>
-      <c r="Q760" s="28" t="inlineStr">
-        <is>
-          <t>Mechanik, Bandspannung, Motoraufl?sung, Encoderwerte und AZD-Parameter pr?fen; danach Reset und erneutes Einrichten ausf?hren</t>
-        </is>
-      </c>
-      <c r="R760" s="28" t="inlineStr">
-        <is>
-          <t>KI: Ich verstehe MAE0048 als Stoerungsmeldung, wenn Motor 3 nach einer Mess- oder Taktposition seine Sollposition trotz maximal drei Nachpositionierungen nicht innerhalb von +/-0.05 mm erreicht. Waehrend dieser Nachpositionierung muessen Abwickler und Aufwickler stillstehen und duerfen nicht selbst nachregeln.</t>
-        </is>
-      </c>
-      <c r="S760" s="4" t="n"/>
-      <c r="T760" s="4" t="n"/>
-      <c r="U760" s="4" t="n"/>
-    </row>
-    <row r="761" hidden="1" ht="120" customHeight="1">
-      <c r="A761" s="10" t="n"/>
-      <c r="B761" s="8" t="n"/>
-      <c r="C761" s="43" t="n"/>
-      <c r="D761" s="11" t="n"/>
-      <c r="E761" s="11" t="n"/>
       <c r="F761" s="15" t="n"/>
       <c r="G761" s="15" t="n"/>
-      <c r="H761" s="15" t="n"/>
-      <c r="I761" s="15" t="n"/>
-      <c r="J761" s="15" t="n"/>
-      <c r="K761" s="15" t="n"/>
-      <c r="L761" s="22" t="n"/>
-      <c r="M761" s="22" t="n"/>
-      <c r="N761" s="22" t="n"/>
+      <c r="H761" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I761" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J761" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K761" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAE0040 Wechsel zu Rückspulbetrieb fehlgeschlagen </t>
+        </is>
+      </c>
+      <c r="L761" s="28" t="n"/>
+      <c r="M761" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N761" s="22" t="inlineStr">
+        <is>
+          <t>Rückspulbetrieb nicht möglich</t>
+        </is>
+      </c>
       <c r="O761" s="22" t="n"/>
-      <c r="P761" s="22" t="n"/>
-      <c r="Q761" s="22" t="n"/>
-      <c r="R761" s="22" t="n"/>
+      <c r="P761" s="22" t="inlineStr">
+        <is>
+          <t>Rückspulen blockiert</t>
+        </is>
+      </c>
+      <c r="Q761" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R761" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0040 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0040 Wechsel zu Rückspulbetrieb fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="762" hidden="1" ht="135" customHeight="1">
-      <c r="A762" s="10" t="n"/>
-      <c r="B762" s="8" t="n"/>
-      <c r="C762" s="43" t="n"/>
-      <c r="D762" s="11" t="n"/>
-      <c r="E762" s="11" t="n"/>
+      <c r="A762" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B762" s="8" t="inlineStr">
+        <is>
+          <t>0041</t>
+        </is>
+      </c>
+      <c r="C762" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D762" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E762" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F762" s="15" t="n"/>
       <c r="G762" s="15" t="n"/>
-      <c r="H762" s="15" t="n"/>
-      <c r="I762" s="15" t="n"/>
-      <c r="J762" s="15" t="n"/>
-      <c r="K762" s="15" t="n"/>
-      <c r="L762" s="22" t="n"/>
-      <c r="M762" s="22" t="n"/>
-      <c r="N762" s="22" t="n"/>
+      <c r="H762" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I762" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J762" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K762" s="15" t="inlineStr">
+        <is>
+          <t>MAE0041 Wechsel zu Etikettenentnahme</t>
+        </is>
+      </c>
+      <c r="L762" s="28" t="n"/>
+      <c r="M762" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N762" s="22" t="inlineStr">
+        <is>
+          <t>Wechsel zu Etikettenentnahme nicht möglich</t>
+        </is>
+      </c>
       <c r="O762" s="22" t="n"/>
-      <c r="P762" s="22" t="n"/>
-      <c r="Q762" s="22" t="n"/>
-      <c r="R762" s="22" t="n"/>
+      <c r="P762" s="22" t="inlineStr">
+        <is>
+          <t>Produktionspause</t>
+        </is>
+      </c>
+      <c r="Q762" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R762" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0041 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0041 Wechsel zu Etikettenentnahme. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="763" hidden="1" ht="135" customHeight="1">
-      <c r="A763" s="10" t="n"/>
-      <c r="B763" s="8" t="n"/>
-      <c r="C763" s="43" t="n"/>
-      <c r="D763" s="11" t="n"/>
-      <c r="E763" s="11" t="n"/>
+      <c r="A763" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B763" s="8" t="inlineStr">
+        <is>
+          <t>0042</t>
+        </is>
+      </c>
+      <c r="C763" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D763" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E763" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F763" s="15" t="n"/>
       <c r="G763" s="15" t="n"/>
-      <c r="H763" s="15" t="n"/>
-      <c r="I763" s="15" t="n"/>
-      <c r="J763" s="15" t="n"/>
-      <c r="K763" s="15" t="n"/>
-      <c r="L763" s="22" t="n"/>
-      <c r="M763" s="22" t="n"/>
-      <c r="N763" s="22" t="n"/>
+      <c r="H763" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I763" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J763" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K763" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAE0042 Wechsel zu Spleissen fehlgeschlagen </t>
+        </is>
+      </c>
+      <c r="L763" s="28" t="n"/>
+      <c r="M763" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N763" s="22" t="inlineStr">
+        <is>
+          <t>Spleissbetrieb nicht möglich</t>
+        </is>
+      </c>
       <c r="O763" s="22" t="n"/>
-      <c r="P763" s="22" t="n"/>
-      <c r="Q763" s="22" t="n"/>
-      <c r="R763" s="22" t="n"/>
+      <c r="P763" s="22" t="inlineStr">
+        <is>
+          <t>Spleissen blockiert</t>
+        </is>
+      </c>
+      <c r="Q763" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R763" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0042 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0042 Wechsel zu Spleissen fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="764" hidden="1" ht="135" customHeight="1">
-      <c r="A764" s="10" t="n"/>
-      <c r="B764" s="8" t="n"/>
-      <c r="C764" s="43" t="n"/>
-      <c r="D764" s="11" t="n"/>
-      <c r="E764" s="11" t="n"/>
+      <c r="A764" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B764" s="8" t="inlineStr">
+        <is>
+          <t>0043</t>
+        </is>
+      </c>
+      <c r="C764" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D764" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E764" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F764" s="15" t="n"/>
       <c r="G764" s="15" t="n"/>
-      <c r="H764" s="15" t="n"/>
-      <c r="I764" s="15" t="n"/>
-      <c r="J764" s="15" t="n"/>
-      <c r="K764" s="15" t="n"/>
-      <c r="L764" s="22" t="n"/>
-      <c r="M764" s="22" t="n"/>
-      <c r="N764" s="22" t="n"/>
-      <c r="O764" s="22" t="n"/>
-      <c r="P764" s="22" t="n"/>
-      <c r="Q764" s="22" t="n"/>
-      <c r="R764" s="22" t="n"/>
+      <c r="H764" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I764" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J764" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K764" s="15" t="inlineStr">
+        <is>
+          <t>MAE0043 Wechsel zu Synchronisieren fehlgeschlagen</t>
+        </is>
+      </c>
+      <c r="L764" s="28" t="n"/>
+      <c r="M764" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N764" s="22" t="inlineStr">
+        <is>
+          <t>Synchronisieren fehlgeschlagen</t>
+        </is>
+      </c>
+      <c r="O764" s="22" t="inlineStr">
+        <is>
+          <t>Achsen nicht bereit oder Blockade im Fahrtweg</t>
+        </is>
+      </c>
+      <c r="P764" s="22" t="inlineStr">
+        <is>
+          <t>Produktionsstopp</t>
+        </is>
+      </c>
+      <c r="Q764" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R764" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0043 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0043 Wechsel zu Synchronisieren fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="765" hidden="1" ht="135" customHeight="1">
-      <c r="A765" s="10" t="n"/>
-      <c r="B765" s="8" t="n"/>
-      <c r="C765" s="43" t="n"/>
-      <c r="D765" s="11" t="n"/>
-      <c r="E765" s="11" t="n"/>
+      <c r="A765" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B765" s="8" t="inlineStr">
+        <is>
+          <t>0044</t>
+        </is>
+      </c>
+      <c r="C765" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D765" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E765" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F765" s="15" t="n"/>
       <c r="G765" s="15" t="n"/>
-      <c r="H765" s="15" t="n"/>
-      <c r="I765" s="15" t="n"/>
-      <c r="J765" s="15" t="n"/>
-      <c r="K765" s="15" t="n"/>
-      <c r="L765" s="22" t="n"/>
-      <c r="M765" s="22" t="n"/>
-      <c r="N765" s="22" t="n"/>
+      <c r="H765" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I765" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J765" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K765" s="15" t="inlineStr">
+        <is>
+          <t>MAE0044 Wechsel zu Produktion abgeschlossen fehlgeschlagen</t>
+        </is>
+      </c>
+      <c r="L765" s="28" t="n"/>
+      <c r="M765" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N765" s="22" t="inlineStr">
+        <is>
+          <t>Produktion abgeschlossen fehlgeschlagen</t>
+        </is>
+      </c>
       <c r="O765" s="22" t="n"/>
-      <c r="P765" s="22" t="n"/>
-      <c r="Q765" s="22" t="n"/>
-      <c r="R765" s="22" t="n"/>
+      <c r="P765" s="22" t="inlineStr">
+        <is>
+          <t>Produktionspause</t>
+        </is>
+      </c>
+      <c r="Q765" s="22" t="inlineStr">
+        <is>
+          <t>Auf Blockade prüfen</t>
+        </is>
+      </c>
+      <c r="R765" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0044 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0044 Wechsel zu Produktion abgeschlossen fehlgeschlagen. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="766" hidden="1">
-      <c r="A766" s="10" t="n"/>
-      <c r="B766" s="8" t="n"/>
-      <c r="C766" s="43" t="n"/>
-      <c r="D766" s="11" t="n"/>
-      <c r="E766" s="11" t="n"/>
+      <c r="A766" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B766" s="8" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C766" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D766" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E766" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F766" s="15" t="n"/>
       <c r="G766" s="15" t="n"/>
-      <c r="H766" s="15" t="n"/>
-      <c r="I766" s="15" t="n"/>
-      <c r="J766" s="15" t="n"/>
-      <c r="K766" s="15" t="n"/>
-      <c r="L766" s="22" t="n"/>
-      <c r="M766" s="22" t="n"/>
-      <c r="N766" s="22" t="n"/>
-      <c r="O766" s="22" t="n"/>
-      <c r="P766" s="22" t="n"/>
-      <c r="Q766" s="22" t="n"/>
-      <c r="R766" s="22" t="n"/>
+      <c r="H766" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I766" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J766" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K766" s="15" t="inlineStr">
+        <is>
+          <t>MAE0045 Störung während Rückspulung</t>
+        </is>
+      </c>
+      <c r="L766" s="28" t="n"/>
+      <c r="M766" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N766" s="22" t="inlineStr">
+        <is>
+          <t>Fehler während Rückspulung</t>
+        </is>
+      </c>
+      <c r="O766" s="22" t="inlineStr">
+        <is>
+          <t>Blockade oder Encoder-Fehler</t>
+        </is>
+      </c>
+      <c r="P766" s="22" t="inlineStr">
+        <is>
+          <t>Rückspulung abgebrochen</t>
+        </is>
+      </c>
+      <c r="Q766" s="22" t="inlineStr">
+        <is>
+          <t>Encoder und Etikettenlauf prüfen</t>
+        </is>
+      </c>
+      <c r="R766" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0045 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0045 Störung während Rückspulung. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="767" hidden="1">
-      <c r="A767" s="10" t="n"/>
-      <c r="B767" s="8" t="n"/>
-      <c r="C767" s="43" t="n"/>
-      <c r="D767" s="11" t="n"/>
-      <c r="E767" s="11" t="n"/>
+      <c r="A767" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B767" s="8" t="inlineStr">
+        <is>
+          <t>0046</t>
+        </is>
+      </c>
+      <c r="C767" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D767" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E767" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F767" s="15" t="n"/>
       <c r="G767" s="15" t="n"/>
-      <c r="H767" s="15" t="n"/>
-      <c r="I767" s="15" t="n"/>
-      <c r="J767" s="15" t="n"/>
-      <c r="K767" s="15" t="n"/>
-      <c r="L767" s="22" t="n"/>
-      <c r="M767" s="22" t="n"/>
-      <c r="N767" s="22" t="n"/>
-      <c r="O767" s="22" t="n"/>
-      <c r="P767" s="22" t="n"/>
-      <c r="Q767" s="22" t="n"/>
-      <c r="R767" s="22" t="n"/>
+      <c r="H767" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I767" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J767" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K767" s="15" t="inlineStr">
+        <is>
+          <t>MAE0045 Störung Motor Etiekttenantrieb</t>
+        </is>
+      </c>
+      <c r="L767" s="28" t="n"/>
+      <c r="M767" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N767" s="22" t="inlineStr">
+        <is>
+          <t>Störung Motor Etiekttenantrieb</t>
+        </is>
+      </c>
+      <c r="O767" s="22" t="inlineStr">
+        <is>
+          <t>Überlast oder Blockade</t>
+        </is>
+      </c>
+      <c r="P767" s="22" t="inlineStr">
+        <is>
+          <t>Etiektten-Antrieb nicht möglich</t>
+        </is>
+      </c>
+      <c r="Q767" s="22" t="inlineStr">
+        <is>
+          <t>Mechanik und Motor prüfen</t>
+        </is>
+      </c>
+      <c r="R767" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0046 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0045 Störung Motor Etiekttenantrieb. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="768" hidden="1">
-      <c r="A768" s="10" t="n"/>
-      <c r="B768" s="8" t="n"/>
-      <c r="C768" s="43" t="n"/>
-      <c r="D768" s="11" t="n"/>
-      <c r="E768" s="11" t="n"/>
+      <c r="A768" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B768" s="8" t="inlineStr">
+        <is>
+          <t>0047</t>
+        </is>
+      </c>
+      <c r="C768" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D768" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E768" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="F768" s="15" t="n"/>
       <c r="G768" s="15" t="n"/>
-      <c r="H768" s="15" t="n"/>
-      <c r="I768" s="15" t="n"/>
-      <c r="J768" s="15" t="n"/>
-      <c r="K768" s="15" t="n"/>
-      <c r="L768" s="22" t="n"/>
-      <c r="M768" s="22" t="n"/>
-      <c r="N768" s="22" t="n"/>
-      <c r="O768" s="22" t="n"/>
-      <c r="P768" s="22" t="n"/>
-      <c r="Q768" s="22" t="n"/>
-      <c r="R768" s="22" t="n"/>
+      <c r="H768" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I768" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J768" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K768" s="15" t="inlineStr">
+        <is>
+          <t>MAE0047 Störung Positionsantrieb Schutzblech Laser</t>
+        </is>
+      </c>
+      <c r="L768" s="28" t="n"/>
+      <c r="M768" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N768" s="22" t="inlineStr">
+        <is>
+          <t>Schutzblech-Laser Positionsantrieb meldet Störung</t>
+        </is>
+      </c>
+      <c r="O768" s="22" t="inlineStr">
+        <is>
+          <t>Überlast oder Blockade</t>
+        </is>
+      </c>
+      <c r="P768" s="22" t="inlineStr">
+        <is>
+          <t>Positionierung nicht möglich</t>
+        </is>
+      </c>
+      <c r="Q768" s="22" t="inlineStr">
+        <is>
+          <t>Mechanik und Motor prüfen</t>
+        </is>
+      </c>
+      <c r="R768" s="22" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0047 als Stoerungsbit bzw. Stoerungsmeldung fuer MAE0047 Störung Positionsantrieb Schutzblech Laser. Microtom soll diesen Wert nur lesen. Der ESP darf ihn im Prozess aktiv verwenden und - falls fachlich vorgesehen - auch setzen oder rueckmelden. Der Wert ist laut Tabelle nicht formatrelevant und eher als Maschinen-/Systemeinstellung zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="769" hidden="1">
-      <c r="A769" s="10" t="n"/>
-      <c r="B769" s="8" t="n"/>
-      <c r="C769" s="43" t="n"/>
-      <c r="D769" s="11" t="n"/>
-      <c r="E769" s="11" t="n"/>
-      <c r="F769" s="15" t="n"/>
-      <c r="G769" s="15" t="n"/>
-      <c r="H769" s="15" t="n"/>
-      <c r="I769" s="15" t="n"/>
-      <c r="J769" s="15" t="n"/>
-      <c r="K769" s="15" t="n"/>
-      <c r="L769" s="22" t="n"/>
-      <c r="M769" s="22" t="n"/>
-      <c r="N769" s="22" t="n"/>
-      <c r="O769" s="22" t="n"/>
-      <c r="P769" s="22" t="n"/>
-      <c r="Q769" s="22" t="n"/>
-      <c r="R769" s="22" t="n"/>
+      <c r="A769" s="10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B769" s="8" t="inlineStr">
+        <is>
+          <t>0048</t>
+        </is>
+      </c>
+      <c r="C769" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D769" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E769" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F769" s="29" t="n"/>
+      <c r="G769" s="29" t="n"/>
+      <c r="H769" s="29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I769" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J769" s="29" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K769" s="29" t="inlineStr">
+        <is>
+          <t>MAE0048 Etikettenantrieb Nachpositionierung Toleranz nicht erreicht</t>
+        </is>
+      </c>
+      <c r="L769" s="28" t="n"/>
+      <c r="M769" s="28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N769" s="28" t="inlineStr">
+        <is>
+          <t>Etikettenantrieb Nachpositionierung: Toleranz +/-0.05 mm nach 3 Versuchen nicht erreicht</t>
+        </is>
+      </c>
+      <c r="O769" s="28" t="inlineStr">
+        <is>
+          <t>Schlupf, mechanische Blockade, falsche Motoraufl?sung, Encoderabweichung oder AZD-Parameter ausserhalb des stabilen Bereichs</t>
+        </is>
+      </c>
+      <c r="P769" s="28" t="inlineStr">
+        <is>
+          <t>Mess-/Taktposition wird verworfen; Produktion oder Einrichten wird abgebrochen, weil die Druckposition nicht garantiert werden kann</t>
+        </is>
+      </c>
+      <c r="Q769" s="28" t="inlineStr">
+        <is>
+          <t>Mechanik, Bandspannung, Motoraufl?sung, Encoderwerte und AZD-Parameter pr?fen; danach Reset und erneutes Einrichten ausf?hren</t>
+        </is>
+      </c>
+      <c r="R769" s="28" t="inlineStr">
+        <is>
+          <t>KI: Ich verstehe MAE0048 als Stoerungsmeldung, wenn Motor 3 nach einer Mess- oder Taktposition seine Sollposition trotz maximal drei Nachpositionierungen nicht innerhalb von +/-0.05 mm erreicht. Waehrend dieser Nachpositionierung muessen Abwickler und Aufwickler stillstehen und duerfen nicht selbst nachregeln.</t>
+        </is>
+      </c>
+      <c r="S769" s="4" t="n"/>
+      <c r="T769" s="4" t="n"/>
+      <c r="U769" s="4" t="n"/>
     </row>
     <row r="770" hidden="1">
       <c r="A770" s="10" t="n"/>
@@ -58305,9 +58808,186 @@
       <c r="Q775" s="22" t="n"/>
       <c r="R775" s="22" t="n"/>
     </row>
-    <row r="776" hidden="1"/>
-    <row r="777" hidden="1"/>
-    <row r="778" hidden="1"/>
+    <row r="776" hidden="1">
+      <c r="A776" s="10" t="n"/>
+      <c r="B776" s="8" t="n"/>
+      <c r="C776" s="43" t="n"/>
+      <c r="D776" s="11" t="n"/>
+      <c r="E776" s="11" t="n"/>
+      <c r="F776" s="15" t="n"/>
+      <c r="G776" s="15" t="n"/>
+      <c r="H776" s="15" t="n"/>
+      <c r="I776" s="15" t="n"/>
+      <c r="J776" s="15" t="n"/>
+      <c r="K776" s="15" t="n"/>
+      <c r="L776" s="22" t="n"/>
+      <c r="M776" s="22" t="n"/>
+      <c r="N776" s="22" t="n"/>
+      <c r="O776" s="22" t="n"/>
+      <c r="P776" s="22" t="n"/>
+      <c r="Q776" s="22" t="n"/>
+      <c r="R776" s="22" t="n"/>
+    </row>
+    <row r="777" hidden="1">
+      <c r="A777" s="10" t="n"/>
+      <c r="B777" s="8" t="n"/>
+      <c r="C777" s="43" t="n"/>
+      <c r="D777" s="11" t="n"/>
+      <c r="E777" s="11" t="n"/>
+      <c r="F777" s="15" t="n"/>
+      <c r="G777" s="15" t="n"/>
+      <c r="H777" s="15" t="n"/>
+      <c r="I777" s="15" t="n"/>
+      <c r="J777" s="15" t="n"/>
+      <c r="K777" s="15" t="n"/>
+      <c r="L777" s="22" t="n"/>
+      <c r="M777" s="22" t="n"/>
+      <c r="N777" s="22" t="n"/>
+      <c r="O777" s="22" t="n"/>
+      <c r="P777" s="22" t="n"/>
+      <c r="Q777" s="22" t="n"/>
+      <c r="R777" s="22" t="n"/>
+    </row>
+    <row r="778" hidden="1">
+      <c r="A778" s="10" t="n"/>
+      <c r="B778" s="8" t="n"/>
+      <c r="C778" s="43" t="n"/>
+      <c r="D778" s="11" t="n"/>
+      <c r="E778" s="11" t="n"/>
+      <c r="F778" s="15" t="n"/>
+      <c r="G778" s="15" t="n"/>
+      <c r="H778" s="15" t="n"/>
+      <c r="I778" s="15" t="n"/>
+      <c r="J778" s="15" t="n"/>
+      <c r="K778" s="15" t="n"/>
+      <c r="L778" s="22" t="n"/>
+      <c r="M778" s="22" t="n"/>
+      <c r="N778" s="22" t="n"/>
+      <c r="O778" s="22" t="n"/>
+      <c r="P778" s="22" t="n"/>
+      <c r="Q778" s="22" t="n"/>
+      <c r="R778" s="22" t="n"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="10" t="n"/>
+      <c r="B779" s="8" t="n"/>
+      <c r="C779" s="43" t="n"/>
+      <c r="D779" s="11" t="n"/>
+      <c r="E779" s="11" t="n"/>
+      <c r="F779" s="15" t="n"/>
+      <c r="G779" s="15" t="n"/>
+      <c r="H779" s="15" t="n"/>
+      <c r="I779" s="15" t="n"/>
+      <c r="J779" s="15" t="n"/>
+      <c r="K779" s="15" t="n"/>
+      <c r="L779" s="22" t="n"/>
+      <c r="M779" s="22" t="n"/>
+      <c r="N779" s="22" t="n"/>
+      <c r="O779" s="22" t="n"/>
+      <c r="P779" s="22" t="n"/>
+      <c r="Q779" s="22" t="n"/>
+      <c r="R779" s="22" t="n"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="10" t="n"/>
+      <c r="B780" s="8" t="n"/>
+      <c r="C780" s="43" t="n"/>
+      <c r="D780" s="11" t="n"/>
+      <c r="E780" s="11" t="n"/>
+      <c r="F780" s="15" t="n"/>
+      <c r="G780" s="15" t="n"/>
+      <c r="H780" s="15" t="n"/>
+      <c r="I780" s="15" t="n"/>
+      <c r="J780" s="15" t="n"/>
+      <c r="K780" s="15" t="n"/>
+      <c r="L780" s="22" t="n"/>
+      <c r="M780" s="22" t="n"/>
+      <c r="N780" s="22" t="n"/>
+      <c r="O780" s="22" t="n"/>
+      <c r="P780" s="22" t="n"/>
+      <c r="Q780" s="22" t="n"/>
+      <c r="R780" s="22" t="n"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="10" t="n"/>
+      <c r="B781" s="8" t="n"/>
+      <c r="C781" s="43" t="n"/>
+      <c r="D781" s="11" t="n"/>
+      <c r="E781" s="11" t="n"/>
+      <c r="F781" s="15" t="n"/>
+      <c r="G781" s="15" t="n"/>
+      <c r="H781" s="15" t="n"/>
+      <c r="I781" s="15" t="n"/>
+      <c r="J781" s="15" t="n"/>
+      <c r="K781" s="15" t="n"/>
+      <c r="L781" s="22" t="n"/>
+      <c r="M781" s="22" t="n"/>
+      <c r="N781" s="22" t="n"/>
+      <c r="O781" s="22" t="n"/>
+      <c r="P781" s="22" t="n"/>
+      <c r="Q781" s="22" t="n"/>
+      <c r="R781" s="22" t="n"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="10" t="n"/>
+      <c r="B782" s="8" t="n"/>
+      <c r="C782" s="43" t="n"/>
+      <c r="D782" s="11" t="n"/>
+      <c r="E782" s="11" t="n"/>
+      <c r="F782" s="15" t="n"/>
+      <c r="G782" s="15" t="n"/>
+      <c r="H782" s="15" t="n"/>
+      <c r="I782" s="15" t="n"/>
+      <c r="J782" s="15" t="n"/>
+      <c r="K782" s="15" t="n"/>
+      <c r="L782" s="22" t="n"/>
+      <c r="M782" s="22" t="n"/>
+      <c r="N782" s="22" t="n"/>
+      <c r="O782" s="22" t="n"/>
+      <c r="P782" s="22" t="n"/>
+      <c r="Q782" s="22" t="n"/>
+      <c r="R782" s="22" t="n"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="10" t="n"/>
+      <c r="B783" s="8" t="n"/>
+      <c r="C783" s="43" t="n"/>
+      <c r="D783" s="11" t="n"/>
+      <c r="E783" s="11" t="n"/>
+      <c r="F783" s="15" t="n"/>
+      <c r="G783" s="15" t="n"/>
+      <c r="H783" s="15" t="n"/>
+      <c r="I783" s="15" t="n"/>
+      <c r="J783" s="15" t="n"/>
+      <c r="K783" s="15" t="n"/>
+      <c r="L783" s="22" t="n"/>
+      <c r="M783" s="22" t="n"/>
+      <c r="N783" s="22" t="n"/>
+      <c r="O783" s="22" t="n"/>
+      <c r="P783" s="22" t="n"/>
+      <c r="Q783" s="22" t="n"/>
+      <c r="R783" s="22" t="n"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="10" t="n"/>
+      <c r="B784" s="8" t="n"/>
+      <c r="C784" s="43" t="n"/>
+      <c r="D784" s="11" t="n"/>
+      <c r="E784" s="11" t="n"/>
+      <c r="F784" s="15" t="n"/>
+      <c r="G784" s="15" t="n"/>
+      <c r="H784" s="15" t="n"/>
+      <c r="I784" s="15" t="n"/>
+      <c r="J784" s="15" t="n"/>
+      <c r="K784" s="15" t="n"/>
+      <c r="L784" s="22" t="n"/>
+      <c r="M784" s="22" t="n"/>
+      <c r="N784" s="22" t="n"/>
+      <c r="O784" s="22" t="n"/>
+      <c r="P784" s="22" t="n"/>
+      <c r="Q784" s="22" t="n"/>
+      <c r="R784" s="22" t="n"/>
+    </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation sqref="M1:M1048576 P2:P119" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -58326,8 +59006,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a32518fee107c04aa9bd7948c0d3f18">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97db55af52189d57b3fce0d0bdbaea8" ns2:_="" ns3:_="" ns4:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
     <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
     <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
@@ -58354,6 +59034,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -58436,6 +59117,11 @@
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -58597,22 +59283,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{581018F7-B077-41F8-932C-95F125681D77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF60DE0-9F1E-42B1-B544-2CDA6286C584}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BA8AE4-C304-4D21-904A-1D0430EAC1A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3F50B1-B11B-43FB-97A4-F70B5A5AC586}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A4D9519-4D37-46AB-809E-0405F788D2A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5C0D531-FD48-4D9B-9E4E-6AFFEFD41BA8}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -51173,7 +51173,7 @@
       </c>
       <c r="E665" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F665" s="15" t="inlineStr">
@@ -51447,7 +51447,7 @@
       </c>
       <c r="E669" s="11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F669" s="15" t="inlineStr">
@@ -53320,7 +53320,7 @@
       </c>
       <c r="E696" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F696" s="15" t="inlineStr">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="E697" s="11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F697" s="15" t="inlineStr">
@@ -59292,13 +59292,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF60DE0-9F1E-42B1-B544-2CDA6286C584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3004EFEF-C355-4181-B29E-DA5E0E831C7D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3F50B1-B11B-43FB-97A4-F70B5A5AC586}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66D25AFB-E4B2-4A92-910D-8F020805505A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5C0D531-FD48-4D9B-9E4E-6AFFEFD41BA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{473561A7-989C-4EE1-959B-8A7E6E682277}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48441,7 +48441,7 @@
       </c>
       <c r="E627" s="6" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="F627" s="15" t="inlineStr">
@@ -59003,302 +59003,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3004EFEF-C355-4181-B29E-DA5E0E831C7D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66D25AFB-E4B2-4A92-910D-8F020805505A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{473561A7-989C-4EE1-959B-8A7E6E682277}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48441,7 +48441,7 @@
       </c>
       <c r="E627" s="6" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F627" s="15" t="inlineStr">
@@ -48513,7 +48513,7 @@
       </c>
       <c r="E628" s="7" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="F628" s="31" t="inlineStr">
@@ -51105,7 +51105,7 @@
       </c>
       <c r="E664" s="11" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F664" s="15" t="inlineStr">
@@ -51818,8 +51818,10 @@
       <c r="D675" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="E675" s="12" t="n">
-        <v>9600</v>
+      <c r="E675" s="12" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
       </c>
       <c r="F675" s="29" t="inlineStr">
         <is>
@@ -53252,7 +53254,7 @@
       </c>
       <c r="E695" s="11" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F695" s="15" t="inlineStr">

--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -59005,4 +59005,302 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8890953C-96EE-40CF-BA4A-BFEBBC839B03}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{461F2087-9DDD-46D2-833B-A8BDD8425AD0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77185E60-849B-46ED-A06B-2C03FBCFB2B7}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48873,7 +48873,7 @@
       </c>
       <c r="E633" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F633" s="15" t="inlineStr">
@@ -59005,302 +59005,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8890953C-96EE-40CF-BA4A-BFEBBC839B03}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{461F2087-9DDD-46D2-833B-A8BDD8425AD0}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77185E60-849B-46ED-A06B-2C03FBCFB2B7}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="rng_Lieferanten">#REF!</definedName>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E531" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F531" s="15" t="inlineStr">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="E545" s="11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F545" s="15" t="inlineStr">
@@ -42745,7 +42745,7 @@
       </c>
       <c r="E546" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F546" s="15" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="E548" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F548" s="15" t="inlineStr">
@@ -47113,7 +47113,7 @@
       </c>
       <c r="E609" s="6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F609" s="15" t="inlineStr">
@@ -47185,7 +47185,7 @@
       </c>
       <c r="E610" s="7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F610" s="31" t="inlineStr">
@@ -47553,7 +47553,7 @@
       </c>
       <c r="E615" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F615" s="15" t="inlineStr">
@@ -47625,7 +47625,7 @@
       </c>
       <c r="E616" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F616" s="31" t="inlineStr">
@@ -47697,7 +47697,7 @@
       </c>
       <c r="E617" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F617" s="15" t="inlineStr">
@@ -47769,7 +47769,7 @@
       </c>
       <c r="E618" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F618" s="31" t="inlineStr">
@@ -47845,7 +47845,7 @@
       </c>
       <c r="E619" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="F619" s="15" t="inlineStr">
@@ -48149,7 +48149,7 @@
       </c>
       <c r="E623" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F623" s="15" t="inlineStr">
@@ -49957,7 +49957,7 @@
       </c>
       <c r="E648" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F648" s="15" t="inlineStr">
@@ -59005,4 +59005,302 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA816280-568C-49A5-B581-050D82F75246}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414F502C-C4B5-4113-86CA-7EBA872E50D0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F846312-43FB-4542-891C-994562E22FAB}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parameter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="rng_Lieferanten">#REF!</definedName>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="E625" s="6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F625" s="15" t="inlineStr">
@@ -59005,302 +59005,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA816280-568C-49A5-B581-050D82F75246}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414F502C-C4B5-4113-86CA-7EBA872E50D0}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F846312-43FB-4542-891C-994562E22FAB}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48073,7 +48073,7 @@
       </c>
       <c r="E622" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F622" s="31" t="inlineStr">
@@ -59005,4 +59005,302 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
+    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
+    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A3B0F1-1E4E-4508-8BE4-9BF4693761CF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB4959D0-53E8-49D4-A3E3-F6734294744A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F46591-B842-4412-8E3F-2B5549EFED20}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48073,7 +48073,7 @@
       </c>
       <c r="E622" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F622" s="31" t="inlineStr">

--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -48441,7 +48441,7 @@
       </c>
       <c r="E627" s="6" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="F627" s="15" t="inlineStr">
@@ -59005,302 +59005,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC1303956E7B004BAA4FB741FFD4FB75" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af0d30918d172d53a6c97a3e981f1432">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c94746f-923d-44d4-92c8-8aca0d670c40" xmlns:ns3="045083a1-3069-4c94-ae09-233755b46388" xmlns:ns4="d728571b-78ef-4dbd-85be-d4d1cda44c95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8b33fdf811bb6ef4bbd77ea5570dd7f" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="9c94746f-923d-44d4-92c8-8aca0d670c40"/>
-    <xsd:import namespace="045083a1-3069-4c94-ae09-233755b46388"/>
-    <xsd:import namespace="d728571b-78ef-4dbd-85be-d4d1cda44c95"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c94746f-923d-44d4-92c8-8aca0d670c40" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1512ac1f-2332-492c-8cad-e2606caf05d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="045083a1-3069-4c94-ae09-233755b46388" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d728571b-78ef-4dbd-85be-d4d1cda44c95" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3e60fd20-1b61-4c9c-a058-6e112eef0d0c}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="d728571b-78ef-4dbd-85be-d4d1cda44c95">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c94746f-923d-44d4-92c8-8aca0d670c40">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d728571b-78ef-4dbd-85be-d4d1cda44c95" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A3B0F1-1E4E-4508-8BE4-9BF4693761CF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB4959D0-53E8-49D4-A3E3-F6734294744A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F46591-B842-4412-8E3F-2B5549EFED20}"/>
 </file>
--- a/master_data/Parameterliste SAR41-MAS-004.xlsx
+++ b/master_data/Parameterliste SAR41-MAS-004.xlsx
@@ -51214,10 +51214,8 @@
           <t>0057</t>
         </is>
       </c>
-      <c r="C665" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C665" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D665" s="11" t="n">
         <v>990</v>
@@ -53825,10 +53823,8 @@
           <t>0012</t>
         </is>
       </c>
-      <c r="C702" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C702" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D702" s="11" t="n">
         <v>990</v>
